--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -5512,7 +5512,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -6047,27 +6047,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T19:05:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6082,17 +6082,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -6110,26 +6110,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.6</v>
+        <v>55.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.1</v>
+        <v>37.6</v>
       </c>
       <c r="R21" t="n">
-        <v>52.9</v>
+        <v>31.2</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>43.7</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6181,142 +6181,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.8043</t>
+          <t>102.6789</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3856</t>
+          <t>0.4845</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.2296</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3155</t>
+          <t>0.3692</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>68.45</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2264</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1576</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6327,27 +6327,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>575929</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-13T19:05:00Z</t>
+          <t>2026-09-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6362,21 +6362,21 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Noah Cameron</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>702070</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>52.4</v>
+        <v>52.5</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6390,26 +6390,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>55.9</v>
+        <v>35.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>37.6</v>
+        <v>42.1</v>
       </c>
       <c r="R22" t="n">
-        <v>31.2</v>
+        <v>52.9</v>
       </c>
       <c r="S22" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>43.7</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6461,142 +6461,142 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.3% barrel, 16.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>45.22</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.97</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>102.6789</t>
+          <t>101.8043</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4845</t>
+          <t>0.3856</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.2296</t>
+          <t>0.1479</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3692</t>
+          <t>0.3155</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>73.63</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>68.45</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>45.75</t>
+          <t>34.68</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>28.7</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>16.1</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.2264</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>7.28</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1576</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.52</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -8287,27 +8287,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>680869</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Zack Gelof</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T19:05:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8317,26 +8317,26 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Payton Tolle</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>801139</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>50.1</v>
+        <v>50</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8350,26 +8350,26 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>39.6</v>
+        <v>47</v>
       </c>
       <c r="Q29" t="n">
-        <v>42.1</v>
+        <v>29.2</v>
       </c>
       <c r="R29" t="n">
-        <v>52.9</v>
+        <v>31.2</v>
       </c>
       <c r="S29" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T29" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U29" t="n">
-        <v>19.1</v>
+        <v>50.3</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -8436,127 +8436,127 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 1 HR</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>11.51</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>43.84</t>
+          <t>43.83</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>88.87</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>99.8028</t>
+          <t>100.7907</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.4619</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1732</t>
+          <t>0.2086</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.2799</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>73.22</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>28.36</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1708</t>
+          <t>0.1701</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>35.99</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.01</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.3497</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1359</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8567,27 +8567,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>680869</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Zack Gelof</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-13T19:05:00Z</t>
+          <t>2026-09-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8597,22 +8597,22 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Payton Tolle</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>801139</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L30" t="n">
@@ -8630,26 +8630,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>47</v>
+        <v>39.6</v>
       </c>
       <c r="Q30" t="n">
-        <v>29.2</v>
+        <v>42.1</v>
       </c>
       <c r="R30" t="n">
-        <v>31.2</v>
+        <v>52.9</v>
       </c>
       <c r="S30" t="n">
-        <v>94.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T30" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>50.3</v>
+        <v>18.3</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8716,127 +8716,127 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 3/25, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.5% barrel, 12.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>43.83</t>
+          <t>43.84</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.87</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>100.7907</t>
+          <t>99.8028</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4619</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.2086</t>
+          <t>0.1732</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.2799</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>73.22</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>28.36</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1701</t>
+          <t>0.1708</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>88.01</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3497</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1359</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>27.18</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8872,7 +8872,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9683,27 +9683,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9713,22 +9713,22 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L34" t="n">
@@ -9746,26 +9746,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>42.1</v>
+        <v>37.1</v>
       </c>
       <c r="R34" t="n">
-        <v>52.9</v>
+        <v>44.2</v>
       </c>
       <c r="S34" t="n">
-        <v>86.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T34" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U34" t="n">
-        <v>52.8</v>
+        <v>24</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9779,7 +9779,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9822,137 +9822,137 @@
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 7/25, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>6.83</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>47.68</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.0298</t>
+          <t>100.4107</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3663</t>
+          <t>0.4273</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.1529</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.2845</t>
+          <t>0.3341</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>7.76</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>37.69</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>21.88</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>10.5</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1608</t>
+          <t>0.1432</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>33.66</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.4202</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.05</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9963,27 +9963,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>691777</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Max Muncy</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-13T20:10:00Z</t>
+          <t>2026-09-13T20:05:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9993,26 +9993,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Bryce Miller</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>682243</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L35" t="n">
-        <v>48.9</v>
+        <v>48.8</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10026,26 +10026,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>35.3</v>
+        <v>35.4</v>
       </c>
       <c r="Q35" t="n">
-        <v>37.1</v>
+        <v>42.1</v>
       </c>
       <c r="R35" t="n">
-        <v>44.2</v>
+        <v>52.9</v>
       </c>
       <c r="S35" t="n">
-        <v>96.59999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U35" t="n">
-        <v>24</v>
+        <v>50.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
@@ -10102,137 +10102,137 @@
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/25, 0 HR</t>
+          <t>Contact streak: 7/21 over last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.6% barrel, 18.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>6.83</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>47.68</t>
+          <t>40.52</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>100.4107</t>
+          <t>101.0298</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4273</t>
+          <t>0.3663</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3341</t>
+          <t>0.2845</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>37.69</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>21.88</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>10.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1432</t>
+          <t>0.1608</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>37.75</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4202</t>
+          <t>0.4024</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.1631</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>27.05</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10828,7 +10828,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11384,7 +11384,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -11664,7 +11664,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -11968,7 +11968,7 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>46.8</v>
+        <v>46.7</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -12001,7 +12001,7 @@
         <v>75</v>
       </c>
       <c r="U42" t="n">
-        <v>77.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -12058,7 +12058,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
@@ -13620,7 +13620,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14237,7 +14237,7 @@
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>12</v>
+        <v>10.8</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
@@ -16640,7 +16640,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -17484,7 +17484,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -18048,7 +18048,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -18604,7 +18604,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -20000,7 +20000,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20057,7 +20057,7 @@
         <v>75</v>
       </c>
       <c r="U71" t="n">
-        <v>51.3</v>
+        <v>49.9</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -22800,7 +22800,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -23360,7 +23360,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -23470,7 +23470,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ83" t="inlineStr">
@@ -23480,7 +23480,7 @@
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/8, 0 HR</t>
+          <t>Last 7 games: 0/9, 0 HR</t>
         </is>
       </c>
       <c r="AL83" t="inlineStr">
@@ -23636,7 +23636,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -26766,7 +26766,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -28446,7 +28446,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -29558,7 +29558,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -30958,7 +30958,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -31493,27 +31493,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-09-13T20:05:00Z</t>
+          <t>2026-09-13T19:05:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -31528,17 +31528,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Bryce Miller</t>
+          <t>Noah Cameron</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>682243</t>
+          <t>702070</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L21" t="n">
@@ -31556,26 +31556,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.6</v>
+        <v>55.9</v>
       </c>
       <c r="Q21" t="n">
-        <v>42.1</v>
+        <v>37.6</v>
       </c>
       <c r="R21" t="n">
-        <v>52.9</v>
+        <v>31.2</v>
       </c>
       <c r="S21" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U21" t="n">
-        <v>43.7</v>
+        <v>1.6</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -31627,142 +31627,142 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 17.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.3% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>45.22</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>89.97</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>101.8043</t>
+          <t>102.6789</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3856</t>
+          <t>0.4845</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1479</t>
+          <t>0.2296</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.3155</t>
+          <t>0.3692</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>68.45</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>34.68</t>
+          <t>45.75</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>28.7</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>16.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2264</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.28</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>37.75</t>
+          <t>37.61</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.4024</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1631</t>
+          <t>0.1576</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>26.52</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2444,7 +2444,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3572,7 +3572,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -9460,7 +9460,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -10300,7 +10300,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10860,7 +10860,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13376,7 +13376,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -13656,7 +13656,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -15336,7 +15336,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -19252,7 +19252,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -20092,7 +20092,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -20652,7 +20652,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -20932,7 +20932,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -23456,7 +23456,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -25700,7 +25700,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -27104,7 +27104,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -28228,7 +28228,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -28508,7 +28508,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -31028,7 +31028,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -31308,7 +31308,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -32148,7 +32148,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -36348,7 +36348,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -37472,7 +37472,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -39992,7 +39992,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -41676,7 +41676,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -41956,7 +41956,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -42236,7 +42236,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -43076,7 +43076,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -44760,7 +44760,7 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -45596,7 +45596,7 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -48676,7 +48676,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48956,7 +48956,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -50636,7 +50636,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -50916,7 +50916,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -51196,7 +51196,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -51756,7 +51756,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -52316,7 +52316,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -52876,7 +52876,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -53156,7 +53156,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -53716,7 +53716,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -54276,7 +54276,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -54836,7 +54836,7 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -55116,7 +55116,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -55676,7 +55676,7 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -55956,7 +55956,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -58246,7 +58246,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -59374,7 +59374,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -61622,7 +61622,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1299,22 +1299,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>656941</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1366,13 +1366,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>74.90000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.2</v>
+        <v>60.5</v>
       </c>
       <c r="R4" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -1381,7 +1381,7 @@
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>40.1</v>
+        <v>60.7</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1390,33 +1390,37 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1433,12 +1437,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1453,122 +1457,122 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.1156</t>
+          <t>103.0426</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5229</t>
+          <t>0.4769</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3758</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>77.16</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.2297</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -1579,22 +1583,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>656941</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1614,12 +1618,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1628,7 +1632,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1642,65 +1646,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>60.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.5</v>
+        <v>30.2</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>65.3</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>60.7</v>
+        <v>40.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1737,122 +1737,122 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>103.0426</t>
+          <t>104.1156</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4769</t>
+          <t>0.5229</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3758</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.16</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>75.42</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>54.49</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2297</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -3036,7 +3036,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3063,7 +3063,7 @@
         <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -3073,14 +3073,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>3</t>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3320,7 +3320,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3347,7 +3347,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -3357,14 +3357,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>2</t>
@@ -3382,12 +3382,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -7195,27 +7195,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>521692</t>
+          <t>690993</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Salvador Perez</t>
+          <t>Colt Keith</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7225,17 +7225,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7244,7 +7244,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>53.8</v>
+        <v>52.6</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7258,26 +7258,26 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>46.7</v>
+        <v>36.1</v>
       </c>
       <c r="Q25" t="n">
-        <v>60.5</v>
+        <v>48.1</v>
       </c>
       <c r="R25" t="n">
-        <v>41.1</v>
+        <v>48.6</v>
       </c>
       <c r="S25" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U25" t="n">
-        <v>12</v>
+        <v>35.6</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -7333,142 +7333,142 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>11.44</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>43.76</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>100.7796</t>
+          <t>100.3346</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.4591</t>
+          <t>0.4328</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.2065</t>
+          <t>0.1625</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.3241</t>
+          <t>0.3375</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>71.61</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>22.49</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>37.38</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.1673</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.08</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.4477</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7479,47 +7479,47 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>686469</t>
+          <t>592626</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Vinnie Pasquantino</t>
+          <t>Joc Pederson</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Sonny Gray</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>543243</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>52.6</v>
+        <v>52.2</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7542,26 +7542,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>40.5</v>
+        <v>49.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>60.5</v>
+        <v>38.6</v>
       </c>
       <c r="R26" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S26" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T26" t="n">
         <v>80</v>
       </c>
       <c r="U26" t="n">
-        <v>25.3</v>
+        <v>56.2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD26" t="inlineStr"/>
@@ -7622,137 +7622,129 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.7% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>42.53</t>
+          <t>49.07</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>91.83</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>100.2834</t>
+          <t>102.03</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4301</t>
+          <t>0.4294</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1943</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3298</t>
+          <t>0.3346</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>72.53</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>15.45</t>
+          <t>25.62</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>43.32</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>29.77</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.2205</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>39.37</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.18</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3936</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1439</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="BG26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>22.85</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr"/>
+      <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7763,27 +7755,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>690993</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colt Keith</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7793,17 +7785,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -7812,7 +7804,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7826,26 +7818,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>36.1</v>
+        <v>44.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="R27" t="n">
-        <v>48.6</v>
+        <v>65.3</v>
       </c>
       <c r="S27" t="n">
-        <v>92.09999999999999</v>
+        <v>47.9</v>
       </c>
       <c r="T27" t="n">
         <v>80</v>
       </c>
       <c r="U27" t="n">
-        <v>35.6</v>
+        <v>45.3</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7859,7 +7851,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7901,12 +7893,12 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7916,12 +7908,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 6/20, 1 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7931,102 +7923,102 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>42.86</t>
+          <t>43.26</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>100.3346</t>
+          <t>101.7196</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4328</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1625</t>
+          <t>0.1749</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3375</t>
+          <t>0.3172</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>71.61</t>
+          <t>75.08</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>54.07</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>37.38</t>
+          <t>35.33</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>26.87</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>10.9</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.1481</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.4142</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1724</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -8036,7 +8028,7 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8047,47 +8039,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>592626</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Joc Pederson</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-18T00:05:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sonny Gray</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>543243</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8096,7 +8088,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>52.2</v>
+        <v>51.8</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8110,40 +8102,40 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>49.6</v>
+        <v>27.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>38.6</v>
+        <v>60.5</v>
       </c>
       <c r="R28" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S28" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T28" t="n">
         <v>80</v>
       </c>
       <c r="U28" t="n">
-        <v>56.2</v>
+        <v>55.9</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
@@ -8158,17 +8150,17 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD28" t="inlineStr"/>
@@ -8185,134 +8177,142 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.7% barrel, 18.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>5.12</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>91.83</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>102.03</t>
+          <t>98.7239</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.4294</t>
+          <t>0.3936</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1943</t>
+          <t>0.1416</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.3346</t>
+          <t>0.2958</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>72.53</t>
+          <t>71.43</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>25.62</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>43.32</t>
+          <t>49.01</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>30.38</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.2205</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>39.37</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>89.18</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.3936</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1439</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr"/>
-      <c r="BH28" t="inlineStr"/>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8323,22 +8323,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>521692</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Salvador Perez</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -8353,17 +8353,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>52</v>
+        <v>51.8</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8386,40 +8386,40 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>44.2</v>
+        <v>46.7</v>
       </c>
       <c r="Q29" t="n">
-        <v>47.7</v>
+        <v>60.5</v>
       </c>
       <c r="R29" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S29" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T29" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U29" t="n">
-        <v>45.3</v>
+        <v>12</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
@@ -8434,17 +8434,17 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 4</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD29" t="inlineStr"/>
@@ -8461,142 +8461,142 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/20, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>11.44</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>43.26</t>
+          <t>43.76</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>101.7196</t>
+          <t>100.7796</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>0.4591</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.1749</t>
+          <t>0.2065</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.3172</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>75.08</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>54.07</t>
+          <t>22.49</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>26.87</t>
+          <t>30.99</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>22.3</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.1481</t>
+          <t>0.1673</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4142</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1724</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -11975,27 +11975,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>693307</t>
+          <t>670231</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Dillon Dingler</t>
+          <t>John Rave</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -12005,17 +12005,17 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -12038,65 +12038,57 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P42" t="n">
-        <v>41.8</v>
+        <v>32.1</v>
       </c>
       <c r="Q42" t="n">
-        <v>48.1</v>
+        <v>60.5</v>
       </c>
       <c r="R42" t="n">
-        <v>48.6</v>
+        <v>41.1</v>
       </c>
       <c r="S42" t="n">
-        <v>81.90000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T42" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U42" t="n">
-        <v>22.6</v>
+        <v>45.1</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Z42" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD42" t="inlineStr"/>
@@ -12113,142 +12105,142 @@
       </c>
       <c r="AH42" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL42" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>36.92</t>
         </is>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>88.16</t>
         </is>
       </c>
       <c r="AQ42" t="inlineStr">
         <is>
-          <t>100.4725</t>
+          <t>99.9569</t>
         </is>
       </c>
       <c r="AR42" t="inlineStr">
         <is>
-          <t>0.4629</t>
+          <t>0.3805</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr">
         <is>
-          <t>0.1955</t>
+          <t>0.1493</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3132</t>
         </is>
       </c>
       <c r="AU42" t="inlineStr">
         <is>
-          <t>71.77</t>
+          <t>73.9</t>
         </is>
       </c>
       <c r="AV42" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>40.14</t>
         </is>
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>44.17</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>25.06</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>0.1904</t>
+          <t>0.1929</t>
         </is>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB42" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC42" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD42" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF42" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG42" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI42" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ42" t="inlineStr"/>
@@ -12259,47 +12251,47 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>693307</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Dillon Dingler</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-17T19:10:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -12308,7 +12300,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>49.6</v>
+        <v>49.7</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12322,61 +12314,65 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>27.2</v>
+        <v>41.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>39.8</v>
+        <v>48.1</v>
       </c>
       <c r="R43" t="n">
-        <v>44.7</v>
+        <v>48.6</v>
       </c>
       <c r="S43" t="n">
-        <v>96.59999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T43" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U43" t="n">
-        <v>81.40000000000001</v>
+        <v>22.6</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W43" t="inlineStr">
+      <c r="Z43" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD43" t="inlineStr"/>
@@ -12393,7 +12389,7 @@
       </c>
       <c r="AH43" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI43" t="inlineStr">
@@ -12403,17 +12399,17 @@
       </c>
       <c r="AJ43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 4/27, 1 HR</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM43" t="inlineStr">
@@ -12423,112 +12419,112 @@
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>9.62</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ43" t="inlineStr">
         <is>
-          <t>98.7904</t>
+          <t>100.4725</t>
         </is>
       </c>
       <c r="AR43" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>0.4629</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>0.1955</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU43" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>71.77</t>
         </is>
       </c>
       <c r="AV43" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>48.9</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
+          <t>28.71</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr">
+        <is>
+          <t>22.8</t>
+        </is>
+      </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>0.1904</t>
+        </is>
+      </c>
+      <c r="BA43" t="inlineStr">
+        <is>
+          <t>8.11</t>
+        </is>
+      </c>
+      <c r="BB43" t="inlineStr">
+        <is>
+          <t>40.78</t>
+        </is>
+      </c>
+      <c r="BC43" t="inlineStr">
+        <is>
+          <t>89.08</t>
+        </is>
+      </c>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>0.4477</t>
+        </is>
+      </c>
+      <c r="BE43" t="inlineStr">
+        <is>
+          <t>0.186</t>
+        </is>
+      </c>
+      <c r="BF43" t="inlineStr">
+        <is>
           <t>29.4</t>
         </is>
       </c>
-      <c r="AY43" t="inlineStr">
-        <is>
-          <t>10.0</t>
-        </is>
-      </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>0.202</t>
-        </is>
-      </c>
-      <c r="BA43" t="inlineStr">
-        <is>
-          <t>9.37</t>
-        </is>
-      </c>
-      <c r="BB43" t="inlineStr">
-        <is>
-          <t>34.46</t>
-        </is>
-      </c>
-      <c r="BC43" t="inlineStr">
-        <is>
-          <t>87.24</t>
-        </is>
-      </c>
-      <c r="BD43" t="inlineStr">
-        <is>
-          <t>0.4123</t>
-        </is>
-      </c>
-      <c r="BE43" t="inlineStr">
-        <is>
-          <t>0.1744</t>
-        </is>
-      </c>
-      <c r="BF43" t="inlineStr">
-        <is>
-          <t>27.75</t>
-        </is>
-      </c>
       <c r="BG43" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI43" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ43" t="inlineStr"/>
@@ -12539,47 +12535,47 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>682626</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Francisco Alvarez</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T19:10:00Z</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Aaron Nola</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>605400</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
@@ -12588,7 +12584,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12602,65 +12598,61 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>54.2</v>
+        <v>27.2</v>
       </c>
       <c r="Q44" t="n">
-        <v>47.7</v>
+        <v>39.8</v>
       </c>
       <c r="R44" t="n">
-        <v>65.3</v>
+        <v>44.7</v>
       </c>
       <c r="S44" t="n">
-        <v>40.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T44" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U44" t="n">
-        <v>4.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr"/>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD44" t="inlineStr"/>
@@ -12677,7 +12669,7 @@
       </c>
       <c r="AH44" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI44" t="inlineStr">
@@ -12687,17 +12679,17 @@
       </c>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM44" t="inlineStr">
@@ -12707,112 +12699,112 @@
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
-          <t>48.98</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>91.21</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ44" t="inlineStr">
         <is>
-          <t>102.9047</t>
+          <t>98.7904</t>
         </is>
       </c>
       <c r="AR44" t="inlineStr">
         <is>
-          <t>0.4293</t>
+          <t>0.395</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr">
         <is>
-          <t>0.2003</t>
+          <t>0.149</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr">
         <is>
-          <t>0.3232</t>
+          <t>0.313</t>
         </is>
       </c>
       <c r="AU44" t="inlineStr">
         <is>
-          <t>74.11</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV44" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>37.89</t>
+          <t>48.9</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
-          <t>13.8</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>0.1721</t>
+          <t>0.202</t>
         </is>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
-          <t>9.31</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BB44" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC44" t="inlineStr">
         <is>
-          <t>88.77</t>
+          <t>87.24</t>
         </is>
       </c>
       <c r="BD44" t="inlineStr">
         <is>
-          <t>0.4142</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
-          <t>0.1724</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="BF44" t="inlineStr">
         <is>
-          <t>27.46</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="BG44" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI44" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ44" t="inlineStr"/>
@@ -12823,27 +12815,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>701678</t>
+          <t>682626</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hao-Yu Lee</t>
+          <t>Francisco Alvarez</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12853,17 +12845,17 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Erick Fedde</t>
+          <t>Aaron Nola</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>607200</t>
+          <t>605400</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
@@ -12872,7 +12864,7 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>49.3</v>
+        <v>49.5</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12886,26 +12878,26 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>33.9</v>
+        <v>54.2</v>
       </c>
       <c r="Q45" t="n">
-        <v>48.1</v>
+        <v>47.7</v>
       </c>
       <c r="R45" t="n">
-        <v>48.6</v>
+        <v>65.3</v>
       </c>
       <c r="S45" t="n">
-        <v>95.5</v>
+        <v>40.2</v>
       </c>
       <c r="T45" t="n">
         <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>29.2</v>
+        <v>4.2</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12919,7 +12911,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12944,7 +12936,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12961,27 +12953,27 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 29.2 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
@@ -12991,102 +12983,102 @@
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>48.98</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>91.21</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>100.1556</t>
+          <t>102.9047</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.2003</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.3232</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>74.11</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>37.89</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>26.3</t>
+          <t>24.68</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>13.8</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1721</t>
         </is>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
-          <t>8.11</t>
+          <t>9.31</t>
         </is>
       </c>
       <c r="BB45" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BC45" t="inlineStr">
         <is>
-          <t>89.08</t>
+          <t>88.77</t>
         </is>
       </c>
       <c r="BD45" t="inlineStr">
         <is>
-          <t>0.4477</t>
+          <t>0.4142</t>
         </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.1724</t>
         </is>
       </c>
       <c r="BF45" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>27.46</t>
         </is>
       </c>
       <c r="BG45" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH45" t="inlineStr">
@@ -13096,7 +13088,7 @@
       </c>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -13107,27 +13099,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>673237</t>
+          <t>701678</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Yainer Diaz</t>
+          <t>Hao-Yu Lee</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -13137,17 +13129,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Erick Fedde</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>607200</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -13156,7 +13148,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>48.9</v>
+        <v>49.3</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -13170,61 +13162,65 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>31.5</v>
+        <v>33.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>52.8</v>
+        <v>48.1</v>
       </c>
       <c r="R46" t="n">
-        <v>41.1</v>
+        <v>48.6</v>
       </c>
       <c r="S46" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T46" t="n">
         <v>50</v>
       </c>
       <c r="U46" t="n">
-        <v>61.7</v>
+        <v>29.2</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W46" t="inlineStr">
+      <c r="Z46" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -13241,12 +13237,12 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
@@ -13256,12 +13252,12 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 9/22 over last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
@@ -13271,112 +13267,112 @@
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>89.34</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>99.9889</t>
+          <t>100.1556</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4174</t>
+          <t>0.389</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3106</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>72.48</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>36.07</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>18.26</t>
+          <t>26.3</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>8.11</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.08</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.4477</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.186</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13387,47 +13383,47 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>673237</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Yainer Diaz</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-17T19:10:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -13436,7 +13432,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13454,22 +13450,22 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>28.3</v>
+        <v>31.5</v>
       </c>
       <c r="Q47" t="n">
-        <v>61.7</v>
+        <v>52.8</v>
       </c>
       <c r="R47" t="n">
-        <v>44.7</v>
+        <v>41.1</v>
       </c>
       <c r="S47" t="n">
-        <v>76.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T47" t="n">
         <v>50</v>
       </c>
       <c r="U47" t="n">
-        <v>54.3</v>
+        <v>61.7</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -13483,7 +13479,7 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
@@ -13526,7 +13522,7 @@
       </c>
       <c r="AI47" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ47" t="inlineStr">
@@ -13536,127 +13532,127 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 9/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>89.34</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>100.1995</t>
+          <t>99.9889</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>0.3815</t>
+          <t>0.4174</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.1306</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3106</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>72.31</t>
+          <t>72.48</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>22.65</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>43.24</t>
+          <t>36.07</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>23.55</t>
+          <t>18.26</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.1077</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>0.4838</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr"/>
@@ -13667,24 +13663,24 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>681393</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>2026-09-17T19:10:00Z</t>
@@ -13697,17 +13693,17 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Michael King</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>650633</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -13716,7 +13712,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13730,26 +13726,26 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>31</v>
+        <v>28.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>41.7</v>
+        <v>61.7</v>
       </c>
       <c r="R48" t="n">
         <v>44.7</v>
       </c>
       <c r="S48" t="n">
-        <v>100</v>
+        <v>76.2</v>
       </c>
       <c r="T48" t="n">
         <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>62.8</v>
+        <v>54.3</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -13763,7 +13759,7 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
@@ -13801,12 +13797,12 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
@@ -13816,112 +13812,112 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Contact streak: 10/24 over last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>98.232</t>
+          <t>100.1995</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.3792</t>
+          <t>0.3815</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.1564</t>
+          <t>0.1306</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>72.31</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>28.08</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>43.24</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>23.55</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.1408</t>
+          <t>0.1077</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>87.24</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.4123</t>
+          <t>0.4838</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1744</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="BG48" t="inlineStr">
@@ -13947,47 +13943,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>681393</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T19:10:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Michael King</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>650633</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13996,7 +13992,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -14010,26 +14006,26 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>35.6</v>
+        <v>31</v>
       </c>
       <c r="Q49" t="n">
-        <v>52.8</v>
+        <v>41.7</v>
       </c>
       <c r="R49" t="n">
-        <v>41.1</v>
+        <v>44.7</v>
       </c>
       <c r="S49" t="n">
-        <v>76.2</v>
+        <v>100</v>
       </c>
       <c r="T49" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>62.8</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -14043,7 +14039,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14081,142 +14077,142 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 10/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.4% barrel, 17.6 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>99.4425</t>
+          <t>98.232</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.3974</t>
+          <t>0.3792</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1676</t>
+          <t>0.1564</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.2976</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.1847</t>
+          <t>0.1408</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>34.46</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.24</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.4123</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.1744</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>27.75</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14227,47 +14223,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>665019</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Kody Clemens</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-18T01:38:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14290,65 +14286,61 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>52.6</v>
+        <v>35.6</v>
       </c>
       <c r="Q50" t="n">
-        <v>20.4</v>
+        <v>52.8</v>
       </c>
       <c r="R50" t="n">
-        <v>28.2</v>
+        <v>41.1</v>
       </c>
       <c r="S50" t="n">
-        <v>92.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T50" t="n">
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>37.8</v>
+        <v>0</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -14365,27 +14357,27 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 1 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14395,104 +14387,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>11.72</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.99</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>101.4875</t>
+          <t>99.4425</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4594</t>
+          <t>0.3974</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.2097</t>
+          <t>0.1676</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3345</t>
+          <t>0.2976</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>72.06</t>
+          <t>73.71</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>46.29</t>
+          <t>41.57</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>33.32</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>23.9</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.2266</t>
+          <t>0.1847</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
+          <t>28.76</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14503,47 +14503,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>666211</t>
+          <t>665019</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Taylor Trammell</t>
+          <t>Kody Clemens</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-18T01:38:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14552,7 +14552,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>48.3</v>
+        <v>48.5</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14566,61 +14566,65 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>38.6</v>
+        <v>52.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>52.8</v>
+        <v>20.4</v>
       </c>
       <c r="R51" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S51" t="n">
-        <v>64.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T51" t="n">
         <v>80</v>
       </c>
       <c r="U51" t="n">
-        <v>10.6</v>
+        <v>37.8</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -14637,27 +14641,27 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14667,112 +14671,104 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>10.95</t>
+          <t>11.72</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>38.27</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>89.11</t>
+          <t>91.99</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>101.0072</t>
+          <t>101.4875</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.4594</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.1613</t>
+          <t>0.2097</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.2836</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>75.93</t>
+          <t>72.06</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>60.32</t>
+          <t>14.49</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>46.29</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>33.32</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>5.8</t>
+          <t>23.9</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.1451</t>
+          <t>0.2266</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>28.76</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -14783,12 +14779,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>672580</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Maikel Garcia</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -14813,7 +14809,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -14832,7 +14828,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>48.1</v>
+        <v>48.3</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14846,11 +14842,11 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>27.3</v>
+        <v>26.6</v>
       </c>
       <c r="Q52" t="n">
         <v>60.5</v>
@@ -14859,27 +14855,27 @@
         <v>41.1</v>
       </c>
       <c r="S52" t="n">
-        <v>59.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>55.9</v>
+        <v>20.9</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -14894,12 +14890,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
@@ -14921,7 +14917,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -14931,17 +14927,17 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Contact streak: 10/27 over last 7 games</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14951,67 +14947,67 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>5.12</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>42.09</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>98.7239</t>
+          <t>100.5105</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.3936</t>
+          <t>0.3891</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.1416</t>
+          <t>0.1138</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.2958</t>
+          <t>0.3224</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>71.43</t>
+          <t>71.83</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>18.43</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>49.01</t>
+          <t>34.81</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>21.04</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
@@ -15067,56 +15063,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>575929</t>
+          <t>666211</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Willson Contreras</t>
+          <t>Taylor Trammell</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-18T00:05:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tyler Alexander</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>641302</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>48</v>
+        <v>48.3</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15130,62 +15126,58 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>56.4</v>
+        <v>38.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>17.7</v>
+        <v>52.8</v>
       </c>
       <c r="R53" t="n">
-        <v>27.6</v>
+        <v>41.1</v>
       </c>
       <c r="S53" t="n">
-        <v>90.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T53" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U53" t="n">
-        <v>26.4</v>
+        <v>10.6</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15210,22 +15202,22 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 4/21, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.5% barrel, 4.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15235,104 +15227,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>13.62</t>
+          <t>10.95</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>38.27</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>90.04</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>102.6842</t>
+          <t>101.0072</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4873</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.231</t>
+          <t>0.1613</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3713</t>
+          <t>0.2836</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>76.7</t>
+          <t>75.93</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>60.32</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>47.17</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>24.9</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.2278</t>
+          <t>0.1451</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.1097</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>24.23</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr"/>
+          <t>28.76</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15343,47 +15343,47 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>575929</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Willson Contreras</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-17T17:10:00Z</t>
+          <t>2026-09-18T00:05:00Z</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Tyler Alexander</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>641302</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>46.9</v>
+        <v>48</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15406,60 +15406,60 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P54" t="n">
-        <v>45.5</v>
+        <v>56.4</v>
       </c>
       <c r="Q54" t="n">
-        <v>46.5</v>
+        <v>17.7</v>
       </c>
       <c r="R54" t="n">
-        <v>41.1</v>
+        <v>27.6</v>
       </c>
       <c r="S54" t="n">
-        <v>52.4</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T54" t="n">
         <v>78</v>
       </c>
       <c r="U54" t="n">
-        <v>5.1</v>
+        <v>26.4</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W54" t="inlineStr">
+      <c r="Z54" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>order MLB 8 vs RotoWire 7</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
@@ -15481,142 +15481,134 @@
       </c>
       <c r="AH54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI54" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.5% barrel, 4.8 HR allowed</t>
         </is>
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>8.86</t>
+          <t>13.62</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>50.92</t>
+          <t>45.71</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>91.84</t>
+          <t>90.04</t>
         </is>
       </c>
       <c r="AQ54" t="inlineStr">
         <is>
-          <t>102.7272</t>
+          <t>102.6842</t>
         </is>
       </c>
       <c r="AR54" t="inlineStr">
         <is>
-          <t>0.4082</t>
+          <t>0.4873</t>
         </is>
       </c>
       <c r="AS54" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.231</t>
         </is>
       </c>
       <c r="AT54" t="inlineStr">
         <is>
-          <t>0.3202</t>
+          <t>0.3713</t>
         </is>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>75.84</t>
+          <t>76.7</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
         <is>
-          <t>58.42</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>24.82</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>24.9</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>0.1442</t>
+          <t>0.2278</t>
         </is>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="BD54" t="inlineStr">
         <is>
-          <t>0.4429</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
-          <t>0.1918</t>
+          <t>0.1097</t>
         </is>
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>32.02</t>
-        </is>
-      </c>
-      <c r="BG54" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH54" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>24.23</t>
+        </is>
+      </c>
+      <c r="BG54" t="inlineStr"/>
+      <c r="BH54" t="inlineStr"/>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr"/>
@@ -15627,27 +15619,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-17T19:10:00Z</t>
+          <t>2026-09-17T17:10:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -15657,26 +15649,26 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Tanner Gordon</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>685299</t>
+          <t>605488</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>46.7</v>
+        <v>46.9</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -15690,26 +15682,26 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>5.4</v>
+        <v>45.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>61.7</v>
+        <v>46.5</v>
       </c>
       <c r="R55" t="n">
-        <v>44.7</v>
+        <v>41.1</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T55" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U55" t="n">
-        <v>45</v>
+        <v>5.1</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -15723,7 +15715,7 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
@@ -15733,7 +15725,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -15741,7 +15733,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr"/>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>order MLB 8 vs RotoWire 7</t>
+        </is>
+      </c>
       <c r="AC55" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15761,12 +15757,12 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
@@ -15776,12 +15772,12 @@
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Contact streak: 10/23 over last 7 games</t>
+          <t>Last 7 games: 2/13, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15791,112 +15787,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>8.86</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>50.92</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>91.84</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>95.2817</t>
+          <t>102.7272</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.4082</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3045</t>
+          <t>0.3202</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>67.03</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>58.42</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>48.2</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>24.82</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1136</t>
+          <t>0.1442</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>10.73</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>90.59</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.4838</t>
+          <t>0.4429</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.2111</t>
+          <t>0.1918</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>33.46</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15907,47 +15903,47 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>701358</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cam Smith</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T19:10:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Seth Lugo</t>
+          <t>Tanner Gordon</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>607625</t>
+          <t>685299</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
@@ -15970,26 +15966,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>40.9</v>
+        <v>5.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>52.8</v>
+        <v>61.7</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>44.7</v>
       </c>
       <c r="S56" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T56" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U56" t="n">
-        <v>49.9</v>
+        <v>45</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -16003,7 +15999,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -16041,142 +16037,142 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 10/23 over last 7 games</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.7% barrel, 17.4 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>101.3692</t>
+          <t>95.2817</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1739</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3145</t>
+          <t>0.3045</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>76.88</t>
+          <t>67.03</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>68.74</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>37.42</t>
+          <t>48.2</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>21.28</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1654</t>
+          <t>0.1136</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>10.73</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>43.38</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.59</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.459</t>
+          <t>0.4838</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.1883</t>
+          <t>0.2111</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>33.46</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16187,24 +16183,24 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>672580</t>
+          <t>701358</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Maikel Garcia</t>
+          <t>Cam Smith</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>HOU</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>HOU</t>
-        </is>
-      </c>
       <c r="F57" t="inlineStr">
         <is>
           <t>2026-09-17T23:15:00Z</t>
@@ -16217,17 +16213,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Seth Lugo</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>607625</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
@@ -16236,7 +16232,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>46.5</v>
+        <v>46.7</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -16250,65 +16246,61 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P57" t="n">
-        <v>26.6</v>
+        <v>40.9</v>
       </c>
       <c r="Q57" t="n">
-        <v>60.5</v>
+        <v>52.8</v>
       </c>
       <c r="R57" t="n">
         <v>41.1</v>
       </c>
       <c r="S57" t="n">
-        <v>81.90000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T57" t="n">
         <v>50</v>
       </c>
       <c r="U57" t="n">
-        <v>20.9</v>
+        <v>49.9</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr"/>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD57" t="inlineStr"/>
@@ -16325,127 +16317,127 @@
       </c>
       <c r="AH57" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.4 HR allowed</t>
         </is>
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
-          <t>42.09</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AQ57" t="inlineStr">
         <is>
-          <t>100.5105</t>
+          <t>101.3692</t>
         </is>
       </c>
       <c r="AR57" t="inlineStr">
         <is>
-          <t>0.3891</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="AS57" t="inlineStr">
         <is>
-          <t>0.1138</t>
+          <t>0.1739</t>
         </is>
       </c>
       <c r="AT57" t="inlineStr">
         <is>
-          <t>0.3224</t>
+          <t>0.3145</t>
         </is>
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>71.83</t>
+          <t>76.88</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>18.43</t>
+          <t>68.74</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>37.42</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>21.04</t>
+          <t>24.79</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>16.7</t>
         </is>
       </c>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.1654</t>
         </is>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="BB57" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>43.38</t>
         </is>
       </c>
       <c r="BC57" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="BD57" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.459</t>
         </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1883</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>28.76</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
@@ -21853,7 +21845,7 @@
         <v>50</v>
       </c>
       <c r="U77" t="n">
-        <v>28.1</v>
+        <v>27.1</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -21910,7 +21902,7 @@
       </c>
       <c r="AI77" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ77" t="inlineStr">
@@ -21920,7 +21912,7 @@
       </c>
       <c r="AK77" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/27, 1 HR</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL77" t="inlineStr">
@@ -24843,22 +24835,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>650333</t>
+          <t>686555</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Luis Arraez</t>
+          <t>Isaac Collins</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -24873,17 +24865,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24906,26 +24898,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>6.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q88" t="n">
-        <v>30.2</v>
+        <v>60.3</v>
       </c>
       <c r="R88" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S88" t="n">
-        <v>94.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T88" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U88" t="n">
-        <v>28.2</v>
+        <v>8.5</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24934,33 +24926,37 @@
       </c>
       <c r="W88" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
+      <c r="Z88" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr"/>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD88" t="inlineStr"/>
@@ -24977,12 +24973,12 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
@@ -24992,127 +24988,127 @@
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>86.24</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>93.8724</t>
+          <t>99.826</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3714</t>
+          <t>0.3247</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.0851</t>
+          <t>0.0948</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.3051</t>
+          <t>0.3052</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>62.92</t>
+          <t>73.33</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>30.34</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>30.24</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>28.31</t>
+          <t>25.18</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>6.6</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1098</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25123,27 +25119,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>668670</t>
+          <t>650333</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Jake Rogers</t>
+          <t>Luis Arraez</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-17T23:40:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -25153,22 +25149,22 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Framber Valdez</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>664285</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L89" t="n">
@@ -25186,26 +25182,26 @@
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P89" t="n">
-        <v>29.1</v>
+        <v>6.9</v>
       </c>
       <c r="Q89" t="n">
-        <v>34.5</v>
+        <v>30.2</v>
       </c>
       <c r="R89" t="n">
-        <v>48.6</v>
+        <v>65.3</v>
       </c>
       <c r="S89" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T89" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U89" t="n">
-        <v>0</v>
+        <v>28.2</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -25219,7 +25215,7 @@
       </c>
       <c r="X89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y89" t="inlineStr">
@@ -25257,12 +25253,12 @@
       </c>
       <c r="AH89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ89" t="inlineStr">
@@ -25272,12 +25268,12 @@
       </c>
       <c r="AK89" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/12, 0 HR</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.9% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM89" t="inlineStr">
@@ -25287,102 +25283,102 @@
       </c>
       <c r="AN89" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>86.24</t>
         </is>
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>98.1269</t>
+          <t>93.8724</t>
         </is>
       </c>
       <c r="AR89" t="inlineStr">
         <is>
-          <t>0.3077</t>
+          <t>0.3714</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.0851</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr">
         <is>
-          <t>0.2705</t>
+          <t>0.3051</t>
         </is>
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>70.64</t>
+          <t>62.92</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>46.53</t>
+          <t>30.24</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>28.31</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.6</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1098</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>5.93</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>90.17</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD89" t="inlineStr">
         <is>
-          <t>0.384</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BF89" t="inlineStr">
         <is>
-          <t>18.04</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BG89" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH89" t="inlineStr">
@@ -25392,7 +25388,7 @@
       </c>
       <c r="BI89" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ89" t="inlineStr"/>
@@ -25403,56 +25399,56 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>694203</t>
+          <t>668670</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Denzer Guzman</t>
+          <t>Jake Rogers</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-18T01:38:00Z</t>
+          <t>2026-09-17T23:40:00Z</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Taj Bradley</t>
+          <t>Framber Valdez</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>671737</t>
+          <t>664285</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>40.9</v>
+        <v>41.2</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
@@ -25466,62 +25462,58 @@
       </c>
       <c r="O90" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P90" t="n">
-        <v>24.5</v>
+        <v>29.1</v>
       </c>
       <c r="Q90" t="n">
-        <v>48.1</v>
+        <v>34.5</v>
       </c>
       <c r="R90" t="n">
-        <v>28.2</v>
+        <v>48.6</v>
       </c>
       <c r="S90" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T90" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U90" t="n">
-        <v>50.3</v>
+        <v>0</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr"/>
       <c r="AC90" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25541,27 +25533,27 @@
       </c>
       <c r="AH90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 1/12, 0 HR</t>
         </is>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM90" t="inlineStr">
@@ -25571,104 +25563,112 @@
       </c>
       <c r="AN90" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>37.23</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>86.57</t>
+          <t>88.45</t>
         </is>
       </c>
       <c r="AQ90" t="inlineStr">
         <is>
-          <t>98.6955</t>
+          <t>98.1269</t>
         </is>
       </c>
       <c r="AR90" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>0.3077</t>
         </is>
       </c>
       <c r="AS90" t="inlineStr">
         <is>
-          <t>0.1127</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>0.2705</t>
         </is>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.64</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>46.53</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>31.52</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>0.1348</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>5.93</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>43.61</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>90.39</t>
+          <t>90.17</t>
         </is>
       </c>
       <c r="BD90" t="inlineStr">
         <is>
-          <t>0.3885</t>
+          <t>0.384</t>
         </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
-          <t>0.1592</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BF90" t="inlineStr">
         <is>
-          <t>29.12</t>
-        </is>
-      </c>
-      <c r="BG90" t="inlineStr"/>
-      <c r="BH90" t="inlineStr"/>
+          <t>18.04</t>
+        </is>
+      </c>
+      <c r="BG90" t="inlineStr">
+        <is>
+          <t>R To L</t>
+        </is>
+      </c>
+      <c r="BH90" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI90" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ90" t="inlineStr"/>
@@ -25679,47 +25679,47 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>686555</t>
+          <t>694203</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Isaac Collins</t>
+          <t>Denzer Guzman</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-18T01:38:00Z</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Taj Bradley</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>671737</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -25728,7 +25728,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>40.6</v>
+        <v>40.9</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25742,26 +25742,26 @@
       </c>
       <c r="O91" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P91" t="n">
-        <v>21.7</v>
+        <v>24.5</v>
       </c>
       <c r="Q91" t="n">
-        <v>60.3</v>
+        <v>48.1</v>
       </c>
       <c r="R91" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S91" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T91" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>8.5</v>
+        <v>50.3</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25775,7 +25775,7 @@
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y91" t="inlineStr">
@@ -25800,7 +25800,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD91" t="inlineStr"/>
@@ -25817,142 +25817,134 @@
       </c>
       <c r="AH91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 21.8 HR allowed</t>
         </is>
       </c>
       <c r="AM91" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN91" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>37.23</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>88.45</t>
+          <t>86.57</t>
         </is>
       </c>
       <c r="AQ91" t="inlineStr">
         <is>
-          <t>99.826</t>
+          <t>98.6955</t>
         </is>
       </c>
       <c r="AR91" t="inlineStr">
         <is>
-          <t>0.3247</t>
+          <t>0.323</t>
         </is>
       </c>
       <c r="AS91" t="inlineStr">
         <is>
-          <t>0.0948</t>
+          <t>0.1127</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr">
         <is>
-          <t>0.3052</t>
+          <t>0.249</t>
         </is>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>73.33</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>30.34</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>39.91</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>25.18</t>
+          <t>23.42</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.1348</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>43.61</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>90.39</t>
         </is>
       </c>
       <c r="BD91" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3885</t>
         </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1592</t>
         </is>
       </c>
       <c r="BF91" t="inlineStr">
         <is>
-          <t>52.6</t>
-        </is>
-      </c>
-      <c r="BG91" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH91" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>29.12</t>
+        </is>
+      </c>
+      <c r="BG91" t="inlineStr"/>
+      <c r="BH91" t="inlineStr"/>
       <c r="BI91" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ91" t="inlineStr"/>
@@ -27075,47 +27067,47 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-09-18T01:38:00Z</t>
+          <t>2026-09-17T23:15:00Z</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Walbert Ureña</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>700712</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -27138,40 +27130,40 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>39.7</v>
+        <v>11.9</v>
       </c>
       <c r="Q96" t="n">
-        <v>20.4</v>
+        <v>60.5</v>
       </c>
       <c r="R96" t="n">
-        <v>28.2</v>
+        <v>41.1</v>
       </c>
       <c r="S96" t="n">
-        <v>90.40000000000001</v>
+        <v>52.4</v>
       </c>
       <c r="T96" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U96" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y96" t="inlineStr">
@@ -27186,12 +27178,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr">
@@ -27218,7 +27210,7 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ96" t="inlineStr">
@@ -27228,119 +27220,127 @@
       </c>
       <c r="AK96" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM96" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN96" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
-          <t>41.12</t>
+          <t>33.72</t>
         </is>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
-          <t>88.95</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ96" t="inlineStr">
         <is>
-          <t>100.8686</t>
+          <t>98.8128</t>
         </is>
       </c>
       <c r="AR96" t="inlineStr">
         <is>
-          <t>0.4287</t>
+          <t>0.3026</t>
         </is>
       </c>
       <c r="AS96" t="inlineStr">
         <is>
-          <t>0.1822</t>
+          <t>0.0777</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr">
         <is>
-          <t>0.3419</t>
+          <t>0.2573</t>
         </is>
       </c>
       <c r="AU96" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>71.17</t>
         </is>
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>13.13</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>37.46</t>
+          <t>33.37</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>19.92</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>0.1912</t>
+          <t>0.1043</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD96" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF96" t="inlineStr">
         <is>
-          <t>22.5</t>
-        </is>
-      </c>
-      <c r="BG96" t="inlineStr"/>
-      <c r="BH96" t="inlineStr"/>
+          <t>52.6</t>
+        </is>
+      </c>
+      <c r="BG96" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH96" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI96" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ96" t="inlineStr"/>
@@ -27351,56 +27351,56 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>641584</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jake Fraley</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-09-17T17:10:00Z</t>
+          <t>2026-09-18T01:38:00Z</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Jeffrey Springs</t>
+          <t>Walbert Ureña</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>605488</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>38.9</v>
+        <v>39.4</v>
       </c>
       <c r="M97" t="inlineStr">
         <is>
@@ -27414,39 +27414,47 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>17.7</v>
+        <v>39.7</v>
       </c>
       <c r="Q97" t="n">
-        <v>46.5</v>
+        <v>20.4</v>
       </c>
       <c r="R97" t="n">
-        <v>41.1</v>
+        <v>28.2</v>
       </c>
       <c r="S97" t="n">
-        <v>76.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T97" t="n">
         <v>50</v>
       </c>
       <c r="U97" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W97" t="inlineStr"/>
-      <c r="X97" t="inlineStr"/>
-      <c r="Y97" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="Z97" t="inlineStr">
         <is>
           <t>Yes</t>
@@ -27454,17 +27462,17 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>not found on RotoWire</t>
+          <t>lineup projected / unconfirmed</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD97" t="inlineStr"/>
@@ -27481,12 +27489,12 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ97" t="inlineStr">
@@ -27496,127 +27504,119 @@
       </c>
       <c r="AK97" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/20, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.6% barrel, 9.0 HR allowed</t>
         </is>
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN97" t="inlineStr">
         <is>
-          <t>7.66</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>25.33</t>
+          <t>41.12</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>84.29</t>
+          <t>88.95</t>
         </is>
       </c>
       <c r="AQ97" t="inlineStr">
         <is>
-          <t>95.9479</t>
+          <t>100.8686</t>
         </is>
       </c>
       <c r="AR97" t="inlineStr">
         <is>
-          <t>0.3564</t>
+          <t>0.4287</t>
         </is>
       </c>
       <c r="AS97" t="inlineStr">
         <is>
-          <t>0.1378</t>
+          <t>0.1822</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr">
         <is>
-          <t>0.2905</t>
+          <t>0.3419</t>
         </is>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>46.92</t>
+          <t>37.46</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>26.24</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>0.1529</t>
+          <t>0.1912</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>35.69</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD97" t="inlineStr">
         <is>
-          <t>0.4429</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
-          <t>0.1918</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="BF97" t="inlineStr">
         <is>
-          <t>32.02</t>
-        </is>
-      </c>
-      <c r="BG97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH97" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>22.5</t>
+        </is>
+      </c>
+      <c r="BG97" t="inlineStr"/>
+      <c r="BH97" t="inlineStr"/>
       <c r="BI97" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ97" t="inlineStr"/>
@@ -27627,56 +27627,56 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>641584</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Jake Fraley</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-09-17T23:15:00Z</t>
+          <t>2026-09-17T17:10:00Z</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Jeffrey Springs</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>605488</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="M98" t="inlineStr">
         <is>
@@ -27690,65 +27690,57 @@
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P98" t="n">
-        <v>11.9</v>
+        <v>17.7</v>
       </c>
       <c r="Q98" t="n">
-        <v>60.5</v>
+        <v>46.5</v>
       </c>
       <c r="R98" t="n">
         <v>41.1</v>
       </c>
       <c r="S98" t="n">
-        <v>47.9</v>
+        <v>76.2</v>
       </c>
       <c r="T98" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U98" t="n">
-        <v>4.5</v>
+        <v>12</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
+      <c r="Z98" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>not found on RotoWire</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD98" t="inlineStr"/>
@@ -27765,7 +27757,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI98" t="inlineStr">
@@ -27780,12 +27772,12 @@
       </c>
       <c r="AK98" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 4/20, 0 HR</t>
         </is>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 31.5 HR allowed</t>
         </is>
       </c>
       <c r="AM98" t="inlineStr">
@@ -27795,97 +27787,97 @@
       </c>
       <c r="AN98" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>7.66</t>
         </is>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>33.72</t>
+          <t>25.33</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>84.29</t>
         </is>
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>98.8128</t>
+          <t>95.9479</t>
         </is>
       </c>
       <c r="AR98" t="inlineStr">
         <is>
-          <t>0.3026</t>
+          <t>0.3564</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>0.0777</t>
+          <t>0.1378</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr">
         <is>
-          <t>0.2573</t>
+          <t>0.2905</t>
         </is>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>71.17</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>13.13</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>33.37</t>
+          <t>46.92</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>19.92</t>
+          <t>26.24</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>0.1043</t>
+          <t>0.1529</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>8.94</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>35.69</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD98" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.4429</t>
         </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1918</t>
         </is>
       </c>
       <c r="BF98" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>32.02</t>
         </is>
       </c>
       <c r="BG98" t="inlineStr">
@@ -27900,7 +27892,7 @@
       </c>
       <c r="BI98" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ98" t="inlineStr"/>
@@ -36881,22 +36873,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>656941</t>
+          <t>695600</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kyle Schwarber</t>
+          <t>Carter Jensen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -36916,12 +36908,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Nolan McLean</t>
+          <t>Miguel Ullola</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>690997</t>
+          <t>699044</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -36948,13 +36940,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>74.90000000000001</v>
+        <v>60.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>30.2</v>
+        <v>60.5</v>
       </c>
       <c r="R4" t="n">
-        <v>65.3</v>
+        <v>41.1</v>
       </c>
       <c r="S4" t="n">
         <v>93.2</v>
@@ -36963,7 +36955,7 @@
         <v>80</v>
       </c>
       <c r="U4" t="n">
-        <v>40.1</v>
+        <v>60.7</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -36972,33 +36964,37 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>RotoWire not confirmed</t>
+        </is>
+      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -37015,12 +37011,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -37035,122 +37031,122 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>17.72</t>
+          <t>14.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>52.46</t>
+          <t>48.78</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.97</t>
+          <t>92.53</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.1156</t>
+          <t>103.0426</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.5229</t>
+          <t>0.4769</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2812</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3758</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>77.16</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>75.42</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>41.56</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>33.04</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>48.3</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2936</t>
+          <t>0.2297</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>15.8</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>36.8</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>88.38</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.3478</t>
+          <t>0.416</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.1246</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>52.6</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>Out To LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>Citi Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr"/>
@@ -37161,22 +37157,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>695600</t>
+          <t>656941</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Carter Jensen</t>
+          <t>Kyle Schwarber</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -37196,12 +37192,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Miguel Ullola</t>
+          <t>Nolan McLean</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>699044</t>
+          <t>690997</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -37210,7 +37206,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>63.4</v>
+        <v>64</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -37224,65 +37220,61 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>60.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>60.5</v>
+        <v>30.2</v>
       </c>
       <c r="R5" t="n">
-        <v>41.1</v>
+        <v>65.3</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>60.7</v>
+        <v>40.1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -37299,12 +37291,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -37319,122 +37311,122 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 15.8% barrel, 2.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher allows elevated contact</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>17.72</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>52.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>92.53</t>
+          <t>92.97</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>103.0426</t>
+          <t>104.1156</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4769</t>
+          <t>0.5229</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2812</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3758</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>77.16</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>75.42</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>54.49</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>33.04</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>48.3</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2297</t>
+          <t>0.2936</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>15.8</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>36.8</t>
+          <t>38.22</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.38</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.416</t>
+          <t>0.3478</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.1246</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>52.6</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Out To LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Citi Field</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -38618,7 +38610,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>60.3</v>
+        <v>60.9</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -38632,7 +38624,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -38645,7 +38637,7 @@
         <v>41.1</v>
       </c>
       <c r="S10" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>80</v>
@@ -38655,14 +38647,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>3</t>
@@ -38680,12 +38672,12 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -38858,7 +38850,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bobby Witt</t>
+          <t>Bobby Witt Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -38902,7 +38894,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>58.6</v>
+        <v>59.3</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -38916,7 +38908,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -38929,7 +38921,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
         <v>50</v>
@@ -38939,14 +38931,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>2</t>
@@ -38964,12 +38956,12 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
+          <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>lineup projected / unconfirmed</t>
+          <t>RotoWire not confirmed</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1378,34 +1378,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11534,34 +11530,30 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB41" t="inlineStr"/>
       <c r="AC41" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12094,34 +12086,30 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB43" t="inlineStr"/>
       <c r="AC43" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -13722,34 +13710,30 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -19534,34 +19518,30 @@
       </c>
       <c r="W70" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB70" t="inlineStr"/>
       <c r="AC70" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -26612,28 +26592,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr"/>
-      <c r="X96" t="inlineStr"/>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y96" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB96" t="inlineStr"/>
       <c r="AC96" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -36926,34 +36910,30 @@
       </c>
       <c r="W134" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X134" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -41626,34 +41606,30 @@
       </c>
       <c r="W151" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB151" t="inlineStr"/>
       <c r="AC151" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -52120,28 +52096,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W189" t="inlineStr"/>
-      <c r="X189" t="inlineStr"/>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X189" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y189" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z189" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z189" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA189" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB189" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB189" t="inlineStr"/>
       <c r="AC189" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -73184,34 +73164,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -12423,27 +12423,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>682674</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Victor Bericoto</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12453,14 +12453,26 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Jack Perkins</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>678022</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L45" t="n">
-        <v>51.9</v>
+        <v>51.8</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -12478,22 +12490,22 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>53.5</v>
+        <v>52.7</v>
       </c>
       <c r="Q45" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="R45" t="n">
         <v>27.6</v>
       </c>
       <c r="S45" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T45" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U45" t="n">
-        <v>37.8</v>
+        <v>65.2</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -12507,7 +12519,7 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -12532,7 +12544,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD45" t="inlineStr"/>
@@ -12549,110 +12561,134 @@
       </c>
       <c r="AH45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL45" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.65</t>
         </is>
       </c>
       <c r="AQ45" t="inlineStr">
         <is>
-          <t>100.3441</t>
+          <t>102.9391</t>
         </is>
       </c>
       <c r="AR45" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.4741</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.2155</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>0.3384</t>
         </is>
       </c>
       <c r="AU45" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>77.39</t>
         </is>
       </c>
       <c r="AV45" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>72.04</t>
         </is>
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>36.5</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>26.5</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>0.173</t>
-        </is>
-      </c>
-      <c r="BA45" t="inlineStr"/>
-      <c r="BB45" t="inlineStr"/>
-      <c r="BC45" t="inlineStr"/>
-      <c r="BD45" t="inlineStr"/>
-      <c r="BE45" t="inlineStr"/>
-      <c r="BF45" t="inlineStr"/>
+          <t>0.1881</t>
+        </is>
+      </c>
+      <c r="BA45" t="inlineStr">
+        <is>
+          <t>9.18</t>
+        </is>
+      </c>
+      <c r="BB45" t="inlineStr">
+        <is>
+          <t>36.86</t>
+        </is>
+      </c>
+      <c r="BC45" t="inlineStr">
+        <is>
+          <t>87.94</t>
+        </is>
+      </c>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>0.3769</t>
+        </is>
+      </c>
+      <c r="BE45" t="inlineStr">
+        <is>
+          <t>0.1503</t>
+        </is>
+      </c>
+      <c r="BF45" t="inlineStr">
+        <is>
+          <t>33.12</t>
+        </is>
+      </c>
       <c r="BG45" t="inlineStr"/>
       <c r="BH45" t="inlineStr"/>
       <c r="BI45" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ45" t="inlineStr"/>
@@ -12663,27 +12699,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>682674</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Victor Bericoto</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12693,24 +12729,12 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>678022</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="n">
         <v>51.8</v>
       </c>
@@ -12730,22 +12754,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>52.7</v>
+        <v>53.5</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="R46" t="n">
         <v>27.6</v>
       </c>
       <c r="S46" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T46" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U46" t="n">
-        <v>65.2</v>
+        <v>35.6</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12759,7 +12783,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12784,7 +12808,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -12801,134 +12825,110 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>90.65</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>102.9391</t>
+          <t>100.3441</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.4741</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.2155</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.3384</t>
+          <t>0.282</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>77.39</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>72.04</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>36.5</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>26.5</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.1881</t>
-        </is>
-      </c>
-      <c r="BA46" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BB46" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
-      </c>
-      <c r="BC46" t="inlineStr">
-        <is>
-          <t>87.94</t>
-        </is>
-      </c>
-      <c r="BD46" t="inlineStr">
-        <is>
-          <t>0.3769</t>
-        </is>
-      </c>
-      <c r="BE46" t="inlineStr">
-        <is>
-          <t>0.1503</t>
-        </is>
-      </c>
-      <c r="BF46" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
+          <t>0.173</t>
+        </is>
+      </c>
+      <c r="BA46" t="inlineStr"/>
+      <c r="BB46" t="inlineStr"/>
+      <c r="BC46" t="inlineStr"/>
+      <c r="BD46" t="inlineStr"/>
+      <c r="BE46" t="inlineStr"/>
+      <c r="BF46" t="inlineStr"/>
       <c r="BG46" t="inlineStr"/>
       <c r="BH46" t="inlineStr"/>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -31863,27 +31863,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>667472</t>
+          <t>668904</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Dane Myers</t>
+          <t>Royce Lewis</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -31893,14 +31893,26 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Ryan Johnson</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>696270</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L117" t="n">
-        <v>43.5</v>
+        <v>43.7</v>
       </c>
       <c r="M117" t="inlineStr">
         <is>
@@ -31914,26 +31926,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>26</v>
+        <v>40.4</v>
       </c>
       <c r="Q117" t="n">
-        <v>41.2</v>
+        <v>46.1</v>
       </c>
       <c r="R117" t="n">
-        <v>39.3</v>
+        <v>28.2</v>
       </c>
       <c r="S117" t="n">
-        <v>88.7</v>
+        <v>71.7</v>
       </c>
       <c r="T117" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U117" t="n">
-        <v>25.3</v>
+        <v>10.8</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -31947,7 +31959,7 @@
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -31972,7 +31984,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -31989,110 +32001,134 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>40.3</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>89.86</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>99.1984</t>
+          <t>100.593</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3677</t>
+          <t>0.3979</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3099</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.04</t>
+          <t>74.65</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>49.82</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>28.49</t>
+          <t>46.51</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>24.4</t>
+          <t>30.78</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1078</t>
-        </is>
-      </c>
-      <c r="BA117" t="inlineStr"/>
-      <c r="BB117" t="inlineStr"/>
-      <c r="BC117" t="inlineStr"/>
-      <c r="BD117" t="inlineStr"/>
-      <c r="BE117" t="inlineStr"/>
-      <c r="BF117" t="inlineStr"/>
+          <t>0.1531</t>
+        </is>
+      </c>
+      <c r="BA117" t="inlineStr">
+        <is>
+          <t>9.48</t>
+        </is>
+      </c>
+      <c r="BB117" t="inlineStr">
+        <is>
+          <t>36.42</t>
+        </is>
+      </c>
+      <c r="BC117" t="inlineStr">
+        <is>
+          <t>87.68</t>
+        </is>
+      </c>
+      <c r="BD117" t="inlineStr">
+        <is>
+          <t>0.4332</t>
+        </is>
+      </c>
+      <c r="BE117" t="inlineStr">
+        <is>
+          <t>0.1833</t>
+        </is>
+      </c>
+      <c r="BF117" t="inlineStr">
+        <is>
+          <t>34.09</t>
+        </is>
+      </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32103,22 +32139,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>667472</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Dane Myers</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -32133,24 +32169,12 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>Patrick Sandoval</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>663776</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="n">
         <v>43.5</v>
       </c>
@@ -32166,26 +32190,26 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>44.4</v>
+        <v>26</v>
       </c>
       <c r="Q118" t="n">
-        <v>34.3</v>
+        <v>41.2</v>
       </c>
       <c r="R118" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S118" t="n">
-        <v>71.7</v>
+        <v>88.7</v>
       </c>
       <c r="T118" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U118" t="n">
-        <v>39.5</v>
+        <v>25.3</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -32199,7 +32223,7 @@
       </c>
       <c r="X118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y118" t="inlineStr">
@@ -32224,7 +32248,7 @@
       </c>
       <c r="AC118" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD118" t="inlineStr"/>
@@ -32241,12 +32265,12 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
@@ -32256,12 +32280,12 @@
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.9% barrel, 6.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
@@ -32271,104 +32295,80 @@
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>89.77</t>
+          <t>89.86</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.1512</t>
+          <t>99.1984</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.4395</t>
+          <t>0.3677</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.334</t>
+          <t>0.3099</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>73.72</t>
+          <t>71.04</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>32.74</t>
+          <t>17.98</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>40.52</t>
+          <t>28.49</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>24.4</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.2176</t>
-        </is>
-      </c>
-      <c r="BA118" t="inlineStr">
-        <is>
-          <t>6.9</t>
-        </is>
-      </c>
-      <c r="BB118" t="inlineStr">
-        <is>
-          <t>36.0</t>
-        </is>
-      </c>
-      <c r="BC118" t="inlineStr">
-        <is>
-          <t>87.8</t>
-        </is>
-      </c>
-      <c r="BD118" t="inlineStr">
-        <is>
-          <t>0.442</t>
-        </is>
-      </c>
-      <c r="BE118" t="inlineStr">
-        <is>
-          <t>0.163</t>
-        </is>
-      </c>
-      <c r="BF118" t="inlineStr">
-        <is>
-          <t>25.7</t>
-        </is>
-      </c>
+          <t>0.1078</t>
+        </is>
+      </c>
+      <c r="BA118" t="inlineStr"/>
+      <c r="BB118" t="inlineStr"/>
+      <c r="BC118" t="inlineStr"/>
+      <c r="BD118" t="inlineStr"/>
+      <c r="BE118" t="inlineStr"/>
+      <c r="BF118" t="inlineStr"/>
       <c r="BG118" t="inlineStr"/>
       <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -32379,27 +32379,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>814430</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Brett Callahan</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -32409,22 +32409,22 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Patrick Sandoval</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>663776</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L119" t="n">
@@ -32442,26 +32442,26 @@
       </c>
       <c r="O119" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P119" t="n">
-        <v>43.3</v>
+        <v>44.4</v>
       </c>
       <c r="Q119" t="n">
-        <v>44.8</v>
+        <v>34.3</v>
       </c>
       <c r="R119" t="n">
         <v>27.6</v>
       </c>
       <c r="S119" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T119" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U119" t="n">
-        <v>7</v>
+        <v>39.5</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -32475,7 +32475,7 @@
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -32500,7 +32500,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr"/>
@@ -32517,134 +32517,134 @@
       </c>
       <c r="AH119" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI119" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/12, 0 HR</t>
+          <t>Last 7 games: 6/23, 1 HR</t>
         </is>
       </c>
       <c r="AL119" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.9% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN119" t="inlineStr">
         <is>
-          <t>11.4</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.77</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
         <is>
-          <t>100.7322</t>
+          <t>100.1512</t>
         </is>
       </c>
       <c r="AR119" t="inlineStr">
         <is>
-          <t>0.377</t>
+          <t>0.4395</t>
         </is>
       </c>
       <c r="AS119" t="inlineStr">
         <is>
+          <t>0.1942</t>
+        </is>
+      </c>
+      <c r="AT119" t="inlineStr">
+        <is>
+          <t>0.334</t>
+        </is>
+      </c>
+      <c r="AU119" t="inlineStr">
+        <is>
+          <t>73.72</t>
+        </is>
+      </c>
+      <c r="AV119" t="inlineStr">
+        <is>
+          <t>32.74</t>
+        </is>
+      </c>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>40.52</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>34.54</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr">
+        <is>
+          <t>9.4</t>
+        </is>
+      </c>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>0.2176</t>
+        </is>
+      </c>
+      <c r="BA119" t="inlineStr">
+        <is>
+          <t>6.9</t>
+        </is>
+      </c>
+      <c r="BB119" t="inlineStr">
+        <is>
+          <t>36.0</t>
+        </is>
+      </c>
+      <c r="BC119" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="BD119" t="inlineStr">
+        <is>
+          <t>0.442</t>
+        </is>
+      </c>
+      <c r="BE119" t="inlineStr">
+        <is>
           <t>0.163</t>
         </is>
       </c>
-      <c r="AT119" t="inlineStr">
-        <is>
-          <t>0.297</t>
-        </is>
-      </c>
-      <c r="AU119" t="inlineStr">
-        <is>
-          <t>74.6</t>
-        </is>
-      </c>
-      <c r="AV119" t="inlineStr">
-        <is>
-          <t>46.7</t>
-        </is>
-      </c>
-      <c r="AW119" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AX119" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
-      <c r="AY119" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="AZ119" t="inlineStr">
-        <is>
-          <t>0.143</t>
-        </is>
-      </c>
-      <c r="BA119" t="inlineStr">
-        <is>
-          <t>7.42</t>
-        </is>
-      </c>
-      <c r="BB119" t="inlineStr">
-        <is>
-          <t>44.67</t>
-        </is>
-      </c>
-      <c r="BC119" t="inlineStr">
-        <is>
-          <t>90.42</t>
-        </is>
-      </c>
-      <c r="BD119" t="inlineStr">
-        <is>
-          <t>0.4293</t>
-        </is>
-      </c>
-      <c r="BE119" t="inlineStr">
-        <is>
-          <t>0.1573</t>
-        </is>
-      </c>
       <c r="BF119" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>25.7</t>
         </is>
       </c>
       <c r="BG119" t="inlineStr"/>
       <c r="BH119" t="inlineStr"/>
       <c r="BI119" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ119" t="inlineStr"/>
@@ -32655,27 +32655,27 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>668904</t>
+          <t>814430</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Royce Lewis</t>
+          <t>Brett Callahan</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -32685,17 +32685,17 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -32718,26 +32718,26 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P120" t="n">
-        <v>40.4</v>
+        <v>43.3</v>
       </c>
       <c r="Q120" t="n">
-        <v>46.1</v>
+        <v>44.8</v>
       </c>
       <c r="R120" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S120" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T120" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
       </c>
       <c r="X120" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y120" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="AC120" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD120" t="inlineStr"/>
@@ -32793,12 +32793,12 @@
       </c>
       <c r="AH120" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI120" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AJ120" t="inlineStr">
@@ -32808,119 +32808,119 @@
       </c>
       <c r="AK120" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 2/12, 0 HR</t>
         </is>
       </c>
       <c r="AL120" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM120" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN120" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>11.4</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AQ120" t="inlineStr">
         <is>
-          <t>100.593</t>
+          <t>100.7322</t>
         </is>
       </c>
       <c r="AR120" t="inlineStr">
         <is>
-          <t>0.3979</t>
+          <t>0.377</t>
         </is>
       </c>
       <c r="AS120" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AU120" t="inlineStr">
         <is>
-          <t>74.65</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV120" t="inlineStr">
         <is>
-          <t>49.82</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>46.51</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>30.78</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>0.1531</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="BA120" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB120" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC120" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD120" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="BE120" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BF120" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="BG120" t="inlineStr"/>
       <c r="BH120" t="inlineStr"/>
       <c r="BI120" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ120" t="inlineStr"/>
@@ -36074,7 +36074,7 @@
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -39483,24 +39483,24 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>685133</t>
+          <t>605170</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Wade Meckler</t>
+          <t>Victor Caratini</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
+          <t>MIN</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
           <t>LAA</t>
         </is>
       </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>MIN</t>
-        </is>
-      </c>
       <c r="F145" t="inlineStr">
         <is>
           <t>2026-09-20T20:07:00Z</t>
@@ -39513,17 +39513,17 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Dean Kremer</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>665152</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -39546,26 +39546,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>11.5</v>
+        <v>29.6</v>
       </c>
       <c r="Q145" t="n">
-        <v>47.7</v>
+        <v>44.6</v>
       </c>
       <c r="R145" t="n">
         <v>28.2</v>
       </c>
       <c r="S145" t="n">
-        <v>92.09999999999999</v>
+        <v>59.8</v>
       </c>
       <c r="T145" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U145" t="n">
-        <v>25.8</v>
+        <v>19.5</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -39604,7 +39604,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr"/>
@@ -39621,12 +39621,12 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI145" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ145" t="inlineStr">
@@ -39636,12 +39636,12 @@
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.3% barrel, 18.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -39651,97 +39651,97 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.19</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>96.6684</t>
+          <t>98.9527</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>0.3844</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>71.39</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>16.29</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.71</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.1107</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>87.96</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4419</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1987</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
@@ -39759,27 +39759,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>682663</t>
+          <t>685133</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Agustin Ramirez</t>
+          <t>Wade Meckler</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -39789,17 +39789,17 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Dean Kremer</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -39822,26 +39822,26 @@
       </c>
       <c r="O146" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P146" t="n">
-        <v>31</v>
+        <v>11.5</v>
       </c>
       <c r="Q146" t="n">
-        <v>43</v>
+        <v>47.7</v>
       </c>
       <c r="R146" t="n">
-        <v>22.6</v>
+        <v>28.2</v>
       </c>
       <c r="S146" t="n">
-        <v>59.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T146" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>78.7</v>
+        <v>25.8</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
       </c>
       <c r="X146" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y146" t="inlineStr">
@@ -39880,7 +39880,7 @@
       </c>
       <c r="AC146" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD146" t="inlineStr"/>
@@ -39897,134 +39897,134 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 7/24, 0 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.3% barrel, 18.5 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>6.66</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>42.38</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>90.03</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>102.6626</t>
+          <t>96.6684</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.351</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1266</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2998</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>75.62</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>56.67</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>42.15</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>18.63</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.96</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4419</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1987</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40311,27 +40311,27 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>682877</t>
+          <t>682663</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Juan Brito</t>
+          <t>Agustin Ramirez</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -40341,14 +40341,26 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Walker Buehler</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>621111</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L148" t="n">
-        <v>40.5</v>
+        <v>40.6</v>
       </c>
       <c r="M148" t="inlineStr">
         <is>
@@ -40362,26 +40374,26 @@
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P148" t="n">
-        <v>16.6</v>
+        <v>31</v>
       </c>
       <c r="Q148" t="n">
-        <v>40.2</v>
+        <v>43</v>
       </c>
       <c r="R148" t="n">
-        <v>39.3</v>
+        <v>22.6</v>
       </c>
       <c r="S148" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T148" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U148" t="n">
-        <v>54.3</v>
+        <v>75.8</v>
       </c>
       <c r="V148" t="inlineStr">
         <is>
@@ -40395,7 +40407,7 @@
       </c>
       <c r="X148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y148" t="inlineStr">
@@ -40420,7 +40432,7 @@
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD148" t="inlineStr"/>
@@ -40437,27 +40449,27 @@
       </c>
       <c r="AH148" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ148" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK148" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL148" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM148" t="inlineStr">
@@ -40467,80 +40479,104 @@
       </c>
       <c r="AN148" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.66</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>42.38</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>90.03</t>
         </is>
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>96.9148</t>
+          <t>102.6626</t>
         </is>
       </c>
       <c r="AR148" t="inlineStr">
         <is>
-          <t>0.359</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="AT148" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.2998</t>
         </is>
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>75.62</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>56.67</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>51.5</t>
+          <t>42.15</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>18.63</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>0.138</t>
-        </is>
-      </c>
-      <c r="BA148" t="inlineStr"/>
-      <c r="BB148" t="inlineStr"/>
-      <c r="BC148" t="inlineStr"/>
-      <c r="BD148" t="inlineStr"/>
-      <c r="BE148" t="inlineStr"/>
-      <c r="BF148" t="inlineStr"/>
+          <t>0.1463</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>8.59</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>38.15</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>88.88</t>
+        </is>
+      </c>
+      <c r="BD148" t="inlineStr">
+        <is>
+          <t>0.4171</t>
+        </is>
+      </c>
+      <c r="BE148" t="inlineStr">
+        <is>
+          <t>0.1645</t>
+        </is>
+      </c>
+      <c r="BF148" t="inlineStr">
+        <is>
+          <t>23.44</t>
+        </is>
+      </c>
       <c r="BG148" t="inlineStr"/>
       <c r="BH148" t="inlineStr"/>
       <c r="BI148" t="inlineStr">
         <is>
-          <t>Great American Ball Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ148" t="inlineStr"/>
@@ -40551,22 +40587,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>682877</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Juan Brito</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -40581,24 +40617,12 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>Jack Perkins</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>678022</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
+      <c r="K149" t="inlineStr"/>
       <c r="L149" t="n">
         <v>40.5</v>
       </c>
@@ -40614,26 +40638,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>21.6</v>
+        <v>16.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>41</v>
+        <v>40.2</v>
       </c>
       <c r="R149" t="n">
-        <v>27.6</v>
+        <v>39.3</v>
       </c>
       <c r="S149" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T149" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U149" t="n">
-        <v>75.90000000000001</v>
+        <v>54.3</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -40647,7 +40671,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -40672,7 +40696,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr"/>
@@ -40689,67 +40713,67 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Hot streak: 4 HR in last 7 games</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>87.9</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>98.4634</t>
+          <t>96.9148</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.359</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.305</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
@@ -40759,64 +40783,40 @@
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>12.3</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>39.1</t>
+          <t>51.5</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>27.8</t>
+          <t>21.2</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.164</t>
-        </is>
-      </c>
-      <c r="BA149" t="inlineStr">
-        <is>
-          <t>9.18</t>
-        </is>
-      </c>
-      <c r="BB149" t="inlineStr">
-        <is>
-          <t>36.86</t>
-        </is>
-      </c>
-      <c r="BC149" t="inlineStr">
-        <is>
-          <t>87.94</t>
-        </is>
-      </c>
-      <c r="BD149" t="inlineStr">
-        <is>
-          <t>0.3769</t>
-        </is>
-      </c>
-      <c r="BE149" t="inlineStr">
-        <is>
-          <t>0.1503</t>
-        </is>
-      </c>
-      <c r="BF149" t="inlineStr">
-        <is>
-          <t>33.12</t>
-        </is>
-      </c>
+          <t>0.138</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr"/>
+      <c r="BB149" t="inlineStr"/>
+      <c r="BC149" t="inlineStr"/>
+      <c r="BD149" t="inlineStr"/>
+      <c r="BE149" t="inlineStr"/>
+      <c r="BF149" t="inlineStr"/>
       <c r="BG149" t="inlineStr"/>
       <c r="BH149" t="inlineStr"/>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Great American Ball Park</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -40827,22 +40827,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>596115</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Trevor Story</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -40857,17 +40857,17 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Jack Perkins</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>678022</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
@@ -40890,26 +40890,26 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>26.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q150" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R150" t="n">
         <v>27.6</v>
       </c>
       <c r="S150" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T150" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U150" t="n">
-        <v>54.3</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
@@ -40923,7 +40923,7 @@
       </c>
       <c r="X150" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y150" t="inlineStr">
@@ -40948,7 +40948,7 @@
       </c>
       <c r="AC150" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD150" t="inlineStr"/>
@@ -40965,134 +40965,134 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Hot streak: 4 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.3% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>6.54</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>40.56</t>
+          <t>36.9</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>88.53</t>
+          <t>87.9</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>99.7938</t>
+          <t>98.4634</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.3559</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.1275</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.2711</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>71.03</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>13.75</t>
+          <t>12.3</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>39.1</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>24.81</t>
+          <t>27.8</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.1294</t>
+          <t>0.164</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>41.51</t>
+          <t>36.86</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.94</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.3993</t>
+          <t>0.3769</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1534</t>
+          <t>0.1503</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>23.37</t>
+          <t>33.12</t>
         </is>
       </c>
       <c r="BG150" t="inlineStr"/>
       <c r="BH150" t="inlineStr"/>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -41103,27 +41103,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>662139</t>
+          <t>596115</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Daulton Varsho</t>
+          <t>Trevor Story</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -41138,17 +41138,17 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
@@ -41170,10 +41170,10 @@
         </is>
       </c>
       <c r="P151" t="n">
-        <v>35.9</v>
+        <v>26.5</v>
       </c>
       <c r="Q151" t="n">
-        <v>37.7</v>
+        <v>43</v>
       </c>
       <c r="R151" t="n">
         <v>27.6</v>
@@ -41185,7 +41185,7 @@
         <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>18.3</v>
+        <v>54.3</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -41241,12 +41241,12 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -41256,12 +41256,12 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/24, 1 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.9% barrel, 10.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.3% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -41271,104 +41271,104 @@
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>6.54</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>37.78</t>
+          <t>40.56</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>87.73</t>
+          <t>88.53</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>99.464</t>
+          <t>99.7938</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.3974</t>
+          <t>0.3559</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.1683</t>
+          <t>0.1275</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.2969</t>
+          <t>0.2711</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>73.71</t>
+          <t>71.03</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>36.67</t>
+          <t>13.75</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>31.55</t>
+          <t>24.81</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1294</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>37.16</t>
+          <t>41.51</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.06</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.4213</t>
+          <t>0.3993</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1534</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>23.37</t>
         </is>
       </c>
       <c r="BG151" t="inlineStr"/>
       <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -41379,27 +41379,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>605170</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Victor Caratini</t>
+          <t>Daulton Varsho</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -41409,22 +41409,22 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L152" t="n">
@@ -41442,26 +41442,26 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>29.6</v>
+        <v>35.9</v>
       </c>
       <c r="Q152" t="n">
-        <v>44.6</v>
+        <v>37.7</v>
       </c>
       <c r="R152" t="n">
-        <v>28.2</v>
+        <v>27.6</v>
       </c>
       <c r="S152" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T152" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U152" t="n">
-        <v>13.6</v>
+        <v>18.3</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -41475,7 +41475,7 @@
       </c>
       <c r="X152" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y152" t="inlineStr">
@@ -41517,134 +41517,134 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 2/24, 1 HR</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.9% barrel, 10.9 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>37.78</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>89.19</t>
+          <t>87.73</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>98.9527</t>
+          <t>99.464</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3844</t>
+          <t>0.3974</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1683</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2969</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>71.39</t>
+          <t>73.71</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>16.29</t>
+          <t>36.67</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>37.71</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>31.55</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1107</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>7.93</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>37.16</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>88.06</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4213</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>24.69</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr"/>
       <c r="BH152" t="inlineStr"/>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -54973,7 +54973,7 @@
         <v>50</v>
       </c>
       <c r="U202" t="n">
-        <v>39.2</v>
+        <v>37.8</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -55034,7 +55034,7 @@
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -55044,7 +55044,7 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 1 HR</t>
+          <t>Last 7 games: 7/28, 1 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -5013,7 +5013,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -6100,7 +6100,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6133,7 +6133,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6190,7 +6190,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
@@ -9411,27 +9411,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>663457</t>
+          <t>671732</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lars Nootbaar</t>
+          <t>Lawrence Butler</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T17:40:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9441,17 +9441,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Gavin Williams</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>668909</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9460,7 +9460,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9474,54 +9474,58 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>47.5</v>
+        <v>37.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>49.2</v>
+        <v>54.2</v>
       </c>
       <c r="R33" t="n">
-        <v>42.2</v>
+        <v>40.6</v>
       </c>
       <c r="S33" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T33" t="n">
         <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>36.3</v>
+        <v>74.5</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr"/>
-      <c r="X33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="Y33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9546,22 +9550,22 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.6% barrel, 25.8 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9571,112 +9575,112 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>9.99</t>
+          <t>8.57</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>44.61</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>91.86</t>
+          <t>89.94</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>101.7802</t>
+          <t>101.8414</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4231</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1809</t>
+          <t>0.1563</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3331</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>73.26</t>
+          <t>73.63</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>35.33</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>28.2</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>18.2</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>0.1616</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>46.05</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>90.12</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4169</t>
+          <t>0.3973</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>25.86</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Chase Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9687,27 +9691,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>671732</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lawrence Butler</t>
+          <t>Fernando Tatis Jr.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-20T17:40:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -9717,17 +9721,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Gavin Williams</t>
+          <t>Sandy Alcantara</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>668909</t>
+          <t>645261</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9750,26 +9754,26 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>37.2</v>
+        <v>58</v>
       </c>
       <c r="Q34" t="n">
-        <v>54.2</v>
+        <v>36.9</v>
       </c>
       <c r="R34" t="n">
-        <v>40.6</v>
+        <v>47.1</v>
       </c>
       <c r="S34" t="n">
-        <v>96.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="T34" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>74.5</v>
+        <v>63.8</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -9783,7 +9787,7 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
@@ -9821,12 +9825,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9841,122 +9845,122 @@
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.6% barrel, 25.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.6% barrel, 22.7 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>44.61</t>
+          <t>53.13</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>89.94</t>
+          <t>93.09</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>101.8414</t>
+          <t>104.4668</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.495</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1563</t>
+          <t>0.2072</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.3756</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>73.63</t>
+          <t>75.65</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>58.12</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>35.52</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>18.2</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1616</t>
+          <t>0.1787</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>6.64</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>46.05</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>90.12</t>
+          <t>89.23</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.3973</t>
+          <t>0.3982</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.1428</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>25.86</t>
+          <t>24.94</t>
         </is>
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9967,22 +9971,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>663457</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Fernando Tatis Jr.</t>
+          <t>Lars Nootbaar</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -10002,12 +10006,12 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Sandy Alcantara</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>645261</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -10030,50 +10034,42 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>58</v>
+        <v>47.5</v>
       </c>
       <c r="Q35" t="n">
-        <v>36.9</v>
+        <v>49.2</v>
       </c>
       <c r="R35" t="n">
-        <v>47.1</v>
+        <v>42.2</v>
       </c>
       <c r="S35" t="n">
         <v>93.2</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>63.8</v>
+        <v>34.9</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -10081,7 +10077,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr"/>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10101,142 +10101,142 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.6% barrel, 22.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>9.99</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>53.13</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>93.09</t>
+          <t>91.86</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>104.4668</t>
+          <t>101.7802</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>0.4231</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2072</t>
+          <t>0.1809</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3756</t>
+          <t>0.3331</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>75.65</t>
+          <t>73.26</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>58.12</t>
+          <t>35.33</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>34.73</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>28.2</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1787</t>
+          <t>0.134</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>89.23</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.3982</t>
+          <t>0.4169</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1428</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>24.94</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG35" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Chase Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -11449,7 +11449,7 @@
         <v>75</v>
       </c>
       <c r="U40" t="n">
-        <v>15.3</v>
+        <v>14.1</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -11502,7 +11502,7 @@
       </c>
       <c r="AI40" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ40" t="inlineStr">
@@ -11512,7 +11512,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 6/28, 0 HR</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>54.4</v>
+        <v>54.3</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>50</v>
       </c>
       <c r="U44" t="n">
-        <v>33.9</v>
+        <v>32</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ44" t="inlineStr">
@@ -12636,7 +12636,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>Contact streak: 9/26 over last 7 games</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL44" t="inlineStr">
@@ -13887,47 +13887,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>608369</t>
+          <t>686948</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corey Seager</t>
+          <t>Drake Baldwin</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-20T18:35:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Spencer Miles</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>693686</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13936,7 +13936,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>53.2</v>
+        <v>53.1</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13954,22 +13954,22 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>61.8</v>
+        <v>56.1</v>
       </c>
       <c r="Q49" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="R49" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T49" t="n">
         <v>80</v>
       </c>
       <c r="U49" t="n">
-        <v>48.5</v>
+        <v>57.2</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -13983,7 +13983,7 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
@@ -14004,7 +14004,7 @@
       <c r="AB49" t="inlineStr"/>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD49" t="inlineStr"/>
@@ -14021,12 +14021,12 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
@@ -14036,112 +14036,112 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Contact streak: 11/29 over last 7 games</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>14.67</t>
+          <t>12.26</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>49.89</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>92.13</t>
+          <t>91.49</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>102.614</t>
+          <t>102.1395</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.5095</t>
+          <t>0.4947</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.2462</t>
+          <t>0.2185</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3678</t>
+          <t>0.3635</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>71.8</t>
+          <t>75.3</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>56.51</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>40.57</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>30.85</t>
+          <t>25.88</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.2034</t>
+          <t>0.1817</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.31</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1192</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BG49" t="inlineStr">
@@ -14151,12 +14151,12 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14167,47 +14167,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>686948</t>
+          <t>608369</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Drake Baldwin</t>
+          <t>Corey Seager</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T18:35:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Spencer Miles</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693686</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14234,22 +14234,22 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>56.1</v>
+        <v>61.8</v>
       </c>
       <c r="Q50" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="R50" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="S50" t="n">
-        <v>93.2</v>
+        <v>100</v>
       </c>
       <c r="T50" t="n">
         <v>80</v>
       </c>
       <c r="U50" t="n">
-        <v>57.2</v>
+        <v>46.9</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
@@ -14284,7 +14284,7 @@
       <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD50" t="inlineStr"/>
@@ -14301,7 +14301,7 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
@@ -14316,112 +14316,112 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Contact streak: 11/29 over last 7 games</t>
+          <t>Last 7 games: 9/29, 1 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>12.26</t>
+          <t>14.67</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>49.89</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.49</t>
+          <t>92.13</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>102.1395</t>
+          <t>102.614</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4947</t>
+          <t>0.5095</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.2185</t>
+          <t>0.2462</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3635</t>
+          <t>0.3678</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>75.3</t>
+          <t>71.8</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>56.51</t>
+          <t>15.16</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>40.57</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>25.88</t>
+          <t>30.85</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1817</t>
+          <t>0.2034</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.1192</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BG50" t="inlineStr">
@@ -14431,12 +14431,12 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14809,7 +14809,7 @@
         <v>50</v>
       </c>
       <c r="U52" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14876,7 +14876,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
@@ -24243,12 +24243,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>672640</t>
+          <t>805300</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Otto Lopez</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -24273,7 +24273,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -24306,11 +24306,11 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P86" t="n">
-        <v>30.1</v>
+        <v>20.8</v>
       </c>
       <c r="Q86" t="n">
         <v>43</v>
@@ -24319,13 +24319,13 @@
         <v>47.1</v>
       </c>
       <c r="S86" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T86" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U86" t="n">
-        <v>34.9</v>
+        <v>81.7</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="X86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y86" t="inlineStr">
@@ -24377,27 +24377,27 @@
       </c>
       <c r="AH86" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM86" t="inlineStr">
@@ -24407,67 +24407,67 @@
       </c>
       <c r="AN86" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>36.99</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>100.1719</t>
+          <t>98.6208</t>
         </is>
       </c>
       <c r="AR86" t="inlineStr">
         <is>
-          <t>0.4242</t>
+          <t>0.3657</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>0.1468</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr">
         <is>
-          <t>0.3286</t>
+          <t>0.3239</t>
         </is>
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>71.84</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>5.44</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>33.63</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>0.1325</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
@@ -24523,27 +24523,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>805300</t>
+          <t>686797</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Brooks Lee</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T20:07:00Z</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -24553,17 +24553,17 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Ryan Johnson</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>696270</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -24572,7 +24572,7 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>47.6</v>
+        <v>47.5</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>
@@ -24586,26 +24586,26 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P87" t="n">
-        <v>20.8</v>
+        <v>21.3</v>
       </c>
       <c r="Q87" t="n">
-        <v>43</v>
+        <v>44.6</v>
       </c>
       <c r="R87" t="n">
-        <v>47.1</v>
+        <v>49.7</v>
       </c>
       <c r="S87" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T87" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U87" t="n">
-        <v>81.7</v>
+        <v>32</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -24619,7 +24619,7 @@
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -24657,142 +24657,142 @@
       </c>
       <c r="AH87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN87" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>36.99</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>88.25</t>
         </is>
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>98.6208</t>
+          <t>97.71</t>
         </is>
       </c>
       <c r="AR87" t="inlineStr">
         <is>
-          <t>0.3657</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>0.3239</t>
+          <t>0.2792</t>
         </is>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>69.92</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>5.44</t>
+          <t>8.42</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.71</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>29.7</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1641</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>38.15</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.68</t>
         </is>
       </c>
       <c r="BD87" t="inlineStr">
         <is>
-          <t>0.4171</t>
+          <t>0.4332</t>
         </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1833</t>
         </is>
       </c>
       <c r="BF87" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>34.09</t>
         </is>
       </c>
       <c r="BG87" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>R To L</t>
         </is>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>80</t>
         </is>
       </c>
       <c r="BI87" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Angel Stadium</t>
         </is>
       </c>
       <c r="BJ87" t="inlineStr"/>
@@ -24803,27 +24803,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>686797</t>
+          <t>672640</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Brooks Lee</t>
+          <t>Otto Lopez</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-09-20T20:07:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -24838,12 +24838,12 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Ryan Johnson</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>696270</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -24866,26 +24866,26 @@
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P88" t="n">
-        <v>21.3</v>
+        <v>30.1</v>
       </c>
       <c r="Q88" t="n">
-        <v>44.6</v>
+        <v>43</v>
       </c>
       <c r="R88" t="n">
-        <v>49.7</v>
+        <v>47.1</v>
       </c>
       <c r="S88" t="n">
         <v>100</v>
       </c>
       <c r="T88" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U88" t="n">
-        <v>32</v>
+        <v>33.7</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -24937,142 +24937,142 @@
       </c>
       <c r="AH88" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.5% barrel, 13.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 20.6 HR allowed</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN88" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>88.25</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="AQ88" t="inlineStr">
         <is>
-          <t>97.71</t>
+          <t>100.1719</t>
         </is>
       </c>
       <c r="AR88" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.4242</t>
         </is>
       </c>
       <c r="AS88" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1468</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr">
         <is>
-          <t>0.2792</t>
+          <t>0.3286</t>
         </is>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>69.92</t>
+          <t>71.84</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>41.71</t>
+          <t>33.63</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>22.85</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>0.1641</t>
+          <t>0.1325</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>38.15</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>87.68</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD88" t="inlineStr">
         <is>
-          <t>0.4332</t>
+          <t>0.4171</t>
         </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
-          <t>0.1833</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF88" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BG88" t="inlineStr">
         <is>
-          <t>R To L</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>76</t>
         </is>
       </c>
       <c r="BI88" t="inlineStr">
         <is>
-          <t>Angel Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ88" t="inlineStr"/>
@@ -25692,7 +25692,7 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>47.3</v>
+        <v>47.2</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>50</v>
       </c>
       <c r="U91" t="n">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ91" t="inlineStr">
@@ -25792,7 +25792,7 @@
       </c>
       <c r="AK91" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/25, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL91" t="inlineStr">
@@ -29003,52 +29003,52 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>668800</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Andrew Knizner</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T23:20:00Z</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Jack Dreyer</t>
+          <t>Brandon Young</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>676263</t>
+          <t>687064</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L103" t="n">
@@ -29066,26 +29066,26 @@
       </c>
       <c r="O103" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P103" t="n">
-        <v>13.4</v>
+        <v>16.9</v>
       </c>
       <c r="Q103" t="n">
-        <v>34.3</v>
+        <v>43.1</v>
       </c>
       <c r="R103" t="n">
-        <v>63.1</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="S103" t="n">
-        <v>94.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T103" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U103" t="n">
-        <v>58.7</v>
+        <v>54.9</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -29099,7 +29099,7 @@
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -29137,12 +29137,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ103" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 6.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.8% barrel, 18.3 HR allowed</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
@@ -29167,112 +29167,112 @@
       </c>
       <c r="AN103" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="AO103" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>35.6</t>
         </is>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>85.53</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
         <is>
-          <t>97.1405</t>
+          <t>99.1565</t>
         </is>
       </c>
       <c r="AR103" t="inlineStr">
         <is>
-          <t>0.3454</t>
+          <t>0.3424</t>
         </is>
       </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>0.1176</t>
+          <t>0.0981</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr">
         <is>
-          <t>0.2899</t>
+          <t>0.2918</t>
         </is>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>69.69</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>6.42</t>
+          <t>30.64</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>31.03</t>
+          <t>31.98</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>23.34</t>
+          <t>20.03</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>0.1319</t>
+          <t>0.122</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>7.75</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>40.17</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>89.88</t>
+          <t>89.33</t>
         </is>
       </c>
       <c r="BD103" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.4159</t>
         </is>
       </c>
       <c r="BE103" t="inlineStr">
         <is>
-          <t>0.1377</t>
+          <t>0.1651</t>
         </is>
       </c>
       <c r="BF103" t="inlineStr">
         <is>
-          <t>27.3</t>
+          <t>26.73</t>
         </is>
       </c>
       <c r="BG103" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>Out To RF</t>
         </is>
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI103" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Oriole Park at Camden Yards</t>
         </is>
       </c>
       <c r="BJ103" t="inlineStr"/>
@@ -29283,56 +29283,56 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>668800</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Andrew Knizner</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-20T23:20:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Brandon Young</t>
+          <t>Jack Dreyer</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>687064</t>
+          <t>676263</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>45.4</v>
+        <v>45.2</v>
       </c>
       <c r="M104" t="inlineStr">
         <is>
@@ -29346,26 +29346,26 @@
       </c>
       <c r="O104" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P104" t="n">
-        <v>16.9</v>
+        <v>13.4</v>
       </c>
       <c r="Q104" t="n">
-        <v>43.1</v>
+        <v>34.3</v>
       </c>
       <c r="R104" t="n">
-        <v>67.59999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="S104" t="n">
-        <v>86.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T104" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U104" t="n">
-        <v>54.9</v>
+        <v>55.6</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -29379,7 +29379,7 @@
       </c>
       <c r="X104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y104" t="inlineStr">
@@ -29417,12 +29417,12 @@
       </c>
       <c r="AH104" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI104" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ104" t="inlineStr">
@@ -29432,12 +29432,12 @@
       </c>
       <c r="AK104" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.8% barrel, 18.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 6.1 HR allowed</t>
         </is>
       </c>
       <c r="AM104" t="inlineStr">
@@ -29447,112 +29447,112 @@
       </c>
       <c r="AN104" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>29.29</t>
         </is>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
-          <t>87.77</t>
+          <t>85.53</t>
         </is>
       </c>
       <c r="AQ104" t="inlineStr">
         <is>
-          <t>99.1565</t>
+          <t>97.1405</t>
         </is>
       </c>
       <c r="AR104" t="inlineStr">
         <is>
-          <t>0.3424</t>
+          <t>0.3454</t>
         </is>
       </c>
       <c r="AS104" t="inlineStr">
         <is>
-          <t>0.0981</t>
+          <t>0.1176</t>
         </is>
       </c>
       <c r="AT104" t="inlineStr">
         <is>
-          <t>0.2918</t>
+          <t>0.2899</t>
         </is>
       </c>
       <c r="AU104" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>69.69</t>
         </is>
       </c>
       <c r="AV104" t="inlineStr">
         <is>
-          <t>30.64</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>31.98</t>
+          <t>31.03</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>20.03</t>
+          <t>23.34</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>0.1319</t>
         </is>
       </c>
       <c r="BA104" t="inlineStr">
         <is>
-          <t>7.75</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="BB104" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="BC104" t="inlineStr">
         <is>
-          <t>89.33</t>
+          <t>89.88</t>
         </is>
       </c>
       <c r="BD104" t="inlineStr">
         <is>
-          <t>0.4159</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="BE104" t="inlineStr">
         <is>
-          <t>0.1651</t>
+          <t>0.1377</t>
         </is>
       </c>
       <c r="BF104" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>27.3</t>
         </is>
       </c>
       <c r="BG104" t="inlineStr">
         <is>
-          <t>Out To RF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI104" t="inlineStr">
         <is>
-          <t>Oriole Park at Camden Yards</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ104" t="inlineStr"/>
@@ -35435,47 +35435,47 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>673962</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Josh Jung</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-09-20T18:35:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Game Over</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Spencer Miles</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>693686</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
@@ -35484,7 +35484,7 @@
         </is>
       </c>
       <c r="L126" t="n">
-        <v>42.6</v>
+        <v>42.5</v>
       </c>
       <c r="M126" t="inlineStr">
         <is>
@@ -35498,26 +35498,26 @@
       </c>
       <c r="O126" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P126" t="n">
-        <v>37.2</v>
+        <v>34.2</v>
       </c>
       <c r="Q126" t="n">
-        <v>11.9</v>
+        <v>21.9</v>
       </c>
       <c r="R126" t="n">
-        <v>42.1</v>
+        <v>41.6</v>
       </c>
       <c r="S126" t="n">
-        <v>96.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T126" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U126" t="n">
-        <v>63.1</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -35531,7 +35531,7 @@
       </c>
       <c r="X126" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y126" t="inlineStr">
@@ -35552,7 +35552,7 @@
       <c r="AB126" t="inlineStr"/>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD126" t="inlineStr"/>
@@ -35569,27 +35569,27 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI126" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL126" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM126" t="inlineStr">
@@ -35599,97 +35599,97 @@
       </c>
       <c r="AN126" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>48.24</t>
+          <t>42.32</t>
         </is>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
-          <t>90.21</t>
+          <t>90.38</t>
         </is>
       </c>
       <c r="AQ126" t="inlineStr">
         <is>
-          <t>100.402</t>
+          <t>99.7373</t>
         </is>
       </c>
       <c r="AR126" t="inlineStr">
         <is>
-          <t>0.4329</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AS126" t="inlineStr">
         <is>
-          <t>0.1585</t>
+          <t>0.1463</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr">
         <is>
-          <t>0.3355</t>
+          <t>0.3136</t>
         </is>
       </c>
       <c r="AU126" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.31</t>
         </is>
       </c>
       <c r="AV126" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>8.58</t>
         </is>
       </c>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>37.55</t>
+          <t>44.22</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>23.71</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>12.8</t>
         </is>
       </c>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BA126" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="BB126" t="inlineStr">
         <is>
-          <t>34.5</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="BC126" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.31</t>
         </is>
       </c>
       <c r="BD126" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.3229</t>
         </is>
       </c>
       <c r="BE126" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.1192</t>
         </is>
       </c>
       <c r="BF126" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>23.09</t>
         </is>
       </c>
       <c r="BG126" t="inlineStr">
@@ -35699,12 +35699,12 @@
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI126" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ126" t="inlineStr"/>
@@ -35715,47 +35715,47 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>673962</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>Josh Jung</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T18:35:00Z</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Game Over</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Spencer Miles</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>693686</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
@@ -35778,26 +35778,26 @@
       </c>
       <c r="O127" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P127" t="n">
-        <v>34.2</v>
+        <v>37.2</v>
       </c>
       <c r="Q127" t="n">
-        <v>21.9</v>
+        <v>11.9</v>
       </c>
       <c r="R127" t="n">
-        <v>41.6</v>
+        <v>42.1</v>
       </c>
       <c r="S127" t="n">
-        <v>64.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T127" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U127" t="n">
-        <v>71.09999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -35811,7 +35811,7 @@
       </c>
       <c r="X127" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y127" t="inlineStr">
@@ -35832,7 +35832,7 @@
       <c r="AB127" t="inlineStr"/>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD127" t="inlineStr"/>
@@ -35849,27 +35849,27 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI127" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL127" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.1% barrel, 12.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.5% barrel, 5.0 HR allowed</t>
         </is>
       </c>
       <c r="AM127" t="inlineStr">
@@ -35879,97 +35879,97 @@
       </c>
       <c r="AN127" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>42.32</t>
+          <t>48.24</t>
         </is>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
-          <t>90.38</t>
+          <t>90.21</t>
         </is>
       </c>
       <c r="AQ127" t="inlineStr">
         <is>
-          <t>99.7373</t>
+          <t>100.402</t>
         </is>
       </c>
       <c r="AR127" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.4329</t>
         </is>
       </c>
       <c r="AS127" t="inlineStr">
         <is>
-          <t>0.1463</t>
+          <t>0.1585</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr">
         <is>
-          <t>0.3136</t>
+          <t>0.3355</t>
         </is>
       </c>
       <c r="AU127" t="inlineStr">
         <is>
-          <t>71.31</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV127" t="inlineStr">
         <is>
-          <t>8.58</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>44.22</t>
+          <t>37.55</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>23.71</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BA127" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>3.5</t>
         </is>
       </c>
       <c r="BB127" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>34.5</t>
         </is>
       </c>
       <c r="BC127" t="inlineStr">
         <is>
-          <t>86.31</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="BD127" t="inlineStr">
         <is>
-          <t>0.3229</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="BE127" t="inlineStr">
         <is>
-          <t>0.1192</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BF127" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="BG127" t="inlineStr">
@@ -35979,12 +35979,12 @@
       </c>
       <c r="BH127" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI127" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ127" t="inlineStr"/>
@@ -36555,24 +36555,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>683011</t>
+          <t>694374</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Anthony Volpe</t>
+          <t>Tim Tawa</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>NYY</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>2026-09-20T20:10:00Z</t>
@@ -36585,17 +36585,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Corbin Burnes</t>
+          <t>Will Warren</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>669203</t>
+          <t>701542</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36618,50 +36618,42 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>25.5</v>
+        <v>40.2</v>
       </c>
       <c r="Q130" t="n">
-        <v>54.5</v>
+        <v>49.2</v>
       </c>
       <c r="R130" t="n">
         <v>42.2</v>
       </c>
       <c r="S130" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T130" t="n">
         <v>50</v>
       </c>
       <c r="U130" t="n">
-        <v>17.7</v>
+        <v>0</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="X130" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -36669,7 +36661,11 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB130" t="inlineStr"/>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>not found on RotoWire</t>
+        </is>
+      </c>
       <c r="AC130" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36689,7 +36685,7 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
@@ -36704,112 +36700,112 @@
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/21, 0 HR</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>6.37</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>43.29</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>88.46</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>98.8902</t>
+          <t>100.6567</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.3581</t>
+          <t>0.3932</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>0.1613</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.2982</t>
+          <t>0.304</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>71.62</t>
+          <t>73.66</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>19.19</t>
+          <t>34.88</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>38.77</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>24.83</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>9.1</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.1195</t>
+          <t>0.1509</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>11.18</t>
+          <t>8.59</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>38.73</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>90.34</t>
+          <t>90.93</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.4081</t>
+          <t>0.4169</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.1839</t>
+          <t>0.161</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>43.67</t>
+          <t>23.96</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
@@ -36835,24 +36831,24 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>694374</t>
+          <t>683011</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Tim Tawa</t>
+          <t>Anthony Volpe</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F131" t="inlineStr">
         <is>
           <t>2026-09-20T20:10:00Z</t>
@@ -36865,17 +36861,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Will Warren</t>
+          <t>Corbin Burnes</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>701542</t>
+          <t>669203</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -36884,7 +36880,7 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>42.2</v>
+        <v>42.1</v>
       </c>
       <c r="M131" t="inlineStr">
         <is>
@@ -36898,54 +36894,58 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P131" t="n">
-        <v>40.2</v>
+        <v>25.5</v>
       </c>
       <c r="Q131" t="n">
-        <v>49.2</v>
+        <v>54.5</v>
       </c>
       <c r="R131" t="n">
         <v>42.2</v>
       </c>
       <c r="S131" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T131" t="n">
         <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>0</v>
+        <v>16.1</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W131" t="inlineStr"/>
-      <c r="X131" t="inlineStr"/>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y131" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -36965,12 +36965,12 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -36980,112 +36980,112 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.6% barrel, 21.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.2% barrel, 3.5 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>6.37</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>43.29</t>
+          <t>38.47</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>88.46</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>100.6567</t>
+          <t>98.8902</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.3932</t>
+          <t>0.3581</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.1613</t>
+          <t>0.126</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>0.2982</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>71.62</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>34.88</t>
+          <t>19.19</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>38.77</t>
+          <t>33.01</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>24.83</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1509</t>
+          <t>0.1195</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>8.59</t>
+          <t>11.18</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>38.73</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>90.93</t>
+          <t>90.34</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4169</t>
+          <t>0.4081</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>0.1839</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>23.96</t>
+          <t>43.67</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
@@ -38000,7 +38000,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -38033,7 +38033,7 @@
         <v>78</v>
       </c>
       <c r="U135" t="n">
-        <v>15.3</v>
+        <v>13.6</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
       </c>
       <c r="AI135" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ135" t="inlineStr">
@@ -38100,7 +38100,7 @@
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL135" t="inlineStr">
@@ -38231,32 +38231,32 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>676439</t>
+          <t>807726</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Hunter Feduccia</t>
+          <t>John Peck</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-20T20:10:00Z</t>
+          <t>2026-09-20T18:10:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Delayed Start</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -38266,21 +38266,21 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>41.5</v>
+        <v>41.4</v>
       </c>
       <c r="M136" t="inlineStr">
         <is>
@@ -38294,17 +38294,17 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>27.1</v>
+        <v>34.4</v>
       </c>
       <c r="Q136" t="n">
-        <v>50.9</v>
+        <v>44.8</v>
       </c>
       <c r="R136" t="n">
-        <v>63.1</v>
+        <v>53.6</v>
       </c>
       <c r="S136" t="n">
         <v>44.8</v>
@@ -38313,7 +38313,7 @@
         <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>2</v>
+        <v>8.5</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38365,12 +38365,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38380,127 +38380,127 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/15, 0 HR</t>
+          <t>Last 7 games: 3/17, 0 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>37.0</t>
+          <t>40.5</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>98.7756</t>
+          <t>98.866</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3475</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.1206</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3058</t>
+          <t>0.341</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>70.71</t>
+          <t>72.2</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>12.56</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>32.73</t>
+          <t>24.3</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>0.021</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.42</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>0.4293</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>0.1573</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>23.97</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -38511,32 +38511,32 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>807726</t>
+          <t>676439</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>John Peck</t>
+          <t>Hunter Feduccia</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-20T18:10:00Z</t>
+          <t>2026-09-20T20:10:00Z</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Delayed Start</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -38546,17 +38546,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L137" t="n">
@@ -38574,17 +38574,17 @@
       </c>
       <c r="O137" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P137" t="n">
-        <v>34.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q137" t="n">
-        <v>44.8</v>
+        <v>50.9</v>
       </c>
       <c r="R137" t="n">
-        <v>53.6</v>
+        <v>63.1</v>
       </c>
       <c r="S137" t="n">
         <v>44.8</v>
@@ -38593,7 +38593,7 @@
         <v>50</v>
       </c>
       <c r="U137" t="n">
-        <v>8.5</v>
+        <v>0.8</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38628,7 +38628,7 @@
       <c r="AB137" t="inlineStr"/>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr"/>
@@ -38645,12 +38645,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38660,127 +38660,127 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/17, 0 HR</t>
+          <t>Last 7 games: 2/16, 0 HR</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.4% barrel, 15.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN137" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
-          <t>40.5</t>
+          <t>37.0</t>
         </is>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>98.866</t>
+          <t>98.7756</t>
         </is>
       </c>
       <c r="AR137" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3475</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.1206</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr">
         <is>
-          <t>0.341</t>
+          <t>0.3058</t>
         </is>
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>72.2</t>
+          <t>70.71</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>12.56</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>32.73</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>26.89</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>0.085</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>7.42</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>49.2</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD137" t="inlineStr">
         <is>
-          <t>0.4293</t>
+          <t>0.444</t>
         </is>
       </c>
       <c r="BE137" t="inlineStr">
         <is>
-          <t>0.1573</t>
+          <t>0.187</t>
         </is>
       </c>
       <c r="BF137" t="inlineStr">
         <is>
-          <t>23.97</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="BG137" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH137" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>79</t>
         </is>
       </c>
       <c r="BI137" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ137" t="inlineStr"/>
@@ -38840,7 +38840,7 @@
         </is>
       </c>
       <c r="L138" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M138" t="inlineStr">
         <is>
@@ -38873,7 +38873,7 @@
         <v>50</v>
       </c>
       <c r="U138" t="n">
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="V138" t="inlineStr">
         <is>
@@ -38930,7 +38930,7 @@
       </c>
       <c r="AI138" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ138" t="inlineStr">
@@ -38940,7 +38940,7 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL138" t="inlineStr">
@@ -42480,7 +42480,7 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>39.3</v>
+        <v>39.2</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>36</v>
+        <v>33.9</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
       </c>
       <c r="AI151" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ151" t="inlineStr">
@@ -42580,7 +42580,7 @@
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 9/26 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
@@ -43130,7 +43130,7 @@
       </c>
       <c r="AI153" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ153" t="inlineStr">
@@ -43140,7 +43140,7 @@
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/17, 0 HR</t>
+          <t>Last 7 games: 2/18, 0 HR</t>
         </is>
       </c>
       <c r="AL153" t="inlineStr">
@@ -55715,7 +55715,7 @@
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>40.1</v>
+        <v>39.1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -55772,7 +55772,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -56802,7 +56802,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>57.3</v>
+        <v>57.2</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -56835,7 +56835,7 @@
         <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>22.9</v>
+        <v>21.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -56892,7 +56892,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -56902,7 +56902,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 0 HR</t>
+          <t>Last 7 games: 6/23, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>48.7</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -5224,7 +5224,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>50.5</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S18" t="n">
         <v>94.90000000000001</v>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>50.5</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -5719,7 +5719,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -7395,27 +7395,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>681715</t>
+          <t>683146</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Heriberto Hernández</t>
+          <t>Brett Baty</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7425,26 +7425,26 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>55.3</v>
+        <v>55.5</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7458,26 +7458,26 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>52.5</v>
+        <v>45.4</v>
       </c>
       <c r="Q26" t="n">
-        <v>41.3</v>
+        <v>48.7</v>
       </c>
       <c r="R26" t="n">
-        <v>38.8</v>
+        <v>42.1</v>
       </c>
       <c r="S26" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U26" t="n">
-        <v>23.4</v>
+        <v>63.3</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -7491,7 +7491,7 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
@@ -7529,27 +7529,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Contact streak: 7/15 over last 7 games</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7559,112 +7559,112 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>12.12</t>
+          <t>11.08</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>43.4</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.56</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>101.636</t>
+          <t>101.8115</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.4588</t>
+          <t>0.4234</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.2145</t>
+          <t>0.1798</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3438</t>
+          <t>0.3242</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>74.07</t>
+          <t>75.15</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>44.06</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>46.12</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.59</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>19.8</t>
+          <t>13.1</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1972</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>0.4176</t>
+          <t>0.4392</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>23.7</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr"/>
@@ -7675,27 +7675,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>683146</t>
+          <t>681715</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Brett Baty</t>
+          <t>Heriberto Hernández</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7705,22 +7705,22 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L27" t="n">
@@ -7738,26 +7738,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>45.4</v>
+        <v>52.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>48.7</v>
+        <v>41.3</v>
       </c>
       <c r="R27" t="n">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="S27" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T27" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U27" t="n">
-        <v>63.3</v>
+        <v>23.4</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7809,27 +7809,27 @@
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Contact streak: 7/15 over last 7 games</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7839,112 +7839,112 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>11.08</t>
+          <t>12.12</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>43.4</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>90.56</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>101.8115</t>
+          <t>101.636</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.4234</t>
+          <t>0.4588</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.1798</t>
+          <t>0.2145</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.3242</t>
+          <t>0.3438</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>75.15</t>
+          <t>74.07</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>44.06</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>46.12</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>26.59</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>13.1</t>
+          <t>19.8</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.1972</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>0.4392</t>
+          <t>0.4176</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>23.7</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr"/>
@@ -8556,7 +8556,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>54</v>
+        <v>54.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8580,7 +8580,7 @@
         <v>50.5</v>
       </c>
       <c r="R30" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S30" t="n">
         <v>96.59999999999999</v>
@@ -8771,7 +8771,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -10476,7 +10476,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -11060,7 +11060,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>46.9</v>
       </c>
       <c r="R39" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S39" t="n">
         <v>93.2</v>
@@ -11275,7 +11275,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
@@ -11340,7 +11340,7 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>52.7</v>
+        <v>52.9</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>50.5</v>
       </c>
       <c r="R40" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S40" t="n">
         <v>93.2</v>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI40" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -13507,47 +13507,47 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>701807</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Carson Benge</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-09-24T23:05:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
@@ -13570,65 +13570,61 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>60.8</v>
+        <v>32.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>33.7</v>
+        <v>48.7</v>
       </c>
       <c r="R48" t="n">
-        <v>38.2</v>
+        <v>42.1</v>
       </c>
       <c r="S48" t="n">
-        <v>92.09999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T48" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U48" t="n">
-        <v>7</v>
+        <v>48.5</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD48" t="inlineStr"/>
@@ -13645,134 +13641,142 @@
       </c>
       <c r="AH48" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 0 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>13.09</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>92.54</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AQ48" t="inlineStr">
         <is>
-          <t>104.8811</t>
+          <t>99.6028</t>
         </is>
       </c>
       <c r="AR48" t="inlineStr">
         <is>
-          <t>0.4926</t>
+          <t>0.434</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr">
         <is>
-          <t>0.2271</t>
+          <t>0.157</t>
         </is>
       </c>
       <c r="AT48" t="inlineStr">
         <is>
-          <t>0.3558</t>
+          <t>0.339</t>
         </is>
       </c>
       <c r="AU48" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>71.0</t>
         </is>
       </c>
       <c r="AV48" t="inlineStr">
         <is>
-          <t>83.78</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>45.03</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>23.35</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>19.0</t>
         </is>
       </c>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>0.2556</t>
+          <t>0.145</t>
         </is>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="BB48" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC48" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD48" t="inlineStr">
         <is>
-          <t>0.3441</t>
+          <t>0.4392</t>
         </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF48" t="inlineStr">
         <is>
-          <t>26.04</t>
-        </is>
-      </c>
-      <c r="BG48" t="inlineStr"/>
-      <c r="BH48" t="inlineStr"/>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG48" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH48" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI48" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ48" t="inlineStr"/>
@@ -13783,47 +13787,47 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>673548</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seiya Suzuki</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -13832,7 +13836,7 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -13846,58 +13850,62 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P49" t="n">
-        <v>47.4</v>
+        <v>60.8</v>
       </c>
       <c r="Q49" t="n">
-        <v>39.8</v>
+        <v>33.7</v>
       </c>
       <c r="R49" t="n">
-        <v>38.8</v>
+        <v>38.2</v>
       </c>
       <c r="S49" t="n">
-        <v>100</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T49" t="n">
         <v>50</v>
       </c>
       <c r="U49" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W49" t="inlineStr">
+      <c r="Z49" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC49" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13917,142 +13925,134 @@
       </c>
       <c r="AH49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI49" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/31, 1 HR</t>
+          <t>Last 7 games: 4/24, 0 HR</t>
         </is>
       </c>
       <c r="AL49" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>13.09</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>49.86</t>
         </is>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>92.54</t>
         </is>
       </c>
       <c r="AQ49" t="inlineStr">
         <is>
-          <t>101.021</t>
+          <t>104.8811</t>
         </is>
       </c>
       <c r="AR49" t="inlineStr">
         <is>
-          <t>0.4443</t>
+          <t>0.4926</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr">
         <is>
-          <t>0.1994</t>
+          <t>0.2271</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr">
         <is>
-          <t>0.3415</t>
+          <t>0.3558</t>
         </is>
       </c>
       <c r="AU49" t="inlineStr">
         <is>
-          <t>73.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AV49" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>83.78</t>
         </is>
       </c>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>45.03</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>23.35</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>42.2</t>
         </is>
       </c>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>0.2113</t>
+          <t>0.2556</t>
         </is>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="BB49" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BC49" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD49" t="inlineStr">
         <is>
-          <t>0.4015</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BF49" t="inlineStr">
         <is>
-          <t>26.01</t>
-        </is>
-      </c>
-      <c r="BG49" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH49" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>26.04</t>
+        </is>
+      </c>
+      <c r="BG49" t="inlineStr"/>
+      <c r="BH49" t="inlineStr"/>
       <c r="BI49" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ49" t="inlineStr"/>
@@ -14063,47 +14063,47 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>673548</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Seiya Suzuki</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-24T23:15:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Brady Singer</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>663903</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -14126,62 +14126,58 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P50" t="n">
-        <v>53.1</v>
+        <v>47.4</v>
       </c>
       <c r="Q50" t="n">
-        <v>54.8</v>
+        <v>39.8</v>
       </c>
       <c r="R50" t="n">
-        <v>30.9</v>
+        <v>38.8</v>
       </c>
       <c r="S50" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T50" t="n">
         <v>50</v>
       </c>
       <c r="U50" t="n">
-        <v>33.7</v>
+        <v>39</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr"/>
       <c r="AC50" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14201,12 +14197,12 @@
       </c>
       <c r="AH50" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI50" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AJ50" t="inlineStr">
@@ -14216,12 +14212,12 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 1 HR</t>
+          <t>Last 7 games: 8/31, 1 HR</t>
         </is>
       </c>
       <c r="AL50" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.9% barrel, 27.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM50" t="inlineStr">
@@ -14231,104 +14227,112 @@
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>41.91</t>
         </is>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="AQ50" t="inlineStr">
         <is>
-          <t>102.718</t>
+          <t>101.021</t>
         </is>
       </c>
       <c r="AR50" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4443</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr">
         <is>
-          <t>0.1949</t>
+          <t>0.1994</t>
         </is>
       </c>
       <c r="AT50" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3415</t>
         </is>
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>73.3</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>40.22</t>
+          <t>40.99</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>32.11</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.2113</t>
         </is>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB50" t="inlineStr">
         <is>
-          <t>42.31</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BC50" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="BD50" t="inlineStr">
         <is>
-          <t>0.4489</t>
+          <t>0.4015</t>
         </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="BF50" t="inlineStr">
         <is>
-          <t>26.86</t>
-        </is>
-      </c>
-      <c r="BG50" t="inlineStr"/>
-      <c r="BH50" t="inlineStr"/>
+          <t>26.01</t>
+        </is>
+      </c>
+      <c r="BG50" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH50" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="BI50" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ50" t="inlineStr"/>
@@ -14339,47 +14343,47 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>701807</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carson Benge</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T23:15:00Z</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Brady Singer</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>663903</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
@@ -14388,7 +14392,7 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>51.4</v>
+        <v>51.5</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -14402,61 +14406,65 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P51" t="n">
-        <v>32.3</v>
+        <v>53.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>48.7</v>
+        <v>54.8</v>
       </c>
       <c r="R51" t="n">
-        <v>41.1</v>
+        <v>30.9</v>
       </c>
       <c r="S51" t="n">
-        <v>94.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T51" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U51" t="n">
-        <v>48.5</v>
+        <v>33.7</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr">
+      <c r="Z51" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD51" t="inlineStr"/>
@@ -14473,12 +14481,12 @@
       </c>
       <c r="AH51" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI51" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ51" t="inlineStr">
@@ -14488,12 +14496,12 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 6/27, 1 HR</t>
         </is>
       </c>
       <c r="AL51" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.9% barrel, 27.4 HR allowed</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
@@ -14503,112 +14511,104 @@
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>46.0</t>
         </is>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ51" t="inlineStr">
         <is>
-          <t>99.6028</t>
+          <t>102.718</t>
         </is>
       </c>
       <c r="AR51" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr">
         <is>
-          <t>0.157</t>
+          <t>0.1949</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU51" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>59.5</t>
         </is>
       </c>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>40.22</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="BB51" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>42.31</t>
         </is>
       </c>
       <c r="BC51" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="BD51" t="inlineStr">
         <is>
-          <t>0.4392</t>
+          <t>0.4489</t>
         </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.18</t>
         </is>
       </c>
       <c r="BF51" t="inlineStr">
         <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH51" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>26.86</t>
+        </is>
+      </c>
+      <c r="BG51" t="inlineStr"/>
+      <c r="BH51" t="inlineStr"/>
       <c r="BI51" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ51" t="inlineStr"/>
@@ -14619,32 +14619,32 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>699024</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Leo Bernal</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-24T16:35:00Z</t>
+          <t>2026-09-25T02:10:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -14654,12 +14654,12 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -14682,61 +14682,65 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>58.6</v>
+        <v>54.3</v>
       </c>
       <c r="Q52" t="n">
+        <v>36</v>
+      </c>
+      <c r="R52" t="n">
         <v>27.6</v>
       </c>
-      <c r="R52" t="n">
-        <v>28.8</v>
-      </c>
       <c r="S52" t="n">
-        <v>86.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T52" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U52" t="n">
-        <v>40.7</v>
+        <v>36.5</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W52" t="inlineStr">
+      <c r="Z52" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD52" t="inlineStr"/>
@@ -14758,7 +14762,7 @@
       </c>
       <c r="AI52" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ52" t="inlineStr">
@@ -14768,127 +14772,119 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 1 HR</t>
+          <t>Last 7 games: 7/29, 1 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.7% barrel, 16.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>9.7</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>58.1</t>
+          <t>47.1</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>91.03</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>102.1888</t>
+          <t>101.2132</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.501</t>
+          <t>0.4893</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>0.2228</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>0.3463</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>37.63</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>35.5</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.185</t>
+          <t>0.1888</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>38.66</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>87.81</t>
+          <t>89.67</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.3392</t>
+          <t>0.3317</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>22.94</t>
-        </is>
-      </c>
-      <c r="BG52" t="inlineStr">
-        <is>
-          <t>In From RF</t>
-        </is>
-      </c>
-      <c r="BH52" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
+          <t>28.71</t>
+        </is>
+      </c>
+      <c r="BG52" t="inlineStr"/>
+      <c r="BH52" t="inlineStr"/>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -14899,32 +14895,32 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>699024</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Leo Bernal</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-25T02:10:00Z</t>
+          <t>2026-09-24T16:35:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -14934,12 +14930,12 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Paul Skenes</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>694973</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
@@ -14948,7 +14944,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14962,65 +14958,61 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>54.3</v>
+        <v>58.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>36</v>
+        <v>27.6</v>
       </c>
       <c r="R53" t="n">
-        <v>27.6</v>
+        <v>28.8</v>
       </c>
       <c r="S53" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T53" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U53" t="n">
-        <v>36.5</v>
+        <v>39.2</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr"/>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD53" t="inlineStr"/>
@@ -15042,7 +15034,7 @@
       </c>
       <c r="AI53" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ53" t="inlineStr">
@@ -15052,119 +15044,127 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/29, 1 HR</t>
+          <t>Last 7 games: 7/27, 1 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.7% barrel, 16.6 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>47.1</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>91.03</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>101.2132</t>
+          <t>102.1888</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.4893</t>
+          <t>0.501</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.2228</t>
+          <t>0.218</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.3463</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>43.5</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>35.5</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.1888</t>
+          <t>0.185</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>6.71</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>87.81</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3317</t>
+          <t>0.3392</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>28.71</t>
-        </is>
-      </c>
-      <c r="BG53" t="inlineStr"/>
-      <c r="BH53" t="inlineStr"/>
+          <t>22.94</t>
+        </is>
+      </c>
+      <c r="BG53" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH53" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -15451,52 +15451,52 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>663330</t>
+          <t>607043</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Jahmai Jones</t>
+          <t>Brandon Nimmo</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-24T22:45:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L55" t="n">
@@ -15514,62 +15514,58 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>49.6</v>
+        <v>45.5</v>
       </c>
       <c r="Q55" t="n">
-        <v>43.5</v>
+        <v>50.5</v>
       </c>
       <c r="R55" t="n">
-        <v>28.7</v>
+        <v>42.1</v>
       </c>
       <c r="S55" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T55" t="n">
         <v>50</v>
       </c>
       <c r="U55" t="n">
-        <v>35.6</v>
+        <v>15.3</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -15589,27 +15585,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 1 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15619,104 +15615,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>46.46</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>91.97</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>102.2774</t>
+          <t>102.0213</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.4581</t>
+          <t>0.4393</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.2108</t>
+          <t>0.1747</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3472</t>
+          <t>0.3357</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>73.39</t>
+          <t>72.34</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>35.63</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>50.74</t>
+          <t>33.73</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>27.92</t>
+          <t>25.77</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>6.3</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1965</t>
+          <t>0.1544</t>
         </is>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB55" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC55" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD55" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>36.7</t>
-        </is>
-      </c>
-      <c r="BG55" t="inlineStr"/>
-      <c r="BH55" t="inlineStr"/>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15727,56 +15731,56 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>607043</t>
+          <t>663330</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Brandon Nimmo</t>
+          <t>Jahmai Jones</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>50.7</v>
+        <v>50.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15790,58 +15794,62 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>45.5</v>
+        <v>49.6</v>
       </c>
       <c r="Q56" t="n">
-        <v>50.5</v>
+        <v>43.5</v>
       </c>
       <c r="R56" t="n">
-        <v>41.1</v>
+        <v>28.7</v>
       </c>
       <c r="S56" t="n">
-        <v>86.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T56" t="n">
         <v>50</v>
       </c>
       <c r="U56" t="n">
-        <v>15.3</v>
+        <v>35.6</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W56" t="inlineStr">
+      <c r="Z56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -15861,27 +15869,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 4/17, 1 HR</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15891,112 +15899,104 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>11.09</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>46.46</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>91.97</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>102.0213</t>
+          <t>102.2774</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.4393</t>
+          <t>0.4581</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1747</t>
+          <t>0.2108</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.3357</t>
+          <t>0.3472</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>72.34</t>
+          <t>73.39</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>35.63</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>33.73</t>
+          <t>50.74</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>25.77</t>
+          <t>27.92</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>6.3</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.1544</t>
+          <t>0.1965</t>
         </is>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BB56" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC56" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BD56" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH56" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>36.7</t>
+        </is>
+      </c>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16917,7 +16917,7 @@
         <v>80</v>
       </c>
       <c r="U60" t="n">
-        <v>25.3</v>
+        <v>24.3</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -16974,7 +16974,7 @@
       </c>
       <c r="AI60" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ60" t="inlineStr">
@@ -16984,7 +16984,7 @@
       </c>
       <c r="AK60" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/25, 1 HR</t>
         </is>
       </c>
       <c r="AL60" t="inlineStr">
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>49.9</v>
+        <v>50</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -17744,7 +17744,7 @@
         <v>50.5</v>
       </c>
       <c r="R63" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S63" t="n">
         <v>76.2</v>
@@ -17935,7 +17935,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI63" t="inlineStr">
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -19964,7 +19964,7 @@
         <v>48.7</v>
       </c>
       <c r="R71" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S71" t="n">
         <v>96.59999999999999</v>
@@ -20155,7 +20155,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI71" t="inlineStr">
@@ -21024,7 +21024,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -29640,7 +29640,7 @@
         </is>
       </c>
       <c r="L106" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="M106" t="inlineStr">
         <is>
@@ -29664,7 +29664,7 @@
         <v>48.7</v>
       </c>
       <c r="R106" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S106" t="n">
         <v>64.3</v>
@@ -29855,7 +29855,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI106" t="inlineStr">
@@ -30172,7 +30172,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -31815,52 +31815,52 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>703607</t>
+          <t>553869</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Henry Bolte</t>
+          <t>Elias Díaz</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-09-25T01:40:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>Peter Lambert</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>663567</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L114" t="n">
@@ -31878,65 +31878,61 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>37.7</v>
+        <v>31.5</v>
       </c>
       <c r="Q114" t="n">
-        <v>32.9</v>
+        <v>50.5</v>
       </c>
       <c r="R114" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="S114" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T114" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U114" t="n">
-        <v>50.3</v>
+        <v>23.7</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr"/>
@@ -31953,27 +31949,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 15.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -31983,104 +31979,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>39.61</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>90.8</t>
+          <t>88.33</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>104.3571</t>
+          <t>100.5511</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>0.3445</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1341</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>0.2666</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>74.34</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>43.86</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>37.93</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>0.1515</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>35.8</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>32.5</t>
-        </is>
-      </c>
-      <c r="BG114" t="inlineStr"/>
-      <c r="BH114" t="inlineStr"/>
+          <t>30.5</t>
+        </is>
+      </c>
+      <c r="BG114" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH114" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -32091,27 +32095,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>668939</t>
+          <t>703607</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Adley Rutschman</t>
+          <t>Henry Bolte</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-09-24T22:45:00Z</t>
+          <t>2026-09-25T01:40:00Z</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -32121,17 +32125,17 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Peter Lambert</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>663567</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -32140,7 +32144,7 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="M115" t="inlineStr">
         <is>
@@ -32154,26 +32158,26 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P115" t="n">
-        <v>31.6</v>
+        <v>37.7</v>
       </c>
       <c r="Q115" t="n">
-        <v>43.2</v>
+        <v>32.9</v>
       </c>
       <c r="R115" t="n">
-        <v>28.7</v>
+        <v>30.9</v>
       </c>
       <c r="S115" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T115" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U115" t="n">
-        <v>19.5</v>
+        <v>50.3</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -32187,7 +32191,7 @@
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -32212,7 +32216,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr"/>
@@ -32229,27 +32233,27 @@
       </c>
       <c r="AH115" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI115" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL115" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
@@ -32259,104 +32263,104 @@
       </c>
       <c r="AN115" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>99.19</t>
+          <t>104.3571</t>
         </is>
       </c>
       <c r="AR115" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.375</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>0.1606</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr">
         <is>
-          <t>0.3271</t>
+          <t>0.318</t>
         </is>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>70.42</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.8</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>0.1705</t>
+          <t>0.128</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>13.3</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="BD115" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>0.357</t>
         </is>
       </c>
       <c r="BE115" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.139</t>
         </is>
       </c>
       <c r="BF115" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="BG115" t="inlineStr"/>
       <c r="BH115" t="inlineStr"/>
       <c r="BI115" t="inlineStr">
         <is>
-          <t>Fenway Park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ115" t="inlineStr"/>
@@ -32367,27 +32371,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>668939</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Adley Rutschman</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-09-24T23:05:00Z</t>
+          <t>2026-09-24T22:45:00Z</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -32397,17 +32401,17 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -32430,26 +32434,26 @@
       </c>
       <c r="O116" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P116" t="n">
-        <v>41.2</v>
+        <v>31.6</v>
       </c>
       <c r="Q116" t="n">
-        <v>33.7</v>
+        <v>43.2</v>
       </c>
       <c r="R116" t="n">
-        <v>38.2</v>
+        <v>28.7</v>
       </c>
       <c r="S116" t="n">
-        <v>88.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T116" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U116" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -32463,7 +32467,7 @@
       </c>
       <c r="X116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y116" t="inlineStr">
@@ -32488,7 +32492,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD116" t="inlineStr"/>
@@ -32505,7 +32509,7 @@
       </c>
       <c r="AH116" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI116" t="inlineStr">
@@ -32520,119 +32524,119 @@
       </c>
       <c r="AK116" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/28, 0 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL116" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>switch hitter; pitcher baseline 13.3% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN116" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="AO116" t="inlineStr">
         <is>
-          <t>49.35</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>103.21</t>
+          <t>99.19</t>
         </is>
       </c>
       <c r="AR116" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.1606</t>
         </is>
       </c>
       <c r="AT116" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3271</t>
         </is>
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>70.42</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>37.44</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>19.72</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>0.1624</t>
+          <t>0.1705</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>13.3</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>38.94</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="BD116" t="inlineStr">
         <is>
-          <t>0.3441</t>
+          <t>0.352</t>
         </is>
       </c>
       <c r="BE116" t="inlineStr">
         <is>
-          <t>0.1309</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="BF116" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>36.7</t>
         </is>
       </c>
       <c r="BG116" t="inlineStr"/>
       <c r="BH116" t="inlineStr"/>
       <c r="BI116" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Fenway Park</t>
         </is>
       </c>
       <c r="BJ116" t="inlineStr"/>
@@ -32643,27 +32647,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>641487</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>J.P. Crawford</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-25T01:40:00Z</t>
+          <t>2026-09-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -32678,12 +32682,12 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Grayson Rodriguez</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>680570</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -32706,26 +32710,26 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P117" t="n">
-        <v>21.1</v>
+        <v>41.2</v>
       </c>
       <c r="Q117" t="n">
-        <v>53.6</v>
+        <v>33.7</v>
       </c>
       <c r="R117" t="n">
-        <v>25.4</v>
+        <v>38.2</v>
       </c>
       <c r="S117" t="n">
         <v>88.7</v>
       </c>
       <c r="T117" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U117" t="n">
-        <v>21.8</v>
+        <v>0</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -32764,7 +32768,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr"/>
@@ -32781,7 +32785,7 @@
       </c>
       <c r="AH117" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI117" t="inlineStr">
@@ -32791,17 +32795,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/28, 1 HR</t>
+          <t>Last 7 games: 2/28, 0 HR</t>
         </is>
       </c>
       <c r="AL117" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.9% barrel, 15.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
@@ -32811,104 +32815,104 @@
       </c>
       <c r="AN117" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>34.49</t>
+          <t>49.35</t>
         </is>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>98.0324</t>
+          <t>103.21</t>
         </is>
       </c>
       <c r="AR117" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>0.1221</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr">
         <is>
-          <t>0.3224</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>71.21</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>37.44</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>23.81</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>19.72</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>0.1204</t>
+          <t>0.1624</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>7.64</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>45.1</t>
+          <t>38.94</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD117" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>0.3441</t>
         </is>
       </c>
       <c r="BE117" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.1309</t>
         </is>
       </c>
       <c r="BF117" t="inlineStr">
         <is>
-          <t>27.6</t>
+          <t>26.04</t>
         </is>
       </c>
       <c r="BG117" t="inlineStr"/>
       <c r="BH117" t="inlineStr"/>
       <c r="BI117" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ117" t="inlineStr"/>
@@ -32919,56 +32923,56 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>553869</t>
+          <t>641487</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Elias Díaz</t>
+          <t>J.P. Crawford</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-25T01:40:00Z</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Grayson Rodriguez</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>680570</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="M118" t="inlineStr">
         <is>
@@ -32982,58 +32986,62 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P118" t="n">
-        <v>31.5</v>
+        <v>21.1</v>
       </c>
       <c r="Q118" t="n">
-        <v>50.5</v>
+        <v>53.6</v>
       </c>
       <c r="R118" t="n">
-        <v>41.1</v>
+        <v>25.4</v>
       </c>
       <c r="S118" t="n">
-        <v>52.4</v>
+        <v>88.7</v>
       </c>
       <c r="T118" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U118" t="n">
-        <v>23.7</v>
+        <v>21.8</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr">
+      <c r="Z118" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X118" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y118" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC118" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -33053,142 +33061,134 @@
       </c>
       <c r="AH118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI118" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 4/28, 1 HR</t>
         </is>
       </c>
       <c r="AL118" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.9% barrel, 15.0 HR allowed</t>
         </is>
       </c>
       <c r="AM118" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN118" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>5.74</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>34.49</t>
         </is>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>88.33</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
         <is>
-          <t>100.5511</t>
+          <t>98.0324</t>
         </is>
       </c>
       <c r="AR118" t="inlineStr">
         <is>
-          <t>0.3445</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>0.1341</t>
+          <t>0.1221</t>
         </is>
       </c>
       <c r="AT118" t="inlineStr">
         <is>
-          <t>0.2666</t>
+          <t>0.3224</t>
         </is>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>74.34</t>
+          <t>71.21</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>43.86</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>35.77</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>22.47</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>0.1515</t>
+          <t>0.1204</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>45.1</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="BD118" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.468</t>
         </is>
       </c>
       <c r="BE118" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="BF118" t="inlineStr">
         <is>
-          <t>30.5</t>
-        </is>
-      </c>
-      <c r="BG118" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH118" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>27.6</t>
+        </is>
+      </c>
+      <c r="BG118" t="inlineStr"/>
+      <c r="BH118" t="inlineStr"/>
       <c r="BI118" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ118" t="inlineStr"/>
@@ -35440,7 +35440,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -36300,7 +36300,7 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>42.5</v>
+        <v>42.7</v>
       </c>
       <c r="M130" t="inlineStr">
         <is>
@@ -36324,7 +36324,7 @@
         <v>48.7</v>
       </c>
       <c r="R130" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S130" t="n">
         <v>52.4</v>
@@ -36515,7 +36515,7 @@
       </c>
       <c r="BH130" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI130" t="inlineStr">
@@ -37108,7 +37108,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -37688,7 +37688,7 @@
         </is>
       </c>
       <c r="L135" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="M135" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
         <v>48.7</v>
       </c>
       <c r="R135" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S135" t="n">
         <v>76.2</v>
@@ -37903,7 +37903,7 @@
       </c>
       <c r="BH135" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI135" t="inlineStr">
@@ -38755,32 +38755,32 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>687462</t>
+          <t>677649</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Spencer Horwitz</t>
+          <t>Ezequiel Duran</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-09-24T16:35:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -38790,17 +38790,17 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Kyle Leahy</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>681517</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L139" t="n">
@@ -38822,22 +38822,22 @@
         </is>
       </c>
       <c r="P139" t="n">
-        <v>20.9</v>
+        <v>20.4</v>
       </c>
       <c r="Q139" t="n">
-        <v>51.3</v>
+        <v>50.5</v>
       </c>
       <c r="R139" t="n">
-        <v>28.8</v>
+        <v>42.1</v>
       </c>
       <c r="S139" t="n">
         <v>64.3</v>
       </c>
       <c r="T139" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U139" t="n">
-        <v>28.9</v>
+        <v>0</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -38872,7 +38872,7 @@
       <c r="AB139" t="inlineStr"/>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr"/>
@@ -38889,12 +38889,12 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI139" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ139" t="inlineStr">
@@ -38904,127 +38904,127 @@
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/16, 0 HR</t>
+          <t>Last 7 games: 2/26, 0 HR</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.7% barrel, 12.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN139" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>5.05</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>36.15</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
-          <t>86.98</t>
+          <t>87.82</t>
         </is>
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>97.4124</t>
+          <t>98.9997</t>
         </is>
       </c>
       <c r="AR139" t="inlineStr">
         <is>
-          <t>0.3685</t>
+          <t>0.3496</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>0.1318</t>
+          <t>0.1146</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr">
         <is>
-          <t>0.3183</t>
+          <t>0.2862</t>
         </is>
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>68.54</t>
+          <t>72.27</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>24.59</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>39.52</t>
+          <t>35.45</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>27.63</t>
+          <t>21.58</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>11.9</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>0.1333</t>
+          <t>0.1355</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>46.13</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD139" t="inlineStr">
         <is>
-          <t>0.4363</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE139" t="inlineStr">
         <is>
-          <t>0.167</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF139" t="inlineStr">
         <is>
-          <t>23.17</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BG139" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH139" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI139" t="inlineStr">
         <is>
-          <t>PNC Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ139" t="inlineStr"/>
@@ -39084,7 +39084,7 @@
         </is>
       </c>
       <c r="L140" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M140" t="inlineStr">
         <is>
@@ -39117,7 +39117,7 @@
         <v>75</v>
       </c>
       <c r="U140" t="n">
-        <v>24</v>
+        <v>22.8</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -39174,7 +39174,7 @@
       </c>
       <c r="AI140" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ140" t="inlineStr">
@@ -39184,7 +39184,7 @@
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 3/20, 1 HR</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
@@ -39315,32 +39315,32 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>677649</t>
+          <t>687462</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ezequiel Duran</t>
+          <t>Spencer Horwitz</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T16:35:00Z</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -39350,21 +39350,21 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Kyle Leahy</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>681517</t>
         </is>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>41.1</v>
+        <v>41</v>
       </c>
       <c r="M141" t="inlineStr">
         <is>
@@ -39382,22 +39382,22 @@
         </is>
       </c>
       <c r="P141" t="n">
-        <v>20.4</v>
+        <v>20.9</v>
       </c>
       <c r="Q141" t="n">
-        <v>50.5</v>
+        <v>51.3</v>
       </c>
       <c r="R141" t="n">
-        <v>41.1</v>
+        <v>28.8</v>
       </c>
       <c r="S141" t="n">
         <v>64.3</v>
       </c>
       <c r="T141" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U141" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
       <c r="AB141" t="inlineStr"/>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr"/>
@@ -39449,12 +39449,12 @@
       </c>
       <c r="AH141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI141" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ141" t="inlineStr">
@@ -39464,127 +39464,127 @@
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/26, 0 HR</t>
+          <t>Last 7 games: 5/17, 0 HR</t>
         </is>
       </c>
       <c r="AL141" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.7% barrel, 12.0 HR allowed</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN141" t="inlineStr">
         <is>
-          <t>5.05</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>32.36</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
-          <t>87.82</t>
+          <t>86.98</t>
         </is>
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>98.9997</t>
+          <t>97.4124</t>
         </is>
       </c>
       <c r="AR141" t="inlineStr">
         <is>
-          <t>0.3496</t>
+          <t>0.3685</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>0.1146</t>
+          <t>0.1318</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr">
         <is>
-          <t>0.2862</t>
+          <t>0.3183</t>
         </is>
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>72.27</t>
+          <t>68.54</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>24.59</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>35.45</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>27.63</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>11.9</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>0.1355</t>
+          <t>0.1333</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>9.73</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>46.13</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="BD141" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.4363</t>
         </is>
       </c>
       <c r="BE141" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.167</t>
         </is>
       </c>
       <c r="BF141" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="BG141" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH141" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI141" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>PNC Park</t>
         </is>
       </c>
       <c r="BJ141" t="inlineStr"/>
@@ -41535,27 +41535,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>664983</t>
+          <t>643376</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Jake McCarthy</t>
+          <t>Danny Jansen</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-09-24T19:10:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -41565,17 +41565,17 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>Eduardo Rodriguez</t>
+          <t>Zac Thornton</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>593958</t>
+          <t>804267</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
@@ -41598,26 +41598,26 @@
       </c>
       <c r="O149" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P149" t="n">
-        <v>16.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q149" t="n">
-        <v>37.8</v>
+        <v>50.5</v>
       </c>
       <c r="R149" t="n">
-        <v>48.7</v>
+        <v>42.1</v>
       </c>
       <c r="S149" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T149" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U149" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="V149" t="inlineStr">
         <is>
@@ -41631,7 +41631,7 @@
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -41652,7 +41652,7 @@
       <c r="AB149" t="inlineStr"/>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr"/>
@@ -41669,12 +41669,12 @@
       </c>
       <c r="AH149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI149" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ149" t="inlineStr">
@@ -41684,127 +41684,127 @@
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/28, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL149" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.7% barrel, 20.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN149" t="inlineStr">
         <is>
-          <t>5.51</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>28.16</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>85.05</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>96.8804</t>
+          <t>97.8804</t>
         </is>
       </c>
       <c r="AR149" t="inlineStr">
         <is>
-          <t>0.4034</t>
+          <t>0.3192</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>0.1378</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT149" t="inlineStr">
         <is>
-          <t>0.3133</t>
+          <t>0.2776</t>
         </is>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>70.89</t>
+          <t>69.85</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>13.4</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>37.87</t>
+          <t>54.05</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>28.84</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>11.7</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>0.1746</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>9.6</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>41.4</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>87.57</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="BD149" t="inlineStr">
         <is>
-          <t>0.4181</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="BE149" t="inlineStr">
         <is>
-          <t>0.1657</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BF149" t="inlineStr">
         <is>
-          <t>27.26</t>
+          <t>30.5</t>
         </is>
       </c>
       <c r="BG149" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH149" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI149" t="inlineStr">
         <is>
-          <t>Coors Field</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ149" t="inlineStr"/>
@@ -41815,56 +41815,56 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>664983</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Jake McCarthy</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-09-25T02:10:00Z</t>
+          <t>2026-09-24T19:10:00Z</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Eduardo Rodriguez</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>593958</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="M150" t="inlineStr">
         <is>
@@ -41878,62 +41878,58 @@
       </c>
       <c r="O150" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P150" t="n">
-        <v>35.4</v>
+        <v>16.7</v>
       </c>
       <c r="Q150" t="n">
-        <v>43.6</v>
+        <v>37.8</v>
       </c>
       <c r="R150" t="n">
-        <v>27.6</v>
+        <v>48.7</v>
       </c>
       <c r="S150" t="n">
-        <v>47.9</v>
+        <v>93.2</v>
       </c>
       <c r="T150" t="n">
         <v>50</v>
       </c>
       <c r="U150" t="n">
-        <v>56.6</v>
+        <v>19.5</v>
       </c>
       <c r="V150" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W150" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X150" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr"/>
       <c r="AC150" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -41953,134 +41949,142 @@
       </c>
       <c r="AH150" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI150" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK150" t="inlineStr">
         <is>
-          <t>Contact streak: 9/24 over last 7 games</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL150" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.7% barrel, 20.1 HR allowed</t>
         </is>
       </c>
       <c r="AM150" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN150" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>5.51</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>40.35</t>
+          <t>28.16</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>85.05</t>
         </is>
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>99.6698</t>
+          <t>96.8804</t>
         </is>
       </c>
       <c r="AR150" t="inlineStr">
         <is>
-          <t>0.4357</t>
+          <t>0.4034</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>0.1665</t>
+          <t>0.1378</t>
         </is>
       </c>
       <c r="AT150" t="inlineStr">
         <is>
-          <t>0.3342</t>
+          <t>0.3133</t>
         </is>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>70.89</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>26.19</t>
+          <t>13.4</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>38.39</t>
+          <t>37.87</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>21.45</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>11.7</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.1746</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>33.66</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>87.57</t>
         </is>
       </c>
       <c r="BD150" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.4181</t>
         </is>
       </c>
       <c r="BE150" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.1657</t>
         </is>
       </c>
       <c r="BF150" t="inlineStr">
         <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="BG150" t="inlineStr"/>
-      <c r="BH150" t="inlineStr"/>
+          <t>27.26</t>
+        </is>
+      </c>
+      <c r="BG150" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH150" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI150" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Coors Field</t>
         </is>
       </c>
       <c r="BJ150" t="inlineStr"/>
@@ -42091,56 +42095,56 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>640459</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-25T02:10:00Z</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>Matthew Boyd</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>571510</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>40.2</v>
+        <v>40.3</v>
       </c>
       <c r="M151" t="inlineStr">
         <is>
@@ -42154,58 +42158,62 @@
       </c>
       <c r="O151" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P151" t="n">
-        <v>28.9</v>
+        <v>35.4</v>
       </c>
       <c r="Q151" t="n">
-        <v>41.3</v>
+        <v>43.6</v>
       </c>
       <c r="R151" t="n">
-        <v>38.8</v>
+        <v>27.6</v>
       </c>
       <c r="S151" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T151" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U151" t="n">
-        <v>32</v>
+        <v>56.6</v>
       </c>
       <c r="V151" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W151" t="inlineStr">
+      <c r="Z151" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB151" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC151" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -42225,142 +42233,134 @@
       </c>
       <c r="AH151" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AJ151" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>Contact streak: 1/3 over last 7 games</t>
+          <t>Contact streak: 9/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL151" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN151" t="inlineStr">
         <is>
-          <t>11.91</t>
+          <t>7.84</t>
         </is>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>35.34</t>
+          <t>40.35</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
-          <t>88.12</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>98.2729</t>
+          <t>99.6698</t>
         </is>
       </c>
       <c r="AR151" t="inlineStr">
         <is>
-          <t>0.2713</t>
+          <t>0.4357</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>0.1092</t>
+          <t>0.1665</t>
         </is>
       </c>
       <c r="AT151" t="inlineStr">
         <is>
-          <t>0.2213</t>
+          <t>0.3342</t>
         </is>
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>22.82</t>
+          <t>26.19</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>56.9</t>
+          <t>38.39</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>20.91</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>0.1813</t>
+          <t>0.1869</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>38.14</t>
+          <t>38.63</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>88.43</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD151" t="inlineStr">
         <is>
-          <t>0.4176</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="BE151" t="inlineStr">
         <is>
-          <t>0.1601</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BF151" t="inlineStr">
         <is>
-          <t>26.2</t>
-        </is>
-      </c>
-      <c r="BG151" t="inlineStr">
-        <is>
-          <t>In From CF</t>
-        </is>
-      </c>
-      <c r="BH151" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="BG151" t="inlineStr"/>
+      <c r="BH151" t="inlineStr"/>
       <c r="BI151" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ151" t="inlineStr"/>
@@ -42371,27 +42371,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>643376</t>
+          <t>640459</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Danny Jansen</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -42406,12 +42406,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>Zac Thornton</t>
+          <t>Matthew Boyd</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>804267</t>
+          <t>571510</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
@@ -42434,17 +42434,17 @@
       </c>
       <c r="O152" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P152" t="n">
-        <v>22.6</v>
+        <v>28.9</v>
       </c>
       <c r="Q152" t="n">
-        <v>50.5</v>
+        <v>41.3</v>
       </c>
       <c r="R152" t="n">
-        <v>41.1</v>
+        <v>38.8</v>
       </c>
       <c r="S152" t="n">
         <v>44.8</v>
@@ -42453,7 +42453,7 @@
         <v>78</v>
       </c>
       <c r="U152" t="n">
-        <v>23.7</v>
+        <v>32</v>
       </c>
       <c r="V152" t="inlineStr">
         <is>
@@ -42488,7 +42488,7 @@
       <c r="AB152" t="inlineStr"/>
       <c r="AC152" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD152" t="inlineStr"/>
@@ -42505,12 +42505,12 @@
       </c>
       <c r="AH152" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI152" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AJ152" t="inlineStr">
@@ -42520,127 +42520,127 @@
       </c>
       <c r="AK152" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Contact streak: 1/3 over last 7 games</t>
         </is>
       </c>
       <c r="AL152" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.6% barrel, 13.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 16.2 HR allowed</t>
         </is>
       </c>
       <c r="AM152" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN152" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>11.91</t>
         </is>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>35.34</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>88.12</t>
         </is>
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>97.8804</t>
+          <t>98.2729</t>
         </is>
       </c>
       <c r="AR152" t="inlineStr">
         <is>
-          <t>0.3192</t>
+          <t>0.2713</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1092</t>
         </is>
       </c>
       <c r="AT152" t="inlineStr">
         <is>
-          <t>0.2776</t>
+          <t>0.2213</t>
         </is>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>69.85</t>
+          <t>72.86</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>22.82</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>28.84</t>
+          <t>20.91</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1813</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>9.6</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>38.14</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.43</t>
         </is>
       </c>
       <c r="BD152" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.4176</t>
         </is>
       </c>
       <c r="BE152" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.1601</t>
         </is>
       </c>
       <c r="BF152" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="BG152" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH152" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI152" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ152" t="inlineStr"/>
@@ -47112,7 +47112,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -47668,7 +47668,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -48224,7 +48224,7 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -48898,7 +48898,7 @@
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
@@ -48908,7 +48908,7 @@
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/22, 0 HR</t>
+          <t>Last 7 games: 2/23, 0 HR</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
@@ -49620,7 +49620,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -50427,47 +50427,47 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>699302</t>
+          <t>703492</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Hector Rodriguez</t>
+          <t>Nick Morabito</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-24T23:15:00Z</t>
+          <t>2026-09-24T18:35:00Z</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Kumar Rocker</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>677958</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
@@ -50490,62 +50490,58 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>21.7</v>
+        <v>20</v>
       </c>
       <c r="Q181" t="n">
-        <v>35.8</v>
+        <v>48.7</v>
       </c>
       <c r="R181" t="n">
-        <v>30.9</v>
+        <v>42.1</v>
       </c>
       <c r="S181" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T181" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U181" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X181" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z181" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB181" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr"/>
       <c r="AC181" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -50565,12 +50561,12 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
@@ -50580,12 +50576,12 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/22, 0 HR</t>
+          <t>Last 7 games: 3/15, 0 HR</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 14.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
@@ -50595,104 +50591,112 @@
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>45.8</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>98.5539</t>
+          <t>100.2027</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>0.308</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>74.6</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>23.2</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>41.8</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.027</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>37.31</t>
+          <t>42.39</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>0.3941</t>
+          <t>0.4392</t>
         </is>
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.178</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>26.7</t>
-        </is>
-      </c>
-      <c r="BG181" t="inlineStr"/>
-      <c r="BH181" t="inlineStr"/>
+          <t>23.7</t>
+        </is>
+      </c>
+      <c r="BG181" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH181" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Globe Life Field</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr"/>
@@ -50703,47 +50707,47 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>703492</t>
+          <t>699302</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Nick Morabito</t>
+          <t>Hector Rodriguez</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-24T18:35:00Z</t>
+          <t>2026-09-24T23:15:00Z</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Kumar Rocker</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>677958</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -50752,72 +50756,76 @@
         </is>
       </c>
       <c r="L182" t="n">
+        <v>36</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>Longshot</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Watch List</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Projected Lineup, Platoon Edge</t>
+        </is>
+      </c>
+      <c r="P182" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Q182" t="n">
         <v>35.8</v>
       </c>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>Longshot</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>Watch List</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>No major boost</t>
-        </is>
-      </c>
-      <c r="P182" t="n">
-        <v>20</v>
-      </c>
-      <c r="Q182" t="n">
-        <v>48.7</v>
-      </c>
       <c r="R182" t="n">
-        <v>41.1</v>
+        <v>30.9</v>
       </c>
       <c r="S182" t="n">
-        <v>44.8</v>
+        <v>59.8</v>
       </c>
       <c r="T182" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U182" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W182" t="inlineStr">
+      <c r="Z182" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC182" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -50837,12 +50845,12 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -50852,12 +50860,12 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 1/22, 0 HR</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.9% barrel, 17.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 14.1 HR allowed</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
@@ -50867,112 +50875,104 @@
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>45.8</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>100.2027</t>
+          <t>98.5539</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.308</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.245</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>74.6</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>49.0</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.8</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>42.39</t>
+          <t>37.31</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>0.4392</t>
+          <t>0.3941</t>
         </is>
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>0.178</t>
+          <t>0.1467</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>23.7</t>
-        </is>
-      </c>
-      <c r="BG182" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH182" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>26.7</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr"/>
+      <c r="BH182" t="inlineStr"/>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>Globe Life Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr"/>
@@ -54072,7 +54072,7 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -54105,7 +54105,7 @@
         <v>75</v>
       </c>
       <c r="U194" t="n">
-        <v>28.9</v>
+        <v>27.6</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -54172,7 +54172,7 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 4/22, 1 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
@@ -54608,7 +54608,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -57096,7 +57096,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -61326,7 +61326,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>65.5</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -61350,7 +61350,7 @@
         <v>48.7</v>
       </c>
       <c r="R3" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -61541,7 +61541,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -61858,7 +61858,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -65490,7 +65490,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>57.5</v>
+        <v>57.6</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -65514,7 +65514,7 @@
         <v>50.5</v>
       </c>
       <c r="R18" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S18" t="n">
         <v>94.90000000000001</v>
@@ -65705,7 +65705,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -65770,7 +65770,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>56.8</v>
+        <v>57</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -65794,7 +65794,7 @@
         <v>50.5</v>
       </c>
       <c r="R19" t="n">
-        <v>41.1</v>
+        <v>42.1</v>
       </c>
       <c r="S19" t="n">
         <v>100</v>
@@ -65985,7 +65985,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -36143,24 +36143,24 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
           <t>KC</t>
         </is>
       </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F129" t="inlineStr">
         <is>
           <t>2026-09-24T18:10:00Z</t>
@@ -36173,17 +36173,17 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>David Sandlin</t>
+          <t>Randy Dobnak</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>689818</t>
+          <t>677976</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
@@ -36192,7 +36192,7 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="M129" t="inlineStr">
         <is>
@@ -36206,26 +36206,26 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P129" t="n">
-        <v>26.8</v>
+        <v>19</v>
       </c>
       <c r="Q129" t="n">
-        <v>31.5</v>
+        <v>36.3</v>
       </c>
       <c r="R129" t="n">
         <v>30.2</v>
       </c>
       <c r="S129" t="n">
-        <v>86.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T129" t="n">
         <v>80</v>
       </c>
       <c r="U129" t="n">
-        <v>23.4</v>
+        <v>29.7</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -36239,7 +36239,7 @@
       </c>
       <c r="X129" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y129" t="inlineStr">
@@ -36260,7 +36260,7 @@
       <c r="AB129" t="inlineStr"/>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD129" t="inlineStr"/>
@@ -36277,27 +36277,27 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI129" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 1 HR</t>
+          <t>Last 7 games: 7/22, 0 HR</t>
         </is>
       </c>
       <c r="AL129" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 5.2 HR allowed</t>
         </is>
       </c>
       <c r="AM129" t="inlineStr">
@@ -36307,97 +36307,97 @@
       </c>
       <c r="AN129" t="inlineStr">
         <is>
-          <t>5.26</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
-          <t>88.83</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ129" t="inlineStr">
         <is>
-          <t>98.6155</t>
+          <t>97.5328</t>
         </is>
       </c>
       <c r="AR129" t="inlineStr">
         <is>
-          <t>0.3908</t>
+          <t>0.393</t>
         </is>
       </c>
       <c r="AS129" t="inlineStr">
         <is>
-          <t>0.1395</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.343</t>
         </is>
       </c>
       <c r="AU129" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV129" t="inlineStr">
         <is>
-          <t>11.49</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>49.01</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>22.2</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.121</t>
         </is>
       </c>
       <c r="BA129" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="BB129" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>44.68</t>
         </is>
       </c>
       <c r="BC129" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>91.39</t>
         </is>
       </c>
       <c r="BD129" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.422</t>
         </is>
       </c>
       <c r="BE129" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.138</t>
         </is>
       </c>
       <c r="BF129" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>23.18</t>
         </is>
       </c>
       <c r="BG129" t="inlineStr">
@@ -36423,24 +36423,24 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
+          <t>KC</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>KC</t>
-        </is>
-      </c>
       <c r="F130" t="inlineStr">
         <is>
           <t>2026-09-24T18:10:00Z</t>
@@ -36453,17 +36453,17 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Randy Dobnak</t>
+          <t>David Sandlin</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>677976</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
@@ -36486,26 +36486,26 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P130" t="n">
-        <v>19</v>
+        <v>26.8</v>
       </c>
       <c r="Q130" t="n">
-        <v>36.3</v>
+        <v>31.5</v>
       </c>
       <c r="R130" t="n">
         <v>30.2</v>
       </c>
       <c r="S130" t="n">
-        <v>93.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T130" t="n">
         <v>80</v>
       </c>
       <c r="U130" t="n">
-        <v>29.7</v>
+        <v>22.6</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -36519,7 +36519,7 @@
       </c>
       <c r="X130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y130" t="inlineStr">
@@ -36540,7 +36540,7 @@
       <c r="AB130" t="inlineStr"/>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD130" t="inlineStr"/>
@@ -36557,27 +36557,27 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI130" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/22, 0 HR</t>
+          <t>Last 7 games: 4/27, 1 HR</t>
         </is>
       </c>
       <c r="AL130" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 5.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM130" t="inlineStr">
@@ -36587,97 +36587,97 @@
       </c>
       <c r="AN130" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.26</t>
         </is>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>37.41</t>
         </is>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.83</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>97.5328</t>
+          <t>98.6155</t>
         </is>
       </c>
       <c r="AR130" t="inlineStr">
         <is>
-          <t>0.393</t>
+          <t>0.3908</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1395</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>11.49</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>49.01</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>44.68</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>91.39</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD130" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE130" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF130" t="inlineStr">
         <is>
-          <t>23.18</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="BG130" t="inlineStr">
@@ -37543,27 +37543,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>670231</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>John Rave</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-09-24T18:20:00Z</t>
+          <t>2026-09-24T18:10:00Z</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -37573,17 +37573,17 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Tyler Phillips</t>
+          <t>David Sandlin</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>663969</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -37592,7 +37592,7 @@
         </is>
       </c>
       <c r="L134" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="M134" t="inlineStr">
         <is>
@@ -37606,26 +37606,26 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P134" t="n">
-        <v>38.8</v>
+        <v>31.6</v>
       </c>
       <c r="Q134" t="n">
-        <v>39.8</v>
+        <v>31.5</v>
       </c>
       <c r="R134" t="n">
-        <v>38.3</v>
+        <v>30.2</v>
       </c>
       <c r="S134" t="n">
-        <v>44.8</v>
+        <v>64.3</v>
       </c>
       <c r="T134" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U134" t="n">
-        <v>37.8</v>
+        <v>44.1</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -37639,7 +37639,7 @@
       </c>
       <c r="X134" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y134" t="inlineStr">
@@ -37660,7 +37660,7 @@
       <c r="AB134" t="inlineStr"/>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD134" t="inlineStr"/>
@@ -37677,12 +37677,12 @@
       </c>
       <c r="AH134" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI134" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ134" t="inlineStr">
@@ -37692,12 +37692,12 @@
       </c>
       <c r="AK134" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 1 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL134" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM134" t="inlineStr">
@@ -37707,112 +37707,112 @@
       </c>
       <c r="AN134" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>8.93</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
         <is>
-          <t>43.25</t>
+          <t>37.97</t>
         </is>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.09</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
         <is>
-          <t>99.9731</t>
+          <t>100.0593</t>
         </is>
       </c>
       <c r="AR134" t="inlineStr">
         <is>
-          <t>0.4133</t>
+          <t>0.3735</t>
         </is>
       </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>0.1778</t>
+          <t>0.143</t>
         </is>
       </c>
       <c r="AT134" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>73.97</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>29.26</t>
+          <t>24.64</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>0.1842</t>
+          <t>0.1775</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>89.41</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD134" t="inlineStr">
         <is>
-          <t>0.4015</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE134" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF134" t="inlineStr">
         <is>
-          <t>26.01</t>
+          <t>24.5</t>
         </is>
       </c>
       <c r="BG134" t="inlineStr">
         <is>
-          <t>In From CF</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH134" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI134" t="inlineStr">
         <is>
-          <t>Wrigley Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ134" t="inlineStr"/>
@@ -38103,27 +38103,27 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>670231</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>John Rave</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-09-24T18:10:00Z</t>
+          <t>2026-09-24T18:20:00Z</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -38133,17 +38133,17 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>David Sandlin</t>
+          <t>Tyler Phillips</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>689818</t>
+          <t>663969</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
@@ -38166,26 +38166,26 @@
       </c>
       <c r="O136" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P136" t="n">
-        <v>31.6</v>
+        <v>38.8</v>
       </c>
       <c r="Q136" t="n">
-        <v>31.5</v>
+        <v>39.8</v>
       </c>
       <c r="R136" t="n">
-        <v>30.2</v>
+        <v>38.3</v>
       </c>
       <c r="S136" t="n">
-        <v>64.3</v>
+        <v>44.8</v>
       </c>
       <c r="T136" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U136" t="n">
-        <v>39.5</v>
+        <v>36</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -38199,7 +38199,7 @@
       </c>
       <c r="X136" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y136" t="inlineStr">
@@ -38220,7 +38220,7 @@
       <c r="AB136" t="inlineStr"/>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD136" t="inlineStr"/>
@@ -38237,12 +38237,12 @@
       </c>
       <c r="AH136" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI136" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ136" t="inlineStr">
@@ -38252,12 +38252,12 @@
       </c>
       <c r="AK136" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/21, 1 HR</t>
         </is>
       </c>
       <c r="AL136" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.1% barrel, 14.3 HR allowed</t>
         </is>
       </c>
       <c r="AM136" t="inlineStr">
@@ -38267,112 +38267,112 @@
       </c>
       <c r="AN136" t="inlineStr">
         <is>
-          <t>8.93</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>43.25</t>
         </is>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
-          <t>88.09</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>100.0593</t>
+          <t>99.9731</t>
         </is>
       </c>
       <c r="AR136" t="inlineStr">
         <is>
-          <t>0.3735</t>
+          <t>0.4133</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>0.1778</t>
         </is>
       </c>
       <c r="AT136" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>73.97</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>29.26</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>0.1775</t>
+          <t>0.1842</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>42.77</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>89.41</t>
         </is>
       </c>
       <c r="BD136" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.4015</t>
         </is>
       </c>
       <c r="BE136" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="BF136" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>26.01</t>
         </is>
       </c>
       <c r="BG136" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH136" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI136" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Wrigley Field</t>
         </is>
       </c>
       <c r="BJ136" t="inlineStr"/>
@@ -48423,56 +48423,56 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>679845</t>
+          <t>676609</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Nick Loftin</t>
+          <t>José Caballero</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-09-24T18:10:00Z</t>
+          <t>2026-09-24T23:05:00Z</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>David Sandlin</t>
+          <t>Ian Seymour</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>689818</t>
+          <t>693855</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L173" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="M173" t="inlineStr">
         <is>
@@ -48486,26 +48486,26 @@
       </c>
       <c r="O173" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P173" t="n">
-        <v>16.5</v>
+        <v>9.4</v>
       </c>
       <c r="Q173" t="n">
-        <v>31.5</v>
+        <v>44.8</v>
       </c>
       <c r="R173" t="n">
-        <v>30.2</v>
+        <v>50.2</v>
       </c>
       <c r="S173" t="n">
-        <v>76.2</v>
+        <v>44.8</v>
       </c>
       <c r="T173" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U173" t="n">
-        <v>57.5</v>
+        <v>17.3</v>
       </c>
       <c r="V173" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -48540,7 +48540,7 @@
       <c r="AB173" t="inlineStr"/>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr"/>
@@ -48557,27 +48557,27 @@
       </c>
       <c r="AH173" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI173" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Contact streak: 8/21 over last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL173" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.4% barrel, 19.0 HR allowed</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
@@ -48587,112 +48587,112 @@
       </c>
       <c r="AN173" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.71</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>27.24</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>84.53</t>
         </is>
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>97.0725</t>
+          <t>96.4163</t>
         </is>
       </c>
       <c r="AR173" t="inlineStr">
         <is>
-          <t>0.3443</t>
+          <t>0.3362</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>0.1144</t>
+          <t>0.1101</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>0.2855</t>
         </is>
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>68.98</t>
+          <t>68.96</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>43.17</t>
+          <t>41.74</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>28.22</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>11.3</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>0.1476</t>
+          <t>0.1278</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>9.41</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>33.7</t>
+          <t>37.45</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>86.9</t>
+          <t>88.42</t>
         </is>
       </c>
       <c r="BD173" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.3966</t>
         </is>
       </c>
       <c r="BE173" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1705</t>
         </is>
       </c>
       <c r="BF173" t="inlineStr">
         <is>
-          <t>24.5</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="BG173" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH173" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>64</t>
         </is>
       </c>
       <c r="BI173" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ173" t="inlineStr"/>
@@ -48703,32 +48703,32 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>676609</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>José Caballero</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-09-24T23:05:00Z</t>
+          <t>2026-09-25T02:10:00Z</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -48738,17 +48738,17 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>Ian Seymour</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>693855</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L174" t="n">
@@ -48766,58 +48766,62 @@
       </c>
       <c r="O174" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P174" t="n">
-        <v>9.4</v>
+        <v>20.8</v>
       </c>
       <c r="Q174" t="n">
-        <v>44.8</v>
+        <v>42.7</v>
       </c>
       <c r="R174" t="n">
-        <v>50.2</v>
+        <v>27.6</v>
       </c>
       <c r="S174" t="n">
-        <v>44.8</v>
+        <v>40.2</v>
       </c>
       <c r="T174" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U174" t="n">
-        <v>17.3</v>
+        <v>37.4</v>
       </c>
       <c r="V174" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W174" t="inlineStr">
+      <c r="Z174" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X174" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y174" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z174" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB174" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC174" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -48837,142 +48841,134 @@
       </c>
       <c r="AH174" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI174" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL174" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.4% barrel, 19.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM174" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN174" t="inlineStr">
         <is>
-          <t>4.71</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>27.24</t>
+          <t>35.0</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
-          <t>84.53</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>96.4163</t>
+          <t>98.774</t>
         </is>
       </c>
       <c r="AR174" t="inlineStr">
         <is>
-          <t>0.3362</t>
+          <t>0.3662</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>0.1101</t>
+          <t>0.116</t>
         </is>
       </c>
       <c r="AT174" t="inlineStr">
         <is>
-          <t>0.2855</t>
+          <t>0.3091</t>
         </is>
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>68.96</t>
+          <t>70.66</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>13.72</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>41.74</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>27.13</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>11.3</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>0.1278</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>9.41</t>
+          <t>9.57</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>37.45</t>
+          <t>38.63</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>88.42</t>
+          <t>89.46</t>
         </is>
       </c>
       <c r="BD174" t="inlineStr">
         <is>
-          <t>0.3966</t>
+          <t>0.3722</t>
         </is>
       </c>
       <c r="BE174" t="inlineStr">
         <is>
-          <t>0.1705</t>
+          <t>0.1568</t>
         </is>
       </c>
       <c r="BF174" t="inlineStr">
         <is>
-          <t>29.45</t>
-        </is>
-      </c>
-      <c r="BG174" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH174" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
+          <t>33.3</t>
+        </is>
+      </c>
+      <c r="BG174" t="inlineStr"/>
+      <c r="BH174" t="inlineStr"/>
       <c r="BI174" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>UNIQLO Field at Dodger Stadium</t>
         </is>
       </c>
       <c r="BJ174" t="inlineStr"/>
@@ -48983,47 +48979,47 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>679845</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Nick Loftin</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-09-25T02:10:00Z</t>
+          <t>2026-09-24T18:10:00Z</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>David Sandlin</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>689818</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -49032,7 +49028,7 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="M175" t="inlineStr">
         <is>
@@ -49046,65 +49042,61 @@
       </c>
       <c r="O175" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P175" t="n">
-        <v>20.8</v>
+        <v>16.5</v>
       </c>
       <c r="Q175" t="n">
-        <v>42.7</v>
+        <v>31.5</v>
       </c>
       <c r="R175" t="n">
-        <v>27.6</v>
+        <v>30.2</v>
       </c>
       <c r="S175" t="n">
-        <v>40.2</v>
+        <v>76.2</v>
       </c>
       <c r="T175" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U175" t="n">
-        <v>37.4</v>
+        <v>54.9</v>
       </c>
       <c r="V175" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W175" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X175" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z175" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB175" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr"/>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr"/>
@@ -49121,134 +49113,142 @@
       </c>
       <c r="AH175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI175" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL175" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 9.6% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 6.0 HR allowed</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN175" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>35.0</t>
+          <t>30.92</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>98.774</t>
+          <t>97.0725</t>
         </is>
       </c>
       <c r="AR175" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3443</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1144</t>
         </is>
       </c>
       <c r="AT175" t="inlineStr">
         <is>
-          <t>0.3091</t>
+          <t>0.294</t>
         </is>
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>70.66</t>
+          <t>68.98</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>13.72</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>43.17</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>27.13</t>
+          <t>28.22</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>6.8</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.1476</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>9.57</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>38.63</t>
+          <t>33.7</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>89.46</t>
+          <t>86.9</t>
         </is>
       </c>
       <c r="BD175" t="inlineStr">
         <is>
-          <t>0.3722</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="BE175" t="inlineStr">
         <is>
-          <t>0.1568</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF175" t="inlineStr">
         <is>
-          <t>33.3</t>
-        </is>
-      </c>
-      <c r="BG175" t="inlineStr"/>
-      <c r="BH175" t="inlineStr"/>
+          <t>24.5</t>
+        </is>
+      </c>
+      <c r="BG175" t="inlineStr">
+        <is>
+          <t>In From RF</t>
+        </is>
+      </c>
+      <c r="BH175" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI175" t="inlineStr">
         <is>
-          <t>UNIQLO Field at Dodger Stadium</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ175" t="inlineStr"/>
@@ -54052,7 +54052,7 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>31.1</v>
+        <v>31</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -54085,7 +54085,7 @@
         <v>80</v>
       </c>
       <c r="U193" t="n">
-        <v>12</v>
+        <v>10.1</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -54142,7 +54142,7 @@
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -54152,7 +54152,7 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/15, 0 HR</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -2152,7 +2152,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2432,7 +2432,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -10680,7 +10680,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -12072,7 +12072,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -17040,7 +17040,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -18948,7 +18948,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -19228,7 +19228,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -20060,7 +20060,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -25248,7 +25248,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -27672,7 +27672,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -39223,47 +39223,47 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>805805</t>
+          <t>699115</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Walker Jenkins</t>
+          <t>Carlos Jorge</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T19:07:00Z</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Trey Yesavage</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>543135</t>
+          <t>702056</t>
         </is>
       </c>
       <c r="K142" t="inlineStr">
@@ -39272,7 +39272,7 @@
         </is>
       </c>
       <c r="L142" t="n">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="M142" t="inlineStr">
         <is>
@@ -39286,62 +39286,58 @@
       </c>
       <c r="O142" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P142" t="n">
-        <v>26.9</v>
+        <v>10</v>
       </c>
       <c r="Q142" t="n">
-        <v>42.3</v>
+        <v>33.4</v>
       </c>
       <c r="R142" t="n">
-        <v>27.1</v>
+        <v>43.9</v>
       </c>
       <c r="S142" t="n">
-        <v>47.9</v>
+        <v>93.2</v>
       </c>
       <c r="T142" t="n">
         <v>80</v>
       </c>
       <c r="U142" t="n">
-        <v>74.2</v>
+        <v>39.8</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X142" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr"/>
       <c r="AC142" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -39361,27 +39357,27 @@
       </c>
       <c r="AH142" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI142" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/19, 1 HR</t>
         </is>
       </c>
       <c r="AL142" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 7.7 HR allowed</t>
         </is>
       </c>
       <c r="AM142" t="inlineStr">
@@ -39391,104 +39387,112 @@
       </c>
       <c r="AN142" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>7.4</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>82.7</t>
         </is>
       </c>
       <c r="AQ142" t="inlineStr">
         <is>
-          <t>97.0592</t>
+          <t>93.3196</t>
         </is>
       </c>
       <c r="AR142" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>0.322</t>
         </is>
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>0.165</t>
+          <t>0.099</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>0.257</t>
         </is>
       </c>
       <c r="AU142" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>68.7</t>
         </is>
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>19.3</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>27.1</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>0.184</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>42.18</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>90.01</t>
         </is>
       </c>
       <c r="BD142" t="inlineStr">
         <is>
-          <t>0.4045</t>
+          <t>0.3414</t>
         </is>
       </c>
       <c r="BE142" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.1268</t>
         </is>
       </c>
       <c r="BF142" t="inlineStr">
         <is>
-          <t>25.04</t>
-        </is>
-      </c>
-      <c r="BG142" t="inlineStr"/>
-      <c r="BH142" t="inlineStr"/>
+          <t>25.74</t>
+        </is>
+      </c>
+      <c r="BG142" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH142" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI142" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ142" t="inlineStr"/>
@@ -39499,47 +39503,47 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>699115</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Carlos Jorge</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-09-26T19:07:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Trey Yesavage</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>702056</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -39548,7 +39552,7 @@
         </is>
       </c>
       <c r="L143" t="n">
-        <v>40.2</v>
+        <v>40</v>
       </c>
       <c r="M143" t="inlineStr">
         <is>
@@ -39562,61 +39566,65 @@
       </c>
       <c r="O143" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P143" t="n">
-        <v>10</v>
+        <v>23.7</v>
       </c>
       <c r="Q143" t="n">
-        <v>33.4</v>
+        <v>36.4</v>
       </c>
       <c r="R143" t="n">
-        <v>43.9</v>
+        <v>23.2</v>
       </c>
       <c r="S143" t="n">
-        <v>93.2</v>
+        <v>59.8</v>
       </c>
       <c r="T143" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U143" t="n">
-        <v>39.8</v>
+        <v>97</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W143" t="inlineStr">
+      <c r="Z143" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X143" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y143" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr"/>
@@ -39633,27 +39641,27 @@
       </c>
       <c r="AH143" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI143" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/19, 1 HR</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 7.7 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
@@ -39663,112 +39671,104 @@
       </c>
       <c r="AN143" t="inlineStr">
         <is>
-          <t>7.4</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>34.13</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>82.7</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ143" t="inlineStr">
         <is>
-          <t>93.3196</t>
+          <t>98.5257</t>
         </is>
       </c>
       <c r="AR143" t="inlineStr">
         <is>
-          <t>0.322</t>
+          <t>0.3795</t>
         </is>
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>0.1368</t>
         </is>
       </c>
       <c r="AT143" t="inlineStr">
         <is>
-          <t>0.257</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>68.7</t>
+          <t>71.08</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>44.88</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>26.66</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>90.01</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD143" t="inlineStr">
         <is>
-          <t>0.3414</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE143" t="inlineStr">
         <is>
-          <t>0.1268</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="BF143" t="inlineStr">
         <is>
-          <t>25.74</t>
-        </is>
-      </c>
-      <c r="BG143" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH143" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>29.09</t>
+        </is>
+      </c>
+      <c r="BG143" t="inlineStr"/>
+      <c r="BH143" t="inlineStr"/>
       <c r="BI143" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ143" t="inlineStr"/>
@@ -39779,22 +39779,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695336</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Thomas Saggese</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -39814,12 +39814,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -39842,26 +39842,26 @@
       </c>
       <c r="O144" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P144" t="n">
-        <v>23.7</v>
+        <v>36.6</v>
       </c>
       <c r="Q144" t="n">
-        <v>36.4</v>
+        <v>45.3</v>
       </c>
       <c r="R144" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S144" t="n">
         <v>59.8</v>
       </c>
       <c r="T144" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U144" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -39917,27 +39917,27 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI144" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Last 7 games: 1/24, 0 HR</t>
         </is>
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM144" t="inlineStr">
@@ -39947,104 +39947,104 @@
       </c>
       <c r="AN144" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
-          <t>34.13</t>
+          <t>43.47</t>
         </is>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>90.55</t>
         </is>
       </c>
       <c r="AQ144" t="inlineStr">
         <is>
-          <t>98.5257</t>
+          <t>100.5499</t>
         </is>
       </c>
       <c r="AR144" t="inlineStr">
         <is>
-          <t>0.3795</t>
+          <t>0.3888</t>
         </is>
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>0.1368</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr">
         <is>
-          <t>0.29</t>
+          <t>0.3034</t>
         </is>
       </c>
       <c r="AU144" t="inlineStr">
         <is>
-          <t>71.08</t>
+          <t>71.48</t>
         </is>
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>17.69</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>44.88</t>
+          <t>28.92</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>26.66</t>
+          <t>27.39</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD144" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4125</t>
         </is>
       </c>
       <c r="BE144" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BF144" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG144" t="inlineStr"/>
       <c r="BH144" t="inlineStr"/>
       <c r="BI144" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ144" t="inlineStr"/>
@@ -40055,22 +40055,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>695336</t>
+          <t>686681</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Thomas Saggese</t>
+          <t>Michael Massey</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -40090,12 +40090,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
@@ -40104,7 +40104,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>40</v>
+        <v>39.7</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -40118,26 +40118,26 @@
       </c>
       <c r="O145" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P145" t="n">
-        <v>36.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q145" t="n">
-        <v>45.3</v>
+        <v>42.9</v>
       </c>
       <c r="R145" t="n">
-        <v>27.6</v>
+        <v>23.2</v>
       </c>
       <c r="S145" t="n">
         <v>59.8</v>
       </c>
       <c r="T145" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U145" t="n">
-        <v>0</v>
+        <v>26.2</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -40193,27 +40193,27 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/24, 0 HR</t>
+          <t>Last 7 games: 5/29, 1 HR</t>
         </is>
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
@@ -40223,104 +40223,104 @@
       </c>
       <c r="AN145" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>5.61</t>
         </is>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>90.55</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="AQ145" t="inlineStr">
         <is>
-          <t>100.5499</t>
+          <t>98.6019</t>
         </is>
       </c>
       <c r="AR145" t="inlineStr">
         <is>
-          <t>0.3888</t>
+          <t>0.3922</t>
         </is>
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.1423</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr">
         <is>
-          <t>0.3034</t>
+          <t>0.2937</t>
         </is>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>71.48</t>
+          <t>71.36</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>28.92</t>
+          <t>48.8</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.1313</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="BD145" t="inlineStr">
         <is>
-          <t>0.4125</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE145" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="BF145" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="BG145" t="inlineStr"/>
       <c r="BH145" t="inlineStr"/>
       <c r="BI145" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ145" t="inlineStr"/>
@@ -40331,27 +40331,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>686681</t>
+          <t>666126</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Michael Massey</t>
+          <t>Carlos Cortes</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-27T01:40:00Z</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -40366,12 +40366,12 @@
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
@@ -40398,13 +40398,13 @@
         </is>
       </c>
       <c r="P146" t="n">
-        <v>27.4</v>
+        <v>28.3</v>
       </c>
       <c r="Q146" t="n">
-        <v>42.9</v>
+        <v>33.8</v>
       </c>
       <c r="R146" t="n">
-        <v>23.2</v>
+        <v>30.9</v>
       </c>
       <c r="S146" t="n">
         <v>59.8</v>
@@ -40413,7 +40413,7 @@
         <v>80</v>
       </c>
       <c r="U146" t="n">
-        <v>26.2</v>
+        <v>40.3</v>
       </c>
       <c r="V146" t="inlineStr">
         <is>
@@ -40469,12 +40469,12 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI146" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ146" t="inlineStr">
@@ -40484,12 +40484,12 @@
       </c>
       <c r="AK146" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/29, 1 HR</t>
+          <t>Last 7 games: 4/15, 1 HR</t>
         </is>
       </c>
       <c r="AL146" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM146" t="inlineStr">
@@ -40499,104 +40499,104 @@
       </c>
       <c r="AN146" t="inlineStr">
         <is>
-          <t>5.61</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AO146" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>38.4</t>
         </is>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>88.82</t>
         </is>
       </c>
       <c r="AQ146" t="inlineStr">
         <is>
-          <t>98.6019</t>
+          <t>99.3327</t>
         </is>
       </c>
       <c r="AR146" t="inlineStr">
         <is>
-          <t>0.3922</t>
+          <t>0.3919</t>
         </is>
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>0.1423</t>
+          <t>0.142</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr">
         <is>
-          <t>0.2937</t>
+          <t>0.3063</t>
         </is>
       </c>
       <c r="AU146" t="inlineStr">
         <is>
-          <t>71.36</t>
+          <t>70.69</t>
         </is>
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>14.06</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>48.8</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>30.1</t>
+          <t>23.01</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>0.1313</t>
+          <t>0.1745</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD146" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="BE146" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.1494</t>
         </is>
       </c>
       <c r="BF146" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BG146" t="inlineStr"/>
       <c r="BH146" t="inlineStr"/>
       <c r="BI146" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ146" t="inlineStr"/>
@@ -40607,27 +40607,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>666126</t>
+          <t>805805</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Carlos Cortes</t>
+          <t>Walker Jenkins</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-09-27T01:40:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -40637,17 +40637,17 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>543135</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
@@ -40656,7 +40656,7 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>39.7</v>
+        <v>39.6</v>
       </c>
       <c r="M147" t="inlineStr">
         <is>
@@ -40670,26 +40670,26 @@
       </c>
       <c r="O147" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P147" t="n">
-        <v>28.3</v>
+        <v>26.9</v>
       </c>
       <c r="Q147" t="n">
-        <v>33.8</v>
+        <v>42.3</v>
       </c>
       <c r="R147" t="n">
-        <v>30.9</v>
+        <v>27.1</v>
       </c>
       <c r="S147" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T147" t="n">
         <v>80</v>
       </c>
       <c r="U147" t="n">
-        <v>40.3</v>
+        <v>74.2</v>
       </c>
       <c r="V147" t="inlineStr">
         <is>
@@ -40703,7 +40703,7 @@
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -40728,7 +40728,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr"/>
@@ -40745,27 +40745,27 @@
       </c>
       <c r="AH147" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI147" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL147" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
@@ -40775,104 +40775,104 @@
       </c>
       <c r="AN147" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>38.4</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>88.82</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AQ147" t="inlineStr">
         <is>
-          <t>99.3327</t>
+          <t>97.0592</t>
         </is>
       </c>
       <c r="AR147" t="inlineStr">
         <is>
-          <t>0.3919</t>
+          <t>0.409</t>
         </is>
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>0.165</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr">
         <is>
-          <t>0.3063</t>
+          <t>0.319</t>
         </is>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>70.69</t>
+          <t>71.9</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>14.06</t>
+          <t>19.3</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>23.01</t>
+          <t>27.1</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>0.1745</t>
+          <t>0.184</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="BD147" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.4045</t>
         </is>
       </c>
       <c r="BE147" t="inlineStr">
         <is>
-          <t>0.1494</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF147" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="BG147" t="inlineStr"/>
       <c r="BH147" t="inlineStr"/>
       <c r="BI147" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ147" t="inlineStr"/>
@@ -41184,7 +41184,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -42292,7 +42292,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -49663,22 +49663,22 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>805346</t>
+          <t>643289</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Ben Ross</t>
+          <t>Mauricio Dubon</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -49693,17 +49693,17 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>Nathan Eovaldi</t>
+          <t>Jack Ralston</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>543135</t>
+          <t>667652</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
@@ -49712,7 +49712,7 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>35.9</v>
+        <v>35.7</v>
       </c>
       <c r="M180" t="inlineStr">
         <is>
@@ -49726,26 +49726,26 @@
       </c>
       <c r="O180" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P180" t="n">
-        <v>32.4</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q180" t="n">
-        <v>42.3</v>
+        <v>49.1</v>
       </c>
       <c r="R180" t="n">
-        <v>27.1</v>
+        <v>21.5</v>
       </c>
       <c r="S180" t="n">
-        <v>40.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T180" t="n">
         <v>50</v>
       </c>
       <c r="U180" t="n">
-        <v>17.3</v>
+        <v>30.2</v>
       </c>
       <c r="V180" t="inlineStr">
         <is>
@@ -49759,7 +49759,7 @@
       </c>
       <c r="X180" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y180" t="inlineStr">
@@ -49784,7 +49784,7 @@
       </c>
       <c r="AC180" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD180" t="inlineStr"/>
@@ -49801,12 +49801,12 @@
       </c>
       <c r="AH180" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI180" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ180" t="inlineStr">
@@ -49816,119 +49816,119 @@
       </c>
       <c r="AK180" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Contact streak: 9/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL180" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM180" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN180" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>30.0</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
-          <t>78.9</t>
+          <t>85.83</t>
         </is>
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>93.4311</t>
+          <t>96.2299</t>
         </is>
       </c>
       <c r="AR180" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.0987</t>
         </is>
       </c>
       <c r="AT180" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>0.2955</t>
         </is>
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>70.8</t>
+          <t>68.87</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>4.1</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>25.72</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>9.8</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.1168</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD180" t="inlineStr">
         <is>
-          <t>0.4045</t>
+          <t>0.411</t>
         </is>
       </c>
       <c r="BE180" t="inlineStr">
         <is>
-          <t>0.1614</t>
+          <t>0.204</t>
         </is>
       </c>
       <c r="BF180" t="inlineStr">
         <is>
-          <t>25.04</t>
+          <t>30.2</t>
         </is>
       </c>
       <c r="BG180" t="inlineStr"/>
       <c r="BH180" t="inlineStr"/>
       <c r="BI180" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ180" t="inlineStr"/>
@@ -49939,27 +49939,27 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>643289</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -49969,26 +49969,26 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>Jack Ralston</t>
+          <t>Quinn Mathews</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>667652</t>
+          <t>687273</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>35.7</v>
+        <v>35.4</v>
       </c>
       <c r="M181" t="inlineStr">
         <is>
@@ -50002,26 +50002,26 @@
       </c>
       <c r="O181" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P181" t="n">
-        <v>9.699999999999999</v>
+        <v>46.7</v>
       </c>
       <c r="Q181" t="n">
-        <v>49.1</v>
+        <v>18.5</v>
       </c>
       <c r="R181" t="n">
-        <v>21.5</v>
+        <v>27.6</v>
       </c>
       <c r="S181" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T181" t="n">
         <v>50</v>
       </c>
       <c r="U181" t="n">
-        <v>30.2</v>
+        <v>4.2</v>
       </c>
       <c r="V181" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
@@ -50077,12 +50077,12 @@
       </c>
       <c r="AH181" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI181" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ181" t="inlineStr">
@@ -50092,119 +50092,119 @@
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Contact streak: 9/28 over last 7 games</t>
+          <t>Last 7 games: 4/27, 0 HR</t>
         </is>
       </c>
       <c r="AL181" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 3.8% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN181" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>49.41</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
-          <t>85.83</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>96.2299</t>
+          <t>103.8654</t>
         </is>
       </c>
       <c r="AR181" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.4138</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>0.0987</t>
+          <t>0.1582</t>
         </is>
       </c>
       <c r="AT181" t="inlineStr">
         <is>
-          <t>0.2955</t>
+          <t>0.3321</t>
         </is>
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>68.87</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>33.02</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>25.72</t>
+          <t>16.71</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>9.8</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>0.1168</t>
+          <t>0.1349</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>34.8</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="BD181" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="BE181" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="BF181" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>25.8</t>
         </is>
       </c>
       <c r="BG181" t="inlineStr"/>
       <c r="BH181" t="inlineStr"/>
       <c r="BI181" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ181" t="inlineStr"/>
@@ -50215,32 +50215,32 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>656716</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Zach McKinstry</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>DET</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T17:10:00Z</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -50250,21 +50250,21 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>Quinn Mathews</t>
+          <t>Kirby Yates</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>687273</t>
+          <t>489446</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>35.4</v>
+        <v>35.2</v>
       </c>
       <c r="M182" t="inlineStr">
         <is>
@@ -50278,65 +50278,61 @@
       </c>
       <c r="O182" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P182" t="n">
-        <v>46.7</v>
+        <v>6.4</v>
       </c>
       <c r="Q182" t="n">
-        <v>18.5</v>
+        <v>40.1</v>
       </c>
       <c r="R182" t="n">
-        <v>27.6</v>
+        <v>59.6</v>
       </c>
       <c r="S182" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T182" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U182" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="V182" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X182" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z182" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB182" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr"/>
       <c r="AC182" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD182" t="inlineStr"/>
@@ -50353,12 +50349,12 @@
       </c>
       <c r="AH182" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI182" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ182" t="inlineStr">
@@ -50368,119 +50364,127 @@
       </c>
       <c r="AK182" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/27, 0 HR</t>
+          <t>Last 7 games: 0/11, 0 HR</t>
         </is>
       </c>
       <c r="AL182" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 3.8% barrel, 4.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
         </is>
       </c>
       <c r="AM182" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN182" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
         <is>
-          <t>49.41</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>85.77</t>
         </is>
       </c>
       <c r="AQ182" t="inlineStr">
         <is>
-          <t>103.8654</t>
+          <t>95.725</t>
         </is>
       </c>
       <c r="AR182" t="inlineStr">
         <is>
-          <t>0.4138</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>0.1582</t>
+          <t>0.0893</t>
         </is>
       </c>
       <c r="AT182" t="inlineStr">
         <is>
-          <t>0.3321</t>
+          <t>0.2903</t>
         </is>
       </c>
       <c r="AU182" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>77.58</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>33.02</t>
+          <t>40.47</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>0.1349</t>
+          <t>0.1202</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>7.96</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>45.4</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>88.8</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="BD182" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3506</t>
         </is>
       </c>
       <c r="BE182" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.1351</t>
         </is>
       </c>
       <c r="BF182" t="inlineStr">
         <is>
-          <t>25.8</t>
-        </is>
-      </c>
-      <c r="BG182" t="inlineStr"/>
-      <c r="BH182" t="inlineStr"/>
+          <t>29.6</t>
+        </is>
+      </c>
+      <c r="BG182" t="inlineStr">
+        <is>
+          <t>Out To RF</t>
+        </is>
+      </c>
+      <c r="BH182" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
       <c r="BI182" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Comerica Park</t>
         </is>
       </c>
       <c r="BJ182" t="inlineStr"/>
@@ -50491,12 +50495,12 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>656716</t>
+          <t>595879</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Zach McKinstry</t>
+          <t>Javier Báez</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -50521,7 +50525,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -50540,7 +50544,7 @@
         </is>
       </c>
       <c r="L183" t="n">
-        <v>35.2</v>
+        <v>35.1</v>
       </c>
       <c r="M183" t="inlineStr">
         <is>
@@ -50554,11 +50558,11 @@
       </c>
       <c r="O183" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P183" t="n">
-        <v>6.4</v>
+        <v>14.6</v>
       </c>
       <c r="Q183" t="n">
         <v>40.1</v>
@@ -50567,13 +50571,13 @@
         <v>59.6</v>
       </c>
       <c r="S183" t="n">
-        <v>52.4</v>
+        <v>44.8</v>
       </c>
       <c r="T183" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U183" t="n">
-        <v>0</v>
+        <v>18.3</v>
       </c>
       <c r="V183" t="inlineStr">
         <is>
@@ -50587,7 +50591,7 @@
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
@@ -50625,27 +50629,27 @@
       </c>
       <c r="AH183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI183" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/11, 0 HR</t>
+          <t>Last 7 games: 2/18, 1 HR</t>
         </is>
       </c>
       <c r="AL183" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
@@ -50655,67 +50659,67 @@
       </c>
       <c r="AN183" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="AO183" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>35.28</t>
         </is>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
-          <t>85.77</t>
+          <t>86.1</t>
         </is>
       </c>
       <c r="AQ183" t="inlineStr">
         <is>
-          <t>95.725</t>
+          <t>97.8075</t>
         </is>
       </c>
       <c r="AR183" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>0.0893</t>
+          <t>0.0961</t>
         </is>
       </c>
       <c r="AT183" t="inlineStr">
         <is>
-          <t>0.2903</t>
+          <t>0.264</t>
         </is>
       </c>
       <c r="AU183" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>73.36</t>
         </is>
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>32.69</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>40.47</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>22.26</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>0.1202</t>
+          <t>0.1266</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
@@ -50771,54 +50775,42 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>595879</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Javier Báez</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>DET</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-09-26T17:10:00Z</t>
+          <t>2026-09-26T23:15:00Z</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Kirby Yates</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>489446</t>
-        </is>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="n">
         <v>35.1</v>
       </c>
@@ -50834,61 +50826,65 @@
       </c>
       <c r="O184" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P184" t="n">
-        <v>14.6</v>
+        <v>15.7</v>
       </c>
       <c r="Q184" t="n">
-        <v>40.1</v>
+        <v>41.2</v>
       </c>
       <c r="R184" t="n">
-        <v>59.6</v>
+        <v>34.3</v>
       </c>
       <c r="S184" t="n">
-        <v>44.8</v>
+        <v>59.8</v>
       </c>
       <c r="T184" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="U184" t="n">
-        <v>18.3</v>
+        <v>22</v>
       </c>
       <c r="V184" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W184" t="inlineStr">
+      <c r="Z184" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X184" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y184" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z184" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB184" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC184" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD184" t="inlineStr"/>
@@ -50905,27 +50901,27 @@
       </c>
       <c r="AH184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI184" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AJ184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK184" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/18, 1 HR</t>
+          <t>Last 7 games: 4/15, 0 HR</t>
         </is>
       </c>
       <c r="AL184" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.0% barrel, 4.8 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM184" t="inlineStr">
@@ -50935,112 +50931,80 @@
       </c>
       <c r="AN184" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.64</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>35.28</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
-          <t>86.1</t>
+          <t>87.45</t>
         </is>
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>97.8075</t>
+          <t>97.1046</t>
         </is>
       </c>
       <c r="AR184" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>0.0961</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT184" t="inlineStr">
         <is>
-          <t>0.264</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>73.36</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>32.69</t>
+          <t>3.87</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>36.53</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>22.26</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>0.1266</t>
-        </is>
-      </c>
-      <c r="BA184" t="inlineStr">
-        <is>
-          <t>7.96</t>
-        </is>
-      </c>
-      <c r="BB184" t="inlineStr">
-        <is>
-          <t>45.4</t>
-        </is>
-      </c>
-      <c r="BC184" t="inlineStr">
-        <is>
-          <t>90.53</t>
-        </is>
-      </c>
-      <c r="BD184" t="inlineStr">
-        <is>
-          <t>0.3506</t>
-        </is>
-      </c>
-      <c r="BE184" t="inlineStr">
-        <is>
-          <t>0.1351</t>
-        </is>
-      </c>
-      <c r="BF184" t="inlineStr">
-        <is>
-          <t>29.6</t>
-        </is>
-      </c>
-      <c r="BG184" t="inlineStr">
-        <is>
-          <t>Out To RF</t>
-        </is>
-      </c>
-      <c r="BH184" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
+          <t>0.1337</t>
+        </is>
+      </c>
+      <c r="BA184" t="inlineStr"/>
+      <c r="BB184" t="inlineStr"/>
+      <c r="BC184" t="inlineStr"/>
+      <c r="BD184" t="inlineStr"/>
+      <c r="BE184" t="inlineStr"/>
+      <c r="BF184" t="inlineStr"/>
+      <c r="BG184" t="inlineStr"/>
+      <c r="BH184" t="inlineStr"/>
       <c r="BI184" t="inlineStr">
         <is>
-          <t>Comerica Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ184" t="inlineStr"/>
@@ -51051,27 +51015,27 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>518595</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Travis d'Arnaud</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>LAA</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>SEA</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-09-26T23:15:00Z</t>
+          <t>2026-09-27T01:40:00Z</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -51081,12 +51045,24 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
-      <c r="K185" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Kade Anderson</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>807739</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L185" t="n">
         <v>35.1</v>
       </c>
@@ -51102,26 +51078,26 @@
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P185" t="n">
-        <v>15.7</v>
+        <v>27.7</v>
       </c>
       <c r="Q185" t="n">
-        <v>41.2</v>
+        <v>38.7</v>
       </c>
       <c r="R185" t="n">
-        <v>34.3</v>
+        <v>25.4</v>
       </c>
       <c r="S185" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T185" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U185" t="n">
-        <v>22</v>
+        <v>4.5</v>
       </c>
       <c r="V185" t="inlineStr">
         <is>
@@ -51135,7 +51111,7 @@
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -51160,7 +51136,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr"/>
@@ -51177,12 +51153,12 @@
       </c>
       <c r="AH185" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI185" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ185" t="inlineStr">
@@ -51192,12 +51168,12 @@
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/15, 0 HR</t>
+          <t>Last 7 games: 3/20, 0 HR</t>
         </is>
       </c>
       <c r="AL185" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.4% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
@@ -51207,80 +51183,104 @@
       </c>
       <c r="AN185" t="inlineStr">
         <is>
-          <t>4.64</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.93</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
-          <t>87.45</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>97.1046</t>
+          <t>97.5183</t>
         </is>
       </c>
       <c r="AR185" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3047</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.1407</t>
         </is>
       </c>
       <c r="AT185" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2445</t>
         </is>
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>3.87</t>
+          <t>13.25</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>30.37</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>31.93</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>0.1337</t>
-        </is>
-      </c>
-      <c r="BA185" t="inlineStr"/>
-      <c r="BB185" t="inlineStr"/>
-      <c r="BC185" t="inlineStr"/>
-      <c r="BD185" t="inlineStr"/>
-      <c r="BE185" t="inlineStr"/>
-      <c r="BF185" t="inlineStr"/>
+          <t>0.0991</t>
+        </is>
+      </c>
+      <c r="BA185" t="inlineStr">
+        <is>
+          <t>8.4</t>
+        </is>
+      </c>
+      <c r="BB185" t="inlineStr">
+        <is>
+          <t>42.1</t>
+        </is>
+      </c>
+      <c r="BC185" t="inlineStr">
+        <is>
+          <t>88.1</t>
+        </is>
+      </c>
+      <c r="BD185" t="inlineStr">
+        <is>
+          <t>0.405</t>
+        </is>
+      </c>
+      <c r="BE185" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
+      </c>
+      <c r="BF185" t="inlineStr">
+        <is>
+          <t>27.4</t>
+        </is>
+      </c>
       <c r="BG185" t="inlineStr"/>
       <c r="BH185" t="inlineStr"/>
       <c r="BI185" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>T-Mobile Park</t>
         </is>
       </c>
       <c r="BJ185" t="inlineStr"/>
@@ -51291,56 +51291,56 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>518595</t>
+          <t>660688</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Travis d'Arnaud</t>
+          <t>Keibert Ruiz</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LAA</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>SEA</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-09-27T01:40:00Z</t>
+          <t>2026-09-26T16:35:00Z</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Kade Anderson</t>
+          <t>Jonah Tong</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>807739</t>
+          <t>804636</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="M186" t="inlineStr">
         <is>
@@ -51354,65 +51354,61 @@
       </c>
       <c r="O186" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P186" t="n">
-        <v>27.7</v>
+        <v>16</v>
       </c>
       <c r="Q186" t="n">
-        <v>38.7</v>
+        <v>35.8</v>
       </c>
       <c r="R186" t="n">
-        <v>25.4</v>
+        <v>44.7</v>
       </c>
       <c r="S186" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T186" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U186" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="V186" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W186" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X186" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z186" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA186" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB186" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr"/>
       <c r="AC186" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD186" t="inlineStr"/>
@@ -51434,7 +51430,7 @@
       </c>
       <c r="AI186" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ186" t="inlineStr">
@@ -51444,119 +51440,127 @@
       </c>
       <c r="AK186" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/20, 0 HR</t>
+          <t>Last 7 games: 3/18, 0 HR</t>
         </is>
       </c>
       <c r="AL186" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.4% barrel, 4.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.0% barrel, 2.3 HR allowed</t>
         </is>
       </c>
       <c r="AM186" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN186" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>3.95</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>87.46</t>
         </is>
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>97.5183</t>
+          <t>97.4349</t>
         </is>
       </c>
       <c r="AR186" t="inlineStr">
         <is>
-          <t>0.3047</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>0.1407</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="AT186" t="inlineStr">
         <is>
-          <t>0.2445</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>67.22</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>13.25</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>30.37</t>
+          <t>54.33</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>31.93</t>
+          <t>26.21</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7.6</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>0.0991</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>42.1</t>
+          <t>38.07</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>89.44</t>
         </is>
       </c>
       <c r="BD186" t="inlineStr">
         <is>
-          <t>0.405</t>
+          <t>0.3604</t>
         </is>
       </c>
       <c r="BE186" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>0.1379</t>
         </is>
       </c>
       <c r="BF186" t="inlineStr">
         <is>
-          <t>27.4</t>
-        </is>
-      </c>
-      <c r="BG186" t="inlineStr"/>
-      <c r="BH186" t="inlineStr"/>
+          <t>33.24</t>
+        </is>
+      </c>
+      <c r="BG186" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH186" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
       <c r="BI186" t="inlineStr">
         <is>
-          <t>T-Mobile Park</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ186" t="inlineStr"/>
@@ -51567,47 +51571,47 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>660688</t>
+          <t>702222</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Keibert Ruiz</t>
+          <t>Justin Crawford</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-09-26T16:35:00Z</t>
+          <t>2026-09-26T23:15:00Z</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Jonah Tong</t>
+          <t>Griffin Jax</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>804636</t>
+          <t>643377</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -51630,61 +51634,65 @@
       </c>
       <c r="O187" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P187" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="Q187" t="n">
-        <v>35.8</v>
+        <v>41.5</v>
       </c>
       <c r="R187" t="n">
-        <v>44.7</v>
+        <v>34.3</v>
       </c>
       <c r="S187" t="n">
-        <v>52.4</v>
+        <v>59.8</v>
       </c>
       <c r="T187" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U187" t="n">
-        <v>7</v>
+        <v>13.6</v>
       </c>
       <c r="V187" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W187" t="inlineStr">
+      <c r="Z187" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X187" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y187" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z187" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA187" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB187" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr"/>
@@ -51701,12 +51709,12 @@
       </c>
       <c r="AH187" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI187" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ187" t="inlineStr">
@@ -51716,127 +51724,119 @@
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/18, 0 HR</t>
+          <t>Last 7 games: 4/19, 0 HR</t>
         </is>
       </c>
       <c r="AL187" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.0% barrel, 2.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.0% barrel, 12.6 HR allowed</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN187" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
-          <t>87.46</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>97.4349</t>
+          <t>98.1205</t>
         </is>
       </c>
       <c r="AR187" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.329</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.072</t>
         </is>
       </c>
       <c r="AT187" t="inlineStr">
         <is>
-          <t>0.2877</t>
+          <t>0.285</t>
         </is>
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>67.22</t>
+          <t>69.2</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>54.33</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>26.21</t>
+          <t>16.4</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>7.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.091</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>8.98</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>38.07</t>
+          <t>41.02</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>89.44</t>
+          <t>88.99</t>
         </is>
       </c>
       <c r="BD187" t="inlineStr">
         <is>
-          <t>0.3604</t>
+          <t>0.3951</t>
         </is>
       </c>
       <c r="BE187" t="inlineStr">
         <is>
-          <t>0.1379</t>
+          <t>0.1499</t>
         </is>
       </c>
       <c r="BF187" t="inlineStr">
         <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="BG187" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH187" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
+          <t>23.09</t>
+        </is>
+      </c>
+      <c r="BG187" t="inlineStr"/>
+      <c r="BH187" t="inlineStr"/>
       <c r="BI187" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ187" t="inlineStr"/>
@@ -51847,27 +51847,27 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>702222</t>
+          <t>663494</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Justin Crawford</t>
+          <t>Bryan Torres</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-09-26T23:15:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -51877,17 +51877,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Griffin Jax</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>643377</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -51896,7 +51896,7 @@
         </is>
       </c>
       <c r="L188" t="n">
-        <v>35</v>
+        <v>34.7</v>
       </c>
       <c r="M188" t="inlineStr">
         <is>
@@ -51914,22 +51914,22 @@
         </is>
       </c>
       <c r="P188" t="n">
-        <v>11</v>
+        <v>7.3</v>
       </c>
       <c r="Q188" t="n">
-        <v>41.5</v>
+        <v>45.3</v>
       </c>
       <c r="R188" t="n">
-        <v>34.3</v>
+        <v>27.6</v>
       </c>
       <c r="S188" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T188" t="n">
         <v>80</v>
       </c>
       <c r="U188" t="n">
-        <v>13.6</v>
+        <v>0</v>
       </c>
       <c r="V188" t="inlineStr">
         <is>
@@ -51943,7 +51943,7 @@
       </c>
       <c r="X188" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y188" t="inlineStr">
@@ -51985,12 +51985,12 @@
       </c>
       <c r="AH188" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI188" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ188" t="inlineStr">
@@ -52000,12 +52000,12 @@
       </c>
       <c r="AK188" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/19, 0 HR</t>
+          <t>Last 7 games: 0/18, 0 HR</t>
         </is>
       </c>
       <c r="AL188" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.0% barrel, 12.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM188" t="inlineStr">
@@ -52015,104 +52015,104 @@
       </c>
       <c r="AN188" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
         <is>
-          <t>35.4</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>98.1205</t>
+          <t>95.7371</t>
         </is>
       </c>
       <c r="AR188" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>0.332</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>0.101</t>
         </is>
       </c>
       <c r="AT188" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>0.288</t>
         </is>
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>69.2</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>48.1</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>16.4</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>0.103</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>8.98</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>41.02</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD188" t="inlineStr">
         <is>
-          <t>0.3951</t>
+          <t>0.4125</t>
         </is>
       </c>
       <c r="BE188" t="inlineStr">
         <is>
-          <t>0.1499</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BF188" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG188" t="inlineStr"/>
       <c r="BH188" t="inlineStr"/>
       <c r="BI188" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ188" t="inlineStr"/>
@@ -52123,27 +52123,27 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>663494</t>
+          <t>669134</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Bryan Torres</t>
+          <t>Luis Campusano</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-27T00:40:00Z</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -52153,24 +52153,12 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I189" t="inlineStr">
-        <is>
-          <t>Dustin May</t>
-        </is>
-      </c>
-      <c r="J189" t="inlineStr">
-        <is>
-          <t>669160</t>
-        </is>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr"/>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="n">
         <v>34.7</v>
       </c>
@@ -52186,26 +52174,26 @@
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P189" t="n">
-        <v>7.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q189" t="n">
-        <v>45.3</v>
+        <v>41.2</v>
       </c>
       <c r="R189" t="n">
-        <v>27.6</v>
+        <v>22.6</v>
       </c>
       <c r="S189" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T189" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U189" t="n">
-        <v>0</v>
+        <v>27.1</v>
       </c>
       <c r="V189" t="inlineStr">
         <is>
@@ -52219,7 +52207,7 @@
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -52244,7 +52232,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr"/>
@@ -52261,27 +52249,27 @@
       </c>
       <c r="AH189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI189" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Last 7 games: 0/18, 0 HR</t>
+          <t>Last 7 games: 5/28, 1 HR</t>
         </is>
       </c>
       <c r="AL189" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
@@ -52291,104 +52279,80 @@
       </c>
       <c r="AN189" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AO189" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>35.53</t>
         </is>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>95.7371</t>
+          <t>98.3374</t>
         </is>
       </c>
       <c r="AR189" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>0.3018</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>0.1113</t>
         </is>
       </c>
       <c r="AT189" t="inlineStr">
         <is>
-          <t>0.288</t>
+          <t>0.2913</t>
         </is>
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>72.96</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>30.48</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>48.1</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>19.94</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>5.6</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>0.103</t>
-        </is>
-      </c>
-      <c r="BA189" t="inlineStr">
-        <is>
-          <t>8.08</t>
-        </is>
-      </c>
-      <c r="BB189" t="inlineStr">
-        <is>
-          <t>44.43</t>
-        </is>
-      </c>
-      <c r="BC189" t="inlineStr">
-        <is>
-          <t>90.11</t>
-        </is>
-      </c>
-      <c r="BD189" t="inlineStr">
-        <is>
-          <t>0.4125</t>
-        </is>
-      </c>
-      <c r="BE189" t="inlineStr">
-        <is>
-          <t>0.1574</t>
-        </is>
-      </c>
-      <c r="BF189" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
+          <t>0.1183</t>
+        </is>
+      </c>
+      <c r="BA189" t="inlineStr"/>
+      <c r="BB189" t="inlineStr"/>
+      <c r="BC189" t="inlineStr"/>
+      <c r="BD189" t="inlineStr"/>
+      <c r="BE189" t="inlineStr"/>
+      <c r="BF189" t="inlineStr"/>
       <c r="BG189" t="inlineStr"/>
       <c r="BH189" t="inlineStr"/>
       <c r="BI189" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ189" t="inlineStr"/>
@@ -52399,27 +52363,27 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>669134</t>
+          <t>691594</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Luis Campusano</t>
+          <t>Javier Sanoja</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>2026-09-27T00:40:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -52429,14 +52393,26 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Brent Suter</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>608718</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
       <c r="L190" t="n">
-        <v>34.7</v>
+        <v>34.5</v>
       </c>
       <c r="M190" t="inlineStr">
         <is>
@@ -52450,26 +52426,26 @@
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P190" t="n">
-        <v>19.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q190" t="n">
-        <v>41.2</v>
+        <v>26.8</v>
       </c>
       <c r="R190" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="S190" t="n">
-        <v>59.8</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T190" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="U190" t="n">
-        <v>27.1</v>
+        <v>53.9</v>
       </c>
       <c r="V190" t="inlineStr">
         <is>
@@ -52483,7 +52459,7 @@
       </c>
       <c r="X190" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y190" t="inlineStr">
@@ -52508,7 +52484,7 @@
       </c>
       <c r="AC190" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD190" t="inlineStr"/>
@@ -52525,7 +52501,7 @@
       </c>
       <c r="AH190" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI190" t="inlineStr">
@@ -52540,12 +52516,12 @@
       </c>
       <c r="AK190" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 1 HR</t>
+          <t>Contact streak: 10/28 over last 7 games</t>
         </is>
       </c>
       <c r="AL190" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM190" t="inlineStr">
@@ -52555,80 +52531,104 @@
       </c>
       <c r="AN190" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
         <is>
-          <t>35.53</t>
+          <t>32.55</t>
         </is>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ190" t="inlineStr">
         <is>
-          <t>98.3374</t>
+          <t>97.4924</t>
         </is>
       </c>
       <c r="AR190" t="inlineStr">
         <is>
-          <t>0.3018</t>
+          <t>0.3518</t>
         </is>
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>0.1113</t>
+          <t>0.0858</t>
         </is>
       </c>
       <c r="AT190" t="inlineStr">
         <is>
-          <t>0.2913</t>
+          <t>0.2897</t>
         </is>
       </c>
       <c r="AU190" t="inlineStr">
         <is>
-          <t>72.96</t>
+          <t>69.0</t>
         </is>
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>30.48</t>
+          <t>6.81</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>19.94</t>
+          <t>19.32</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>5.6</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>0.1183</t>
-        </is>
-      </c>
-      <c r="BA190" t="inlineStr"/>
-      <c r="BB190" t="inlineStr"/>
-      <c r="BC190" t="inlineStr"/>
-      <c r="BD190" t="inlineStr"/>
-      <c r="BE190" t="inlineStr"/>
-      <c r="BF190" t="inlineStr"/>
+          <t>0.1572</t>
+        </is>
+      </c>
+      <c r="BA190" t="inlineStr">
+        <is>
+          <t>6.67</t>
+        </is>
+      </c>
+      <c r="BB190" t="inlineStr">
+        <is>
+          <t>31.36</t>
+        </is>
+      </c>
+      <c r="BC190" t="inlineStr">
+        <is>
+          <t>86.29</t>
+        </is>
+      </c>
+      <c r="BD190" t="inlineStr">
+        <is>
+          <t>0.4033</t>
+        </is>
+      </c>
+      <c r="BE190" t="inlineStr">
+        <is>
+          <t>0.1519</t>
+        </is>
+      </c>
+      <c r="BF190" t="inlineStr">
+        <is>
+          <t>23.51</t>
+        </is>
+      </c>
       <c r="BG190" t="inlineStr"/>
       <c r="BH190" t="inlineStr"/>
       <c r="BI190" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ190" t="inlineStr"/>
@@ -52639,27 +52639,27 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>691594</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Javier Sanoja</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -52669,22 +52669,22 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Brent Suter</t>
+          <t>Michael Wacha</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>608718</t>
+          <t>608379</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L191" t="n">
@@ -52702,26 +52702,26 @@
       </c>
       <c r="O191" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>11.1</v>
+        <v>2.8</v>
       </c>
       <c r="Q191" t="n">
-        <v>26.8</v>
+        <v>38</v>
       </c>
       <c r="R191" t="n">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
       <c r="S191" t="n">
-        <v>81.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T191" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U191" t="n">
-        <v>53.9</v>
+        <v>28.2</v>
       </c>
       <c r="V191" t="inlineStr">
         <is>
@@ -52735,7 +52735,7 @@
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -52777,27 +52777,27 @@
       </c>
       <c r="AH191" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI191" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Contact streak: 10/28 over last 7 games</t>
+          <t>Last 7 games: 8/26, 0 HR</t>
         </is>
       </c>
       <c r="AL191" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
@@ -52807,104 +52807,104 @@
       </c>
       <c r="AN191" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO191" t="inlineStr">
         <is>
-          <t>32.55</t>
+          <t>13.07</t>
         </is>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>84.52</t>
         </is>
       </c>
       <c r="AQ191" t="inlineStr">
         <is>
-          <t>97.4924</t>
+          <t>92.8</t>
         </is>
       </c>
       <c r="AR191" t="inlineStr">
         <is>
-          <t>0.3518</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>0.0858</t>
+          <t>0.0734</t>
         </is>
       </c>
       <c r="AT191" t="inlineStr">
         <is>
-          <t>0.2897</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU191" t="inlineStr">
         <is>
-          <t>69.0</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>6.81</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>19.32</t>
+          <t>23.58</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>0.1572</t>
+          <t>0.0747</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>7.12</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>35.86</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>87.92</t>
         </is>
       </c>
       <c r="BD191" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4102</t>
         </is>
       </c>
       <c r="BE191" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1647</t>
         </is>
       </c>
       <c r="BF191" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>29.09</t>
         </is>
       </c>
       <c r="BG191" t="inlineStr"/>
       <c r="BH191" t="inlineStr"/>
       <c r="BI191" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ191" t="inlineStr"/>
@@ -52915,22 +52915,22 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>701675</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Nathan Church</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -52945,17 +52945,17 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Michael Wacha</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>608379</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -52964,7 +52964,7 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="M192" t="inlineStr">
         <is>
@@ -52978,26 +52978,26 @@
       </c>
       <c r="O192" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>2.8</v>
+        <v>14.2</v>
       </c>
       <c r="Q192" t="n">
-        <v>38</v>
+        <v>45.3</v>
       </c>
       <c r="R192" t="n">
-        <v>23.2</v>
+        <v>27.6</v>
       </c>
       <c r="S192" t="n">
-        <v>88.7</v>
+        <v>47.9</v>
       </c>
       <c r="T192" t="n">
         <v>80</v>
       </c>
       <c r="U192" t="n">
-        <v>28.2</v>
+        <v>16.1</v>
       </c>
       <c r="V192" t="inlineStr">
         <is>
@@ -53011,7 +53011,7 @@
       </c>
       <c r="X192" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y192" t="inlineStr">
@@ -53053,12 +53053,12 @@
       </c>
       <c r="AH192" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI192" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ192" t="inlineStr">
@@ -53068,12 +53068,12 @@
       </c>
       <c r="AK192" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/26, 0 HR</t>
+          <t>Last 7 games: 5/22, 0 HR</t>
         </is>
       </c>
       <c r="AL192" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.1% barrel, 24.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
         </is>
       </c>
       <c r="AM192" t="inlineStr">
@@ -53083,104 +53083,104 @@
       </c>
       <c r="AN192" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>13.07</t>
+          <t>33.52</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
-          <t>84.52</t>
+          <t>86.62</t>
         </is>
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>92.8</t>
+          <t>97.4595</t>
         </is>
       </c>
       <c r="AR192" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3336</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>0.0734</t>
+          <t>0.1046</t>
         </is>
       </c>
       <c r="AT192" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2736</t>
         </is>
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>34.01</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>22.16</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>0.0747</t>
+          <t>0.1046</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>35.86</t>
+          <t>44.43</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>87.92</t>
+          <t>90.11</t>
         </is>
       </c>
       <c r="BD192" t="inlineStr">
         <is>
-          <t>0.4102</t>
+          <t>0.4125</t>
         </is>
       </c>
       <c r="BE192" t="inlineStr">
         <is>
-          <t>0.1647</t>
+          <t>0.1574</t>
         </is>
       </c>
       <c r="BF192" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>25.22</t>
         </is>
       </c>
       <c r="BG192" t="inlineStr"/>
       <c r="BH192" t="inlineStr"/>
       <c r="BI192" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ192" t="inlineStr"/>
@@ -53191,27 +53191,27 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>701675</t>
+          <t>640459</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Nathan Church</t>
+          <t>Brian Navarreto</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -53221,26 +53221,26 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Brent Suter</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>608718</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>34.4</v>
+        <v>34.1</v>
       </c>
       <c r="M193" t="inlineStr">
         <is>
@@ -53254,26 +53254,26 @@
       </c>
       <c r="O193" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P193" t="n">
-        <v>14.2</v>
+        <v>30.9</v>
       </c>
       <c r="Q193" t="n">
-        <v>45.3</v>
+        <v>26.8</v>
       </c>
       <c r="R193" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S193" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T193" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U193" t="n">
-        <v>16.1</v>
+        <v>32</v>
       </c>
       <c r="V193" t="inlineStr">
         <is>
@@ -53287,7 +53287,7 @@
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -53329,12 +53329,12 @@
       </c>
       <c r="AH193" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI193" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ193" t="inlineStr">
@@ -53344,12 +53344,12 @@
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/22, 0 HR</t>
+          <t>Contact streak: 2/6 over last 7 games</t>
         </is>
       </c>
       <c r="AL193" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 15.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
@@ -53359,104 +53359,104 @@
       </c>
       <c r="AN193" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>11.63</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
         <is>
-          <t>33.52</t>
+          <t>36.46</t>
         </is>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
-          <t>86.62</t>
+          <t>88.61</t>
         </is>
       </c>
       <c r="AQ193" t="inlineStr">
         <is>
-          <t>97.4595</t>
+          <t>98.6055</t>
         </is>
       </c>
       <c r="AR193" t="inlineStr">
         <is>
-          <t>0.3336</t>
+          <t>0.2797</t>
         </is>
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>0.1046</t>
+          <t>0.1169</t>
         </is>
       </c>
       <c r="AT193" t="inlineStr">
         <is>
-          <t>0.2736</t>
+          <t>0.2227</t>
         </is>
       </c>
       <c r="AU193" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.86</t>
         </is>
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>22.96</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>34.01</t>
+          <t>54.52</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>24.41</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>0.1046</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>90.11</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="BD193" t="inlineStr">
         <is>
-          <t>0.4125</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="BE193" t="inlineStr">
         <is>
-          <t>0.1574</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF193" t="inlineStr">
         <is>
-          <t>25.22</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG193" t="inlineStr"/>
       <c r="BH193" t="inlineStr"/>
       <c r="BI193" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ193" t="inlineStr"/>
@@ -53467,27 +53467,27 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>640459</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Brian Navarreto</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-27T00:40:00Z</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -53497,26 +53497,14 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I194" t="inlineStr">
-        <is>
-          <t>Brent Suter</t>
-        </is>
-      </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>608718</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="n">
-        <v>34.1</v>
+        <v>33.9</v>
       </c>
       <c r="M194" t="inlineStr">
         <is>
@@ -53530,26 +53518,26 @@
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P194" t="n">
-        <v>30.9</v>
+        <v>3.8</v>
       </c>
       <c r="Q194" t="n">
-        <v>26.8</v>
+        <v>41.2</v>
       </c>
       <c r="R194" t="n">
-        <v>21.5</v>
+        <v>22.6</v>
       </c>
       <c r="S194" t="n">
-        <v>40.2</v>
+        <v>95.5</v>
       </c>
       <c r="T194" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U194" t="n">
-        <v>32</v>
+        <v>10.8</v>
       </c>
       <c r="V194" t="inlineStr">
         <is>
@@ -53563,7 +53551,7 @@
       </c>
       <c r="X194" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y194" t="inlineStr">
@@ -53588,7 +53576,7 @@
       </c>
       <c r="AC194" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD194" t="inlineStr"/>
@@ -53605,12 +53593,12 @@
       </c>
       <c r="AH194" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI194" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ194" t="inlineStr">
@@ -53620,12 +53608,12 @@
       </c>
       <c r="AK194" t="inlineStr">
         <is>
-          <t>Contact streak: 2/6 over last 7 games</t>
+          <t>Last 7 games: 5/26, 0 HR</t>
         </is>
       </c>
       <c r="AL194" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM194" t="inlineStr">
@@ -53635,104 +53623,80 @@
       </c>
       <c r="AN194" t="inlineStr">
         <is>
-          <t>11.63</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>36.46</t>
+          <t>20.72</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
-          <t>88.61</t>
+          <t>85.43</t>
         </is>
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>98.6055</t>
+          <t>94.9526</t>
         </is>
       </c>
       <c r="AR194" t="inlineStr">
         <is>
-          <t>0.2797</t>
+          <t>0.3303</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>0.1169</t>
+          <t>0.0848</t>
         </is>
       </c>
       <c r="AT194" t="inlineStr">
         <is>
-          <t>0.2227</t>
+          <t>0.2877</t>
         </is>
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>72.86</t>
+          <t>66.89</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>22.96</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>54.52</t>
+          <t>44.77</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>24.41</t>
+          <t>21.35</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>0.1911</t>
-        </is>
-      </c>
-      <c r="BA194" t="inlineStr">
-        <is>
-          <t>6.67</t>
-        </is>
-      </c>
-      <c r="BB194" t="inlineStr">
-        <is>
-          <t>31.36</t>
-        </is>
-      </c>
-      <c r="BC194" t="inlineStr">
-        <is>
-          <t>86.29</t>
-        </is>
-      </c>
-      <c r="BD194" t="inlineStr">
-        <is>
-          <t>0.4033</t>
-        </is>
-      </c>
-      <c r="BE194" t="inlineStr">
-        <is>
-          <t>0.1519</t>
-        </is>
-      </c>
-      <c r="BF194" t="inlineStr">
-        <is>
-          <t>23.51</t>
-        </is>
-      </c>
+          <t>0.1017</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr"/>
+      <c r="BB194" t="inlineStr"/>
+      <c r="BC194" t="inlineStr"/>
+      <c r="BD194" t="inlineStr"/>
+      <c r="BE194" t="inlineStr"/>
+      <c r="BF194" t="inlineStr"/>
       <c r="BG194" t="inlineStr"/>
       <c r="BH194" t="inlineStr"/>
       <c r="BI194" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ194" t="inlineStr"/>
@@ -53743,12 +53707,12 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -53773,14 +53737,14 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr"/>
       <c r="L195" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="M195" t="inlineStr">
         <is>
@@ -53794,11 +53758,11 @@
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P195" t="n">
-        <v>3.8</v>
+        <v>15.4</v>
       </c>
       <c r="Q195" t="n">
         <v>41.2</v>
@@ -53807,13 +53771,13 @@
         <v>22.6</v>
       </c>
       <c r="S195" t="n">
-        <v>95.5</v>
+        <v>47.9</v>
       </c>
       <c r="T195" t="n">
         <v>60</v>
       </c>
       <c r="U195" t="n">
-        <v>10.8</v>
+        <v>62.4</v>
       </c>
       <c r="V195" t="inlineStr">
         <is>
@@ -53827,7 +53791,7 @@
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
@@ -53869,22 +53833,22 @@
       </c>
       <c r="AH195" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI195" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL195" t="inlineStr">
@@ -53899,67 +53863,67 @@
       </c>
       <c r="AN195" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>20.72</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
-          <t>85.43</t>
+          <t>87.52</t>
         </is>
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>94.9526</t>
+          <t>97.6767</t>
         </is>
       </c>
       <c r="AR195" t="inlineStr">
         <is>
-          <t>0.3303</t>
+          <t>0.3173</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>0.0848</t>
+          <t>0.1014</t>
         </is>
       </c>
       <c r="AT195" t="inlineStr">
         <is>
-          <t>0.2877</t>
+          <t>0.2847</t>
         </is>
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>66.89</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>17.53</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>32.03</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>21.35</t>
+          <t>24.33</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>0.1017</t>
+          <t>0.1051</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr"/>
@@ -53983,27 +53947,27 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>2026-09-27T00:40:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -54016,11 +53980,23 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Jack Ralston</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>667652</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L196" t="n">
-        <v>33.6</v>
+        <v>33.5</v>
       </c>
       <c r="M196" t="inlineStr">
         <is>
@@ -54034,26 +54010,26 @@
       </c>
       <c r="O196" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P196" t="n">
         <v>15.4</v>
       </c>
       <c r="Q196" t="n">
-        <v>41.2</v>
+        <v>48.7</v>
       </c>
       <c r="R196" t="n">
-        <v>22.6</v>
+        <v>21.5</v>
       </c>
       <c r="S196" t="n">
         <v>47.9</v>
       </c>
       <c r="T196" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U196" t="n">
-        <v>62.4</v>
+        <v>0</v>
       </c>
       <c r="V196" t="inlineStr">
         <is>
@@ -54092,7 +54068,7 @@
       </c>
       <c r="AC196" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD196" t="inlineStr"/>
@@ -54109,110 +54085,134 @@
       </c>
       <c r="AH196" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI196" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ196" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK196" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/26, 0 HR</t>
         </is>
       </c>
       <c r="AL196" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM196" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN196" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="AO196" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>28.53</t>
         </is>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
-          <t>87.52</t>
+          <t>87.15</t>
         </is>
       </c>
       <c r="AQ196" t="inlineStr">
         <is>
-          <t>97.6767</t>
+          <t>96.6742</t>
         </is>
       </c>
       <c r="AR196" t="inlineStr">
         <is>
-          <t>0.3173</t>
+          <t>0.3474</t>
         </is>
       </c>
       <c r="AS196" t="inlineStr">
         <is>
-          <t>0.1014</t>
+          <t>0.1191</t>
         </is>
       </c>
       <c r="AT196" t="inlineStr">
         <is>
-          <t>0.2847</t>
+          <t>0.2822</t>
         </is>
       </c>
       <c r="AU196" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV196" t="inlineStr">
         <is>
-          <t>17.53</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW196" t="inlineStr">
         <is>
-          <t>32.03</t>
+          <t>46.63</t>
         </is>
       </c>
       <c r="AX196" t="inlineStr">
         <is>
-          <t>24.33</t>
+          <t>31.62</t>
         </is>
       </c>
       <c r="AY196" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ196" t="inlineStr">
         <is>
-          <t>0.1051</t>
-        </is>
-      </c>
-      <c r="BA196" t="inlineStr"/>
-      <c r="BB196" t="inlineStr"/>
-      <c r="BC196" t="inlineStr"/>
-      <c r="BD196" t="inlineStr"/>
-      <c r="BE196" t="inlineStr"/>
-      <c r="BF196" t="inlineStr"/>
+          <t>0.1467</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>11.6</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>39.5</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="BD196" t="inlineStr">
+        <is>
+          <t>0.411</t>
+        </is>
+      </c>
+      <c r="BE196" t="inlineStr">
+        <is>
+          <t>0.204</t>
+        </is>
+      </c>
+      <c r="BF196" t="inlineStr">
+        <is>
+          <t>30.2</t>
+        </is>
+      </c>
       <c r="BG196" t="inlineStr"/>
       <c r="BH196" t="inlineStr"/>
       <c r="BI196" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ196" t="inlineStr"/>
@@ -54223,27 +54223,27 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>641680</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Jonah Heim</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-27T01:40:00Z</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -54258,12 +54258,12 @@
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Jack Ralston</t>
+          <t>Hayden Wesneski</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>667652</t>
+          <t>669713</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -54290,13 +54290,13 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>15.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q197" t="n">
-        <v>48.7</v>
+        <v>33.3</v>
       </c>
       <c r="R197" t="n">
-        <v>21.5</v>
+        <v>30.9</v>
       </c>
       <c r="S197" t="n">
         <v>47.9</v>
@@ -54305,7 +54305,7 @@
         <v>75</v>
       </c>
       <c r="U197" t="n">
-        <v>0</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V197" t="inlineStr">
         <is>
@@ -54344,7 +54344,7 @@
       </c>
       <c r="AC197" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD197" t="inlineStr"/>
@@ -54361,12 +54361,12 @@
       </c>
       <c r="AH197" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI197" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ197" t="inlineStr">
@@ -54376,119 +54376,119 @@
       </c>
       <c r="AK197" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/26, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL197" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 11.6% barrel, 4.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
         </is>
       </c>
       <c r="AM197" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN197" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>5.96</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>33.03</t>
         </is>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
-          <t>87.15</t>
+          <t>87.47</t>
         </is>
       </c>
       <c r="AQ197" t="inlineStr">
         <is>
-          <t>96.6742</t>
+          <t>97.7142</t>
         </is>
       </c>
       <c r="AR197" t="inlineStr">
         <is>
-          <t>0.3474</t>
+          <t>0.3565</t>
         </is>
       </c>
       <c r="AS197" t="inlineStr">
         <is>
-          <t>0.1191</t>
+          <t>0.1326</t>
         </is>
       </c>
       <c r="AT197" t="inlineStr">
         <is>
-          <t>0.2822</t>
+          <t>0.2823</t>
         </is>
       </c>
       <c r="AU197" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV197" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>39.58</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>31.62</t>
+          <t>26.78</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ197" t="inlineStr">
         <is>
-          <t>0.1467</t>
+          <t>0.1498</t>
         </is>
       </c>
       <c r="BA197" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="BB197" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>40.7</t>
         </is>
       </c>
       <c r="BC197" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD197" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>0.3947</t>
         </is>
       </c>
       <c r="BE197" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>0.1494</t>
         </is>
       </c>
       <c r="BF197" t="inlineStr">
         <is>
-          <t>30.2</t>
+          <t>23.41</t>
         </is>
       </c>
       <c r="BG197" t="inlineStr"/>
       <c r="BH197" t="inlineStr"/>
       <c r="BI197" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ197" t="inlineStr"/>
@@ -54499,27 +54499,27 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>641680</t>
+          <t>669242</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Jonah Heim</t>
+          <t>Tommy Edman</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>SF</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>2026-09-27T01:40:00Z</t>
+          <t>2026-09-26T20:05:00Z</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -54529,26 +54529,26 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Hayden Wesneski</t>
+          <t>Matt Wilkinson</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>669713</t>
+          <t>683363</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>33.5</v>
+        <v>32.6</v>
       </c>
       <c r="M198" t="inlineStr">
         <is>
@@ -54566,22 +54566,22 @@
         </is>
       </c>
       <c r="P198" t="n">
-        <v>21.2</v>
+        <v>20.4</v>
       </c>
       <c r="Q198" t="n">
-        <v>33.3</v>
+        <v>36.2</v>
       </c>
       <c r="R198" t="n">
-        <v>30.9</v>
+        <v>19.3</v>
       </c>
       <c r="S198" t="n">
-        <v>47.9</v>
+        <v>40.2</v>
       </c>
       <c r="T198" t="n">
         <v>75</v>
       </c>
       <c r="U198" t="n">
-        <v>9.300000000000001</v>
+        <v>37.4</v>
       </c>
       <c r="V198" t="inlineStr">
         <is>
@@ -54595,7 +54595,7 @@
       </c>
       <c r="X198" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y198" t="inlineStr">
@@ -54620,7 +54620,7 @@
       </c>
       <c r="AC198" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD198" t="inlineStr"/>
@@ -54637,134 +54637,134 @@
       </c>
       <c r="AH198" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI198" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK198" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL198" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.1% barrel, 4.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.5% barrel, 4.0 HR allowed</t>
         </is>
       </c>
       <c r="AM198" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN198" t="inlineStr">
         <is>
-          <t>5.96</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>34.79</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
-          <t>87.47</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>97.7142</t>
+          <t>98.7097</t>
         </is>
       </c>
       <c r="AR198" t="inlineStr">
         <is>
-          <t>0.3565</t>
+          <t>0.3634</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>0.1326</t>
+          <t>0.1153</t>
         </is>
       </c>
       <c r="AT198" t="inlineStr">
         <is>
-          <t>0.2823</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>13.58</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>39.58</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>26.78</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>0.1498</t>
+          <t>0.1437</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>40.7</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.1</t>
         </is>
       </c>
       <c r="BD198" t="inlineStr">
         <is>
-          <t>0.3947</t>
+          <t>0.382</t>
         </is>
       </c>
       <c r="BE198" t="inlineStr">
         <is>
-          <t>0.1494</t>
+          <t>0.155</t>
         </is>
       </c>
       <c r="BF198" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="BG198" t="inlineStr"/>
       <c r="BH198" t="inlineStr"/>
       <c r="BI198" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>Oracle Park</t>
         </is>
       </c>
       <c r="BJ198" t="inlineStr"/>
@@ -54775,27 +54775,27 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>805300</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Jakob Marsee</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SF</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-09-26T20:05:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -54805,17 +54805,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Matt Wilkinson</t>
+          <t>Brent Suter</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>683363</t>
+          <t>608718</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -54838,26 +54838,26 @@
       </c>
       <c r="O199" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P199" t="n">
-        <v>20.4</v>
+        <v>20.8</v>
       </c>
       <c r="Q199" t="n">
-        <v>36.2</v>
+        <v>26.8</v>
       </c>
       <c r="R199" t="n">
-        <v>19.3</v>
+        <v>21.5</v>
       </c>
       <c r="S199" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T199" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U199" t="n">
-        <v>37.4</v>
+        <v>32</v>
       </c>
       <c r="V199" t="inlineStr">
         <is>
@@ -54871,7 +54871,7 @@
       </c>
       <c r="X199" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y199" t="inlineStr">
@@ -54896,7 +54896,7 @@
       </c>
       <c r="AC199" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD199" t="inlineStr"/>
@@ -54913,7 +54913,7 @@
       </c>
       <c r="AH199" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI199" t="inlineStr">
@@ -54923,124 +54923,124 @@
       </c>
       <c r="AJ199" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK199" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 8/24 over last 7 games</t>
         </is>
       </c>
       <c r="AL199" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.5% barrel, 4.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM199" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN199" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AO199" t="inlineStr">
         <is>
-          <t>34.79</t>
+          <t>36.57</t>
         </is>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.78</t>
         </is>
       </c>
       <c r="AQ199" t="inlineStr">
         <is>
-          <t>98.7097</t>
+          <t>98.5574</t>
         </is>
       </c>
       <c r="AR199" t="inlineStr">
         <is>
-          <t>0.3634</t>
+          <t>0.3664</t>
         </is>
       </c>
       <c r="AS199" t="inlineStr">
         <is>
-          <t>0.1153</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="AT199" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.3239</t>
         </is>
       </c>
       <c r="AU199" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>70.29</t>
         </is>
       </c>
       <c r="AV199" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>5.23</t>
         </is>
       </c>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>40.88</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>23.19</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="AZ199" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1461</t>
         </is>
       </c>
       <c r="BA199" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BB199" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="BC199" t="inlineStr">
         <is>
-          <t>89.1</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="BD199" t="inlineStr">
         <is>
-          <t>0.382</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="BE199" t="inlineStr">
         <is>
-          <t>0.155</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF199" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG199" t="inlineStr"/>
       <c r="BH199" t="inlineStr"/>
       <c r="BI199" t="inlineStr">
         <is>
-          <t>Oracle Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ199" t="inlineStr"/>
@@ -55051,56 +55051,56 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>805300</t>
+          <t>676391</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Jakob Marsee</t>
+          <t>Ernie Clement</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>TOR</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CIN</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T19:07:00Z</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Brent Suter</t>
+          <t>Rhett Lowder</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>608718</t>
+          <t>695076</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L200" t="n">
-        <v>32.6</v>
+        <v>32</v>
       </c>
       <c r="M200" t="inlineStr">
         <is>
@@ -55114,65 +55114,61 @@
       </c>
       <c r="O200" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P200" t="n">
-        <v>20.8</v>
+        <v>4.8</v>
       </c>
       <c r="Q200" t="n">
-        <v>26.8</v>
+        <v>54</v>
       </c>
       <c r="R200" t="n">
-        <v>21.5</v>
+        <v>43.9</v>
       </c>
       <c r="S200" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T200" t="n">
         <v>50</v>
       </c>
       <c r="U200" t="n">
-        <v>32</v>
+        <v>0.8</v>
       </c>
       <c r="V200" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X200" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y200" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z200" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X200" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z200" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA200" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB200" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB200" t="inlineStr"/>
       <c r="AC200" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD200" t="inlineStr"/>
@@ -55189,7 +55185,7 @@
       </c>
       <c r="AH200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI200" t="inlineStr">
@@ -55204,12 +55200,12 @@
       </c>
       <c r="AK200" t="inlineStr">
         <is>
-          <t>Contact streak: 8/24 over last 7 games</t>
+          <t>Last 7 games: 3/24, 0 HR</t>
         </is>
       </c>
       <c r="AL200" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.0% barrel, 18.0 HR allowed</t>
         </is>
       </c>
       <c r="AM200" t="inlineStr">
@@ -55219,104 +55215,112 @@
       </c>
       <c r="AN200" t="inlineStr">
         <is>
-          <t>5.09</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
         <is>
-          <t>36.57</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
-          <t>87.78</t>
+          <t>84.92</t>
         </is>
       </c>
       <c r="AQ200" t="inlineStr">
         <is>
-          <t>98.5574</t>
+          <t>94.5834</t>
         </is>
       </c>
       <c r="AR200" t="inlineStr">
         <is>
-          <t>0.3664</t>
+          <t>0.331</t>
         </is>
       </c>
       <c r="AS200" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.0846</t>
         </is>
       </c>
       <c r="AT200" t="inlineStr">
         <is>
-          <t>0.3239</t>
+          <t>0.268</t>
         </is>
       </c>
       <c r="AU200" t="inlineStr">
         <is>
-          <t>70.29</t>
+          <t>67.39</t>
         </is>
       </c>
       <c r="AV200" t="inlineStr">
         <is>
-          <t>5.23</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>40.88</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>23.19</t>
+          <t>28.39</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="AZ200" t="inlineStr">
         <is>
-          <t>0.1461</t>
+          <t>0.1105</t>
         </is>
       </c>
       <c r="BA200" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>10.0</t>
         </is>
       </c>
       <c r="BB200" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC200" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>90.3</t>
         </is>
       </c>
       <c r="BD200" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.467</t>
         </is>
       </c>
       <c r="BE200" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.192</t>
         </is>
       </c>
       <c r="BF200" t="inlineStr">
         <is>
-          <t>23.51</t>
-        </is>
-      </c>
-      <c r="BG200" t="inlineStr"/>
-      <c r="BH200" t="inlineStr"/>
+          <t>27.3</t>
+        </is>
+      </c>
+      <c r="BG200" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH200" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
       <c r="BI200" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Rogers Centre</t>
         </is>
       </c>
       <c r="BJ200" t="inlineStr"/>
@@ -55327,47 +55331,47 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>676391</t>
+          <t>691182</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Ernie Clement</t>
+          <t>Adael Amador</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>TOR</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>CIN</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-09-26T19:07:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Rhett Lowder</t>
+          <t>Davis Martin</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>695076</t>
+          <t>663436</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -55376,7 +55380,7 @@
         </is>
       </c>
       <c r="L201" t="n">
-        <v>32</v>
+        <v>31.9</v>
       </c>
       <c r="M201" t="inlineStr">
         <is>
@@ -55390,61 +55394,65 @@
       </c>
       <c r="O201" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P201" t="n">
-        <v>4.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Q201" t="n">
-        <v>54</v>
+        <v>43.4</v>
       </c>
       <c r="R201" t="n">
-        <v>43.9</v>
+        <v>27.6</v>
       </c>
       <c r="S201" t="n">
-        <v>44.8</v>
+        <v>47.9</v>
       </c>
       <c r="T201" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U201" t="n">
-        <v>0.8</v>
+        <v>17.3</v>
       </c>
       <c r="V201" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X201" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y201" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W201" t="inlineStr">
+      <c r="Z201" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X201" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y201" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z201" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA201" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB201" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB201" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC201" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD201" t="inlineStr"/>
@@ -55461,12 +55469,12 @@
       </c>
       <c r="AH201" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI201" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ201" t="inlineStr">
@@ -55476,12 +55484,12 @@
       </c>
       <c r="AK201" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL201" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.0% barrel, 18.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.5% barrel, 15.8 HR allowed</t>
         </is>
       </c>
       <c r="AM201" t="inlineStr">
@@ -55491,112 +55499,104 @@
       </c>
       <c r="AN201" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>6.34</t>
         </is>
       </c>
       <c r="AO201" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>24.35</t>
         </is>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
-          <t>84.92</t>
+          <t>83.96</t>
         </is>
       </c>
       <c r="AQ201" t="inlineStr">
         <is>
-          <t>94.5834</t>
+          <t>96.0789</t>
         </is>
       </c>
       <c r="AR201" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.306</t>
         </is>
       </c>
       <c r="AS201" t="inlineStr">
         <is>
-          <t>0.0846</t>
+          <t>0.1013</t>
         </is>
       </c>
       <c r="AT201" t="inlineStr">
         <is>
-          <t>0.268</t>
+          <t>0.2697</t>
         </is>
       </c>
       <c r="AU201" t="inlineStr">
         <is>
-          <t>67.39</t>
+          <t>69.34</t>
         </is>
       </c>
       <c r="AV201" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>50.63</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>28.39</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>3.1</t>
         </is>
       </c>
       <c r="AZ201" t="inlineStr">
         <is>
-          <t>0.1105</t>
+          <t>0.1832</t>
         </is>
       </c>
       <c r="BA201" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="BB201" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="BC201" t="inlineStr">
         <is>
-          <t>90.3</t>
+          <t>90.42</t>
         </is>
       </c>
       <c r="BD201" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>0.4279</t>
         </is>
       </c>
       <c r="BE201" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>0.158</t>
         </is>
       </c>
       <c r="BF201" t="inlineStr">
         <is>
-          <t>27.3</t>
-        </is>
-      </c>
-      <c r="BG201" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="BH201" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
+          <t>24.32</t>
+        </is>
+      </c>
+      <c r="BG201" t="inlineStr"/>
+      <c r="BH201" t="inlineStr"/>
       <c r="BI201" t="inlineStr">
         <is>
-          <t>Rogers Centre</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ201" t="inlineStr"/>
@@ -55607,27 +55607,27 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>691182</t>
+          <t>691858</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Adael Amador</t>
+          <t>Jared Serna</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -55637,26 +55637,26 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Davis Martin</t>
+          <t>Brent Suter</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>663436</t>
+          <t>608718</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>31.9</v>
+        <v>31.4</v>
       </c>
       <c r="M202" t="inlineStr">
         <is>
@@ -55674,22 +55674,22 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>9.199999999999999</v>
+        <v>19.2</v>
       </c>
       <c r="Q202" t="n">
-        <v>43.4</v>
+        <v>26.8</v>
       </c>
       <c r="R202" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="S202" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T202" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U202" t="n">
-        <v>17.3</v>
+        <v>0</v>
       </c>
       <c r="V202" t="inlineStr">
         <is>
@@ -55703,7 +55703,7 @@
       </c>
       <c r="X202" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y202" t="inlineStr">
@@ -55728,7 +55728,7 @@
       </c>
       <c r="AC202" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD202" t="inlineStr"/>
@@ -55745,12 +55745,12 @@
       </c>
       <c r="AH202" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI202" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ202" t="inlineStr">
@@ -55760,12 +55760,12 @@
       </c>
       <c r="AK202" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 1/11, 0 HR</t>
         </is>
       </c>
       <c r="AL202" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.5% barrel, 15.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
         </is>
       </c>
       <c r="AM202" t="inlineStr">
@@ -55775,104 +55775,104 @@
       </c>
       <c r="AN202" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AO202" t="inlineStr">
         <is>
-          <t>24.35</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
-          <t>83.96</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ202" t="inlineStr">
         <is>
-          <t>96.0789</t>
+          <t>98.077</t>
         </is>
       </c>
       <c r="AR202" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="AS202" t="inlineStr">
         <is>
-          <t>0.1013</t>
+          <t>0.057</t>
         </is>
       </c>
       <c r="AT202" t="inlineStr">
         <is>
-          <t>0.2697</t>
+          <t>0.183</t>
         </is>
       </c>
       <c r="AU202" t="inlineStr">
         <is>
-          <t>69.34</t>
+          <t>71.2</t>
         </is>
       </c>
       <c r="AV202" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>11.1</t>
         </is>
       </c>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>50.63</t>
+          <t>29.4</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>11.8</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
         <is>
-          <t>3.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ202" t="inlineStr">
         <is>
-          <t>0.1832</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA202" t="inlineStr">
         <is>
-          <t>7.49</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="BB202" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>31.36</t>
         </is>
       </c>
       <c r="BC202" t="inlineStr">
         <is>
-          <t>90.42</t>
+          <t>86.29</t>
         </is>
       </c>
       <c r="BD202" t="inlineStr">
         <is>
-          <t>0.4279</t>
+          <t>0.4033</t>
         </is>
       </c>
       <c r="BE202" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BF202" t="inlineStr">
         <is>
-          <t>24.32</t>
+          <t>23.51</t>
         </is>
       </c>
       <c r="BG202" t="inlineStr"/>
       <c r="BH202" t="inlineStr"/>
       <c r="BI202" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BJ202" t="inlineStr"/>
@@ -55883,27 +55883,27 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>691858</t>
+          <t>664728</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Jared Serna</t>
+          <t>Kyle Isbel</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>KC</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-09-26T20:10:00Z</t>
+          <t>2026-09-26T23:10:00Z</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -55913,22 +55913,22 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Brent Suter</t>
+          <t>Tanner Bibee</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>608718</t>
+          <t>676440</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L203" t="n">
@@ -55950,22 +55950,22 @@
         </is>
       </c>
       <c r="P203" t="n">
-        <v>19.2</v>
+        <v>11.5</v>
       </c>
       <c r="Q203" t="n">
-        <v>26.8</v>
+        <v>42.9</v>
       </c>
       <c r="R203" t="n">
-        <v>21.5</v>
+        <v>23.2</v>
       </c>
       <c r="S203" t="n">
-        <v>59.8</v>
+        <v>40.2</v>
       </c>
       <c r="T203" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U203" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="V203" t="inlineStr">
         <is>
@@ -55979,7 +55979,7 @@
       </c>
       <c r="X203" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y203" t="inlineStr">
@@ -56004,7 +56004,7 @@
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD203" t="inlineStr"/>
@@ -56021,12 +56021,12 @@
       </c>
       <c r="AH203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ203" t="inlineStr">
@@ -56036,12 +56036,12 @@
       </c>
       <c r="AK203" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/11, 0 HR</t>
+          <t>Last 7 games: 4/16, 0 HR</t>
         </is>
       </c>
       <c r="AL203" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 9.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
         </is>
       </c>
       <c r="AM203" t="inlineStr">
@@ -56051,104 +56051,104 @@
       </c>
       <c r="AN203" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO203" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.08</t>
         </is>
       </c>
       <c r="AQ203" t="inlineStr">
         <is>
-          <t>98.077</t>
+          <t>98.7573</t>
         </is>
       </c>
       <c r="AR203" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.297</t>
         </is>
       </c>
       <c r="AS203" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>0.0749</t>
         </is>
       </c>
       <c r="AT203" t="inlineStr">
         <is>
-          <t>0.183</t>
+          <t>0.2531</t>
         </is>
       </c>
       <c r="AU203" t="inlineStr">
         <is>
-          <t>71.2</t>
+          <t>71.1</t>
         </is>
       </c>
       <c r="AV203" t="inlineStr">
         <is>
-          <t>11.1</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>29.4</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>19.64</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ203" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.0994</t>
         </is>
       </c>
       <c r="BA203" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="BB203" t="inlineStr">
         <is>
-          <t>31.36</t>
+          <t>38.56</t>
         </is>
       </c>
       <c r="BC203" t="inlineStr">
         <is>
-          <t>86.29</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="BD203" t="inlineStr">
         <is>
-          <t>0.4033</t>
+          <t>0.4074</t>
         </is>
       </c>
       <c r="BE203" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1646</t>
         </is>
       </c>
       <c r="BF203" t="inlineStr">
         <is>
-          <t>23.51</t>
+          <t>28.11</t>
         </is>
       </c>
       <c r="BG203" t="inlineStr"/>
       <c r="BH203" t="inlineStr"/>
       <c r="BI203" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Kauffman Stadium</t>
         </is>
       </c>
       <c r="BJ203" t="inlineStr"/>
@@ -56159,27 +56159,27 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>664728</t>
+          <t>701785</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Kyle Isbel</t>
+          <t>Kaelen Culpepper</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>KC</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-09-26T23:10:00Z</t>
+          <t>2026-09-26T20:10:00Z</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -56189,17 +56189,17 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Tanner Bibee</t>
+          <t>Nathan Eovaldi</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>676440</t>
+          <t>543135</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
@@ -56208,7 +56208,7 @@
         </is>
       </c>
       <c r="L204" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="M204" t="inlineStr">
         <is>
@@ -56222,26 +56222,26 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P204" t="n">
-        <v>11.5</v>
+        <v>17.4</v>
       </c>
       <c r="Q204" t="n">
-        <v>42.9</v>
+        <v>42.3</v>
       </c>
       <c r="R204" t="n">
-        <v>23.2</v>
+        <v>27.1</v>
       </c>
       <c r="S204" t="n">
-        <v>40.2</v>
+        <v>47.9</v>
       </c>
       <c r="T204" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U204" t="n">
-        <v>19.5</v>
+        <v>3.4</v>
       </c>
       <c r="V204" t="inlineStr">
         <is>
@@ -56255,7 +56255,7 @@
       </c>
       <c r="X204" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y204" t="inlineStr">
@@ -56280,7 +56280,7 @@
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD204" t="inlineStr"/>
@@ -56297,12 +56297,12 @@
       </c>
       <c r="AH204" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI204" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ204" t="inlineStr">
@@ -56312,12 +56312,12 @@
       </c>
       <c r="AK204" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/16, 0 HR</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL204" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 28.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 19.8 HR allowed</t>
         </is>
       </c>
       <c r="AM204" t="inlineStr">
@@ -56327,67 +56327,67 @@
       </c>
       <c r="AN204" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>3.6</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>30.6</t>
         </is>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
-          <t>88.08</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AQ204" t="inlineStr">
         <is>
-          <t>98.7573</t>
+          <t>97.517</t>
         </is>
       </c>
       <c r="AR204" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>0.365</t>
         </is>
       </c>
       <c r="AS204" t="inlineStr">
         <is>
-          <t>0.0749</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AT204" t="inlineStr">
         <is>
-          <t>0.2531</t>
+          <t>0.298</t>
         </is>
       </c>
       <c r="AU204" t="inlineStr">
         <is>
-          <t>71.1</t>
+          <t>73.7</t>
         </is>
       </c>
       <c r="AV204" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>35.4</t>
         </is>
       </c>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>19.64</t>
+          <t>24.7</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ204" t="inlineStr">
         <is>
-          <t>0.0994</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="BA204" t="inlineStr">
@@ -56397,34 +56397,34 @@
       </c>
       <c r="BB204" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="BC204" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="BD204" t="inlineStr">
         <is>
-          <t>0.4074</t>
+          <t>0.4045</t>
         </is>
       </c>
       <c r="BE204" t="inlineStr">
         <is>
-          <t>0.1646</t>
+          <t>0.1614</t>
         </is>
       </c>
       <c r="BF204" t="inlineStr">
         <is>
-          <t>28.11</t>
+          <t>25.04</t>
         </is>
       </c>
       <c r="BG204" t="inlineStr"/>
       <c r="BH204" t="inlineStr"/>
       <c r="BI204" t="inlineStr">
         <is>
-          <t>Kauffman Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ204" t="inlineStr"/>
@@ -57768,7 +57768,7 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -64146,7 +64146,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -64426,7 +64426,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -3061,7 +3061,7 @@
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -13640,7 +13640,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -16419,27 +16419,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>624424</t>
+          <t>547180</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Michael Conforto</t>
+          <t>Bryce Harper</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-09-27T19:05:00Z</t>
+          <t>2026-09-27T18:30:00Z</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -16449,17 +16449,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Tanner Houck</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>656557</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -16468,7 +16468,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>53.6</v>
+        <v>53.5</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16482,26 +16482,26 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>45.8</v>
+        <v>48.8</v>
       </c>
       <c r="Q58" t="n">
-        <v>52</v>
+        <v>33.8</v>
       </c>
       <c r="R58" t="n">
-        <v>41.1</v>
+        <v>52.8</v>
       </c>
       <c r="S58" t="n">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T58" t="n">
         <v>80</v>
       </c>
       <c r="U58" t="n">
-        <v>39.5</v>
+        <v>12</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y58" t="inlineStr">
@@ -16525,7 +16525,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -16533,14 +16533,10 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD58" t="inlineStr"/>
@@ -16557,27 +16553,27 @@
       </c>
       <c r="AH58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI58" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/23, 1 HR</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM58" t="inlineStr">
@@ -16587,112 +16583,112 @@
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>10.83</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>44.35</t>
         </is>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
-          <t>90.25</t>
+          <t>90.32</t>
         </is>
       </c>
       <c r="AQ58" t="inlineStr">
         <is>
-          <t>100.6403</t>
+          <t>101.6224</t>
         </is>
       </c>
       <c r="AR58" t="inlineStr">
         <is>
-          <t>0.4275</t>
+          <t>0.4836</t>
         </is>
       </c>
       <c r="AS58" t="inlineStr">
         <is>
-          <t>0.1931</t>
+          <t>0.2135</t>
         </is>
       </c>
       <c r="AT58" t="inlineStr">
         <is>
-          <t>0.3307</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>72.92</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>33.09</t>
+          <t>45.01</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>43.81</t>
+          <t>38.54</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>32.94</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>27.7</t>
         </is>
       </c>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>0.2005</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BB58" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="BC58" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="BD58" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.4093</t>
         </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr"/>
@@ -16703,27 +16699,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>547180</t>
+          <t>624424</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bryce Harper</t>
+          <t>Michael Conforto</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-09-27T18:30:00Z</t>
+          <t>2026-09-27T19:05:00Z</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -16733,17 +16729,17 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Tanner Houck</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>656557</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
@@ -16766,26 +16762,26 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>48.8</v>
+        <v>45.8</v>
       </c>
       <c r="Q59" t="n">
-        <v>33.8</v>
+        <v>52</v>
       </c>
       <c r="R59" t="n">
-        <v>52.8</v>
+        <v>41.1</v>
       </c>
       <c r="S59" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T59" t="n">
         <v>80</v>
       </c>
       <c r="U59" t="n">
-        <v>12</v>
+        <v>37.8</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -16799,7 +16795,7 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -16809,7 +16805,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -16817,10 +16813,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr"/>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>order MLB 6 vs RotoWire 5</t>
+        </is>
+      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD59" t="inlineStr"/>
@@ -16837,27 +16837,27 @@
       </c>
       <c r="AH59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI59" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
@@ -16867,112 +16867,112 @@
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>10.83</t>
+          <t>11.03</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>44.35</t>
+          <t>42.67</t>
         </is>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
-          <t>90.32</t>
+          <t>90.25</t>
         </is>
       </c>
       <c r="AQ59" t="inlineStr">
         <is>
-          <t>101.6224</t>
+          <t>100.6403</t>
         </is>
       </c>
       <c r="AR59" t="inlineStr">
         <is>
-          <t>0.4836</t>
+          <t>0.4275</t>
         </is>
       </c>
       <c r="AS59" t="inlineStr">
         <is>
-          <t>0.2135</t>
+          <t>0.1931</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.3307</t>
         </is>
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>72.92</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>45.01</t>
+          <t>33.09</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>38.54</t>
+          <t>43.81</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>32.94</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
-          <t>27.7</t>
+          <t>14.1</t>
         </is>
       </c>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2005</t>
         </is>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB59" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BC59" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD59" t="inlineStr">
         <is>
-          <t>0.4093</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr"/>
@@ -25412,7 +25412,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -27080,7 +27080,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -29892,7 +29892,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -30147,27 +30147,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>695670</t>
+          <t>681393</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Harry Ford</t>
+          <t>Connor Norby</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-09-27T17:05:00Z</t>
+          <t>2026-09-27T19:10:00Z</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -30177,17 +30177,17 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Sean Manaea</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>640455</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -30210,26 +30210,26 @@
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P107" t="n">
-        <v>40.3</v>
+        <v>30.5</v>
       </c>
       <c r="Q107" t="n">
-        <v>54.3</v>
+        <v>41.2</v>
       </c>
       <c r="R107" t="n">
-        <v>50.7</v>
+        <v>46.1</v>
       </c>
       <c r="S107" t="n">
-        <v>52.4</v>
+        <v>100</v>
       </c>
       <c r="T107" t="n">
         <v>78</v>
       </c>
       <c r="U107" t="n">
-        <v>16.6</v>
+        <v>23.7</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
       </c>
       <c r="X107" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y107" t="inlineStr">
@@ -30264,7 +30264,7 @@
       <c r="AB107" t="inlineStr"/>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD107" t="inlineStr"/>
@@ -30281,12 +30281,12 @@
       </c>
       <c r="AH107" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI107" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ107" t="inlineStr">
@@ -30296,12 +30296,12 @@
       </c>
       <c r="AK107" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/13, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL107" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM107" t="inlineStr">
@@ -30311,97 +30311,97 @@
       </c>
       <c r="AN107" t="inlineStr">
         <is>
-          <t>14.57</t>
+          <t>8.21</t>
         </is>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>38.31</t>
+          <t>36.47</t>
         </is>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
-          <t>87.25</t>
+          <t>87.67</t>
         </is>
       </c>
       <c r="AQ107" t="inlineStr">
         <is>
-          <t>99.0803</t>
+          <t>98.1726</t>
         </is>
       </c>
       <c r="AR107" t="inlineStr">
         <is>
-          <t>0.3539</t>
+          <t>0.3799</t>
         </is>
       </c>
       <c r="AS107" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.1557</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr">
         <is>
-          <t>0.2856</t>
+          <t>0.307</t>
         </is>
       </c>
       <c r="AU107" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>70.28</t>
         </is>
       </c>
       <c r="AV107" t="inlineStr">
         <is>
-          <t>5.42</t>
+          <t>8.69</t>
         </is>
       </c>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>32.84</t>
+          <t>41.75</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>36.28</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>0.1078</t>
+          <t>0.1352</t>
         </is>
       </c>
       <c r="BA107" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB107" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC107" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD107" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE107" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BF107" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG107" t="inlineStr">
@@ -30411,12 +30411,12 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI107" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ107" t="inlineStr"/>
@@ -30427,27 +30427,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>681393</t>
+          <t>695670</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Connor Norby</t>
+          <t>Harry Ford</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-09-27T19:10:00Z</t>
+          <t>2026-09-27T17:05:00Z</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -30457,17 +30457,17 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Sean Manaea</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>640455</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -30476,7 +30476,7 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>49.1</v>
+        <v>49</v>
       </c>
       <c r="M108" t="inlineStr">
         <is>
@@ -30490,26 +30490,26 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P108" t="n">
-        <v>30.5</v>
+        <v>40.3</v>
       </c>
       <c r="Q108" t="n">
-        <v>41.2</v>
+        <v>54.3</v>
       </c>
       <c r="R108" t="n">
-        <v>46.1</v>
+        <v>50.7</v>
       </c>
       <c r="S108" t="n">
-        <v>100</v>
+        <v>52.4</v>
       </c>
       <c r="T108" t="n">
         <v>78</v>
       </c>
       <c r="U108" t="n">
-        <v>23.7</v>
+        <v>14.1</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
       </c>
       <c r="X108" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y108" t="inlineStr">
@@ -30544,7 +30544,7 @@
       <c r="AB108" t="inlineStr"/>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD108" t="inlineStr"/>
@@ -30561,12 +30561,12 @@
       </c>
       <c r="AH108" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ108" t="inlineStr">
@@ -30576,12 +30576,12 @@
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL108" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
         </is>
       </c>
       <c r="AM108" t="inlineStr">
@@ -30591,97 +30591,97 @@
       </c>
       <c r="AN108" t="inlineStr">
         <is>
-          <t>8.21</t>
+          <t>14.57</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>36.47</t>
+          <t>38.31</t>
         </is>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
-          <t>87.67</t>
+          <t>87.25</t>
         </is>
       </c>
       <c r="AQ108" t="inlineStr">
         <is>
-          <t>98.1726</t>
+          <t>99.0803</t>
         </is>
       </c>
       <c r="AR108" t="inlineStr">
         <is>
-          <t>0.3799</t>
+          <t>0.3539</t>
         </is>
       </c>
       <c r="AS108" t="inlineStr">
         <is>
-          <t>0.1557</t>
+          <t>0.1696</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr">
         <is>
-          <t>0.307</t>
+          <t>0.2856</t>
         </is>
       </c>
       <c r="AU108" t="inlineStr">
         <is>
-          <t>70.28</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="AV108" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>5.42</t>
         </is>
       </c>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>32.84</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>36.28</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>0.1352</t>
+          <t>0.1078</t>
         </is>
       </c>
       <c r="BA108" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BB108" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="BC108" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="BD108" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="BE108" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.1869</t>
         </is>
       </c>
       <c r="BF108" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="BG108" t="inlineStr">
@@ -30691,12 +30691,12 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BI108" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ108" t="inlineStr"/>
@@ -30707,27 +30707,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>670623</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Isaac Paredes</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-09-27T19:05:00Z</t>
+          <t>2026-09-27T19:10:00Z</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -30737,17 +30737,17 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Seth Johnson</t>
+          <t>Andre Pallante</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>686751</t>
+          <t>669467</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -30770,26 +30770,26 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P109" t="n">
-        <v>18.2</v>
+        <v>36.7</v>
       </c>
       <c r="Q109" t="n">
-        <v>48.9</v>
+        <v>25.3</v>
       </c>
       <c r="R109" t="n">
-        <v>60.9</v>
+        <v>45.1</v>
       </c>
       <c r="S109" t="n">
-        <v>96.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T109" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U109" t="n">
-        <v>80.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -30803,7 +30803,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -30841,27 +30841,27 @@
       </c>
       <c r="AH109" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI109" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL109" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 11.1% barrel, 4.4 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.3% barrel, 14.0 HR allowed</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -30871,112 +30871,112 @@
       </c>
       <c r="AN109" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>7.86</t>
         </is>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>43.27</t>
         </is>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
-          <t>86.49</t>
+          <t>90.47</t>
         </is>
       </c>
       <c r="AQ109" t="inlineStr">
         <is>
-          <t>97.0057</t>
+          <t>100.4077</t>
         </is>
       </c>
       <c r="AR109" t="inlineStr">
         <is>
-          <t>0.3758</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS109" t="inlineStr">
         <is>
-          <t>0.1334</t>
+          <t>0.1719</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr">
         <is>
-          <t>0.3221</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU109" t="inlineStr">
         <is>
-          <t>67.74</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV109" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>13.27</t>
         </is>
       </c>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>51.65</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>31.22</t>
+          <t>23.57</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>0.1914</t>
+          <t>0.1729</t>
         </is>
       </c>
       <c r="BA109" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>5.27</t>
         </is>
       </c>
       <c r="BB109" t="inlineStr">
         <is>
-          <t>48.5</t>
+          <t>35.91</t>
         </is>
       </c>
       <c r="BC109" t="inlineStr">
         <is>
-          <t>90.58</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="BD109" t="inlineStr">
         <is>
-          <t>0.3669</t>
+          <t>0.3845</t>
         </is>
       </c>
       <c r="BE109" t="inlineStr">
         <is>
-          <t>0.1444</t>
+          <t>0.1279</t>
         </is>
       </c>
       <c r="BF109" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>17.12</t>
         </is>
       </c>
       <c r="BG109" t="inlineStr">
         <is>
-          <t>Out To CF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI109" t="inlineStr">
         <is>
-          <t>Sutter Health Park</t>
+          <t>American Family Field</t>
         </is>
       </c>
       <c r="BJ109" t="inlineStr"/>
@@ -30987,47 +30987,47 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>687637</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Dylan Beavers</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-09-27T19:10:00Z</t>
+          <t>2026-09-27T17:05:00Z</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>Delayed Start</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Andre Pallante</t>
+          <t>Elmer Rodríguez</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>669467</t>
+          <t>695684</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -31036,7 +31036,7 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>49</v>
+        <v>48.9</v>
       </c>
       <c r="M110" t="inlineStr">
         <is>
@@ -31050,26 +31050,26 @@
       </c>
       <c r="O110" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P110" t="n">
-        <v>36.7</v>
+        <v>32.9</v>
       </c>
       <c r="Q110" t="n">
-        <v>25.3</v>
+        <v>31.6</v>
       </c>
       <c r="R110" t="n">
-        <v>45.1</v>
+        <v>54.7</v>
       </c>
       <c r="S110" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T110" t="n">
         <v>80</v>
       </c>
       <c r="U110" t="n">
-        <v>70.59999999999999</v>
+        <v>39.4</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -31083,7 +31083,7 @@
       </c>
       <c r="X110" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y110" t="inlineStr">
@@ -31104,7 +31104,7 @@
       <c r="AB110" t="inlineStr"/>
       <c r="AC110" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD110" t="inlineStr"/>
@@ -31121,12 +31121,12 @@
       </c>
       <c r="AH110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI110" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ110" t="inlineStr">
@@ -31141,7 +31141,7 @@
       </c>
       <c r="AL110" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.3% barrel, 14.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.5% barrel, 2.0 HR allowed</t>
         </is>
       </c>
       <c r="AM110" t="inlineStr">
@@ -31151,77 +31151,77 @@
       </c>
       <c r="AN110" t="inlineStr">
         <is>
-          <t>7.86</t>
+          <t>8.67</t>
         </is>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
-          <t>43.27</t>
+          <t>35.21</t>
         </is>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
-          <t>90.47</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AQ110" t="inlineStr">
         <is>
-          <t>100.4077</t>
+          <t>99.1677</t>
         </is>
       </c>
       <c r="AR110" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.3807</t>
         </is>
       </c>
       <c r="AS110" t="inlineStr">
         <is>
-          <t>0.1719</t>
+          <t>0.1635</t>
         </is>
       </c>
       <c r="AT110" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3097</t>
         </is>
       </c>
       <c r="AU110" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV110" t="inlineStr">
         <is>
-          <t>13.27</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>40.46</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>23.57</t>
+          <t>34.54</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>0.1729</t>
+          <t>0.1534</t>
         </is>
       </c>
       <c r="BA110" t="inlineStr">
         <is>
-          <t>5.27</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="BB110" t="inlineStr">
         <is>
-          <t>35.91</t>
+          <t>36.6</t>
         </is>
       </c>
       <c r="BC110" t="inlineStr">
@@ -31231,32 +31231,32 @@
       </c>
       <c r="BD110" t="inlineStr">
         <is>
-          <t>0.3845</t>
+          <t>0.387</t>
         </is>
       </c>
       <c r="BE110" t="inlineStr">
         <is>
-          <t>0.1279</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="BF110" t="inlineStr">
         <is>
-          <t>17.12</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BG110" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI110" t="inlineStr">
         <is>
-          <t>American Family Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ110" t="inlineStr"/>
@@ -31267,47 +31267,47 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>687637</t>
+          <t>670623</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dylan Beavers</t>
+          <t>Isaac Paredes</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-09-27T17:05:00Z</t>
+          <t>2026-09-27T19:05:00Z</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Delayed Start</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Elmer Rodríguez</t>
+          <t>Seth Johnson</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>695684</t>
+          <t>686751</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -31330,26 +31330,26 @@
       </c>
       <c r="O111" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P111" t="n">
-        <v>32.9</v>
+        <v>18.2</v>
       </c>
       <c r="Q111" t="n">
-        <v>31.6</v>
+        <v>48.9</v>
       </c>
       <c r="R111" t="n">
-        <v>54.7</v>
+        <v>60.9</v>
       </c>
       <c r="S111" t="n">
-        <v>93.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T111" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U111" t="n">
-        <v>39.4</v>
+        <v>79</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
       </c>
       <c r="X111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y111" t="inlineStr">
@@ -31384,7 +31384,7 @@
       <c r="AB111" t="inlineStr"/>
       <c r="AC111" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD111" t="inlineStr"/>
@@ -31401,27 +31401,27 @@
       </c>
       <c r="AH111" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI111" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL111" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.5% barrel, 2.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 11.1% barrel, 4.4 HR allowed</t>
         </is>
       </c>
       <c r="AM111" t="inlineStr">
@@ -31431,112 +31431,112 @@
       </c>
       <c r="AN111" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>30.73</t>
         </is>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>86.49</t>
         </is>
       </c>
       <c r="AQ111" t="inlineStr">
         <is>
-          <t>99.1677</t>
+          <t>97.0057</t>
         </is>
       </c>
       <c r="AR111" t="inlineStr">
         <is>
-          <t>0.3807</t>
+          <t>0.3758</t>
         </is>
       </c>
       <c r="AS111" t="inlineStr">
         <is>
-          <t>0.1635</t>
+          <t>0.1334</t>
         </is>
       </c>
       <c r="AT111" t="inlineStr">
         <is>
-          <t>0.3097</t>
+          <t>0.3221</t>
         </is>
       </c>
       <c r="AU111" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>67.74</t>
         </is>
       </c>
       <c r="AV111" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>40.46</t>
+          <t>51.65</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>34.54</t>
+          <t>31.22</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>23.5</t>
         </is>
       </c>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>0.1534</t>
+          <t>0.1914</t>
         </is>
       </c>
       <c r="BA111" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>11.13</t>
         </is>
       </c>
       <c r="BB111" t="inlineStr">
         <is>
-          <t>36.6</t>
+          <t>48.5</t>
         </is>
       </c>
       <c r="BC111" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>90.58</t>
         </is>
       </c>
       <c r="BD111" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>0.3669</t>
         </is>
       </c>
       <c r="BE111" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>0.1444</t>
         </is>
       </c>
       <c r="BF111" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>22.32</t>
         </is>
       </c>
       <c r="BG111" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>Out To CF</t>
         </is>
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="BI111" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Sutter Health Park</t>
         </is>
       </c>
       <c r="BJ111" t="inlineStr"/>
@@ -31547,22 +31547,22 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>680777</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Ryan Jeffers</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>TEX</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -31577,17 +31577,17 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>MacKenzie Gore</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>669022</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -31610,26 +31610,26 @@
       </c>
       <c r="O112" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P112" t="n">
-        <v>24</v>
+        <v>38.2</v>
       </c>
       <c r="Q112" t="n">
-        <v>60.1</v>
+        <v>46.4</v>
       </c>
       <c r="R112" t="n">
-        <v>46.1</v>
+        <v>29.6</v>
       </c>
       <c r="S112" t="n">
-        <v>76.2</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T112" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U112" t="n">
-        <v>45</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -31664,7 +31664,7 @@
       <c r="AB112" t="inlineStr"/>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD112" t="inlineStr"/>
@@ -31681,7 +31681,7 @@
       </c>
       <c r="AH112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI112" t="inlineStr">
@@ -31696,12 +31696,12 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Contact streak: 10/22 over last 7 games</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL112" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 9.2% barrel, 19.3 HR allowed</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -31711,112 +31711,112 @@
       </c>
       <c r="AN112" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>9.17</t>
         </is>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="AQ112" t="inlineStr">
         <is>
-          <t>100.1023</t>
+          <t>100.7372</t>
         </is>
       </c>
       <c r="AR112" t="inlineStr">
         <is>
-          <t>0.391</t>
+          <t>0.4182</t>
         </is>
       </c>
       <c r="AS112" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1752</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU112" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>73.14</t>
         </is>
       </c>
       <c r="AV112" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>36.89</t>
         </is>
       </c>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>37.74</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>27.68</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>0.1814</t>
         </is>
       </c>
       <c r="BA112" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="BB112" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>41.93</t>
         </is>
       </c>
       <c r="BC112" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.49</t>
         </is>
       </c>
       <c r="BD112" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>0.3933</t>
         </is>
       </c>
       <c r="BE112" t="inlineStr">
         <is>
-          <t>0.2001</t>
+          <t>0.1516</t>
         </is>
       </c>
       <c r="BF112" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="BG112" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI112" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BJ112" t="inlineStr"/>
@@ -31827,24 +31827,24 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>694249</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Cole Carrigg</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
           <t>COL</t>
         </is>
       </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F113" t="inlineStr">
         <is>
           <t>2026-09-27T19:10:00Z</t>
@@ -31857,17 +31857,17 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -31876,7 +31876,7 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>48.7</v>
+        <v>48.9</v>
       </c>
       <c r="M113" t="inlineStr">
         <is>
@@ -31890,26 +31890,26 @@
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>29.1</v>
+        <v>24</v>
       </c>
       <c r="Q113" t="n">
-        <v>39.2</v>
+        <v>60.1</v>
       </c>
       <c r="R113" t="n">
         <v>46.1</v>
       </c>
       <c r="S113" t="n">
-        <v>94.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T113" t="n">
         <v>75</v>
       </c>
       <c r="U113" t="n">
-        <v>54.3</v>
+        <v>45</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -31923,7 +31923,7 @@
       </c>
       <c r="X113" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y113" t="inlineStr">
@@ -31944,7 +31944,7 @@
       <c r="AB113" t="inlineStr"/>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD113" t="inlineStr"/>
@@ -31961,27 +31961,27 @@
       </c>
       <c r="AH113" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI113" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
         <is>
-          <t>Contact streak: 9/25 over last 7 games</t>
+          <t>Contact streak: 10/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL113" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
         </is>
       </c>
       <c r="AM113" t="inlineStr">
@@ -31991,97 +31991,97 @@
       </c>
       <c r="AN113" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>41.0</t>
         </is>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ113" t="inlineStr">
         <is>
-          <t>99.1475</t>
+          <t>100.1023</t>
         </is>
       </c>
       <c r="AR113" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>0.391</t>
         </is>
       </c>
       <c r="AS113" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT113" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.326</t>
         </is>
       </c>
       <c r="AU113" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV113" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr">
         <is>
-          <t>11.0</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="BA113" t="inlineStr">
         <is>
-          <t>8.3</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BB113" t="inlineStr">
         <is>
-          <t>39.0</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="BC113" t="inlineStr">
         <is>
-          <t>88.4</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD113" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.487</t>
         </is>
       </c>
       <c r="BE113" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>0.2001</t>
         </is>
       </c>
       <c r="BF113" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BG113" t="inlineStr">
@@ -32107,22 +32107,22 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>680777</t>
+          <t>694249</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ryan Jeffers</t>
+          <t>Cole Carrigg</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>TEX</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -32142,12 +32142,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>MacKenzie Gore</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>669022</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -32156,7 +32156,7 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="M114" t="inlineStr">
         <is>
@@ -32174,22 +32174,22 @@
         </is>
       </c>
       <c r="P114" t="n">
-        <v>38.2</v>
+        <v>29.1</v>
       </c>
       <c r="Q114" t="n">
-        <v>46.4</v>
+        <v>39.2</v>
       </c>
       <c r="R114" t="n">
-        <v>29.6</v>
+        <v>46.1</v>
       </c>
       <c r="S114" t="n">
         <v>94.90000000000001</v>
       </c>
       <c r="T114" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U114" t="n">
-        <v>3.4</v>
+        <v>54.3</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -32224,7 +32224,7 @@
       <c r="AB114" t="inlineStr"/>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD114" t="inlineStr"/>
@@ -32241,27 +32241,27 @@
       </c>
       <c r="AH114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI114" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Contact streak: 9/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL114" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 9.2% barrel, 19.3 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM114" t="inlineStr">
@@ -32271,112 +32271,112 @@
       </c>
       <c r="AN114" t="inlineStr">
         <is>
-          <t>9.17</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>100.7372</t>
+          <t>99.1475</t>
         </is>
       </c>
       <c r="AR114" t="inlineStr">
         <is>
-          <t>0.4182</t>
+          <t>0.404</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>0.1752</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="AT114" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>73.14</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>37.74</t>
+          <t>48.0</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>27.68</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>0.1814</t>
+          <t>0.191</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>8.3</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>41.93</t>
+          <t>39.0</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>89.49</t>
+          <t>88.4</t>
         </is>
       </c>
       <c r="BD114" t="inlineStr">
         <is>
-          <t>0.3933</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE114" t="inlineStr">
         <is>
-          <t>0.1516</t>
+          <t>0.156</t>
         </is>
       </c>
       <c r="BF114" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>22.5</t>
         </is>
       </c>
       <c r="BG114" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI114" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ114" t="inlineStr"/>
@@ -33808,7 +33808,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -36875,27 +36875,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>695734</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Daylen Lile</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>2026-09-27T17:05:00Z</t>
+          <t>2026-09-27T19:10:00Z</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -36905,17 +36905,17 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Sean Manaea</t>
+          <t>Kyle Freeland</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>640455</t>
+          <t>607536</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -36942,22 +36942,22 @@
         </is>
       </c>
       <c r="P131" t="n">
-        <v>36.3</v>
+        <v>18.8</v>
       </c>
       <c r="Q131" t="n">
-        <v>54.3</v>
+        <v>61.5</v>
       </c>
       <c r="R131" t="n">
-        <v>50.7</v>
+        <v>46.1</v>
       </c>
       <c r="S131" t="n">
-        <v>64.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T131" t="n">
         <v>50</v>
       </c>
       <c r="U131" t="n">
-        <v>9.300000000000001</v>
+        <v>42</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -36971,7 +36971,7 @@
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -36992,7 +36992,7 @@
       <c r="AB131" t="inlineStr"/>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr"/>
@@ -37009,12 +37009,12 @@
       </c>
       <c r="AH131" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI131" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ131" t="inlineStr">
@@ -37024,12 +37024,12 @@
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/22, 0 HR</t>
+          <t>Contact streak: 10/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL131" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
@@ -37039,97 +37039,97 @@
       </c>
       <c r="AN131" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>99.0897</t>
+          <t>97.5114</t>
         </is>
       </c>
       <c r="AR131" t="inlineStr">
         <is>
-          <t>0.4462</t>
+          <t>0.397</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>0.1754</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr">
         <is>
-          <t>0.3326</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>70.78</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>9.85</t>
+          <t>7.2</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>40.31</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>21.8</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.117</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>10.44</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>44.99</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>89.38</t>
+          <t>90.89</t>
         </is>
       </c>
       <c r="BD131" t="inlineStr">
         <is>
-          <t>0.4367</t>
+          <t>0.487</t>
         </is>
       </c>
       <c r="BE131" t="inlineStr">
         <is>
-          <t>0.1869</t>
+          <t>0.2001</t>
         </is>
       </c>
       <c r="BF131" t="inlineStr">
         <is>
-          <t>28.75</t>
+          <t>27.54</t>
         </is>
       </c>
       <c r="BG131" t="inlineStr">
@@ -37139,12 +37139,12 @@
       </c>
       <c r="BH131" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>70</t>
         </is>
       </c>
       <c r="BI131" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ131" t="inlineStr"/>
@@ -37155,27 +37155,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>695734</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Daylen Lile</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>2026-09-27T19:10:00Z</t>
+          <t>2026-09-27T17:05:00Z</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -37185,17 +37185,17 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Kyle Freeland</t>
+          <t>Sean Manaea</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>607536</t>
+          <t>640455</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
@@ -37204,7 +37204,7 @@
         </is>
       </c>
       <c r="L132" t="n">
-        <v>46.6</v>
+        <v>46.5</v>
       </c>
       <c r="M132" t="inlineStr">
         <is>
@@ -37222,22 +37222,22 @@
         </is>
       </c>
       <c r="P132" t="n">
-        <v>18.8</v>
+        <v>36.3</v>
       </c>
       <c r="Q132" t="n">
-        <v>61.5</v>
+        <v>54.3</v>
       </c>
       <c r="R132" t="n">
-        <v>46.1</v>
+        <v>50.7</v>
       </c>
       <c r="S132" t="n">
-        <v>86.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="T132" t="n">
         <v>50</v>
       </c>
       <c r="U132" t="n">
-        <v>42</v>
+        <v>8.1</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -37251,7 +37251,7 @@
       </c>
       <c r="X132" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y132" t="inlineStr">
@@ -37272,7 +37272,7 @@
       <c r="AB132" t="inlineStr"/>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD132" t="inlineStr"/>
@@ -37289,12 +37289,12 @@
       </c>
       <c r="AH132" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ132" t="inlineStr">
@@ -37304,12 +37304,12 @@
       </c>
       <c r="AK132" t="inlineStr">
         <is>
-          <t>Contact streak: 10/25 over last 7 games</t>
+          <t>Last 7 games: 4/23, 0 HR</t>
         </is>
       </c>
       <c r="AL132" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.6% barrel, 25.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.4% barrel, 20.0 HR allowed</t>
         </is>
       </c>
       <c r="AM132" t="inlineStr">
@@ -37319,97 +37319,97 @@
       </c>
       <c r="AN132" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>38.7</t>
         </is>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>97.5114</t>
+          <t>99.0897</t>
         </is>
       </c>
       <c r="AR132" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>0.4462</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1754</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3326</t>
         </is>
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>70.78</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>7.2</t>
+          <t>9.85</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>40.31</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>21.8</t>
+          <t>33.95</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>0.117</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>10.59</t>
+          <t>10.44</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>44.99</t>
+          <t>42.11</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>90.89</t>
+          <t>89.38</t>
         </is>
       </c>
       <c r="BD132" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>0.4367</t>
         </is>
       </c>
       <c r="BE132" t="inlineStr">
         <is>
-          <t>0.2001</t>
+          <t>0.1869</t>
         </is>
       </c>
       <c r="BF132" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>28.75</t>
         </is>
       </c>
       <c r="BG132" t="inlineStr">
@@ -37419,12 +37419,12 @@
       </c>
       <c r="BH132" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>62</t>
         </is>
       </c>
       <c r="BI132" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BJ132" t="inlineStr"/>
@@ -38604,7 +38604,7 @@
         </is>
       </c>
       <c r="L137" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="M137" t="inlineStr">
         <is>
@@ -38637,7 +38637,7 @@
         <v>78</v>
       </c>
       <c r="U137" t="n">
-        <v>40.3</v>
+        <v>37.3</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
       </c>
       <c r="AI137" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ137" t="inlineStr">
@@ -38704,7 +38704,7 @@
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Contact streak: 7/19 over last 7 games</t>
         </is>
       </c>
       <c r="AL137" t="inlineStr">
@@ -39980,7 +39980,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -41944,7 +41944,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -42504,7 +42504,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -45559,27 +45559,27 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>607208</t>
+          <t>621020</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Trea Turner</t>
+          <t>Dansby Swanson</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>BOS</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-09-27T18:30:00Z</t>
+          <t>2026-09-27T19:05:00Z</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -45589,17 +45589,17 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Tanner Houck</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>656557</t>
         </is>
       </c>
       <c r="K162" t="inlineStr">
@@ -45622,26 +45622,26 @@
       </c>
       <c r="O162" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P162" t="n">
-        <v>26.3</v>
+        <v>38.2</v>
       </c>
       <c r="Q162" t="n">
-        <v>33.8</v>
+        <v>52</v>
       </c>
       <c r="R162" t="n">
-        <v>52.8</v>
+        <v>41.1</v>
       </c>
       <c r="S162" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T162" t="n">
         <v>50</v>
       </c>
       <c r="U162" t="n">
-        <v>20.9</v>
+        <v>26.4</v>
       </c>
       <c r="V162" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
       </c>
       <c r="X162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y162" t="inlineStr">
@@ -45665,7 +45665,7 @@
       </c>
       <c r="Z162" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
@@ -45673,10 +45673,14 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB162" t="inlineStr"/>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>order MLB 9 vs RotoWire 8</t>
+        </is>
+      </c>
       <c r="AC162" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2025</t>
         </is>
       </c>
       <c r="AD162" t="inlineStr"/>
@@ -45693,27 +45697,27 @@
       </c>
       <c r="AH162" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI162" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ162" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK162" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/23, 1 HR</t>
         </is>
       </c>
       <c r="AL162" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
         </is>
       </c>
       <c r="AM162" t="inlineStr">
@@ -45723,112 +45727,112 @@
       </c>
       <c r="AN162" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>8.62</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>39.93</t>
+          <t>42.83</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>88.67</t>
+          <t>89.73</t>
         </is>
       </c>
       <c r="AQ162" t="inlineStr">
         <is>
-          <t>99.2398</t>
+          <t>99.9083</t>
         </is>
       </c>
       <c r="AR162" t="inlineStr">
         <is>
-          <t>0.3764</t>
+          <t>0.4098</t>
         </is>
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>0.1267</t>
+          <t>0.1757</t>
         </is>
       </c>
       <c r="AT162" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3149</t>
         </is>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>71.45</t>
+          <t>71.32</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>18.65</t>
+          <t>8.61</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>35.38</t>
+          <t>47.83</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>29.19</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>17.8</t>
+          <t>20.5</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>0.1418</t>
+          <t>0.1821</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>6.79</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>33.1</t>
+          <t>46.3</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>87.32</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="BD162" t="inlineStr">
         <is>
-          <t>0.4093</t>
+          <t>0.491</t>
         </is>
       </c>
       <c r="BE162" t="inlineStr">
         <is>
-          <t>0.1495</t>
+          <t>0.199</t>
         </is>
       </c>
       <c r="BF162" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>21.5</t>
         </is>
       </c>
       <c r="BG162" t="inlineStr">
         <is>
-          <t>In From RF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH162" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI162" t="inlineStr">
         <is>
-          <t>Citizens Bank Park</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ162" t="inlineStr"/>
@@ -45839,27 +45843,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>621020</t>
+          <t>607208</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Dansby Swanson</t>
+          <t>Trea Turner</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>BOS</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-09-27T19:05:00Z</t>
+          <t>2026-09-27T18:30:00Z</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -45869,17 +45873,17 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Tanner Houck</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>656557</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
@@ -45888,7 +45892,7 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="M163" t="inlineStr">
         <is>
@@ -45902,26 +45906,26 @@
       </c>
       <c r="O163" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P163" t="n">
-        <v>38.2</v>
+        <v>26.3</v>
       </c>
       <c r="Q163" t="n">
-        <v>52</v>
+        <v>33.8</v>
       </c>
       <c r="R163" t="n">
-        <v>41.1</v>
+        <v>52.8</v>
       </c>
       <c r="S163" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T163" t="n">
         <v>50</v>
       </c>
       <c r="U163" t="n">
-        <v>26.4</v>
+        <v>19.5</v>
       </c>
       <c r="V163" t="inlineStr">
         <is>
@@ -45935,7 +45939,7 @@
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
@@ -45945,7 +45949,7 @@
       </c>
       <c r="Z163" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
@@ -45953,14 +45957,10 @@
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr"/>
@@ -45977,27 +45977,27 @@
       </c>
       <c r="AH163" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI163" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/23, 1 HR</t>
+          <t>Last 7 games: 7/28, 0 HR</t>
         </is>
       </c>
       <c r="AL163" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 10.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.8% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
@@ -46007,112 +46007,112 @@
       </c>
       <c r="AN163" t="inlineStr">
         <is>
-          <t>8.62</t>
+          <t>5.94</t>
         </is>
       </c>
       <c r="AO163" t="inlineStr">
         <is>
-          <t>42.83</t>
+          <t>39.93</t>
         </is>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
-          <t>89.73</t>
+          <t>88.67</t>
         </is>
       </c>
       <c r="AQ163" t="inlineStr">
         <is>
-          <t>99.9083</t>
+          <t>99.2398</t>
         </is>
       </c>
       <c r="AR163" t="inlineStr">
         <is>
-          <t>0.4098</t>
+          <t>0.3764</t>
         </is>
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>0.1757</t>
+          <t>0.1267</t>
         </is>
       </c>
       <c r="AT163" t="inlineStr">
         <is>
-          <t>0.3149</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU163" t="inlineStr">
         <is>
-          <t>71.32</t>
+          <t>71.45</t>
         </is>
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>18.65</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>47.83</t>
+          <t>35.38</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>29.19</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>20.5</t>
+          <t>17.8</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>0.1821</t>
+          <t>0.1418</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>6.79</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>46.3</t>
+          <t>33.1</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.32</t>
         </is>
       </c>
       <c r="BD163" t="inlineStr">
         <is>
-          <t>0.491</t>
+          <t>0.4093</t>
         </is>
       </c>
       <c r="BE163" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>0.1495</t>
         </is>
       </c>
       <c r="BF163" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG163" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From RF</t>
         </is>
       </c>
       <c r="BH163" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="BI163" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Citizens Bank Park</t>
         </is>
       </c>
       <c r="BJ163" t="inlineStr"/>
@@ -48948,7 +48948,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -56236,7 +56236,7 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -62510,7 +62510,7 @@
       </c>
       <c r="AI222" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ222" t="inlineStr">
@@ -62520,7 +62520,7 @@
       </c>
       <c r="AK222" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/18, 0 HR</t>
+          <t>Last 7 games: 1/19, 0 HR</t>
         </is>
       </c>
       <c r="AL222" t="inlineStr">
@@ -65813,7 +65813,7 @@
         <v>50</v>
       </c>
       <c r="U234" t="n">
-        <v>14.6</v>
+        <v>13.3</v>
       </c>
       <c r="V234" t="inlineStr">
         <is>
@@ -65874,7 +65874,7 @@
       </c>
       <c r="AI234" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ234" t="inlineStr">
@@ -65884,7 +65884,7 @@
       </c>
       <c r="AK234" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL234" t="inlineStr">
@@ -68840,7 +68840,7 @@
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -72484,7 +72484,7 @@
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -73044,7 +73044,7 @@
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -73604,7 +73604,7 @@
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -74444,7 +74444,7 @@
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -74724,7 +74724,7 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -75004,7 +75004,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Player challenge</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -79031,7 +79031,7 @@
         <v>80</v>
       </c>
       <c r="U10" t="n">
-        <v>10.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -79088,7 +79088,7 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -79098,7 +79098,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 0 HR</t>
+          <t>Last 7 games: 4/22, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1040,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1600,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -2712,7 +2712,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -8540,7 +8540,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -9652,7 +9652,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11320,7 +11320,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -12992,7 +12992,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -14104,7 +14104,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14384,7 +14384,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -16052,7 +16052,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -16612,7 +16612,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -16892,7 +16892,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -19668,7 +19668,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -21382,7 +21382,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -23054,7 +23054,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -24442,7 +24442,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -26382,7 +26382,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1068,7 +1068,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1092,7 +1092,7 @@
         <v>37.3</v>
       </c>
       <c r="R3" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>33.9</v>
       </c>
       <c r="R7" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2390,12 +2390,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>33.9</v>
       </c>
       <c r="R8" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2740,7 +2740,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>33.9</v>
       </c>
       <c r="R9" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -2950,12 +2950,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -3296,7 +3296,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>37.3</v>
       </c>
       <c r="R11" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S11" t="n">
         <v>96.59999999999999</v>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -3576,7 +3576,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>33.9</v>
       </c>
       <c r="R12" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -3786,12 +3786,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>37.3</v>
       </c>
       <c r="R23" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S23" t="n">
         <v>76.2</v>
@@ -6850,12 +6850,12 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -8592,7 +8592,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>46.6</v>
+        <v>46.7</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>37.3</v>
       </c>
       <c r="R30" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S30" t="n">
         <v>86.40000000000001</v>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="BG30" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -9424,7 +9424,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9448,7 +9448,7 @@
         <v>37.3</v>
       </c>
       <c r="R33" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S33" t="n">
         <v>94.90000000000001</v>
@@ -9634,12 +9634,12 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -9704,7 +9704,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>46.1</v>
+        <v>46.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>33.9</v>
       </c>
       <c r="R34" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S34" t="n">
         <v>64.3</v>
@@ -9914,12 +9914,12 @@
       </c>
       <c r="BG34" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -11096,7 +11096,7 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -11120,7 +11120,7 @@
         <v>37.3</v>
       </c>
       <c r="R39" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S39" t="n">
         <v>93.2</v>
@@ -11306,12 +11306,12 @@
       </c>
       <c r="BG39" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
@@ -11652,7 +11652,7 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>44</v>
+        <v>44.1</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -11676,7 +11676,7 @@
         <v>37.3</v>
       </c>
       <c r="R41" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S41" t="n">
         <v>64.3</v>
@@ -11862,12 +11862,12 @@
       </c>
       <c r="BG41" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI41" t="inlineStr">
@@ -13608,7 +13608,7 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>41.9</v>
+        <v>42</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>33.9</v>
       </c>
       <c r="R48" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S48" t="n">
         <v>52.4</v>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="BG48" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI48" t="inlineStr">
@@ -14188,7 +14188,7 @@
         <v>33.9</v>
       </c>
       <c r="R50" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S50" t="n">
         <v>86.40000000000001</v>
@@ -14374,12 +14374,12 @@
       </c>
       <c r="BG50" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI50" t="inlineStr">
@@ -14679,52 +14679,52 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HOU</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-30T21:00:00Z</t>
+          <t>2026-09-30T18:00:00Z</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Warmup</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Hunter Brown</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>686613</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -14742,23 +14742,23 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P52" t="n">
-        <v>49.9</v>
+        <v>15.3</v>
       </c>
       <c r="Q52" t="n">
-        <v>20.7</v>
+        <v>32.1</v>
       </c>
       <c r="R52" t="n">
-        <v>41.6</v>
+        <v>53.9</v>
       </c>
       <c r="S52" t="n">
-        <v>44.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T52" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -14775,7 +14775,7 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -14813,7 +14813,7 @@
       </c>
       <c r="AH52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI52" t="inlineStr">
@@ -14828,12 +14828,12 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL52" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 12.8 HR allowed</t>
+          <t>switch hitter; pitcher baseline 7.0% barrel, 16.9 HR allowed</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
@@ -14843,112 +14843,112 @@
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ52" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR52" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>70.93</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>6.96</t>
         </is>
       </c>
       <c r="BB52" t="inlineStr">
         <is>
-          <t>35.49</t>
+          <t>41.34</t>
         </is>
       </c>
       <c r="BC52" t="inlineStr">
         <is>
-          <t>86.17</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BD52" t="inlineStr">
         <is>
-          <t>0.3208</t>
+          <t>0.3597</t>
         </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
-          <t>0.1164</t>
+          <t>0.127</t>
         </is>
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>22.11</t>
+          <t>16.9</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>Daikin Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr"/>
@@ -14959,56 +14959,56 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>HOU</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-30T18:00:00Z</t>
+          <t>2026-09-30T21:00:00Z</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Hunter Brown</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>686613</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -15022,23 +15022,23 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P53" t="n">
-        <v>15.3</v>
+        <v>49.9</v>
       </c>
       <c r="Q53" t="n">
-        <v>32.1</v>
+        <v>20.7</v>
       </c>
       <c r="R53" t="n">
-        <v>53.4</v>
+        <v>41.6</v>
       </c>
       <c r="S53" t="n">
-        <v>96.59999999999999</v>
+        <v>44.8</v>
       </c>
       <c r="T53" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U53" t="n">
         <v>0</v>
@@ -15055,7 +15055,7 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
@@ -15093,7 +15093,7 @@
       </c>
       <c r="AH53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI53" t="inlineStr">
@@ -15108,12 +15108,12 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL53" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 7.0% barrel, 16.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 12.8 HR allowed</t>
         </is>
       </c>
       <c r="AM53" t="inlineStr">
@@ -15123,112 +15123,112 @@
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ53" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR53" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS53" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>70.93</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>6.96</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>41.34</t>
+          <t>35.49</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>86.17</t>
         </is>
       </c>
       <c r="BD53" t="inlineStr">
         <is>
-          <t>0.3597</t>
+          <t>0.3208</t>
         </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>0.1164</t>
         </is>
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>22.11</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>73</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Daikin Park</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr"/>
@@ -16396,7 +16396,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16420,7 +16420,7 @@
         <v>37.3</v>
       </c>
       <c r="R58" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S58" t="n">
         <v>44.8</v>
@@ -16606,12 +16606,12 @@
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
@@ -17252,7 +17252,7 @@
         <v>37.3</v>
       </c>
       <c r="R61" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S61" t="n">
         <v>52.4</v>
@@ -17438,12 +17438,12 @@
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
@@ -19448,7 +19448,7 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>33.9</v>
       </c>
       <c r="R69" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S69" t="n">
         <v>44.8</v>
@@ -19658,12 +19658,12 @@
       </c>
       <c r="BG69" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI69" t="inlineStr">
@@ -21446,7 +21446,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>62.7</v>
+        <v>62.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>37.3</v>
       </c>
       <c r="R3" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -21656,12 +21656,12 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -22582,7 +22582,7 @@
         <v>33.9</v>
       </c>
       <c r="R7" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -22768,12 +22768,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -22838,7 +22838,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.7</v>
+        <v>56.8</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>33.9</v>
       </c>
       <c r="R8" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -23048,12 +23048,12 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -23118,7 +23118,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>56.1</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -23142,7 +23142,7 @@
         <v>33.9</v>
       </c>
       <c r="R9" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S9" t="n">
         <v>100</v>
@@ -23328,12 +23328,12 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -23674,7 +23674,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>55.5</v>
+        <v>55.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>37.3</v>
       </c>
       <c r="R11" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S11" t="n">
         <v>96.59999999999999</v>
@@ -23884,12 +23884,12 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -23954,7 +23954,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>53.9</v>
+        <v>54</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23978,7 +23978,7 @@
         <v>33.9</v>
       </c>
       <c r="R12" t="n">
-        <v>53.4</v>
+        <v>53.9</v>
       </c>
       <c r="S12" t="n">
         <v>76.2</v>
@@ -24164,12 +24164,12 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>Calm</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1044,7 +1044,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -9400,7 +9400,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9680,7 +9680,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -11072,7 +11072,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -11628,7 +11628,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -13584,7 +13584,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -16372,7 +16372,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -17204,7 +17204,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -21422,7 +21422,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -22534,7 +22534,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22814,7 +22814,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -23094,7 +23094,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -23650,7 +23650,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -23930,7 +23930,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Warmup</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1066,34 +1066,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1350,34 +1346,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1874,34 +1866,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2158,34 +2146,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2442,34 +2426,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2726,34 +2706,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3010,34 +2986,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3294,34 +3266,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3818,34 +3786,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4102,34 +4066,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5934,34 +5894,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6458,34 +6414,30 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6982,34 +6934,30 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7818,34 +7766,30 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8340,28 +8284,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr"/>
-      <c r="X30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8616,28 +8564,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr"/>
-      <c r="X31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="Y31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8892,28 +8844,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="Y32" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9170,34 +9126,30 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11124,34 +11076,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11408,34 +11356,30 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11932,34 +11876,30 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12216,34 +12156,30 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12500,34 +12436,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12784,34 +12716,30 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13068,34 +12996,30 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13352,34 +13276,30 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13876,34 +13796,30 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed</t>
-        </is>
-      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14160,34 +14076,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15992,34 +15904,30 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 9</t>
-        </is>
-      </c>
+      <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -994,12 +994,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -1101,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -1348,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1362,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1375,7 +1371,7 @@
         <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1385,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1608,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1632,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1656,7 +1648,7 @@
         <v>54.7</v>
       </c>
       <c r="R5" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -1842,12 +1834,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -1888,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1912,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1936,7 +1928,7 @@
         <v>40.1</v>
       </c>
       <c r="R6" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -2122,12 +2114,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2168,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2192,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2216,7 +2208,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -2402,12 +2394,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3008,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3032,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3056,7 +3048,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -3242,12 +3234,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -3268,7 +3260,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3339,7 +3331,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3349,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3852,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3876,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3900,7 +3888,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -4086,12 +4074,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -4132,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4156,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4180,7 +4168,7 @@
         <v>40.1</v>
       </c>
       <c r="R14" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -4366,12 +4354,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -4412,7 +4400,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4436,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4460,7 +4448,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -4646,12 +4634,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -4667,24 +4655,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-06T00:00:00Z</t>
@@ -4697,17 +4685,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4716,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4730,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="Q16" t="n">
         <v>33.4</v>
@@ -4743,13 +4731,13 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>14.6</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4763,7 +4751,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4801,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4816,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4831,97 +4819,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4248</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3093</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1302</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4947,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4977,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -4996,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5010,11 +4998,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.2</v>
+        <v>30.5</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -5023,49 +5011,45 @@
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>14.6</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5085,22 +5069,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -5115,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4248</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3093</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5231,27 +5215,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05T21:00:00Z</t>
+          <t>2026-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -5261,26 +5245,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5294,26 +5278,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>25.8</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.1</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -5327,7 +5311,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -5348,7 +5332,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5365,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5380,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5395,112 +5379,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1302</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -5511,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5541,7 +5525,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5560,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5574,11 +5558,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>30.5</v>
+        <v>47.4</v>
       </c>
       <c r="Q19" t="n">
         <v>33.4</v>
@@ -5587,49 +5571,45 @@
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5649,22 +5629,22 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -5679,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>100.7514</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4497</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>70.79</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -5795,56 +5775,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06T00:00:00Z</t>
+          <t>2026-10-05T21:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5858,65 +5838,61 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>47.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>33.4</v>
+        <v>38.1</v>
       </c>
       <c r="R20" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S20" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -5933,12 +5909,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5948,12 +5924,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5963,112 +5939,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.7514</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4497</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6104,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6128,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6152,7 +6128,7 @@
         <v>53.5</v>
       </c>
       <c r="R21" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S21" t="n">
         <v>64.3</v>
@@ -6338,12 +6314,12 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6384,7 +6360,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -6408,7 +6384,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>44.8</v>
+        <v>44.4</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6432,7 +6408,7 @@
         <v>40.1</v>
       </c>
       <c r="R22" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S22" t="n">
         <v>86.40000000000001</v>
@@ -6618,12 +6594,12 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -6688,7 +6664,7 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>43.8</v>
+        <v>44.4</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6702,7 +6678,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P23" t="n">
@@ -6715,7 +6691,7 @@
         <v>41.1</v>
       </c>
       <c r="S23" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T23" t="n">
         <v>80</v>
@@ -6725,39 +6701,35 @@
       </c>
       <c r="V23" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6972,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>43.4</v>
+        <v>44</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6986,7 +6958,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
@@ -6999,7 +6971,7 @@
         <v>41.1</v>
       </c>
       <c r="S24" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T24" t="n">
         <v>80</v>
@@ -7009,39 +6981,35 @@
       </c>
       <c r="V24" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7212,7 +7180,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>George Lombard</t>
+          <t>George Lombard Jr.</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -7256,7 +7224,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>43.1</v>
+        <v>43.7</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7270,7 +7238,7 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P25" t="n">
@@ -7283,7 +7251,7 @@
         <v>41.1</v>
       </c>
       <c r="S25" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T25" t="n">
         <v>50</v>
@@ -7293,39 +7261,35 @@
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -7516,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7540,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>42.4</v>
+        <v>42.1</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7564,7 +7528,7 @@
         <v>38.1</v>
       </c>
       <c r="R26" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S26" t="n">
         <v>52.4</v>
@@ -7750,12 +7714,12 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7796,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7820,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7844,7 +7808,7 @@
         <v>38.1</v>
       </c>
       <c r="R27" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S27" t="n">
         <v>76.2</v>
@@ -8030,12 +7994,12 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8076,7 +8040,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -8100,7 +8064,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>41.8</v>
+        <v>41.4</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8124,7 +8088,7 @@
         <v>54.7</v>
       </c>
       <c r="R28" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S28" t="n">
         <v>76.2</v>
@@ -8310,12 +8274,12 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -8356,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8380,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8404,7 +8368,7 @@
         <v>54.7</v>
       </c>
       <c r="R29" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S29" t="n">
         <v>52.4</v>
@@ -8590,12 +8554,12 @@
       </c>
       <c r="BG29" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8916,7 +8880,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8940,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>36.7</v>
+        <v>36.4</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8964,7 +8928,7 @@
         <v>40.1</v>
       </c>
       <c r="R31" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S31" t="n">
         <v>64.3</v>
@@ -9150,12 +9114,12 @@
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -9171,12 +9135,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -9196,12 +9160,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -9220,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>36.4</v>
+        <v>36.1</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9234,26 +9198,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>2.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q32" t="n">
-        <v>40.1</v>
+        <v>38.1</v>
       </c>
       <c r="R32" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S32" t="n">
-        <v>93.2</v>
+        <v>44.8</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U32" t="n">
-        <v>43.1</v>
+        <v>72.7</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9267,7 +9231,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9305,27 +9269,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9335,67 +9299,67 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>92.8164</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3233</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
@@ -9430,12 +9394,12 @@
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -9451,12 +9415,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -9476,12 +9440,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -9500,7 +9464,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>36.4</v>
+        <v>36</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9514,26 +9478,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Platoon Edge, Hot Hitter/Streak</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>13.7</v>
+        <v>2.9</v>
       </c>
       <c r="Q33" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="R33" t="n">
         <v>38.1</v>
       </c>
-      <c r="R33" t="n">
-        <v>40.6</v>
-      </c>
       <c r="S33" t="n">
-        <v>44.8</v>
+        <v>93.2</v>
       </c>
       <c r="T33" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>72.7</v>
+        <v>43.1</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9547,7 +9511,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9585,27 +9549,27 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9615,67 +9579,67 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>92.8164</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.3233</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
@@ -9710,12 +9674,12 @@
       </c>
       <c r="BG33" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -11202,7 +11166,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -11226,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>69.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11250,7 +11214,7 @@
         <v>54.7</v>
       </c>
       <c r="R2" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S2" t="n">
         <v>94.90000000000001</v>
@@ -11436,12 +11400,12 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -11506,7 +11470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.3</v>
+        <v>59</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11520,7 +11484,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -11533,7 +11497,7 @@
         <v>41.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>80</v>
@@ -11543,39 +11507,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -11790,7 +11750,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>57.9</v>
+        <v>58.5</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -11804,7 +11764,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -11817,7 +11777,7 @@
         <v>41.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -11827,39 +11787,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12050,7 +12006,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -12074,7 +12030,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>55.8</v>
+        <v>55.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12098,7 +12054,7 @@
         <v>54.7</v>
       </c>
       <c r="R5" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S5" t="n">
         <v>96.59999999999999</v>
@@ -12284,12 +12240,12 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -12330,7 +12286,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -12354,7 +12310,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>55.4</v>
+        <v>55</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12378,7 +12334,7 @@
         <v>40.1</v>
       </c>
       <c r="R6" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S6" t="n">
         <v>94.90000000000001</v>
@@ -12564,12 +12520,12 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -12610,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12634,7 +12590,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>54.8</v>
+        <v>54.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12658,7 +12614,7 @@
         <v>54.7</v>
       </c>
       <c r="R7" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -12844,12 +12800,12 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -13450,7 +13406,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13474,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>51.8</v>
+        <v>51.4</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13498,7 +13454,7 @@
         <v>54.7</v>
       </c>
       <c r="R10" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S10" t="n">
         <v>86.40000000000001</v>
@@ -13684,12 +13640,12 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -13710,7 +13666,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Luis Garcia</t>
+          <t>Luis García Jr.</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -13754,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>50.6</v>
+        <v>51.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13768,7 +13724,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -13781,7 +13737,7 @@
         <v>41.1</v>
       </c>
       <c r="S11" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -13791,39 +13747,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14294,7 +14246,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -14318,7 +14270,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>49.1</v>
+        <v>48.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14342,7 +14294,7 @@
         <v>54.7</v>
       </c>
       <c r="R13" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S13" t="n">
         <v>44.8</v>
@@ -14528,12 +14480,12 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -14574,7 +14526,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -14598,7 +14550,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.1</v>
+        <v>47.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14622,7 +14574,7 @@
         <v>40.1</v>
       </c>
       <c r="R14" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S14" t="n">
         <v>96.59999999999999</v>
@@ -14808,12 +14760,12 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -14854,7 +14806,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -14878,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47.8</v>
+        <v>47.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14902,7 +14854,7 @@
         <v>54.7</v>
       </c>
       <c r="R15" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S15" t="n">
         <v>93.2</v>
@@ -15088,12 +15040,12 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -15109,24 +15061,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yandy Díaz</t>
+          <t>Jazz Chisholm Jr.</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>NYY</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>NYY</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-06T00:00:00Z</t>
@@ -15139,17 +15091,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Cam Schlittler</t>
+          <t>Freddy Peralta</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>693645</t>
+          <t>642547</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -15158,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.3</v>
+        <v>46.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15172,11 +15124,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>41</v>
+        <v>42.2</v>
       </c>
       <c r="Q16" t="n">
         <v>33.4</v>
@@ -15185,13 +15137,13 @@
         <v>41.1</v>
       </c>
       <c r="S16" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T16" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>14.6</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15205,7 +15157,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -15243,12 +15195,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -15258,12 +15210,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -15273,97 +15225,97 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.4248</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3093</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>37.37</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>7.57</t>
+          <t>6.85</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>38.87</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>88.58</t>
+          <t>87.72</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3434</t>
+          <t>0.368</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1302</t>
+          <t>0.1417</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>25.76</t>
+          <t>28.41</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -15389,12 +15341,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -15419,7 +15371,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -15438,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15452,11 +15404,11 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>42.2</v>
+        <v>30.5</v>
       </c>
       <c r="Q17" t="n">
         <v>33.4</v>
@@ -15465,49 +15417,45 @@
         <v>41.1</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>14.6</v>
+        <v>18.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15527,22 +15475,22 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
@@ -15557,67 +15505,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.4248</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3093</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -15673,27 +15621,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-10-05T21:00:00Z</t>
+          <t>2026-10-06T00:00:00Z</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -15703,26 +15651,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Anthony Kay</t>
+          <t>Cam Schlittler</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>641743</t>
+          <t>693645</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45.7</v>
+        <v>46.3</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15736,26 +15684,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>25.8</v>
+        <v>41</v>
       </c>
       <c r="Q18" t="n">
-        <v>38.1</v>
+        <v>33.4</v>
       </c>
       <c r="R18" t="n">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="S18" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>23.4</v>
+        <v>20.9</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -15769,7 +15717,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -15790,7 +15738,7 @@
       <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -15807,12 +15755,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -15822,12 +15770,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.6% barrel, 13.6 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -15837,112 +15785,112 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1617</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>8.1</t>
+          <t>7.57</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>38.87</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.58</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.419</t>
+          <t>0.3434</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.153</t>
+          <t>0.1302</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>22.0</t>
+          <t>25.76</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>None</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>Progressive Field</t>
+          <t>Tropicana Field</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr"/>
@@ -15953,12 +15901,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -15983,7 +15931,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -16002,7 +15950,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>45.7</v>
+        <v>46</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -16016,11 +15964,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>30.5</v>
+        <v>47.4</v>
       </c>
       <c r="Q19" t="n">
         <v>33.4</v>
@@ -16029,49 +15977,45 @@
         <v>41.1</v>
       </c>
       <c r="S19" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T19" t="n">
         <v>80</v>
       </c>
       <c r="U19" t="n">
-        <v>18.3</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16091,22 +16035,22 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -16121,67 +16065,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>100.7514</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4497</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>70.79</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1975</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -16237,56 +16181,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-06T00:00:00Z</t>
+          <t>2026-10-05T21:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Freddy Peralta</t>
+          <t>Anthony Kay</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>642547</t>
+          <t>641743</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>45.4</v>
+        <v>45.3</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16300,65 +16244,61 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>47.4</v>
+        <v>25.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>33.4</v>
+        <v>38.1</v>
       </c>
       <c r="R20" t="n">
-        <v>41.1</v>
+        <v>38.1</v>
       </c>
       <c r="S20" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD20" t="inlineStr"/>
@@ -16375,12 +16315,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -16390,12 +16330,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.8% barrel, 22.4 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.1% barrel, 21.0 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -16405,112 +16345,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.7514</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4497</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6.85</t>
+          <t>8.1</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>87.72</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>0.419</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1417</t>
+          <t>0.153</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Tropicana Field</t>
+          <t>Progressive Field</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -16546,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -16570,7 +16510,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16594,7 +16534,7 @@
         <v>53.5</v>
       </c>
       <c r="R21" t="n">
-        <v>40.6</v>
+        <v>38.1</v>
       </c>
       <c r="S21" t="n">
         <v>64.3</v>
@@ -16780,12 +16720,12 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>In From CF</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>61</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1045,7 +1045,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1091,7 +1091,7 @@
         <v>43.9</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1101,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1855,56 +1851,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1918,62 +1914,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>57.9</v>
+        <v>51.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>74.2</v>
+        <v>100</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1998,129 +1990,137 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2131,56 +2131,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2194,26 +2194,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>51.1</v>
+        <v>57.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R7" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>74.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2274,137 +2274,129 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -3523,56 +3515,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3586,62 +3578,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3661,134 +3649,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -3799,24 +3795,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-07T01:30:00Z</t>
@@ -3829,17 +3825,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3862,26 +3858,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.2</v>
+        <v>48.2</v>
       </c>
       <c r="R13" t="n">
         <v>22.6</v>
       </c>
       <c r="S13" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>41.7</v>
+        <v>13.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3895,7 +3891,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3937,127 +3933,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1911</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3358</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -4075,47 +4071,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4124,7 +4120,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4138,58 +4134,62 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.6</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S14" t="n">
-        <v>86.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>32</v>
+        <v>41.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4209,27 +4209,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4239,112 +4239,104 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>101.7846</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3358</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4355,47 +4347,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4404,7 +4396,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>48.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4418,62 +4410,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>39.5</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R15" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>37.8</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4493,134 +4481,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4631,12 +4627,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4661,7 +4657,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4680,7 +4676,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4694,11 +4690,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q16" t="n">
         <v>48.2</v>
@@ -4707,13 +4703,13 @@
         <v>22.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4727,7 +4723,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4769,7 +4765,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -4784,12 +4780,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4799,67 +4795,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4907,56 +4903,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4970,26 +4966,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.7</v>
+        <v>38.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>48.3</v>
+        <v>25.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -5003,7 +4999,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -5045,12 +5041,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5060,127 +5056,119 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5191,24 +5179,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -5221,26 +5209,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5254,62 +5242,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>32.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
         <v>43.9</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>48.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5334,22 +5318,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5359,97 +5343,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>102.7231</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>59.43</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -5475,24 +5459,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -5505,26 +5489,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5538,26 +5522,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>53.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>24</v>
       </c>
       <c r="R19" t="n">
         <v>43.9</v>
       </c>
       <c r="S19" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>48.7</v>
+        <v>29.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -5571,7 +5555,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -5614,22 +5598,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5639,97 +5623,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>102.7231</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -5755,56 +5739,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>44.1</v>
+        <v>44.5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5818,62 +5802,58 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>40.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S20" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5893,12 +5873,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -5908,12 +5888,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -5923,104 +5903,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.8422</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -6031,32 +6019,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6066,21 +6054,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>43.7</v>
+        <v>44.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6094,26 +6082,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R21" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S21" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>26.1</v>
+        <v>5.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -6169,12 +6157,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -6184,12 +6172,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -6199,112 +6187,104 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>100.8422</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1709</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>
@@ -6315,12 +6295,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -6345,7 +6325,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -6364,7 +6344,7 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>43.4</v>
+        <v>43.7</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6378,11 +6358,11 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>39.3</v>
+        <v>36.4</v>
       </c>
       <c r="Q22" t="n">
         <v>24</v>
@@ -6391,49 +6371,45 @@
         <v>43.9</v>
       </c>
       <c r="S22" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T22" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6458,22 +6434,22 @@
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -6483,67 +6459,67 @@
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
@@ -6599,56 +6575,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>681624</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Andy Pages</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6662,26 +6638,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>36.4</v>
+        <v>28.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R23" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S23" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T23" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>66</v>
+        <v>52.8</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6695,7 +6671,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6737,27 +6713,27 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -6767,112 +6743,104 @@
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>40.77</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>88.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>99.6965</t>
+          <t>100.2761</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.4378</t>
+          <t>0.3871</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.1686</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.3349</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>72.85</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>26.4</t>
+          <t>27.66</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>38.53</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>29.0</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.1925</t>
+          <t>0.1175</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr"/>
+      <c r="BH23" t="inlineStr"/>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6883,12 +6851,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>806956</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Ethan Salas</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -6913,7 +6881,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -6932,7 +6900,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>41.1</v>
+        <v>39.5</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6946,11 +6914,11 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P24" t="n">
-        <v>28.7</v>
+        <v>22.6</v>
       </c>
       <c r="Q24" t="n">
         <v>46.2</v>
@@ -6959,13 +6927,13 @@
         <v>22.6</v>
       </c>
       <c r="S24" t="n">
-        <v>71.7</v>
+        <v>59.8</v>
       </c>
       <c r="T24" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U24" t="n">
-        <v>52.8</v>
+        <v>40.3</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -6979,7 +6947,7 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -7004,7 +6972,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr"/>
@@ -7026,92 +6994,92 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>100.2761</t>
+          <t>98.8542</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>0.3871</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>0.1175</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr">
@@ -7159,32 +7127,32 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>806956</t>
+          <t>669221</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ethan Salas</t>
+          <t>Sean Murphy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -7194,12 +7162,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -7208,7 +7176,7 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>39.5</v>
+        <v>37.9</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -7222,65 +7190,61 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>22.6</v>
+        <v>34</v>
       </c>
       <c r="Q25" t="n">
-        <v>46.2</v>
+        <v>26.6</v>
       </c>
       <c r="R25" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S25" t="n">
-        <v>59.8</v>
+        <v>64.3</v>
       </c>
       <c r="T25" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
-        <v>40.3</v>
+        <v>3.4</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr"/>
@@ -7297,12 +7261,12 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ25" t="inlineStr">
@@ -7312,119 +7276,127 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 3/21, 0 HR</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>9.76</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>41.7</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>88.19</t>
         </is>
       </c>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>98.8542</t>
+          <t>101.2803</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.3548</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.2853</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>72.6</t>
         </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>29.59</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>49.12</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>25.37</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>6.9</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.1456</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG25" t="inlineStr"/>
-      <c r="BH25" t="inlineStr"/>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr"/>
@@ -7435,12 +7407,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>571771</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Enrique Hernández</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -7465,7 +7437,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -7484,7 +7456,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>38.7</v>
+        <v>37.8</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7498,11 +7470,11 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>33.9</v>
+        <v>32.6</v>
       </c>
       <c r="Q26" t="n">
         <v>24</v>
@@ -7511,49 +7483,45 @@
         <v>43.9</v>
       </c>
       <c r="S26" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T26" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U26" t="n">
-        <v>12</v>
+        <v>28.5</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7573,27 +7541,27 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Last 7 games: 3/16, 1 HR</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
@@ -7603,67 +7571,67 @@
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>8.52</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>39.49</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>89.39</t>
         </is>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>99.9102</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.3751</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.2814</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>70.82</t>
         </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>14.73</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>25.54</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>5.8</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.1735</t>
         </is>
       </c>
       <c r="BA26" t="inlineStr">
@@ -7719,12 +7687,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>669221</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sean Murphy</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -7749,7 +7717,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -7768,7 +7736,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>37.9</v>
+        <v>37.6</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7782,26 +7750,26 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>No major boost</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P27" t="n">
-        <v>34</v>
+        <v>15.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>26.6</v>
+        <v>24.6</v>
       </c>
       <c r="R27" t="n">
         <v>43.9</v>
       </c>
       <c r="S27" t="n">
-        <v>64.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -7815,7 +7783,7 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
@@ -7858,7 +7826,7 @@
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -7868,12 +7836,12 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/21, 0 HR</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
@@ -7883,67 +7851,67 @@
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>9.76</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>41.7</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>88.19</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>101.2803</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>0.3548</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.2853</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
         <is>
-          <t>72.6</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>49.12</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>25.37</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>0.1456</t>
+          <t>0.146</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr">
@@ -7999,47 +7967,47 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>687957</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Dustin Harris</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -8048,7 +8016,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>37.6</v>
+        <v>37.3</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -8062,58 +8030,62 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P28" t="n">
-        <v>15.3</v>
+        <v>4.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>24.6</v>
+        <v>46.2</v>
       </c>
       <c r="R28" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S28" t="n">
-        <v>94.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T28" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>16.6</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W28" t="inlineStr">
+      <c r="Z28" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8133,12 +8105,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ28" t="inlineStr">
@@ -8148,12 +8120,12 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
@@ -8163,112 +8135,104 @@
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>85.71</t>
         </is>
       </c>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>95.2049</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3345</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.0841</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.2891</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>66.89</t>
         </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.1</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>21.42</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>0.108</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="BG28" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG28" t="inlineStr"/>
+      <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr"/>
@@ -8279,56 +8243,56 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>687957</t>
+          <t>500743</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Dustin Harris</t>
+          <t>Miguel Rojas</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L29" t="n">
-        <v>37.3</v>
+        <v>36.4</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8342,62 +8306,58 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>4.2</v>
+        <v>17.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S29" t="n">
-        <v>95.5</v>
+        <v>76.2</v>
       </c>
       <c r="T29" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U29" t="n">
-        <v>16.6</v>
+        <v>14.1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8417,12 +8377,12 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AJ29" t="inlineStr">
@@ -8432,12 +8392,12 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 3/14, 0 HR</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM29" t="inlineStr">
@@ -8447,104 +8407,112 @@
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="AQ29" t="inlineStr">
         <is>
-          <t>95.2049</t>
+          <t>98.0168</t>
         </is>
       </c>
       <c r="AR29" t="inlineStr">
         <is>
-          <t>0.3345</t>
+          <t>0.3776</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
-          <t>0.0841</t>
+          <t>0.1083</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>0.2891</t>
+          <t>0.3039</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
         <is>
-          <t>66.89</t>
+          <t>68.8</t>
         </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>5.28</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>21.42</t>
+          <t>23.17</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>0.1273</t>
         </is>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG29" t="inlineStr"/>
-      <c r="BH29" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG29" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI29" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ29" t="inlineStr"/>
@@ -8555,56 +8523,56 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>630105</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Jake Cronenworth</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L30" t="n">
-        <v>35.6</v>
+        <v>36</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8618,62 +8586,58 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>16.4</v>
+        <v>33.9</v>
       </c>
       <c r="Q30" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S30" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T30" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U30" t="n">
-        <v>57.8</v>
+        <v>12</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8693,27 +8657,27 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8723,104 +8687,112 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>32.49</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>87.59</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>97.7612</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.3215</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.2882</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>71.25</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>24.61</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>8.2</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1065</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG30" t="inlineStr"/>
-      <c r="BH30" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG30" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI30" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ30" t="inlineStr"/>
@@ -8831,32 +8803,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>669242</t>
+          <t>630105</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Tommy Edman</t>
+          <t>Jake Cronenworth</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -8866,21 +8838,21 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>34.2</v>
+        <v>35.6</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8898,22 +8870,22 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>20.2</v>
+        <v>16.4</v>
       </c>
       <c r="Q31" t="n">
-        <v>22.9</v>
+        <v>46.2</v>
       </c>
       <c r="R31" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S31" t="n">
         <v>40.2</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U31" t="n">
-        <v>60.7</v>
+        <v>57.8</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -8969,12 +8941,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -8989,7 +8961,7 @@
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8999,112 +8971,104 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>34.37</t>
+          <t>32.49</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>87.59</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>98.7457</t>
+          <t>97.7612</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.3662</t>
+          <t>0.3215</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3084</t>
+          <t>0.2882</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>71.25</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>13.58</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>31.96</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>24.61</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>8.2</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1437</t>
+          <t>0.1065</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH31" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr"/>
+      <c r="BH31" t="inlineStr"/>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -11415,7 +11379,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -11434,7 +11398,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55.9</v>
+        <v>55.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11448,7 +11412,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -11461,7 +11425,7 @@
         <v>43.9</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -11471,39 +11435,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12225,56 +12185,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>54.2</v>
+        <v>54.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12288,62 +12248,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>57.9</v>
+        <v>51.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S6" t="n">
-        <v>88.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>74.2</v>
+        <v>100</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -12368,129 +12324,137 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1801</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -12501,56 +12465,56 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>53.9</v>
+        <v>54.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12564,26 +12528,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>51.1</v>
+        <v>57.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R7" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S7" t="n">
-        <v>90.40000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T7" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U7" t="n">
-        <v>100</v>
+        <v>74.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -12597,7 +12561,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -12644,137 +12608,129 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1801</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr"/>
@@ -13893,56 +13849,56 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>49.8</v>
+        <v>50.4</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -13956,62 +13912,58 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R12" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14031,134 +13983,142 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr"/>
@@ -14169,24 +14129,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>592518</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manny Machado</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>SD</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-07T01:30:00Z</t>
@@ -14199,17 +14159,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -14232,26 +14192,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.9</v>
+        <v>47.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>46.2</v>
+        <v>48.2</v>
       </c>
       <c r="R13" t="n">
         <v>22.6</v>
       </c>
       <c r="S13" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>41.7</v>
+        <v>13.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -14265,7 +14225,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -14307,127 +14267,127 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.66</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>45.97</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>90.94</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>101.7846</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4425</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1911</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3358</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>44.79</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>28.71</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>29.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1885</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr"/>
@@ -14445,47 +14405,47 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592518</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Manny Machado</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -14494,7 +14454,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>48.7</v>
+        <v>49.8</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14508,58 +14468,62 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.1</v>
+        <v>47.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>26.6</v>
+        <v>46.2</v>
       </c>
       <c r="R14" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S14" t="n">
-        <v>86.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>32</v>
+        <v>41.7</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14579,27 +14543,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -14609,112 +14573,104 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>10.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>45.97</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>90.94</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>101.7846</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4425</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1911</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3358</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>74.64</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>44.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>28.71</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>29.1</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1885</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14725,47 +14681,47 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14774,7 +14730,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>47</v>
+        <v>48.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14788,62 +14744,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>39.5</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R15" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S15" t="n">
-        <v>90.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>37.8</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14863,134 +14815,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>34.35</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -15001,12 +14961,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -15031,7 +14991,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -15050,7 +15010,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>46.1</v>
+        <v>47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15064,11 +15024,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>38.2</v>
+        <v>39.5</v>
       </c>
       <c r="Q16" t="n">
         <v>48.2</v>
@@ -15077,13 +15037,13 @@
         <v>22.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>25.3</v>
+        <v>37.8</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -15097,7 +15057,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -15139,7 +15099,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -15154,12 +15114,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -15169,67 +15129,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -15277,56 +15237,56 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>45.2</v>
+        <v>46.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15340,26 +15300,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.7</v>
+        <v>38.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R17" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>71.7</v>
       </c>
       <c r="T17" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>48.3</v>
+        <v>25.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -15373,7 +15333,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -15415,12 +15375,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -15430,127 +15390,119 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>34.35</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -15561,24 +15513,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>663586</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Austin Riley</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -15591,26 +15543,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>45</v>
+        <v>44.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -15624,62 +15576,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>32.7</v>
+        <v>53.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>24</v>
+        <v>26.6</v>
       </c>
       <c r="R18" t="n">
         <v>43.9</v>
       </c>
       <c r="S18" t="n">
-        <v>95.5</v>
+        <v>52.4</v>
       </c>
       <c r="T18" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>29.2</v>
+        <v>48.7</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15704,22 +15652,22 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -15729,97 +15677,97 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>46.07</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>102.7231</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4188</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1956</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3083</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>75.83</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>59.43</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>30.87</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>18.1</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1519</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG18" t="inlineStr">
@@ -15845,24 +15793,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>663586</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Austin Riley</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>2026-10-06T22:00:00Z</t>
@@ -15875,26 +15823,26 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -15908,26 +15856,26 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>53.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>26.6</v>
+        <v>24</v>
       </c>
       <c r="R19" t="n">
         <v>43.9</v>
       </c>
       <c r="S19" t="n">
-        <v>52.4</v>
+        <v>93.2</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>48.7</v>
+        <v>29.2</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -15941,7 +15889,7 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
@@ -15984,22 +15932,22 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -16009,97 +15957,97 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>13.24</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.07</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>102.7231</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.4188</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.1956</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3083</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>75.83</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>30.87</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>18.1</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.1519</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG19" t="inlineStr">
@@ -16125,56 +16073,56 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>44.1</v>
+        <v>44.5</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16188,62 +16136,58 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>40.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R20" t="n">
-        <v>22.6</v>
+        <v>43.9</v>
       </c>
       <c r="S20" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T20" t="n">
         <v>50</v>
       </c>
       <c r="U20" t="n">
-        <v>5.1</v>
+        <v>13</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16263,12 +16207,12 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -16278,12 +16222,12 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
@@ -16293,104 +16237,112 @@
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>100.8422</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>0.1758</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>25.43</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr"/>
-      <c r="BH20" t="inlineStr"/>
+          <t>26.46</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>In From LF</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr"/>
@@ -16401,32 +16353,32 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>691777</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Max Muncy</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -16436,21 +16388,21 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>43.7</v>
+        <v>44.1</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16464,26 +16416,26 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P21" t="n">
-        <v>35.1</v>
+        <v>40.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R21" t="n">
-        <v>43.9</v>
+        <v>22.6</v>
       </c>
       <c r="S21" t="n">
         <v>81.90000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U21" t="n">
-        <v>26.1</v>
+        <v>5.1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -16539,12 +16491,12 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -16554,12 +16506,12 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/17, 0 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -16569,112 +16521,104 @@
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>40.17</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>100.9708</t>
+          <t>100.8422</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.3621</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.1493</t>
+          <t>0.1709</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>42.11</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>22.51</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>0.1594</t>
+          <t>0.1758</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>26.46</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>In From LF</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
+          <t>25.43</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr"/>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -765,7 +765,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -811,7 +811,7 @@
         <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1044,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1068,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.1</v>
+        <v>57.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1092,7 +1088,7 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -1283,7 +1279,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1579,27 +1575,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1609,26 +1605,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1642,26 +1638,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>79.3</v>
+        <v>54.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R5" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>8.800000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1675,7 +1671,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1713,12 +1709,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1728,127 +1724,127 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>104.473</t>
+          <t>101.2045</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2987</t>
+          <t>0.2228</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.03</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -1859,56 +1855,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1922,26 +1918,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>54.2</v>
+        <v>79.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>16.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1955,7 +1951,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1993,12 +1989,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -2008,127 +2004,127 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2045</t>
+          <t>104.473</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.5811</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2228</t>
+          <t>0.2987</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.4054</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>75.03</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.2679</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -2164,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2188,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2212,7 +2208,7 @@
         <v>26.6</v>
       </c>
       <c r="R7" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -2403,7 +2399,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -2444,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2468,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2492,7 +2488,7 @@
         <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -2683,7 +2679,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -2699,27 +2695,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuña Jr.</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2729,17 +2725,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2748,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2766,22 +2762,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R9" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>63.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2795,7 +2791,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2833,142 +2829,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -2979,47 +2975,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -3028,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>54.2</v>
+        <v>54.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3042,62 +3038,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>63.3</v>
+        <v>53.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3117,142 +3109,142 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -3293,7 +3285,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,7 +3318,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -3339,7 +3331,7 @@
         <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -3349,39 +3341,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3827,56 +3815,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3890,62 +3878,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3965,142 +3949,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4111,27 +4095,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4141,26 +4125,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4174,26 +4158,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R14" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4207,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4245,142 +4229,142 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -4391,27 +4375,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4426,12 +4410,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4440,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4458,13 +4442,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R15" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -4473,7 +4457,7 @@
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>32</v>
+        <v>25.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4525,142 +4509,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4701,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4720,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4734,7 +4718,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -4747,7 +4731,7 @@
         <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -4757,39 +4741,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4955,47 +4935,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -5004,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>48.7</v>
+        <v>49.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5018,62 +4998,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>38.2</v>
+        <v>45.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>25.3</v>
+        <v>32</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5093,142 +5069,142 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -5824,7 +5800,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5848,7 +5824,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -5872,7 +5848,7 @@
         <v>26.6</v>
       </c>
       <c r="R20" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S20" t="n">
         <v>52.4</v>
@@ -6063,7 +6039,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -6104,7 +6080,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -6128,7 +6104,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6152,7 +6128,7 @@
         <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S21" t="n">
         <v>93.2</v>
@@ -6343,7 +6319,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -6359,27 +6335,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>806956</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Ethan Salas</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -6389,26 +6365,26 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>46.1</v>
+        <v>45.9</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6422,26 +6398,26 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P22" t="n">
-        <v>39.3</v>
+        <v>22.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R22" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U22" t="n">
-        <v>13</v>
+        <v>40.3</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -6455,7 +6431,7 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
@@ -6476,7 +6452,7 @@
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD22" t="inlineStr"/>
@@ -6493,12 +6469,12 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -6508,127 +6484,127 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Contact streak: 7/18 over last 7 games</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>33.3</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>90.1</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.8542</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.316</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.129</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.227</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>17.5</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>43.3</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.206</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr"/>
@@ -6639,56 +6615,56 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>806956</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethan Salas</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>45.9</v>
+        <v>45.7</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6702,26 +6678,26 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P23" t="n">
-        <v>22.6</v>
+        <v>39.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R23" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S23" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T23" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U23" t="n">
-        <v>40.3</v>
+        <v>13</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -6735,7 +6711,7 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
@@ -6756,7 +6732,7 @@
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD23" t="inlineStr"/>
@@ -6773,12 +6749,12 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
@@ -6788,127 +6764,127 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Contact streak: 7/18 over last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>3.3</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>33.3</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>90.1</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>98.8542</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>0.316</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>0.227</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>17.5</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>43.3</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr"/>
@@ -6944,7 +6920,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -6968,7 +6944,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>45.3</v>
+        <v>44.9</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6992,7 +6968,7 @@
         <v>24</v>
       </c>
       <c r="R24" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S24" t="n">
         <v>64.3</v>
@@ -7183,7 +7159,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -7504,7 +7480,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -7528,7 +7504,7 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>39.5</v>
+        <v>39</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -7552,7 +7528,7 @@
         <v>24</v>
       </c>
       <c r="R26" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S26" t="n">
         <v>44.8</v>
@@ -7743,7 +7719,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -7784,7 +7760,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -7808,7 +7784,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>39.2</v>
+        <v>38.8</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7832,7 +7808,7 @@
         <v>24.6</v>
       </c>
       <c r="R27" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S27" t="n">
         <v>94.90000000000001</v>
@@ -8023,7 +7999,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -8344,7 +8320,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -8368,7 +8344,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>38.1</v>
+        <v>37.6</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8392,7 +8368,7 @@
         <v>24</v>
       </c>
       <c r="R29" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S29" t="n">
         <v>76.2</v>
@@ -8583,7 +8559,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -8624,7 +8600,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -8648,7 +8624,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>37.6</v>
+        <v>37.2</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8672,7 +8648,7 @@
         <v>24</v>
       </c>
       <c r="R30" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S30" t="n">
         <v>52.4</v>
@@ -8863,7 +8839,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -8879,47 +8855,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>800325</t>
+          <t>657041</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luis Lara</t>
+          <t>Lane Thomas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8928,7 +8904,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>36.6</v>
+        <v>35.8</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8942,65 +8918,61 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>16.6</v>
+        <v>24.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>47.3</v>
+        <v>26.6</v>
       </c>
       <c r="R31" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S31" t="n">
-        <v>47.9</v>
+        <v>64.3</v>
       </c>
       <c r="T31" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD31" t="inlineStr"/>
@@ -9017,12 +8989,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
@@ -9032,127 +9004,127 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 1/16, 0 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>38.02</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>88.85</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>98.8409</t>
+          <t>99.4812</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>0.3371</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>0.1201</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.293</t>
+          <t>0.2906</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>71.4</t>
+          <t>72.63</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>24.73</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>30.6</t>
+          <t>42.12</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>24.6</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>8.9</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>0.1449</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG31" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -9163,27 +9135,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>657041</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lane Thomas</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9198,12 +9170,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9212,7 +9184,7 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>36.3</v>
+        <v>35.8</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -9230,13 +9202,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>24.7</v>
+        <v>10.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R32" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S32" t="n">
         <v>64.3</v>
@@ -9245,7 +9217,7 @@
         <v>50</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>24.9</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9280,7 +9252,7 @@
       <c r="AB32" t="inlineStr"/>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD32" t="inlineStr"/>
@@ -9297,12 +9269,12 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
@@ -9312,127 +9284,127 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/16, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>88.85</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>99.4812</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.3371</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1201</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.2906</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>72.63</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>24.73</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>42.12</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>24.6</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>8.9</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1449</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9468,7 +9440,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -9492,7 +9464,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9516,7 +9488,7 @@
         <v>26.6</v>
       </c>
       <c r="R33" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S33" t="n">
         <v>76.2</v>
@@ -9707,7 +9679,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -9723,12 +9695,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>687401</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Joey Ortiz</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -9753,7 +9725,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -9786,11 +9758,11 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>10.5</v>
+        <v>17.1</v>
       </c>
       <c r="Q34" t="n">
         <v>48.2</v>
@@ -9799,52 +9771,48 @@
         <v>40.1</v>
       </c>
       <c r="S34" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T34" t="n">
         <v>50</v>
       </c>
       <c r="U34" t="n">
-        <v>24.9</v>
+        <v>22.4</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9861,12 +9829,12 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -9876,7 +9844,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 7/26, 0 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
@@ -9891,67 +9859,67 @@
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>36.16</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.91</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>99.2209</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3403</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2904</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>30.57</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>31.91</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>19.68</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>8.4</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.1185</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
@@ -10007,12 +9975,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Joey Ortiz</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -10037,7 +10005,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -10056,7 +10024,7 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>34.5</v>
+        <v>34.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -10070,11 +10038,11 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>17.1</v>
+        <v>5.4</v>
       </c>
       <c r="Q35" t="n">
         <v>48.2</v>
@@ -10083,49 +10051,45 @@
         <v>40.1</v>
       </c>
       <c r="S35" t="n">
-        <v>40.2</v>
+        <v>52.4</v>
       </c>
       <c r="T35" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>22.4</v>
+        <v>17.3</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10145,12 +10109,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -10160,12 +10124,12 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/26, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
@@ -10175,67 +10139,67 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>36.16</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>87.91</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>99.2209</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.3403</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.2904</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>30.57</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>8.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1185</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
@@ -10596,7 +10560,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -10620,7 +10584,7 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>29</v>
+        <v>28.5</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10644,7 +10608,7 @@
         <v>26.6</v>
       </c>
       <c r="R37" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S37" t="n">
         <v>44.8</v>
@@ -10835,7 +10799,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI37" t="inlineStr">
@@ -11207,7 +11171,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -11226,7 +11190,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>58.2</v>
+        <v>59.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -11240,7 +11204,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -11253,7 +11217,7 @@
         <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -11263,39 +11227,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11486,7 +11446,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -11510,7 +11470,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>58.1</v>
+        <v>57.7</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -11534,7 +11494,7 @@
         <v>26.6</v>
       </c>
       <c r="R3" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S3" t="n">
         <v>96.59999999999999</v>
@@ -11725,7 +11685,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -12021,27 +11981,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>660271</t>
+          <t>701538</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Shohei Ohtani</t>
+          <t>Jackson Merrill</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -12051,26 +12011,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Dustin May</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>669160</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>57.2</v>
+        <v>57</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -12084,26 +12044,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Elite Power, Strong Barrel</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>79.3</v>
+        <v>54.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>24</v>
+        <v>46.2</v>
       </c>
       <c r="R5" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>86.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>8.800000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -12117,7 +12077,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -12155,12 +12115,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -12170,127 +12130,127 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/28, 0 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>18.53</t>
+          <t>12.58</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>54.08</t>
+          <t>46.96</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>93.78</t>
+          <t>90.96</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>104.473</t>
+          <t>101.2045</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5811</t>
+          <t>0.4907</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.2987</t>
+          <t>0.2228</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.4054</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>75.03</t>
+          <t>72.95</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>52.94</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>37.7</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.2679</t>
+          <t>0.1881</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>90.18</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.4132</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1595</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>25.43</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr"/>
@@ -12301,56 +12261,56 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>701538</t>
+          <t>660271</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jackson Merrill</t>
+          <t>Shohei Ohtani</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Dustin May</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>669160</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>57</v>
+        <v>56.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -12364,26 +12324,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>54.2</v>
+        <v>79.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>46.2</v>
+        <v>24</v>
       </c>
       <c r="R6" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U6" t="n">
-        <v>16.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -12397,7 +12357,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -12435,12 +12395,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -12450,127 +12410,127 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Last 7 games: 5/28, 0 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.2% barrel, 16.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>lift-pull EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>18.53</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>46.96</t>
+          <t>54.08</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.96</t>
+          <t>93.78</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2045</t>
+          <t>104.473</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4907</t>
+          <t>0.5811</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.2228</t>
+          <t>0.2987</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.4054</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>72.95</t>
+          <t>75.03</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>52.94</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>29.92</t>
+          <t>31.92</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>23.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1881</t>
+          <t>0.2679</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>90.18</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.4132</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.1595</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.43</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr"/>
@@ -12606,7 +12566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -12630,7 +12590,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.3</v>
+        <v>55.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -12654,7 +12614,7 @@
         <v>26.6</v>
       </c>
       <c r="R7" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S7" t="n">
         <v>93.2</v>
@@ -12845,7 +12805,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -12886,7 +12846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12910,7 +12870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>55.7</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -12934,7 +12894,7 @@
         <v>24</v>
       </c>
       <c r="R8" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S8" t="n">
         <v>94.90000000000001</v>
@@ -13125,7 +13085,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -13141,27 +13101,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuña Jr.</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -13171,17 +13131,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -13190,7 +13150,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.2</v>
+        <v>54.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -13208,22 +13168,22 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>50.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R9" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>100</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>63.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -13237,7 +13197,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -13275,142 +13235,142 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr"/>
@@ -13421,47 +13381,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -13470,7 +13430,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>54.2</v>
+        <v>54.7</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -13484,62 +13444,58 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>50.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R10" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>100</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>63.3</v>
+        <v>53.3</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -13559,142 +13515,142 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1951</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr"/>
@@ -13735,7 +13691,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -13754,7 +13710,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>53.5</v>
+        <v>53.4</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -13768,7 +13724,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
@@ -13781,7 +13737,7 @@
         <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>95.5</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T11" t="n">
         <v>80</v>
@@ -13791,39 +13747,35 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14269,56 +14221,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Chris Sale</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>519242</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>52.4</v>
+        <v>51.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -14332,62 +14284,58 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>47.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>48.2</v>
+        <v>24</v>
       </c>
       <c r="R13" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U13" t="n">
-        <v>13.3</v>
+        <v>48.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14407,142 +14355,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>26.88</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1342</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>35.19</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.62</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3249</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1122</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>26.46</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -14553,27 +14501,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teoscar Hernández</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -14583,26 +14531,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Chris Sale</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>519242</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>52</v>
+        <v>51.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -14616,26 +14564,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>45.7</v>
+        <v>47.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>24</v>
+        <v>48.2</v>
       </c>
       <c r="R14" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>96.59999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>48.3</v>
+        <v>13.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -14649,7 +14597,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -14687,142 +14635,142 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.2% barrel, 10.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>26.88</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.62</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3249</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1122</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>26.46</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr"/>
@@ -14833,27 +14781,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Michael Harris II</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-06T22:00:00Z</t>
+          <t>2026-10-07T01:30:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -14868,12 +14816,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Yoshinobu Yamamoto</t>
+          <t>Nick Pivetta</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>808967</t>
+          <t>601713</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -14882,7 +14830,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>50.4</v>
+        <v>50.7</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -14900,13 +14848,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>45.1</v>
+        <v>38.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>26.6</v>
+        <v>48.2</v>
       </c>
       <c r="R15" t="n">
-        <v>54.9</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
         <v>86.40000000000001</v>
@@ -14915,7 +14863,7 @@
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>32</v>
+        <v>25.3</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -14967,142 +14915,142 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>47.05</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.76</t>
+          <t>40.24</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3257</t>
+          <t>0.3834</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1186</t>
+          <t>0.1638</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>22.66</t>
+          <t>34.35</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>L To R</t>
+          <t>In From LF</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>83</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -15143,7 +15091,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -15162,7 +15110,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>49.7</v>
+        <v>50.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -15176,7 +15124,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P16" t="n">
@@ -15189,7 +15137,7 @@
         <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T16" t="n">
         <v>50</v>
@@ -15199,39 +15147,35 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15397,47 +15341,47 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-10-07T01:30:00Z</t>
+          <t>2026-10-06T22:00:00Z</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Nick Pivetta</t>
+          <t>Yoshinobu Yamamoto</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>601713</t>
+          <t>808967</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -15446,7 +15390,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>48.7</v>
+        <v>49.9</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -15460,62 +15404,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>38.2</v>
+        <v>45.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>48.2</v>
+        <v>26.6</v>
       </c>
       <c r="R17" t="n">
-        <v>40.1</v>
+        <v>51.9</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>25.3</v>
+        <v>32</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -15535,142 +15475,142 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.3% barrel, 8.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 18.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>47.05</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>40.24</t>
+          <t>36.76</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3834</t>
+          <t>0.3257</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1638</t>
+          <t>0.1186</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>34.35</t>
+          <t>22.66</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>In From LF</t>
+          <t>L To R</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr"/>
@@ -16266,7 +16206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -16290,7 +16230,7 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>46.5</v>
+        <v>46</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -16314,7 +16254,7 @@
         <v>26.6</v>
       </c>
       <c r="R20" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S20" t="n">
         <v>52.4</v>
@@ -16505,7 +16445,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -16546,7 +16486,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -16570,7 +16510,7 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>46.3</v>
+        <v>45.9</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -16594,7 +16534,7 @@
         <v>24</v>
       </c>
       <c r="R21" t="n">
-        <v>54.9</v>
+        <v>51.9</v>
       </c>
       <c r="S21" t="n">
         <v>93.2</v>
@@ -16785,7 +16725,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -808,7 +808,7 @@
         <v>38.8</v>
       </c>
       <c r="R2" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -1106,34 +1106,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2510,34 +2506,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3263,56 +3255,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sean Newcomb</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>656794</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,61 +3306,65 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.3</v>
+        <v>57.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>28.5</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>50.6</v>
+        <v>22.6</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>74.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3397,142 +3381,110 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1874</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>88.76</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.3761</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1236</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>0.1801</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -3543,24 +3495,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-07T20:00:00Z</t>
@@ -3573,26 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3606,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>38.8</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>41.2</v>
+        <v>34.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3639,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3660,7 +3612,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3682,7 +3634,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3692,112 +3644,112 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3823,44 +3775,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Daniel Espino</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>682982</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>53.9</v>
+        <v>53.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3874,65 +3838,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>50</v>
+      </c>
+      <c r="U13" t="n">
         <v>41.2</v>
       </c>
-      <c r="R13" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>60</v>
-      </c>
-      <c r="U13" t="n">
-        <v>74.2</v>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3949,110 +3909,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1801</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.2069</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -4154,34 +4146,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4396,7 +4384,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4420,7 +4408,7 @@
         <v>38.8</v>
       </c>
       <c r="R15" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -4718,34 +4706,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5562,34 +5546,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6872,7 +6852,7 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>49.4</v>
+        <v>49.1</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6896,7 +6876,7 @@
         <v>38.8</v>
       </c>
       <c r="R24" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S24" t="n">
         <v>52.4</v>
@@ -7952,7 +7932,7 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>46.9</v>
+        <v>46.6</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7976,7 +7956,7 @@
         <v>28.5</v>
       </c>
       <c r="R28" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S28" t="n">
         <v>96.59999999999999</v>
@@ -8232,7 +8212,7 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>46.8</v>
+        <v>46.5</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -8256,7 +8236,7 @@
         <v>38.8</v>
       </c>
       <c r="R29" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S29" t="n">
         <v>44.8</v>
@@ -8554,34 +8534,30 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 1 vs RotoWire 2</t>
-        </is>
-      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9299,47 +9275,47 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9362,61 +9338,65 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>18.8</v>
+        <v>30.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>38.8</v>
+        <v>34.3</v>
       </c>
       <c r="R33" t="n">
-        <v>50.6</v>
+        <v>38.2</v>
       </c>
       <c r="S33" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T33" t="n">
         <v>80</v>
       </c>
       <c r="U33" t="n">
-        <v>43.1</v>
+        <v>18.3</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W33" t="inlineStr">
+      <c r="Z33" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD33" t="inlineStr"/>
@@ -9433,142 +9413,134 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="BG33" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH33" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG33" t="inlineStr"/>
+      <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9579,47 +9551,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9628,7 +9600,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>45.5</v>
+        <v>45.2</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9642,65 +9614,61 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>30.5</v>
+        <v>18.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="R34" t="n">
-        <v>38.2</v>
+        <v>48.6</v>
       </c>
       <c r="S34" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T34" t="n">
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>18.3</v>
+        <v>43.1</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr"/>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9717,134 +9685,142 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>97.5005</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr"/>
-      <c r="BH34" t="inlineStr"/>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH34" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -10696,7 +10672,7 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10720,7 +10696,7 @@
         <v>28.1</v>
       </c>
       <c r="R38" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S38" t="n">
         <v>100</v>
@@ -12052,7 +12028,7 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>43.5</v>
+        <v>43.2</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -12076,7 +12052,7 @@
         <v>28.5</v>
       </c>
       <c r="R43" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S43" t="n">
         <v>86.40000000000001</v>
@@ -12835,27 +12811,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>663656</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Kyle Tucker</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12865,17 +12841,17 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -12884,7 +12860,7 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -12902,22 +12878,22 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>24</v>
+        <v>33.9</v>
       </c>
       <c r="Q46" t="n">
-        <v>38.5</v>
+        <v>37.3</v>
       </c>
       <c r="R46" t="n">
-        <v>50.6</v>
+        <v>48.9</v>
       </c>
       <c r="S46" t="n">
-        <v>64.3</v>
+        <v>52.4</v>
       </c>
       <c r="T46" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U46" t="n">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -12931,7 +12907,7 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
@@ -12952,7 +12928,7 @@
       <c r="AB46" t="inlineStr"/>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD46" t="inlineStr"/>
@@ -12969,7 +12945,7 @@
       </c>
       <c r="AH46" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI46" t="inlineStr">
@@ -12984,112 +12960,112 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.72</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>37.53</t>
         </is>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AQ46" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>98.7109</t>
         </is>
       </c>
       <c r="AR46" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1598</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.3433</t>
         </is>
       </c>
       <c r="AU46" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.58</t>
         </is>
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>20.59</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>42.96</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>18.5</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1658</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD46" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF46" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG46" t="inlineStr">
@@ -13099,12 +13075,12 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI46" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ46" t="inlineStr"/>
@@ -13115,27 +13091,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>663656</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kyle Tucker</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -13145,17 +13121,17 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
@@ -13164,7 +13140,7 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -13182,22 +13158,22 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>33.9</v>
+        <v>24</v>
       </c>
       <c r="Q47" t="n">
-        <v>37.3</v>
+        <v>38.5</v>
       </c>
       <c r="R47" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S47" t="n">
-        <v>52.4</v>
+        <v>64.3</v>
       </c>
       <c r="T47" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U47" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -13206,37 +13182,33 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 8 vs RotoWire 6</t>
-        </is>
-      </c>
+      <c r="AB47" t="inlineStr"/>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD47" t="inlineStr"/>
@@ -13253,7 +13225,7 @@
       </c>
       <c r="AH47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI47" t="inlineStr">
@@ -13268,112 +13240,112 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>switch hitter; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>7.72</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
-          <t>37.53</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ47" t="inlineStr">
         <is>
-          <t>98.7109</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR47" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr">
         <is>
-          <t>0.1598</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT47" t="inlineStr">
         <is>
-          <t>0.3433</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU47" t="inlineStr">
         <is>
-          <t>71.58</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>42.96</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>18.5</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>0.1658</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD47" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF47" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="BG47" t="inlineStr">
@@ -13383,12 +13355,12 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI47" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ47" t="inlineStr"/>
@@ -13490,34 +13462,30 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 9 vs RotoWire 8</t>
-        </is>
-      </c>
+      <c r="AB48" t="inlineStr"/>
       <c r="AC48" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14324,28 +14292,32 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="Y51" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>not found on RotoWire</t>
-        </is>
-      </c>
+      <c r="AB51" t="inlineStr"/>
       <c r="AC51" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -14560,7 +14532,7 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>41.7</v>
+        <v>41.4</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -14584,7 +14556,7 @@
         <v>38.8</v>
       </c>
       <c r="R52" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S52" t="n">
         <v>86.40000000000001</v>
@@ -14840,7 +14812,7 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>41.5</v>
+        <v>41.2</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -14864,7 +14836,7 @@
         <v>28.1</v>
       </c>
       <c r="R53" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S53" t="n">
         <v>52.4</v>
@@ -15120,7 +15092,7 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -15144,7 +15116,7 @@
         <v>28.1</v>
       </c>
       <c r="R54" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S54" t="n">
         <v>76.2</v>
@@ -15924,7 +15896,7 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -15948,7 +15920,7 @@
         <v>38.8</v>
       </c>
       <c r="R57" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S57" t="n">
         <v>76.2</v>
@@ -16772,7 +16744,7 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -16796,7 +16768,7 @@
         <v>28.5</v>
       </c>
       <c r="R60" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S60" t="n">
         <v>64.3</v>
@@ -17052,7 +17024,7 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>35.5</v>
+        <v>35.2</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -17076,7 +17048,7 @@
         <v>28.1</v>
       </c>
       <c r="R61" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S61" t="n">
         <v>44.8</v>
@@ -17332,7 +17304,7 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>35.1</v>
+        <v>34.8</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -17356,7 +17328,7 @@
         <v>28.5</v>
       </c>
       <c r="R62" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S62" t="n">
         <v>93.2</v>
@@ -20866,7 +20838,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>67.3</v>
+        <v>67</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -20890,7 +20862,7 @@
         <v>38.8</v>
       </c>
       <c r="R2" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S2" t="n">
         <v>96.59999999999999</v>
@@ -21188,34 +21160,30 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 4 vs RotoWire 1</t>
-        </is>
-      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22592,34 +22560,30 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 3 vs RotoWire 4</t>
-        </is>
-      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -23345,56 +23309,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>666176</t>
+          <t>665487</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jo Adell</t>
+          <t>Fernando Tatis</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Sean Newcomb</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>656794</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="n">
-        <v>54.1</v>
+        <v>53.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -23408,61 +23360,65 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>53.3</v>
+        <v>57.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>28.5</v>
+        <v>41.2</v>
       </c>
       <c r="R11" t="n">
-        <v>50.6</v>
+        <v>22.6</v>
       </c>
       <c r="S11" t="n">
-        <v>94.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U11" t="n">
-        <v>34.9</v>
+        <v>74.2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="Z11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -23479,142 +23435,110 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>12.19</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>46.43</t>
+          <t>53.27</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>90.79</t>
+          <t>93.02</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>103.0119</t>
+          <t>104.4475</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4755</t>
+          <t>0.4964</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2176</t>
+          <t>0.2079</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3763</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>77.46</t>
+          <t>75.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>72.81</t>
+          <t>57.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.1</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>27.56</t>
+          <t>22.36</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>27.2</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1874</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>6.26</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>39.56</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>88.76</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>0.3761</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>0.1236</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>0.1801</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr"/>
@@ -23625,24 +23549,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>678246</t>
+          <t>666176</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miguel Vargas</t>
+          <t>Jo Adell</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-07T20:00:00Z</t>
@@ -23655,26 +23579,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>54</v>
+        <v>53.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -23688,26 +23612,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>50</v>
+        <v>53.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>38.8</v>
+        <v>28.5</v>
       </c>
       <c r="R12" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U12" t="n">
-        <v>41.2</v>
+        <v>34.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -23721,7 +23645,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -23742,7 +23666,7 @@
       <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -23764,7 +23688,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -23774,112 +23698,112 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/22, 1 HR</t>
+          <t>Last 7 games: 6/26, 1 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>11.92</t>
+          <t>11.42</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>46.43</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>90.79</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.1212</t>
+          <t>103.0119</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4693</t>
+          <t>0.4755</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.2144</t>
+          <t>0.2176</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3603</t>
+          <t>0.3398</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.91</t>
+          <t>77.46</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>33.23</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>44.84</t>
+          <t>40.1</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>27.56</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>27.9</t>
+          <t>27.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.2069</t>
+          <t>0.1874</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -23905,44 +23829,56 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>665487</t>
+          <t>678246</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fernando Tatis</t>
+          <t>Miguel Vargas</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Daniel Espino</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>682982</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>53.9</v>
+        <v>53.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -23956,65 +23892,61 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>57.9</v>
+        <v>50</v>
       </c>
       <c r="Q13" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="R13" t="n">
+        <v>48.6</v>
+      </c>
+      <c r="S13" t="n">
+        <v>100</v>
+      </c>
+      <c r="T13" t="n">
+        <v>50</v>
+      </c>
+      <c r="U13" t="n">
         <v>41.2</v>
       </c>
-      <c r="R13" t="n">
-        <v>22.6</v>
-      </c>
-      <c r="S13" t="n">
-        <v>88.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>60</v>
-      </c>
-      <c r="U13" t="n">
-        <v>74.2</v>
-      </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -24031,110 +23963,142 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/22, 1 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>12.19</t>
+          <t>11.92</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>53.27</t>
+          <t>42.81</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>93.02</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>104.4475</t>
+          <t>100.1212</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.4964</t>
+          <t>0.4693</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.2079</t>
+          <t>0.2144</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3763</t>
+          <t>0.3603</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>75.58</t>
+          <t>72.91</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>57.84</t>
+          <t>33.23</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>44.84</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>22.36</t>
+          <t>35.31</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>27.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1801</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+          <t>0.2069</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>36.4</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>85.3</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.317</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.135</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr"/>
@@ -24236,34 +24200,30 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 6 vs RotoWire 5</t>
-        </is>
-      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -24478,7 +24438,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.8</v>
+        <v>51.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -24502,7 +24462,7 @@
         <v>38.8</v>
       </c>
       <c r="R15" t="n">
-        <v>50.6</v>
+        <v>48.6</v>
       </c>
       <c r="S15" t="n">
         <v>94.90000000000001</v>
@@ -24800,34 +24760,30 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 2 vs RotoWire 3</t>
-        </is>
-      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25644,34 +25600,30 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>MLB Stats API; RotoWire</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>RotoWire not confirmed; order MLB 5 vs RotoWire 7</t>
-        </is>
-      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>58.8</v>
+        <v>59.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1371,7 +1371,7 @@
         <v>48.9</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -1381,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2161,7 +2157,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2180,7 +2176,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2194,7 +2190,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2207,7 +2203,7 @@
         <v>48.9</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2217,39 +2213,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2415,24 +2407,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -2445,17 +2437,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -2464,7 +2456,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2478,26 +2470,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>51.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="R8" t="n">
         <v>48.9</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2511,7 +2503,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2549,127 +2541,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -2695,24 +2687,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -2725,17 +2717,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -2744,7 +2736,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2758,62 +2750,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R9" t="n">
         <v>48.9</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>100</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2833,127 +2821,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4335,27 +4323,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -4365,17 +4353,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4384,7 +4372,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4398,26 +4386,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="R15" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="S15" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>44.1</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4431,7 +4419,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4452,7 +4440,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4469,127 +4457,127 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>46.98</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4599,12 +4587,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -4615,27 +4603,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4645,17 +4633,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4664,7 +4652,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4678,26 +4666,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="R16" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>44.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4711,7 +4699,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4732,7 +4720,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4749,127 +4737,127 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>40.12</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>29.94</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>0.1471</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>36.4</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.1615</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -4879,12 +4867,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -4895,24 +4883,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -4925,17 +4913,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4944,7 +4932,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4958,62 +4946,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.1</v>
+        <v>39.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.9</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5033,12 +5017,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5048,12 +5032,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5063,97 +5047,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">
@@ -7648,7 +7632,7 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>47.1</v>
+        <v>47.7</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -7662,7 +7646,7 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -7675,7 +7659,7 @@
         <v>48.9</v>
       </c>
       <c r="S27" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T27" t="n">
         <v>50</v>
@@ -7685,39 +7669,35 @@
       </c>
       <c r="V27" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
       <c r="AC27" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8443,24 +8423,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>573262</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Mike Yastrzemski</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -8473,17 +8453,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -8492,7 +8472,7 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>46.1</v>
+        <v>46.4</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -8506,26 +8486,26 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>32.7</v>
+        <v>34.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="R30" t="n">
         <v>48.9</v>
       </c>
       <c r="S30" t="n">
-        <v>93.2</v>
+        <v>76.2</v>
       </c>
       <c r="T30" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U30" t="n">
-        <v>29.2</v>
+        <v>24</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -8539,7 +8519,7 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
@@ -8577,12 +8557,12 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
@@ -8592,12 +8572,12 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Last 7 games: 3/19, 1 HR</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -8607,97 +8587,97 @@
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>7.31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>42.88</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>90.52</t>
         </is>
       </c>
       <c r="AQ30" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.7248</t>
         </is>
       </c>
       <c r="AR30" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.3833</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1477</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>71.24</t>
         </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.65</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>43.03</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>30.91</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>13.5</t>
         </is>
       </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1602</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG30" t="inlineStr">
@@ -8723,47 +8703,47 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>665862</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jazz Chisholm</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -8772,7 +8752,7 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>45.9</v>
+        <v>46.1</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -8786,62 +8766,58 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P31" t="n">
-        <v>42.2</v>
+        <v>32.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>34.3</v>
+        <v>37.3</v>
       </c>
       <c r="R31" t="n">
-        <v>38.2</v>
+        <v>48.9</v>
       </c>
       <c r="S31" t="n">
-        <v>71.7</v>
+        <v>93.2</v>
       </c>
       <c r="T31" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U31" t="n">
-        <v>14.6</v>
+        <v>29.2</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
       <c r="AC31" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8866,22 +8842,22 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/23, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
@@ -8891,87 +8867,87 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>10.24</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>89.98</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>100.4248</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR31" t="inlineStr">
         <is>
-          <t>0.4005</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
-          <t>0.1791</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>0.3093</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>30.19</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -8981,14 +8957,22 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG31" t="inlineStr"/>
-      <c r="BH31" t="inlineStr"/>
+          <t>26.63</t>
+        </is>
+      </c>
+      <c r="BG31" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH31" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI31" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ31" t="inlineStr"/>
@@ -8999,27 +8983,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>665862</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jazz Chisholm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -9029,17 +9013,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Walker Buehler</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>621111</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -9062,26 +9046,26 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P32" t="n">
-        <v>39.5</v>
+        <v>42.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>43.4</v>
+        <v>34.3</v>
       </c>
       <c r="R32" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S32" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T32" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U32" t="n">
-        <v>37.8</v>
+        <v>14.6</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -9095,7 +9079,7 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
@@ -9137,27 +9121,27 @@
       </c>
       <c r="AH32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 5/23, 0 HR</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM32" t="inlineStr">
@@ -9167,104 +9151,104 @@
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.24</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>42.95</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>89.98</t>
         </is>
       </c>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>100.4248</t>
         </is>
       </c>
       <c r="AR32" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4005</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.1791</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3093</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>73.2</t>
         </is>
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.19</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>22.6</t>
         </is>
       </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>0.1446</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>38.43</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>88.88</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>0.4164</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>0.1645</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF32" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>28.96</t>
         </is>
       </c>
       <c r="BG32" t="inlineStr"/>
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ32" t="inlineStr"/>
@@ -9275,27 +9259,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cody Bellinger</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -9305,17 +9289,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -9324,7 +9308,7 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>45.5</v>
+        <v>45.9</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -9338,26 +9322,26 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>30.5</v>
+        <v>39.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>34.3</v>
+        <v>43.4</v>
       </c>
       <c r="R33" t="n">
-        <v>38.2</v>
+        <v>22.6</v>
       </c>
       <c r="S33" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T33" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U33" t="n">
-        <v>18.3</v>
+        <v>37.8</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -9371,7 +9355,7 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
@@ -9413,12 +9397,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
@@ -9428,12 +9412,12 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/28, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
@@ -9443,104 +9427,104 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>88.93</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ33" t="inlineStr">
         <is>
-          <t>98.5475</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR33" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
-          <t>0.1505</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>0.3314</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>44.36</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>0.1779</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr">
         <is>
-          <t>28.96</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="BG33" t="inlineStr"/>
       <c r="BH33" t="inlineStr"/>
       <c r="BI33" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ33" t="inlineStr"/>
@@ -9551,47 +9535,47 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>803011</t>
+          <t>641355</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sam Antonacci</t>
+          <t>Cody Bellinger</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Nick Martinez</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607259</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -9600,7 +9584,7 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>45.2</v>
+        <v>45.5</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -9614,61 +9598,65 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>18.8</v>
+        <v>30.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>38.8</v>
+        <v>34.3</v>
       </c>
       <c r="R34" t="n">
-        <v>48.6</v>
+        <v>38.2</v>
       </c>
       <c r="S34" t="n">
-        <v>93.2</v>
+        <v>95.5</v>
       </c>
       <c r="T34" t="n">
         <v>80</v>
       </c>
       <c r="U34" t="n">
-        <v>43.1</v>
+        <v>18.3</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W34" t="inlineStr">
+      <c r="Z34" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD34" t="inlineStr"/>
@@ -9685,142 +9673,134 @@
       </c>
       <c r="AH34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI34" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 3/28, 1 HR</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>33.6</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.93</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>97.5005</t>
+          <t>98.5475</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>0.1505</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>0.3314</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>7.1</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>44.36</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>31.85</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>20.6</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.1779</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>6.86</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>33.38</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>87.39</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.4114</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF34" t="inlineStr">
         <is>
-          <t>39.4</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>28.96</t>
+        </is>
+      </c>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr"/>
@@ -9831,47 +9811,47 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>663757</t>
+          <t>803011</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Trent Grisham</t>
+          <t>Sam Antonacci</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NYY</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TB</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-10-08T00:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Nick Martinez</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>607259</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -9894,65 +9874,61 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>47.4</v>
+        <v>18.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>34.3</v>
+        <v>38.8</v>
       </c>
       <c r="R35" t="n">
-        <v>38.2</v>
+        <v>48.6</v>
       </c>
       <c r="S35" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T35" t="n">
         <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>43.1</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr"/>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD35" t="inlineStr"/>
@@ -9969,12 +9945,12 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI35" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -9984,119 +9960,127 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/20, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>5.0</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>33.6</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>90.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>100.7514</t>
+          <t>97.5005</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>0.4497</t>
+          <t>0.399</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>0.2038</t>
+          <t>0.115</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.3469</t>
+          <t>0.348</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>70.79</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>7.1</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>21.6</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>22.8</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>0.1975</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>6.86</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>33.38</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>87.39</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr">
         <is>
-          <t>0.4114</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF35" t="inlineStr">
         <is>
-          <t>28.96</t>
-        </is>
-      </c>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>Yankee Stadium</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr"/>
@@ -10107,27 +10091,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>664034</t>
+          <t>663757</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ty France</t>
+          <t>Trent Grisham</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>NYY</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>TB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-08T00:00:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -10137,14 +10121,26 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Nick Martinez</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>607259</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L36" t="n">
-        <v>45</v>
+        <v>45.2</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -10158,26 +10154,26 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>40.6</v>
+        <v>47.4</v>
       </c>
       <c r="Q36" t="n">
-        <v>41.2</v>
+        <v>34.3</v>
       </c>
       <c r="R36" t="n">
-        <v>22.6</v>
+        <v>38.2</v>
       </c>
       <c r="S36" t="n">
-        <v>90.40000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T36" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U36" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -10191,7 +10187,7 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
@@ -10216,7 +10212,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD36" t="inlineStr"/>
@@ -10233,12 +10229,12 @@
       </c>
       <c r="AH36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -10248,12 +10244,12 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/26, 0 HR</t>
+          <t>Last 7 games: 2/20, 0 HR</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.9% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
@@ -10263,80 +10259,104 @@
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>10.98</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>45.63</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>90.9</t>
+          <t>90.75</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>100.8422</t>
+          <t>100.7514</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>0.4222</t>
+          <t>0.4497</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>0.1709</t>
+          <t>0.2038</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.3469</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>71.7</t>
+          <t>70.79</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>9.51</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>24.97</t>
+          <t>31.05</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>16.8</t>
+          <t>22.8</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>0.1758</t>
-        </is>
-      </c>
-      <c r="BA36" t="inlineStr"/>
-      <c r="BB36" t="inlineStr"/>
-      <c r="BC36" t="inlineStr"/>
-      <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
-      <c r="BF36" t="inlineStr"/>
+          <t>0.1975</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>6.86</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>33.38</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>87.39</t>
+        </is>
+      </c>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>0.4114</t>
+        </is>
+      </c>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>0.1502</t>
+        </is>
+      </c>
+      <c r="BF36" t="inlineStr">
+        <is>
+          <t>28.96</t>
+        </is>
+      </c>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Yankee Stadium</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr"/>
@@ -10347,24 +10367,24 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>664034</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Ty France</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>2026-10-08T02:00:00Z</t>
@@ -10377,26 +10397,14 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Walker Buehler</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>621111</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="n">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -10410,26 +10418,26 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>38.2</v>
+        <v>40.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>43.4</v>
+        <v>41.2</v>
       </c>
       <c r="R37" t="n">
         <v>22.6</v>
       </c>
       <c r="S37" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T37" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U37" t="n">
-        <v>25.3</v>
+        <v>5.1</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -10443,7 +10451,7 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
@@ -10468,7 +10476,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD37" t="inlineStr"/>
@@ -10490,22 +10498,22 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Last 7 games: 4/26, 0 HR</t>
         </is>
       </c>
       <c r="AL37" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -10515,99 +10523,75 @@
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.9</t>
         </is>
       </c>
       <c r="AQ37" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.8422</t>
         </is>
       </c>
       <c r="AR37" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4222</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1709</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3273</t>
         </is>
       </c>
       <c r="AU37" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>71.7</t>
         </is>
       </c>
       <c r="AV37" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>19.53</t>
         </is>
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>36.64</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>24.97</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>16.8</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BA37" t="inlineStr">
-        <is>
-          <t>8.73</t>
-        </is>
-      </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>38.43</t>
-        </is>
-      </c>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>88.88</t>
-        </is>
-      </c>
-      <c r="BD37" t="inlineStr">
-        <is>
-          <t>0.4164</t>
-        </is>
-      </c>
-      <c r="BE37" t="inlineStr">
-        <is>
-          <t>0.1645</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>23.44</t>
-        </is>
-      </c>
+          <t>0.1758</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr"/>
+      <c r="BB37" t="inlineStr"/>
+      <c r="BC37" t="inlineStr"/>
+      <c r="BD37" t="inlineStr"/>
+      <c r="BE37" t="inlineStr"/>
+      <c r="BF37" t="inlineStr"/>
       <c r="BG37" t="inlineStr"/>
       <c r="BH37" t="inlineStr"/>
       <c r="BI37" t="inlineStr">
@@ -10623,56 +10607,56 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>José Ramírez</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sean Newcomb</t>
+          <t>Walker Buehler</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>656794</t>
+          <t>621111</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>44.5</v>
+        <v>44.9</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -10686,58 +10670,62 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>25.8</v>
+        <v>38.2</v>
       </c>
       <c r="Q38" t="n">
-        <v>28.1</v>
+        <v>43.4</v>
       </c>
       <c r="R38" t="n">
-        <v>48.6</v>
+        <v>22.6</v>
       </c>
       <c r="S38" t="n">
-        <v>100</v>
+        <v>71.7</v>
       </c>
       <c r="T38" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="U38" t="n">
-        <v>23.4</v>
+        <v>25.3</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="Z38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>MLB Stats API; RotoWire</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr"/>
+          <t>RotoWire projected lineup; MLB probable pitchers</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>lineup projected / unconfirmed</t>
+        </is>
+      </c>
       <c r="AC38" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10757,27 +10745,27 @@
       </c>
       <c r="AH38" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL38" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 22.0 HR allowed</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
@@ -10787,112 +10775,104 @@
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ38" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR38" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU38" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV38" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="BB38" t="inlineStr">
         <is>
-          <t>39.56</t>
+          <t>38.43</t>
         </is>
       </c>
       <c r="BC38" t="inlineStr">
         <is>
-          <t>88.76</t>
+          <t>88.88</t>
         </is>
       </c>
       <c r="BD38" t="inlineStr">
         <is>
-          <t>0.3761</t>
+          <t>0.4164</t>
         </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
-          <t>0.1236</t>
+          <t>0.1645</t>
         </is>
       </c>
       <c r="BF38" t="inlineStr">
         <is>
-          <t>22.19</t>
-        </is>
-      </c>
-      <c r="BG38" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH38" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
+          <t>23.44</t>
+        </is>
+      </c>
+      <c r="BG38" t="inlineStr"/>
+      <c r="BH38" t="inlineStr"/>
       <c r="BI38" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ38" t="inlineStr"/>
@@ -10903,27 +10883,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>573262</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mike Yastrzemski</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -10933,26 +10913,26 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Sean Newcomb</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>656794</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>44.1</v>
+        <v>44.5</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -10966,62 +10946,58 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>34.7</v>
+        <v>25.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>35.6</v>
+        <v>28.1</v>
       </c>
       <c r="R39" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S39" t="n">
-        <v>59.8</v>
+        <v>100</v>
       </c>
       <c r="T39" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="U39" t="n">
-        <v>24</v>
+        <v>23.4</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr"/>
       <c r="AC39" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -11041,27 +11017,27 @@
       </c>
       <c r="AH39" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/19, 1 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>switch hitter; pitcher baseline 6.3% barrel, 4.3 HR allowed</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -11071,97 +11047,97 @@
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>7.31</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>42.88</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>90.52</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ39" t="inlineStr">
         <is>
-          <t>99.7248</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR39" t="inlineStr">
         <is>
-          <t>0.3833</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr">
         <is>
-          <t>0.1477</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>71.24</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
         <is>
-          <t>8.65</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>43.03</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>0.1602</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>39.56</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>88.76</t>
         </is>
       </c>
       <c r="BD39" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3761</t>
         </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1236</t>
         </is>
       </c>
       <c r="BF39" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>22.19</t>
         </is>
       </c>
       <c r="BG39" t="inlineStr">
@@ -11171,12 +11147,12 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI39" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ39" t="inlineStr"/>
@@ -15323,42 +15299,54 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>593428</t>
+          <t>645277</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Xander Bogaerts</t>
+          <t>Ozzie Albies</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>MIL</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-10-08T02:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Tyler Glasnow</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>607192</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L55" t="n">
         <v>40.8</v>
       </c>
@@ -15374,65 +15362,61 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P55" t="n">
-        <v>28.7</v>
+        <v>15.3</v>
       </c>
       <c r="Q55" t="n">
-        <v>41.2</v>
+        <v>34.7</v>
       </c>
       <c r="R55" t="n">
-        <v>22.6</v>
+        <v>48.9</v>
       </c>
       <c r="S55" t="n">
-        <v>71.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T55" t="n">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="U55" t="n">
-        <v>52.8</v>
+        <v>0</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr"/>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD55" t="inlineStr"/>
@@ -15449,27 +15433,27 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI55" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Contact streak: 7/20 over last 7 games</t>
+          <t>Last 7 games: 3/25, 0 HR</t>
         </is>
       </c>
       <c r="AL55" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
@@ -15479,80 +15463,112 @@
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>5.92</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>87.22</t>
         </is>
       </c>
       <c r="AQ55" t="inlineStr">
         <is>
-          <t>100.2761</t>
+          <t>96.687</t>
         </is>
       </c>
       <c r="AR55" t="inlineStr">
         <is>
-          <t>0.3871</t>
+          <t>0.346</t>
         </is>
       </c>
       <c r="AS55" t="inlineStr">
         <is>
-          <t>0.1327</t>
+          <t>0.1184</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr">
         <is>
-          <t>0.3256</t>
+          <t>0.2808</t>
         </is>
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>72.24</t>
+          <t>68.86</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>5.67</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>43.52</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>23.27</t>
+          <t>31.48</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
-          <t>12.4</t>
+          <t>20.2</t>
         </is>
       </c>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>0.1175</t>
-        </is>
-      </c>
-      <c r="BA55" t="inlineStr"/>
-      <c r="BB55" t="inlineStr"/>
-      <c r="BC55" t="inlineStr"/>
-      <c r="BD55" t="inlineStr"/>
-      <c r="BE55" t="inlineStr"/>
-      <c r="BF55" t="inlineStr"/>
-      <c r="BG55" t="inlineStr"/>
-      <c r="BH55" t="inlineStr"/>
+          <t>0.146</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>8.35</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
+        <is>
+          <t>89.53</t>
+        </is>
+      </c>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>0.3296</t>
+        </is>
+      </c>
+      <c r="BE55" t="inlineStr">
+        <is>
+          <t>0.1357</t>
+        </is>
+      </c>
+      <c r="BF55" t="inlineStr">
+        <is>
+          <t>29.06</t>
+        </is>
+      </c>
+      <c r="BG55" t="inlineStr">
+        <is>
+          <t>L To R</t>
+        </is>
+      </c>
+      <c r="BH55" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>Petco Park</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr"/>
@@ -15563,56 +15579,44 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>645277</t>
+          <t>593428</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ozzie Albies</t>
+          <t>Xander Bogaerts</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>MIL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-08T02:00:00Z</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pre-Game</t>
+          <t>Scheduled</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Tyler Glasnow</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>607192</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="n">
-        <v>40.1</v>
+        <v>40.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -15626,26 +15630,26 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>15.3</v>
+        <v>28.7</v>
       </c>
       <c r="Q56" t="n">
-        <v>34.7</v>
+        <v>41.2</v>
       </c>
       <c r="R56" t="n">
-        <v>48.9</v>
+        <v>22.6</v>
       </c>
       <c r="S56" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T56" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>52.8</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -15659,7 +15663,7 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
@@ -15684,7 +15688,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD56" t="inlineStr"/>
@@ -15701,27 +15705,27 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI56" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/25, 0 HR</t>
+          <t>Contact streak: 7/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL56" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -15731,112 +15735,80 @@
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>4.13</t>
+          <t>5.92</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
-          <t>87.22</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ56" t="inlineStr">
         <is>
-          <t>96.687</t>
+          <t>100.2761</t>
         </is>
       </c>
       <c r="AR56" t="inlineStr">
         <is>
-          <t>0.346</t>
+          <t>0.3871</t>
         </is>
       </c>
       <c r="AS56" t="inlineStr">
         <is>
-          <t>0.1184</t>
+          <t>0.1327</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr">
         <is>
-          <t>0.2808</t>
+          <t>0.3256</t>
         </is>
       </c>
       <c r="AU56" t="inlineStr">
         <is>
-          <t>68.86</t>
+          <t>72.24</t>
         </is>
       </c>
       <c r="AV56" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>27.73</t>
         </is>
       </c>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>43.52</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>31.48</t>
+          <t>23.27</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
-          <t>20.2</t>
+          <t>12.4</t>
         </is>
       </c>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>0.146</t>
-        </is>
-      </c>
-      <c r="BA56" t="inlineStr">
-        <is>
-          <t>8.35</t>
-        </is>
-      </c>
-      <c r="BB56" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="BC56" t="inlineStr">
-        <is>
-          <t>89.53</t>
-        </is>
-      </c>
-      <c r="BD56" t="inlineStr">
-        <is>
-          <t>0.3296</t>
-        </is>
-      </c>
-      <c r="BE56" t="inlineStr">
-        <is>
-          <t>0.1357</t>
-        </is>
-      </c>
-      <c r="BF56" t="inlineStr">
-        <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="BG56" t="inlineStr">
-        <is>
-          <t>L To R</t>
-        </is>
-      </c>
-      <c r="BH56" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
+          <t>0.1175</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr"/>
+      <c r="BB56" t="inlineStr"/>
+      <c r="BC56" t="inlineStr"/>
+      <c r="BD56" t="inlineStr"/>
+      <c r="BE56" t="inlineStr"/>
+      <c r="BF56" t="inlineStr"/>
+      <c r="BG56" t="inlineStr"/>
+      <c r="BH56" t="inlineStr"/>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Petco Park</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr"/>
@@ -16176,7 +16148,7 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>37.4</v>
+        <v>38</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -16190,7 +16162,7 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P58" t="n">
@@ -16203,7 +16175,7 @@
         <v>48.9</v>
       </c>
       <c r="S58" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T58" t="n">
         <v>50</v>
@@ -16213,39 +16185,35 @@
       </c>
       <c r="V58" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr"/>
       <c r="AC58" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -16416,7 +16384,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mauricio Dubon</t>
+          <t>Mauricio Dubón</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -16441,7 +16409,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -16460,7 +16428,7 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>36.3</v>
+        <v>35.3</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -16474,7 +16442,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -16487,7 +16455,7 @@
         <v>48.9</v>
       </c>
       <c r="S59" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T59" t="n">
         <v>50</v>
@@ -16497,39 +16465,35 @@
       </c>
       <c r="V59" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr"/>
       <c r="AC59" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -21398,7 +21362,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>58.8</v>
+        <v>59.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -21412,7 +21376,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -21425,7 +21389,7 @@
         <v>48.9</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>80</v>
@@ -21435,39 +21399,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22215,7 +22175,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -22234,7 +22194,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>56.9</v>
+        <v>56.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -22248,7 +22208,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -22261,7 +22221,7 @@
         <v>48.9</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -22271,39 +22231,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22469,24 +22425,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>660670</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Ronald Acuña Jr.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>ATL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>LAD</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>ATL</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -22499,17 +22455,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -22518,7 +22474,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>56.2</v>
+        <v>56.4</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -22532,26 +22488,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>51.1</v>
+        <v>58.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>37.3</v>
+        <v>35.6</v>
       </c>
       <c r="R8" t="n">
         <v>48.9</v>
       </c>
       <c r="S8" t="n">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -22565,7 +22521,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -22603,127 +22559,127 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>13.81</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>46.2</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.53</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>102.9585</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.507</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.2461</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3753</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>75.91</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>61.27</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>36.58</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.44</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.2056</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>7.16</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
@@ -22749,24 +22705,24 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>660670</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ronald Acuna</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -22779,17 +22735,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -22798,7 +22754,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>55.8</v>
+        <v>56.2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -22812,62 +22768,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>58.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R9" t="n">
         <v>48.9</v>
       </c>
       <c r="S9" t="n">
-        <v>95.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T9" t="n">
         <v>50</v>
       </c>
       <c r="U9" t="n">
-        <v>53.3</v>
+        <v>100</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -22887,127 +22839,127 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>13.81</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>46.2</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.53</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>102.9585</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.2461</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3753</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>36.58</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.2056</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -24389,27 +24341,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>671739</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Michael Harris II</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>CWS</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CLE</t>
+          <t>LAD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-10-07T20:00:00Z</t>
+          <t>2026-10-07T22:00:00Z</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -24419,17 +24371,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Daniel Espino</t>
+          <t>Tyler Glasnow</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>682982</t>
+          <t>607192</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -24438,7 +24390,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>51.5</v>
+        <v>52.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -24452,26 +24404,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>45.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>38.8</v>
+        <v>35.6</v>
       </c>
       <c r="R15" t="n">
-        <v>48.6</v>
+        <v>48.9</v>
       </c>
       <c r="S15" t="n">
-        <v>94.90000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>44.1</v>
+        <v>32</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -24485,7 +24437,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -24506,7 +24458,7 @@
       <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -24523,127 +24475,127 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Contact streak: 9/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>9.94</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>46.34</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>90.41</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>103.0958</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.4653</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1816</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3339</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>74.72</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>46.98</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>35.66</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>22.42</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1859</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>8.35</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>85.3</t>
+          <t>89.53</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.317</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>0.1357</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -24653,12 +24605,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>77</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>Rate Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr"/>
@@ -24669,27 +24621,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LAD</t>
+          <t>CWS</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>CLE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-10-07T22:00:00Z</t>
+          <t>2026-10-07T20:00:00Z</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -24699,17 +24651,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Tyler Mahle</t>
+          <t>Daniel Espino</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>641816</t>
+          <t>682982</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -24718,7 +24670,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -24732,26 +24684,26 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>39.3</v>
+        <v>37</v>
       </c>
       <c r="Q16" t="n">
-        <v>37.3</v>
+        <v>38.8</v>
       </c>
       <c r="R16" t="n">
-        <v>48.9</v>
+        <v>48.6</v>
       </c>
       <c r="S16" t="n">
-        <v>100</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T16" t="n">
         <v>80</v>
       </c>
       <c r="U16" t="n">
-        <v>13</v>
+        <v>44.1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -24765,7 +24717,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -24786,7 +24738,7 @@
       <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -24803,127 +24755,127 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 12.1% barrel, 3.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
+          <t>40.12</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>29.94</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>0.1471</t>
+        </is>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>12.1</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
           <t>36.4</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>26.93</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>18.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.1615</t>
-        </is>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>7.16</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>37.1</t>
-        </is>
-      </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>89.27</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3976</t>
+          <t>0.317</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1502</t>
+          <t>0.135</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>26.63</t>
+          <t>39.4</t>
         </is>
       </c>
       <c r="BG16" t="inlineStr">
@@ -24933,12 +24885,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Rate Field</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr"/>
@@ -24949,24 +24901,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>671739</t>
+          <t>518692</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Michael Harris</t>
+          <t>Freddie Freeman</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>LAD</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>ATL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>LAD</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-07T22:00:00Z</t>
@@ -24979,17 +24931,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Tyler Glasnow</t>
+          <t>Tyler Mahle</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>607192</t>
+          <t>641816</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -24998,7 +24950,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -25012,62 +24964,58 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>45.1</v>
+        <v>39.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>35.6</v>
+        <v>37.3</v>
       </c>
       <c r="R17" t="n">
         <v>48.9</v>
       </c>
       <c r="S17" t="n">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="T17" t="n">
         <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -25087,12 +25035,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -25102,12 +25050,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Contact streak: 9/27 over last 7 games</t>
+          <t>Last 7 games: 6/29, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.3% barrel, 7.9 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 15.5 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -25117,97 +25065,97 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>9.94</t>
+          <t>8.79</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>42.62</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>90.41</t>
+          <t>89.92</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>103.0958</t>
+          <t>100.1411</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.4653</t>
+          <t>0.4642</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1816</t>
+          <t>0.1811</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3339</t>
+          <t>0.3591</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>74.72</t>
+          <t>70.01</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>46.98</t>
+          <t>7.77</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>35.66</t>
+          <t>36.4</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>22.42</t>
+          <t>26.93</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>18.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1859</t>
+          <t>0.1615</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>8.35</t>
+          <t>7.16</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>37.1</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>89.53</t>
+          <t>89.27</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3976</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1357</t>
+          <t>0.1502</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>26.63</t>
         </is>
       </c>
       <c r="BG17" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1636,7 +1648,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S5" t="n">
         <v>90.40000000000001</v>
@@ -1824,8 +1836,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -1864,12 +1884,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1908,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1922,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1932,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -1925,39 +1945,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2116,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2140,7 +2164,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2188,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2202,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2212,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -2201,39 +2225,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2396,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2416,7 +2444,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2468,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2464,7 +2492,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S8" t="n">
         <v>92.09999999999999</v>
@@ -2652,8 +2680,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2667,12 +2703,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2692,12 +2728,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2716,7 +2752,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,62 +2766,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2805,27 +2837,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2835,67 +2867,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -2928,8 +2960,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -2943,24 +2983,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -2968,22 +3008,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -2992,7 +3032,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,65 +3046,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -3081,27 +3117,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -3111,101 +3147,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3219,12 +3263,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,12 +3288,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3268,7 +3312,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3326,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>49.9</v>
       </c>
       <c r="Q11" t="n">
         <v>21.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3357,27 +3397,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3427,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3520,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3495,12 +3543,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -3520,12 +3568,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3544,7 +3592,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>36.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,26 +3606,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>23.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3591,7 +3639,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3633,12 +3681,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3648,12 +3696,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3663,67 +3711,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -3756,8 +3804,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -3771,12 +3827,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3796,12 +3852,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3820,7 +3876,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,26 +3890,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3867,7 +3923,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3909,27 +3965,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3939,67 +3995,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -4032,8 +4088,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4047,24 +4111,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4072,22 +4136,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4096,7 +4160,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,65 +4174,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4185,7 +4245,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4195,17 +4255,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4215,101 +4275,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4323,24 +4391,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4348,7 +4416,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -4358,12 +4426,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4440,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4390,13 +4458,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S15" t="n">
         <v>47.9</v>
@@ -4405,7 +4473,7 @@
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4444,7 +4512,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4461,27 +4529,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4559,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4599,24 +4675,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4624,22 +4700,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -4648,7 +4724,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>27.7</v>
+        <v>32.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4666,22 +4742,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>36.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4695,7 +4771,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4720,7 +4796,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4813,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4828,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,101 +4843,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -4900,7 +4984,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -4924,7 +5008,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4948,7 +5032,7 @@
         <v>9.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S17" t="n">
         <v>40.2</v>
@@ -5136,8 +5220,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -5176,7 +5268,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -5200,7 +5292,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5224,7 +5316,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -5412,8 +5504,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -5452,7 +5552,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5576,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5500,7 +5600,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="n">
         <v>88.7</v>
@@ -5688,8 +5788,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6054,7 +6162,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6186,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56.2</v>
+        <v>57.1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6200,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Elite Power, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6210,10 @@
         <v>21.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S2" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -6115,39 +6223,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026 P:2026/2025</t>
@@ -6290,8 +6394,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6330,12 +6442,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -6354,7 +6466,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>49.9</v>
+        <v>51.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6480,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6490,10 @@
         <v>21.5</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
@@ -6391,39 +6503,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6674,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6606,12 +6722,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -6630,7 +6746,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.3</v>
+        <v>48.7</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6760,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6770,10 @@
         <v>21.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
@@ -6667,39 +6783,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6954,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -6882,7 +7002,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +7026,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6930,7 +7050,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S5" t="n">
         <v>90.40000000000001</v>
@@ -7118,8 +7238,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7158,12 +7286,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -7182,7 +7310,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>42.9</v>
+        <v>41.9</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7324,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7334,10 @@
         <v>21.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T6" t="n">
         <v>78</v>
@@ -7219,39 +7347,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7518,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7434,7 +7566,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7590,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>39.9</v>
+        <v>40.9</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7604,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7614,10 @@
         <v>21.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S7" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T7" t="n">
         <v>78</v>
@@ -7495,39 +7627,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7798,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7710,7 +7846,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7870,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.3</v>
+        <v>38.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7758,7 +7894,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S8" t="n">
         <v>92.09999999999999</v>
@@ -7946,8 +8082,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -7961,12 +8105,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>691019</t>
+          <t>805367</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kyle Teel</t>
+          <t>Chase Meidroth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7986,12 +8130,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -8010,7 +8154,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>36.6</v>
+        <v>37.9</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,62 +8168,58 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>37</v>
+        <v>13.2</v>
       </c>
       <c r="Q9" t="n">
         <v>21.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S9" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T9" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U9" t="n">
-        <v>44.1</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8099,27 +8239,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -8129,67 +8269,67 @@
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>44.25</t>
+          <t>35.05</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>86.48</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.3924</t>
+          <t>97.4786</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.3873</t>
+          <t>0.3435</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1692</t>
+          <t>0.1003</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3258</t>
+          <t>0.3007</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>71.29</t>
+          <t>67.05</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>40.12</t>
+          <t>38.75</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>29.94</t>
+          <t>20.68</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1471</t>
+          <t>0.1174</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -8222,8 +8362,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8237,24 +8385,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>691019</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Kyle Teel</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8262,22 +8410,22 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8286,7 +8434,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>36.2</v>
+        <v>37.5</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,65 +8448,61 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>25.8</v>
+        <v>37</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S10" t="n">
-        <v>95.5</v>
+        <v>64.3</v>
       </c>
       <c r="T10" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>23.4</v>
+        <v>44.1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -8375,27 +8519,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
@@ -8405,101 +8549,109 @@
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>44.25</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>86.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>100.3924</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.3873</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.1692</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3258</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>71.29</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>23.36</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>40.12</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>29.94</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.1471</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8513,12 +8665,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>805367</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chase Meidroth</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,12 +8690,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8562,7 +8714,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>36.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8728,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>13.2</v>
+        <v>49.9</v>
       </c>
       <c r="Q11" t="n">
         <v>21.5</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>81.90000000000001</v>
+        <v>44.8</v>
       </c>
       <c r="T11" t="n">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>77.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8651,27 +8799,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8829,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>35.05</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>97.4786</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3435</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1003</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3007</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>67.05</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>38.75</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>20.68</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1174</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8922,16 @@
           <t>21.47</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -8789,12 +8945,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>663993</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nathaniel Lowe</t>
+          <t>Jose Ramirez</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -8814,12 +8970,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -8838,7 +8994,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>34.9</v>
+        <v>36.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,26 +9008,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>36.3</v>
+        <v>25.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U12" t="n">
-        <v>10.1</v>
+        <v>23.4</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8885,7 +9041,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8927,12 +9083,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8942,12 +9098,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 3/16, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8957,67 +9113,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>41.43</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>89.42</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>100.8354</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4178</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1618</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3254</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>73.86</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>26.2</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.3</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1803</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -9050,8 +9206,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9065,12 +9229,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>663993</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Nathaniel Lowe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -9090,12 +9254,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -9114,7 +9278,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>33</v>
+        <v>35.2</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,26 +9292,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>32.4</v>
+        <v>36.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>48.7</v>
+        <v>10.1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -9161,7 +9325,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -9203,27 +9367,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 3/16, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -9233,67 +9397,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>41.43</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>89.42</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.8354</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.4178</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.1618</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.3254</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>73.86</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>37.82</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>34.82</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>26.2</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>17.3</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.1803</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -9326,8 +9490,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9341,24 +9513,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9366,22 +9538,22 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9390,7 +9562,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32.6</v>
+        <v>33.5</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,65 +9576,61 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>22.9</v>
+        <v>24</v>
       </c>
       <c r="Q14" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>52.4</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>36.3</v>
+        <v>45</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9479,7 +9647,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9489,17 +9657,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9509,101 +9677,109 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+          <t>21.47</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9617,24 +9793,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>672275</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Patrick Bailey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9642,7 +9818,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -9652,12 +9828,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9842,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>32.6</v>
+        <v>33.3</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9684,13 +9860,13 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>24</v>
+        <v>32.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S15" t="n">
         <v>47.9</v>
@@ -9699,7 +9875,7 @@
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>45</v>
+        <v>48.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9738,7 +9914,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9755,27 +9931,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9961,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>7.07</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>40.6</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>89.81</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>99.7502</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3785</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1475</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2941</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>72.41</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>25.78</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>35.3</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.67</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>8.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1212</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -9893,24 +10077,24 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682668</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Luisangel Acuna</t>
+          <t>Angel Martinez</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9918,22 +10102,22 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -9942,7 +10126,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>27.7</v>
+        <v>32.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9960,22 +10144,22 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>22.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T16" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>23.4</v>
+        <v>36.3</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -9989,7 +10173,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -10014,7 +10198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10215,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10230,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/13, 1 HR</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,101 +10245,109 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>88.32</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>99.2967</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3165</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0721</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2696</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.75</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>24.98</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>32.36</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>16.44</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0449</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+          <t>18.9</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10194,7 +10386,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -10218,7 +10410,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10242,7 +10434,7 @@
         <v>9.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S17" t="n">
         <v>40.2</v>
@@ -10430,8 +10622,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10470,7 +10670,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -10494,7 +10694,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.9</v>
+        <v>27.2</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10518,7 +10718,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S18" t="n">
         <v>59.8</v>
@@ -10706,8 +10906,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Rate Field</t>
@@ -10746,7 +10954,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10978,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10794,7 +11002,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>29.6</v>
       </c>
       <c r="S19" t="n">
         <v>88.7</v>
@@ -10982,8 +11190,16 @@
           <t>18.9</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>In From CF</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Rate Field</t>

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -1624,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1651,7 +1651,7 @@
         <v>29.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -1661,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -2468,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2482,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2495,7 +2491,7 @@
         <v>29.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2505,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -3263,24 +3255,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3293,17 +3285,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -3312,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3326,26 +3318,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
         <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>44.8</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3359,7 +3351,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3380,7 +3372,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3397,12 +3389,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -3412,12 +3404,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3427,97 +3419,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -3543,24 +3535,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -3573,17 +3565,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -3592,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3606,65 +3598,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.8</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3681,12 +3669,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3696,12 +3684,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3711,97 +3699,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -3876,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3890,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3903,7 +3891,7 @@
         <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -3913,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4111,24 +4095,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4141,17 +4125,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -4178,22 +4162,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R14" t="n">
         <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>45</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -4207,7 +4191,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -4228,7 +4212,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -4245,7 +4229,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -4255,17 +4239,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -4275,97 +4259,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -4391,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -4426,12 +4410,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4440,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4454,65 +4438,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.4</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>29.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -4529,27 +4509,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4559,97 +4539,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -4675,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4705,7 +4685,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4724,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.9</v>
+        <v>27.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4738,11 +4718,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>22.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
         <v>9.6</v>
@@ -4751,49 +4731,45 @@
         <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
         <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>36.3</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -4813,7 +4789,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -4823,12 +4799,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4843,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4959,12 +4935,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4989,7 +4965,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -5008,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -5022,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
         <v>29.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5097,7 +5069,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -5107,17 +5079,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5127,67 +5099,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -5243,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5273,7 +5245,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5292,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5306,11 +5278,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>9.699999999999999</v>
@@ -5319,52 +5291,48 @@
         <v>29.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -5381,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5396,7 +5364,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -5411,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5527,12 +5495,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -5557,7 +5525,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -5576,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5590,11 +5558,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
@@ -5603,49 +5571,45 @@
         <v>29.6</v>
       </c>
       <c r="S19" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -5665,27 +5629,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5695,67 +5659,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
@@ -7026,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.8</v>
+        <v>46.4</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -7040,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -7053,7 +7017,7 @@
         <v>29.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
@@ -7063,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -7870,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>38.6</v>
+        <v>39.2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7884,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7897,7 +7857,7 @@
         <v>29.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7907,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026 P:2026</t>
@@ -8665,24 +8621,24 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>695657</t>
+          <t>608070</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Colson Montgomery</t>
+          <t>José Ramírez</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8695,17 +8651,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8714,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>36.8</v>
+        <v>37.2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8728,26 +8684,26 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Strong Barrel</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>49.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>21.5</v>
+        <v>9.6</v>
       </c>
       <c r="R11" t="n">
         <v>29.6</v>
       </c>
       <c r="S11" t="n">
-        <v>44.8</v>
+        <v>100</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8761,7 +8717,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8782,7 +8738,7 @@
       <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -8799,12 +8755,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -8814,12 +8770,12 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 1/25, 0 HR</t>
+          <t>Last 7 games: 8/29, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8829,97 +8785,97 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>12.75</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>41.98</t>
+          <t>38.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>88.84</t>
+          <t>88.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>101.7218</t>
+          <t>99.2749</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4219</t>
+          <t>0.4075</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.2136</t>
+          <t>0.1361</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3081</t>
+          <t>0.3301</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>76.72</t>
+          <t>70.41</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>70.86</t>
+          <t>12.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.41</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.44</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>17.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2312</t>
+          <t>0.1591</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
@@ -8945,24 +8901,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>608070</t>
+          <t>695657</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jose Ramirez</t>
+          <t>Colson Montgomery</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -8975,17 +8931,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8994,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>36.5</v>
+        <v>36.8</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -9008,65 +8964,61 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>25.8</v>
+        <v>49.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>9.6</v>
+        <v>21.5</v>
       </c>
       <c r="R12" t="n">
         <v>29.6</v>
       </c>
       <c r="S12" t="n">
-        <v>95.5</v>
+        <v>44.8</v>
       </c>
       <c r="T12" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U12" t="n">
-        <v>23.4</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -9083,12 +9035,12 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -9098,12 +9050,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 8/29, 0 HR</t>
+          <t>Last 7 games: 1/25, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -9113,97 +9065,97 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>12.75</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>38.26</t>
+          <t>41.98</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>88.69</t>
+          <t>88.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>99.2749</t>
+          <t>101.7218</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.4075</t>
+          <t>0.4219</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.1361</t>
+          <t>0.2136</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.3301</t>
+          <t>0.3081</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>70.41</t>
+          <t>76.72</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>12.84</t>
+          <t>70.86</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>50.41</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>33.44</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.1591</t>
+          <t>0.2312</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG12" t="inlineStr">
@@ -9278,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>35.2</v>
+        <v>35.8</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9292,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9305,7 +9257,7 @@
         <v>29.6</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -9315,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -9513,24 +9461,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>695731</t>
+          <t>682657</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Braden Montgomery</t>
+          <t>Angel Martínez</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>CLE</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>CWS</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CLE</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9543,17 +9491,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Parker Messick</t>
+          <t>Hagen Smith</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>800048</t>
+          <t>696146</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -9580,22 +9528,22 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>24</v>
+        <v>22.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>20.1</v>
+        <v>9.6</v>
       </c>
       <c r="R14" t="n">
         <v>29.6</v>
       </c>
       <c r="S14" t="n">
-        <v>52.4</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>75</v>
       </c>
       <c r="U14" t="n">
-        <v>45</v>
+        <v>36.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -9609,7 +9557,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -9630,7 +9578,7 @@
       <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -9647,7 +9595,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
@@ -9657,17 +9605,17 @@
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Contact streak: 11/25 over last 7 games</t>
+          <t>Last 7 games: 6/25, 1 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
+          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -9677,97 +9625,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>40.9</t>
+          <t>33.64</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.38</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>100.0698</t>
+          <t>98.404</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>0.3746</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>0.1347</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>0.2858</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>71.01</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.7</t>
+          <t>15.88</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>35.7</t>
+          <t>44.74</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>26.8</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>15.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>0.1882</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.3481</t>
+          <t>0.224</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.1198</t>
+          <t>0.066</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>21.47</t>
+          <t>18.9</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr">
@@ -9793,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>672275</t>
+          <t>695731</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Patrick Bailey</t>
+          <t>Braden Montgomery</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>CWS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>CLE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CWS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-09T00:00:00Z</t>
@@ -9828,12 +9776,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Hagen Smith</t>
+          <t>Parker Messick</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>696146</t>
+          <t>800048</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9842,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>33.3</v>
+        <v>33.5</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9856,65 +9804,61 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>32.4</v>
+        <v>24</v>
       </c>
       <c r="Q15" t="n">
-        <v>9.6</v>
+        <v>20.1</v>
       </c>
       <c r="R15" t="n">
         <v>29.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T15" t="n">
         <v>75</v>
       </c>
       <c r="U15" t="n">
-        <v>48.7</v>
+        <v>45</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -9931,27 +9875,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Contact streak: 11/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 5.2% barrel, 13.1 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9961,97 +9905,97 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>40.9</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>89.81</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>99.7502</t>
+          <t>100.0698</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3785</t>
+          <t>0.392</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1475</t>
+          <t>0.137</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2941</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.41</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>25.78</t>
+          <t>8.7</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>35.3</t>
+          <t>35.7</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>27.67</t>
+          <t>17.9</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>8.8</t>
+          <t>6.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.1212</t>
+          <t>0.124</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.0</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.224</t>
+          <t>0.3481</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>0.1198</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>18.9</t>
+          <t>21.47</t>
         </is>
       </c>
       <c r="BG15" t="inlineStr">
@@ -10077,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>682657</t>
+          <t>677587</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Angel Martinez</t>
+          <t>Brayan Rocchio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -10107,7 +10051,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -10126,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>32.9</v>
+        <v>27.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -10140,11 +10084,11 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>22.9</v>
+        <v>13.7</v>
       </c>
       <c r="Q16" t="n">
         <v>9.6</v>
@@ -10153,49 +10097,45 @@
         <v>29.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>44.8</v>
       </c>
       <c r="T16" t="n">
         <v>75</v>
       </c>
       <c r="U16" t="n">
-        <v>36.3</v>
+        <v>72.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -10215,7 +10155,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
@@ -10225,12 +10165,12 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/25, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -10245,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>33.64</t>
+          <t>31.65</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>98.404</t>
+          <t>97.253</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3746</t>
+          <t>0.3524</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.1067</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2858</t>
+          <t>0.2943</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>71.01</t>
+          <t>69.86</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>15.88</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>44.74</t>
+          <t>43.71</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>26.8</t>
+          <t>25.23</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1882</t>
+          <t>0.1287</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10361,12 +10301,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>677587</t>
+          <t>683953</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Brayan Rocchio</t>
+          <t>Travis Bazzana</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -10391,7 +10331,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -10410,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>27.3</v>
+        <v>27.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10424,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge, Hot Hitter/Streak</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>13.7</v>
+        <v>20.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="R17" t="n">
         <v>29.6</v>
       </c>
       <c r="S17" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T17" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>72.7</v>
+        <v>12</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026</t>
+          <t>H:2026 P:2026</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10499,7 +10435,7 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
@@ -10509,17 +10445,17 @@
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/25, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10529,67 +10465,67 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>31.65</t>
+          <t>36.2</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.253</t>
+          <t>98.2866</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3524</t>
+          <t>0.347</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1067</t>
+          <t>0.123</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2943</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.86</t>
+          <t>69.7</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>12.2</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>43.71</t>
+          <t>38.9</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>28.8</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.1287</t>
+          <t>0.163</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
@@ -10645,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>683953</t>
+          <t>680757</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Travis Bazzana</t>
+          <t>Steven Kwan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10675,7 +10611,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10694,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>27.2</v>
+        <v>27.4</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10708,11 +10644,11 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>20.9</v>
+        <v>2.9</v>
       </c>
       <c r="Q18" t="n">
         <v>9.699999999999999</v>
@@ -10721,52 +10657,48 @@
         <v>29.6</v>
       </c>
       <c r="S18" t="n">
-        <v>59.8</v>
+        <v>93.2</v>
       </c>
       <c r="T18" t="n">
         <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>12</v>
+        <v>43.1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026 P:2026</t>
+          <t>H:2026/2025 P:2026</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -10783,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10798,7 +10730,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/25, 0 HR</t>
+          <t>Contact streak: 11/27 over last 7 games</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
@@ -10813,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>36.2</t>
+          <t>13.14</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>84.59</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>98.2866</t>
+          <t>92.8324</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.347</t>
+          <t>0.3499</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>0.0741</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>0.3226</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.7</t>
+          <t>62.73</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>12.2</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>38.9</t>
+          <t>27.81</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>28.8</t>
+          <t>23.44</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.163</t>
+          <t>0.0775</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10929,12 +10861,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>680757</t>
+          <t>595978</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Steven Kwan</t>
+          <t>Austin Hedges</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -10959,7 +10891,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -10978,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>26.8</v>
+        <v>26.6</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10992,11 +10924,11 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.9</v>
+        <v>12.3</v>
       </c>
       <c r="Q19" t="n">
         <v>9.699999999999999</v>
@@ -11005,49 +10937,45 @@
         <v>29.6</v>
       </c>
       <c r="S19" t="n">
-        <v>88.7</v>
+        <v>52.4</v>
       </c>
       <c r="T19" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U19" t="n">
-        <v>43.1</v>
+        <v>28.9</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026</t>
@@ -11067,27 +10995,27 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>Contact streak: 11/27 over last 7 games</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 1.9% barrel, 1.0 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -11097,67 +11025,67 @@
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>13.14</t>
+          <t>32.34</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>84.59</t>
+          <t>86.52</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>92.8324</t>
+          <t>97.7334</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>0.3499</t>
+          <t>0.305</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>0.0741</t>
+          <t>0.0951</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>0.3226</t>
+          <t>0.2707</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
         <is>
-          <t>62.73</t>
+          <t>69.82</t>
         </is>
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>27.81</t>
+          <t>47.88</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>23.44</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>5.7</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>0.0775</t>
+          <t>0.1258</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">

--- a/outputs/hr_rankings.xlsx
+++ b/outputs/hr_rankings.xlsx
@@ -760,12 +760,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>56</v>
+        <v>58.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Elite Power, Strong Barrel</t>
+          <t>Elite Power, Strong Barrel</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>38.7</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S2" t="n">
-        <v>81.90000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="T2" t="n">
         <v>50</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1011,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>669257</t>
+          <t>606192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Will Smith</t>
+          <t>Teoscar Hernández</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1036,12 +1040,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>55</v>
+        <v>54.5</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,62 +1078,58 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge, Hot Hitter/Streak</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>51.1</v>
+        <v>45.7</v>
       </c>
       <c r="Q3" t="n">
         <v>38.7</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S3" t="n">
-        <v>90.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>78</v>
       </c>
       <c r="U3" t="n">
-        <v>100</v>
+        <v>48.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
+          <t>Contact streak: 8/25 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1174,72 +1174,72 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>12.34</t>
+          <t>10.94</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>42.97</t>
+          <t>45.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>89.76</t>
+          <t>90.27</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>100.2559</t>
+          <t>101.5782</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.5002</t>
+          <t>0.4427</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2249</t>
+          <t>0.1878</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.3296</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>69.84</t>
+          <t>72.62</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>26.95</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>39.15</t>
+          <t>28.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12.1</t>
+          <t>18.7</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1765</t>
+          <t>0.1727</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
@@ -1272,8 +1272,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1287,12 +1295,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>606192</t>
+          <t>669257</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Teoscar Hernandez</t>
+          <t>Will Smith</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1312,12 +1320,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>50.8</v>
+        <v>54.4</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,62 +1358,58 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>45.7</v>
+        <v>51.1</v>
       </c>
       <c r="Q4" t="n">
         <v>38.7</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="T4" t="n">
         <v>78</v>
       </c>
       <c r="U4" t="n">
-        <v>48.3</v>
+        <v>100</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1425,22 +1429,22 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 8/25 over last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1450,72 +1454,72 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>10.94</t>
+          <t>12.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.19</t>
+          <t>42.97</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.27</t>
+          <t>89.76</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.5782</t>
+          <t>100.2559</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4427</t>
+          <t>0.5002</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.1878</t>
+          <t>0.2249</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3296</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>72.62</t>
+          <t>69.84</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>26.95</t>
+          <t>6.31</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>30.74</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>39.15</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>12.1</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1727</t>
+          <t>0.1765</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1548,8 +1552,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1563,12 +1575,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>605141</t>
+          <t>681624</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mookie Betts</t>
+          <t>Andy Pages</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1588,12 +1600,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>45.1</v>
+        <v>50.9</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,62 +1638,58 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>32.7</v>
+        <v>36.4</v>
       </c>
       <c r="Q5" t="n">
         <v>38.7</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S5" t="n">
-        <v>88.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>78</v>
       </c>
       <c r="U5" t="n">
-        <v>29.2</v>
+        <v>66</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1701,22 +1709,22 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/26, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1731,67 +1739,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.11</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>40.77</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>88.81</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>98.5265</t>
+          <t>99.6965</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4311</t>
+          <t>0.4378</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1567</t>
+          <t>0.1686</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3363</t>
+          <t>0.3349</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>69.46</t>
+          <t>72.85</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>26.4</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>38.53</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>33.31</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>22.1</t>
+          <t>24.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1823</t>
+          <t>0.1925</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -1824,8 +1832,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium</t>
@@ -1839,12 +1855,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>518692</t>
+          <t>605141</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Freddie Freeman</t>
+          <t>Mookie Betts</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1864,12 +1880,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>44.9</v>
+        <v>48.8</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,62 +1918,58 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.3</v>
+        <v>32.7</v>
       </c>
       <c r="Q6" t="n">
         <v>38.7</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>48.1</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>93.2</v>
       </c>
       <c r="T6" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U6" t="n">
-        <v>13</v>
+        <v>29.2</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1977,27 +1989,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/29, 0 HR</t>
+          <t>Last 7 games: 5/26, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.7% barrel, 10.8 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -2007,67 +2019,67 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>8.79</t>
+          <t>7.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>37.34</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>89.92</t>
+          <t>89.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>100.1411</t>
+          <t>98.5265</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4642</t>
+          <t>0.4311</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1811</t>
+          <t>0.1567</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3591</t>
+          <t>0.3363</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.01</t>
+          <t>69.46</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7.77</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.4</t>
+          <t>40.94</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>26.93</t>
+          <t>33.31</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>18.4</t>
+          <t>22.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1615</t>
+          <t>0.1823</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2100,8 +2112,16 @@
           <t>25.77</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>Varies</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>UNIQLO Field at Dodger Stadium<